--- a/rawdata_2608.xlsx
+++ b/rawdata_2608.xlsx
@@ -8,16 +8,20 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Desktop\연구전략기획팀(26.09.~)\1. 연구 현황 종합 보고(월간)\26.08\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A52D2A9F-A1AB-4964-BA88-E5C67071F670}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{180A052D-BEA5-4CEF-9351-DCC6C101F580}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{A72AC5CA-02C8-41D1-B4F6-8C7A45B1F0D9}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{A72AC5CA-02C8-41D1-B4F6-8C7A45B1F0D9}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
+    <sheet name="2023" sheetId="3" r:id="rId3"/>
+    <sheet name="2024" sheetId="4" r:id="rId4"/>
+    <sheet name="2025" sheetId="5" r:id="rId5"/>
+    <sheet name="2026" sheetId="6" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$AC$242</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$AC$241</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -41,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5781" uniqueCount="971">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5832" uniqueCount="985">
   <si>
     <t>연도</t>
   </si>
@@ -2239,12 +2243,6 @@
   </si>
   <si>
     <t>2026-05-22</t>
-  </si>
-  <si>
-    <t>Concierto de solistas coreanos y Orquesta Diesis (한국인 솔리스트들과 디에시스 오케스트라의 콘서트)</t>
-  </si>
-  <si>
-    <t>2026-02-08</t>
   </si>
   <si>
     <t>20210031</t>
@@ -2991,15 +2989,280 @@
     <t>금액(억원)</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
+  <si>
+    <t>구분</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>3</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t>월</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>4</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t>월</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>5</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t>월</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>6</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t>월</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>7</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t>월</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>8</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t>월</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>9</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t>월</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>10</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t>월</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>11</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t>월</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>12</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t>월</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>1</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t>월</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>2</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t>월</t>
+    </r>
+  </si>
+  <si>
+    <t>소계</t>
+  </si>
+  <si>
+    <t>공연·발표·대국</t>
+  </si>
+  <si>
+    <t>설계·디자인·전시</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="176" formatCode="0_ "/>
+    <numFmt numFmtId="181" formatCode="#,##0;#,##0;\-"/>
   </numFmts>
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="20">
     <font>
       <sz val="11"/>
       <color indexed="8"/>
@@ -3087,8 +3350,69 @@
       <charset val="129"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <name val="Noto Sans CJK SC"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <name val="Noto Sans CJK SC"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Noto Sans CJK SC"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="9"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -3118,8 +3442,20 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-4.9989318521683403E-2"/>
+        <bgColor rgb="FFEDF2F9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF2CC"/>
+        <bgColor rgb="FFF2F2F2"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="11">
+  <borders count="15">
     <border>
       <left/>
       <right/>
@@ -3257,16 +3593,77 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB4B4B4"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB4B4B4"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFB4B4B4"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB4B4B4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB4B4B4"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFB4B4B4"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFB4B4B4"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB4B4B4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB4B4B4"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB4B4B4"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB4B4B4"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB4B4B4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB4B4B4"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFB4B4B4"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB4B4B4"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB4B4B4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -3381,10 +3778,43 @@
     <xf numFmtId="0" fontId="10" fillId="5" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="11" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="11" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="12" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="13" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="181" fontId="17" fillId="0" borderId="13" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="181" fontId="13" fillId="7" borderId="14" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="2"/>
+    <xf numFmtId="181" fontId="19" fillId="4" borderId="13" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="181" fontId="17" fillId="4" borderId="13" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="3">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
     <cellStyle name="표준 2" xfId="1" xr:uid="{AC0109F7-6861-4FF6-9B6A-E9C7781BF44E}"/>
+    <cellStyle name="표준 3" xfId="2" xr:uid="{AC96740F-B100-47A8-9F55-39238C291EC6}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -3696,10 +4126,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{63FAA86C-8A23-43AE-9575-239B5BAA1E0F}">
-  <dimension ref="A1:AC242"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:AC241"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
   <sheetData>
-    <row r="1" spans="1:28" ht="28.35" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:28" ht="28.35" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3785,7 +4215,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="2" spans="1:28" ht="28.35" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:28" ht="28.35" customHeight="1">
       <c r="A2" s="2" t="s">
         <v>28</v>
       </c>
@@ -3869,7 +4299,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="3" spans="1:28" ht="28.35" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:28" ht="28.35" customHeight="1">
       <c r="A3" s="2" t="s">
         <v>28</v>
       </c>
@@ -3955,7 +4385,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="4" spans="1:28" ht="28.35" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:28" ht="28.35" customHeight="1">
       <c r="A4" s="2" t="s">
         <v>28</v>
       </c>
@@ -4039,7 +4469,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="5" spans="1:28" ht="28.35" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:28" ht="28.35" customHeight="1">
       <c r="A5" s="2" t="s">
         <v>28</v>
       </c>
@@ -4123,7 +4553,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="6" spans="1:28" ht="28.35" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:28" ht="28.35" customHeight="1">
       <c r="A6" s="2" t="s">
         <v>28</v>
       </c>
@@ -4207,7 +4637,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="7" spans="1:28" ht="28.35" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:28" ht="28.35" customHeight="1">
       <c r="A7" s="2" t="s">
         <v>28</v>
       </c>
@@ -4291,7 +4721,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="8" spans="1:28" ht="28.35" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:28" ht="28.35" customHeight="1">
       <c r="A8" s="2" t="s">
         <v>28</v>
       </c>
@@ -4375,7 +4805,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="9" spans="1:28" ht="28.35" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:28" ht="28.35" customHeight="1">
       <c r="A9" s="2" t="s">
         <v>28</v>
       </c>
@@ -4459,7 +4889,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="10" spans="1:28" ht="28.35" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:28" ht="28.35" customHeight="1">
       <c r="A10" s="2" t="s">
         <v>28</v>
       </c>
@@ -4543,7 +4973,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="11" spans="1:28" ht="28.35" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:28" ht="28.35" customHeight="1">
       <c r="A11" s="2" t="s">
         <v>28</v>
       </c>
@@ -4627,7 +5057,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="12" spans="1:28" ht="28.35" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:28" ht="28.35" customHeight="1">
       <c r="A12" s="2" t="s">
         <v>28</v>
       </c>
@@ -4709,7 +5139,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="13" spans="1:28" ht="28.35" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:28" ht="28.35" customHeight="1">
       <c r="A13" s="2" t="s">
         <v>28</v>
       </c>
@@ -4793,7 +5223,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="14" spans="1:28" ht="28.35" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:28" ht="28.35" customHeight="1">
       <c r="A14" s="2" t="s">
         <v>28</v>
       </c>
@@ -4877,7 +5307,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="15" spans="1:28" ht="28.35" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:28" ht="28.35" customHeight="1">
       <c r="A15" s="2" t="s">
         <v>28</v>
       </c>
@@ -4961,7 +5391,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="16" spans="1:28" ht="28.35" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:28" ht="28.35" customHeight="1">
       <c r="A16" s="2" t="s">
         <v>28</v>
       </c>
@@ -5045,7 +5475,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="17" spans="1:28" ht="28.35" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:28" ht="28.35" customHeight="1">
       <c r="A17" s="2" t="s">
         <v>28</v>
       </c>
@@ -5129,7 +5559,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="18" spans="1:28" ht="28.35" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:28" ht="28.35" customHeight="1">
       <c r="A18" s="2" t="s">
         <v>28</v>
       </c>
@@ -5213,7 +5643,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="19" spans="1:28" ht="28.35" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:28" ht="28.35" customHeight="1">
       <c r="A19" s="2" t="s">
         <v>28</v>
       </c>
@@ -5299,7 +5729,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="20" spans="1:28" ht="28.35" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:28" ht="28.35" customHeight="1">
       <c r="A20" s="2" t="s">
         <v>28</v>
       </c>
@@ -5383,7 +5813,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="21" spans="1:28" ht="28.35" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:28" ht="28.35" customHeight="1">
       <c r="A21" s="2" t="s">
         <v>28</v>
       </c>
@@ -5467,7 +5897,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="22" spans="1:28" ht="28.35" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:28" ht="28.35" customHeight="1">
       <c r="A22" s="2" t="s">
         <v>28</v>
       </c>
@@ -5551,7 +5981,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="23" spans="1:28" ht="28.35" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:28" ht="28.35" customHeight="1">
       <c r="A23" s="2" t="s">
         <v>28</v>
       </c>
@@ -5629,7 +6059,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="24" spans="1:28" ht="28.35" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:28" ht="28.35" customHeight="1">
       <c r="A24" s="2" t="s">
         <v>28</v>
       </c>
@@ -5707,7 +6137,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="25" spans="1:28" ht="28.35" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:28" ht="28.35" customHeight="1">
       <c r="A25" s="2" t="s">
         <v>28</v>
       </c>
@@ -5785,7 +6215,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="26" spans="1:28" ht="28.35" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:28" ht="28.35" customHeight="1">
       <c r="A26" s="2" t="s">
         <v>28</v>
       </c>
@@ -5863,7 +6293,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="27" spans="1:28" ht="28.35" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:28" ht="28.35" customHeight="1">
       <c r="A27" s="2" t="s">
         <v>28</v>
       </c>
@@ -5941,7 +6371,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="28" spans="1:28" ht="28.35" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:28" ht="28.35" customHeight="1">
       <c r="A28" s="2" t="s">
         <v>28</v>
       </c>
@@ -6019,7 +6449,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="29" spans="1:28" ht="28.35" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:28" ht="28.35" customHeight="1">
       <c r="A29" s="2" t="s">
         <v>28</v>
       </c>
@@ -6097,7 +6527,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="30" spans="1:28" ht="28.35" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:28" ht="28.35" customHeight="1">
       <c r="A30" s="2" t="s">
         <v>28</v>
       </c>
@@ -6181,7 +6611,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="31" spans="1:28" ht="28.35" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:28" ht="28.35" customHeight="1">
       <c r="A31" s="2" t="s">
         <v>28</v>
       </c>
@@ -6265,7 +6695,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="32" spans="1:28" ht="28.35" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:28" ht="28.35" customHeight="1">
       <c r="A32" s="2" t="s">
         <v>28</v>
       </c>
@@ -6349,7 +6779,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="33" spans="1:28" ht="28.35" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:28" ht="28.35" customHeight="1">
       <c r="A33" s="2" t="s">
         <v>28</v>
       </c>
@@ -6433,7 +6863,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="34" spans="1:28" ht="28.35" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:28" ht="28.35" customHeight="1">
       <c r="A34" s="2" t="s">
         <v>28</v>
       </c>
@@ -6517,7 +6947,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="35" spans="1:28" ht="28.35" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:28" ht="28.35" customHeight="1">
       <c r="A35" s="2" t="s">
         <v>28</v>
       </c>
@@ -6601,7 +7031,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="36" spans="1:28" ht="28.35" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:28" ht="28.35" customHeight="1">
       <c r="A36" s="2" t="s">
         <v>28</v>
       </c>
@@ -6685,7 +7115,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="37" spans="1:28" ht="28.35" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:28" ht="28.35" customHeight="1">
       <c r="A37" s="2" t="s">
         <v>28</v>
       </c>
@@ -6769,7 +7199,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="38" spans="1:28" ht="28.35" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:28" ht="28.35" customHeight="1">
       <c r="A38" s="2" t="s">
         <v>28</v>
       </c>
@@ -6853,7 +7283,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="39" spans="1:28" ht="28.35" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:28" ht="28.35" customHeight="1">
       <c r="A39" s="2" t="s">
         <v>28</v>
       </c>
@@ -6937,7 +7367,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="40" spans="1:28" ht="28.35" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:28" ht="28.35" customHeight="1">
       <c r="A40" s="2" t="s">
         <v>28</v>
       </c>
@@ -7021,7 +7451,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="41" spans="1:28" ht="28.35" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:28" ht="28.35" customHeight="1">
       <c r="A41" s="2" t="s">
         <v>28</v>
       </c>
@@ -7105,7 +7535,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="42" spans="1:28" ht="28.35" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:28" ht="28.35" customHeight="1">
       <c r="A42" s="2" t="s">
         <v>28</v>
       </c>
@@ -7189,7 +7619,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="43" spans="1:28" ht="28.35" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:28" ht="28.35" customHeight="1">
       <c r="A43" s="2" t="s">
         <v>28</v>
       </c>
@@ -7273,7 +7703,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="44" spans="1:28" ht="28.35" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:28" ht="28.35" customHeight="1">
       <c r="A44" s="2" t="s">
         <v>28</v>
       </c>
@@ -7357,7 +7787,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="45" spans="1:28" ht="28.35" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:28" ht="28.35" customHeight="1">
       <c r="A45" s="2" t="s">
         <v>28</v>
       </c>
@@ -7441,7 +7871,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="46" spans="1:28" ht="28.35" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:28" ht="28.35" customHeight="1">
       <c r="A46" s="2" t="s">
         <v>28</v>
       </c>
@@ -7527,7 +7957,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="47" spans="1:28" ht="28.35" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:28" ht="28.35" customHeight="1">
       <c r="A47" s="2" t="s">
         <v>28</v>
       </c>
@@ -7611,7 +8041,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:28" ht="28.35" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:28" ht="28.35" customHeight="1">
       <c r="A48" s="2" t="s">
         <v>28</v>
       </c>
@@ -7695,7 +8125,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="49" spans="1:28" ht="28.35" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:28" ht="28.35" customHeight="1">
       <c r="A49" s="2" t="s">
         <v>28</v>
       </c>
@@ -7779,7 +8209,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="50" spans="1:28" ht="28.35" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:28" ht="28.35" customHeight="1">
       <c r="A50" s="2" t="s">
         <v>28</v>
       </c>
@@ -7863,7 +8293,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="51" spans="1:28" ht="28.35" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:28" ht="28.35" customHeight="1">
       <c r="A51" s="2" t="s">
         <v>28</v>
       </c>
@@ -7947,7 +8377,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="52" spans="1:28" ht="28.35" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:28" ht="28.35" customHeight="1">
       <c r="A52" s="2" t="s">
         <v>28</v>
       </c>
@@ -8031,7 +8461,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="53" spans="1:28" ht="28.35" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:28" ht="28.35" customHeight="1">
       <c r="A53" s="2" t="s">
         <v>28</v>
       </c>
@@ -8115,7 +8545,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="54" spans="1:28" ht="28.35" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:28" ht="28.35" customHeight="1">
       <c r="A54" s="2" t="s">
         <v>28</v>
       </c>
@@ -8199,7 +8629,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="55" spans="1:28" ht="28.35" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:28" ht="28.35" customHeight="1">
       <c r="A55" s="2" t="s">
         <v>28</v>
       </c>
@@ -8283,7 +8713,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="56" spans="1:28" ht="28.35" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:28" ht="28.35" customHeight="1">
       <c r="A56" s="2" t="s">
         <v>28</v>
       </c>
@@ -8369,7 +8799,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="57" spans="1:28" ht="28.35" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:28" ht="28.35" customHeight="1">
       <c r="A57" s="2" t="s">
         <v>28</v>
       </c>
@@ -8453,7 +8883,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="58" spans="1:28" ht="28.35" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:28" ht="28.35" customHeight="1">
       <c r="A58" s="2" t="s">
         <v>28</v>
       </c>
@@ -8537,7 +8967,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="59" spans="1:28" ht="28.35" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:28" ht="28.35" customHeight="1">
       <c r="A59" s="2" t="s">
         <v>28</v>
       </c>
@@ -8621,7 +9051,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="60" spans="1:28" ht="28.35" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:28" ht="28.35" customHeight="1">
       <c r="A60" s="2" t="s">
         <v>28</v>
       </c>
@@ -8705,7 +9135,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="61" spans="1:28" ht="28.35" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:28" ht="28.35" customHeight="1">
       <c r="A61" s="2" t="s">
         <v>28</v>
       </c>
@@ -8787,7 +9217,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="62" spans="1:28" ht="28.35" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:28" ht="28.35" customHeight="1">
       <c r="A62" s="2" t="s">
         <v>28</v>
       </c>
@@ -8871,7 +9301,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="63" spans="1:28" ht="28.35" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:28" ht="28.35" customHeight="1">
       <c r="A63" s="2" t="s">
         <v>28</v>
       </c>
@@ -8955,7 +9385,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="64" spans="1:28" ht="28.35" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:28" ht="28.35" customHeight="1">
       <c r="A64" s="2" t="s">
         <v>28</v>
       </c>
@@ -9039,7 +9469,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="65" spans="1:28" ht="28.35" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:28" ht="28.35" customHeight="1">
       <c r="A65" s="2" t="s">
         <v>28</v>
       </c>
@@ -9123,7 +9553,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="66" spans="1:28" ht="28.35" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:28" ht="28.35" customHeight="1">
       <c r="A66" s="2" t="s">
         <v>28</v>
       </c>
@@ -9207,7 +9637,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="67" spans="1:28" ht="28.35" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:28" ht="28.35" customHeight="1">
       <c r="A67" s="2" t="s">
         <v>28</v>
       </c>
@@ -9289,7 +9719,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="68" spans="1:28" ht="28.35" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:28" ht="28.35" customHeight="1">
       <c r="A68" s="2" t="s">
         <v>28</v>
       </c>
@@ -9373,7 +9803,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="69" spans="1:28" ht="28.35" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:28" ht="28.35" customHeight="1">
       <c r="A69" s="2" t="s">
         <v>28</v>
       </c>
@@ -9457,7 +9887,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="70" spans="1:28" ht="28.35" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:28" ht="28.35" customHeight="1">
       <c r="A70" s="2" t="s">
         <v>28</v>
       </c>
@@ -9541,7 +9971,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="71" spans="1:28" ht="28.35" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:28" ht="28.35" customHeight="1">
       <c r="A71" s="2" t="s">
         <v>28</v>
       </c>
@@ -9625,7 +10055,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="72" spans="1:28" ht="28.35" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:28" ht="28.35" customHeight="1">
       <c r="A72" s="2" t="s">
         <v>28</v>
       </c>
@@ -9709,7 +10139,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="73" spans="1:28" ht="28.35" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:28" ht="28.35" customHeight="1">
       <c r="A73" s="2" t="s">
         <v>28</v>
       </c>
@@ -9793,7 +10223,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="74" spans="1:28" ht="28.35" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:28" ht="28.35" customHeight="1">
       <c r="A74" s="2" t="s">
         <v>28</v>
       </c>
@@ -9877,7 +10307,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="75" spans="1:28" ht="28.35" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:28" ht="28.35" customHeight="1">
       <c r="A75" s="2" t="s">
         <v>28</v>
       </c>
@@ -9961,7 +10391,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="76" spans="1:28" ht="28.35" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:28" ht="28.35" customHeight="1">
       <c r="A76" s="2" t="s">
         <v>28</v>
       </c>
@@ -10045,7 +10475,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="77" spans="1:28" ht="28.35" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:28" ht="28.35" customHeight="1">
       <c r="A77" s="2" t="s">
         <v>28</v>
       </c>
@@ -10129,7 +10559,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="78" spans="1:28" ht="28.35" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:28" ht="28.35" customHeight="1">
       <c r="A78" s="2" t="s">
         <v>28</v>
       </c>
@@ -10213,7 +10643,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="79" spans="1:28" ht="28.35" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:28" ht="28.35" customHeight="1">
       <c r="A79" s="2" t="s">
         <v>28</v>
       </c>
@@ -10299,7 +10729,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="80" spans="1:28" ht="28.35" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:28" ht="28.35" customHeight="1">
       <c r="A80" s="2" t="s">
         <v>28</v>
       </c>
@@ -10383,7 +10813,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="81" spans="1:28" ht="28.35" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:28" ht="28.35" customHeight="1">
       <c r="A81" s="2" t="s">
         <v>28</v>
       </c>
@@ -10467,7 +10897,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="82" spans="1:28" ht="28.35" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:28" ht="28.35" customHeight="1">
       <c r="A82" s="2" t="s">
         <v>28</v>
       </c>
@@ -10553,7 +10983,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="83" spans="1:28" ht="28.35" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:28" ht="28.35" customHeight="1">
       <c r="A83" s="2" t="s">
         <v>28</v>
       </c>
@@ -10637,7 +11067,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="84" spans="1:28" ht="28.35" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:28" ht="28.35" customHeight="1">
       <c r="A84" s="2" t="s">
         <v>28</v>
       </c>
@@ -10721,7 +11151,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="85" spans="1:28" ht="28.35" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:28" ht="28.35" customHeight="1">
       <c r="A85" s="2" t="s">
         <v>28</v>
       </c>
@@ -10805,7 +11235,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="86" spans="1:28" ht="28.35" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:28" ht="28.35" customHeight="1">
       <c r="A86" s="2" t="s">
         <v>28</v>
       </c>
@@ -10889,7 +11319,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="87" spans="1:28" ht="28.35" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:28" ht="28.35" customHeight="1">
       <c r="A87" s="2" t="s">
         <v>28</v>
       </c>
@@ -10975,7 +11405,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="88" spans="1:28" ht="28.35" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:28" ht="28.35" customHeight="1">
       <c r="A88" s="2" t="s">
         <v>28</v>
       </c>
@@ -11053,7 +11483,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="89" spans="1:28" ht="28.35" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:28" ht="28.35" customHeight="1">
       <c r="A89" s="2" t="s">
         <v>28</v>
       </c>
@@ -11137,7 +11567,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="90" spans="1:28" ht="28.35" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:28" ht="28.35" customHeight="1">
       <c r="A90" s="2" t="s">
         <v>28</v>
       </c>
@@ -11221,7 +11651,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="91" spans="1:28" ht="28.35" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:28" ht="28.35" customHeight="1">
       <c r="A91" s="2" t="s">
         <v>28</v>
       </c>
@@ -11305,7 +11735,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="92" spans="1:28" ht="28.35" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:28" ht="28.35" customHeight="1">
       <c r="A92" s="2" t="s">
         <v>28</v>
       </c>
@@ -11389,7 +11819,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="93" spans="1:28" ht="28.35" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:28" ht="28.35" customHeight="1">
       <c r="A93" s="2" t="s">
         <v>28</v>
       </c>
@@ -11473,7 +11903,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="94" spans="1:28" ht="28.35" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:28" ht="28.35" customHeight="1">
       <c r="A94" s="2" t="s">
         <v>28</v>
       </c>
@@ -11557,7 +11987,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="95" spans="1:28" ht="28.35" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:28" ht="28.35" customHeight="1">
       <c r="A95" s="2" t="s">
         <v>28</v>
       </c>
@@ -11641,7 +12071,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="96" spans="1:28" ht="28.35" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:28" ht="28.35" customHeight="1">
       <c r="A96" s="2" t="s">
         <v>28</v>
       </c>
@@ -11725,7 +12155,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="97" spans="1:28" ht="28.35" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:28" ht="28.35" customHeight="1">
       <c r="A97" s="2" t="s">
         <v>28</v>
       </c>
@@ -11809,7 +12239,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="98" spans="1:28" ht="28.35" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:28" ht="28.35" customHeight="1">
       <c r="A98" s="2" t="s">
         <v>28</v>
       </c>
@@ -11893,7 +12323,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="99" spans="1:28" ht="28.35" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:28" ht="28.35" customHeight="1">
       <c r="A99" s="2" t="s">
         <v>28</v>
       </c>
@@ -11977,7 +12407,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="100" spans="1:28" ht="28.35" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:28" ht="28.35" customHeight="1">
       <c r="A100" s="2" t="s">
         <v>28</v>
       </c>
@@ -12061,7 +12491,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="101" spans="1:28" ht="28.35" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:28" ht="28.35" customHeight="1">
       <c r="A101" s="2" t="s">
         <v>28</v>
       </c>
@@ -12145,7 +12575,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="102" spans="1:28" ht="28.35" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:28" ht="28.35" customHeight="1">
       <c r="A102" s="2" t="s">
         <v>28</v>
       </c>
@@ -12229,7 +12659,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="103" spans="1:28" ht="28.35" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:28" ht="28.35" customHeight="1">
       <c r="A103" s="2" t="s">
         <v>28</v>
       </c>
@@ -12313,7 +12743,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="104" spans="1:28" ht="28.35" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:28" ht="28.35" customHeight="1">
       <c r="A104" s="2" t="s">
         <v>28</v>
       </c>
@@ -12391,7 +12821,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="105" spans="1:28" ht="28.35" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:28" ht="28.35" customHeight="1">
       <c r="A105" s="2" t="s">
         <v>28</v>
       </c>
@@ -12469,7 +12899,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="106" spans="1:28" ht="28.35" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:28" ht="28.35" customHeight="1">
       <c r="A106" s="2" t="s">
         <v>28</v>
       </c>
@@ -12547,7 +12977,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="107" spans="1:28" ht="28.35" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:28" ht="28.35" customHeight="1">
       <c r="A107" s="2" t="s">
         <v>28</v>
       </c>
@@ -12629,7 +13059,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="108" spans="1:28" ht="28.35" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:28" ht="28.35" customHeight="1">
       <c r="A108" s="2" t="s">
         <v>28</v>
       </c>
@@ -12713,7 +13143,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="109" spans="1:28" ht="28.35" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:28" ht="28.35" customHeight="1">
       <c r="A109" s="2" t="s">
         <v>28</v>
       </c>
@@ -12797,7 +13227,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="110" spans="1:28" ht="28.35" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:28" ht="28.35" customHeight="1">
       <c r="A110" s="2" t="s">
         <v>28</v>
       </c>
@@ -12883,7 +13313,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="111" spans="1:28" ht="28.35" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:28" ht="28.35" customHeight="1">
       <c r="A111" s="2" t="s">
         <v>28</v>
       </c>
@@ -12969,7 +13399,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="112" spans="1:28" ht="28.35" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:28" ht="28.35" customHeight="1">
       <c r="A112" s="2" t="s">
         <v>28</v>
       </c>
@@ -13053,7 +13483,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="113" spans="1:28" ht="28.35" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:28" ht="28.35" customHeight="1">
       <c r="A113" s="2" t="s">
         <v>28</v>
       </c>
@@ -13137,7 +13567,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="114" spans="1:28" ht="28.35" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:28" ht="28.35" customHeight="1">
       <c r="A114" s="2" t="s">
         <v>28</v>
       </c>
@@ -13223,7 +13653,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="115" spans="1:28" ht="28.35" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:28" ht="28.35" customHeight="1">
       <c r="A115" s="2" t="s">
         <v>28</v>
       </c>
@@ -13307,7 +13737,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="116" spans="1:28" ht="28.35" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:28" ht="28.35" customHeight="1">
       <c r="A116" s="2" t="s">
         <v>28</v>
       </c>
@@ -13391,7 +13821,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="117" spans="1:28" ht="28.35" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:28" ht="28.35" customHeight="1">
       <c r="A117" s="2" t="s">
         <v>28</v>
       </c>
@@ -13475,7 +13905,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="118" spans="1:28" ht="28.35" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:28" ht="28.35" customHeight="1">
       <c r="A118" s="2" t="s">
         <v>28</v>
       </c>
@@ -13559,7 +13989,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="119" spans="1:28" ht="28.35" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:28" ht="28.35" customHeight="1">
       <c r="A119" s="2" t="s">
         <v>28</v>
       </c>
@@ -13643,7 +14073,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="120" spans="1:28" ht="28.35" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:28" ht="28.35" customHeight="1">
       <c r="A120" s="2" t="s">
         <v>28</v>
       </c>
@@ -13727,7 +14157,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="121" spans="1:28" ht="28.35" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:28" ht="28.35" customHeight="1">
       <c r="A121" s="2" t="s">
         <v>28</v>
       </c>
@@ -13811,7 +14241,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="122" spans="1:28" ht="28.35" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:28" ht="28.35" customHeight="1">
       <c r="A122" s="2" t="s">
         <v>28</v>
       </c>
@@ -13893,7 +14323,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="123" spans="1:28" ht="28.35" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:28" ht="28.35" customHeight="1">
       <c r="A123" s="2" t="s">
         <v>28</v>
       </c>
@@ -13977,7 +14407,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="124" spans="1:28" ht="28.35" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:28" ht="28.35" customHeight="1">
       <c r="A124" s="2" t="s">
         <v>28</v>
       </c>
@@ -14061,7 +14491,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="125" spans="1:28" ht="28.35" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:28" ht="28.35" customHeight="1">
       <c r="A125" s="2" t="s">
         <v>28</v>
       </c>
@@ -14145,7 +14575,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="126" spans="1:28" ht="28.35" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:28" ht="28.35" customHeight="1">
       <c r="A126" s="2" t="s">
         <v>28</v>
       </c>
@@ -14229,7 +14659,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="127" spans="1:28" ht="28.35" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:28" ht="28.35" customHeight="1">
       <c r="A127" s="2" t="s">
         <v>28</v>
       </c>
@@ -14315,7 +14745,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="128" spans="1:28" ht="28.35" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:28" ht="28.35" customHeight="1">
       <c r="A128" s="2" t="s">
         <v>28</v>
       </c>
@@ -14399,7 +14829,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="129" spans="1:28" ht="28.35" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:28" ht="28.35" customHeight="1">
       <c r="A129" s="2" t="s">
         <v>28</v>
       </c>
@@ -14483,7 +14913,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="130" spans="1:28" ht="28.35" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:28" ht="28.35" customHeight="1">
       <c r="A130" s="2" t="s">
         <v>28</v>
       </c>
@@ -14565,7 +14995,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="131" spans="1:28" ht="28.35" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:28" ht="28.35" customHeight="1">
       <c r="A131" s="2" t="s">
         <v>28</v>
       </c>
@@ -14649,7 +15079,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="132" spans="1:28" ht="28.35" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:28" ht="28.35" customHeight="1">
       <c r="A132" s="2" t="s">
         <v>28</v>
       </c>
@@ -14733,7 +15163,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="133" spans="1:28" ht="28.35" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:28" ht="28.35" customHeight="1">
       <c r="A133" s="2" t="s">
         <v>28</v>
       </c>
@@ -14817,7 +15247,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="134" spans="1:28" ht="28.35" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:28" ht="28.35" customHeight="1">
       <c r="A134" s="2" t="s">
         <v>28</v>
       </c>
@@ -14901,7 +15331,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="135" spans="1:28" ht="28.35" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:28" ht="28.35" customHeight="1">
       <c r="A135" s="2" t="s">
         <v>28</v>
       </c>
@@ -14985,7 +15415,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="136" spans="1:28" ht="28.35" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:28" ht="28.35" customHeight="1">
       <c r="A136" s="2" t="s">
         <v>28</v>
       </c>
@@ -15069,7 +15499,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="137" spans="1:28" ht="28.35" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:28" ht="28.35" customHeight="1">
       <c r="A137" s="2" t="s">
         <v>28</v>
       </c>
@@ -15153,7 +15583,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="138" spans="1:28" ht="28.35" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:28" ht="28.35" customHeight="1">
       <c r="A138" s="2" t="s">
         <v>28</v>
       </c>
@@ -15237,7 +15667,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="139" spans="1:28" ht="28.35" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:28" ht="28.35" customHeight="1">
       <c r="A139" s="2" t="s">
         <v>28</v>
       </c>
@@ -15321,7 +15751,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="140" spans="1:28" ht="28.35" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:28" ht="28.35" customHeight="1">
       <c r="A140" s="2" t="s">
         <v>28</v>
       </c>
@@ -15405,7 +15835,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="141" spans="1:28" ht="28.35" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:28" ht="28.35" customHeight="1">
       <c r="A141" s="2" t="s">
         <v>28</v>
       </c>
@@ -15485,7 +15915,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="142" spans="1:28" ht="28.35" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:28" ht="28.35" customHeight="1">
       <c r="A142" s="2" t="s">
         <v>28</v>
       </c>
@@ -15569,7 +15999,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="143" spans="1:28" ht="28.35" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:28" ht="28.35" customHeight="1">
       <c r="A143" s="2" t="s">
         <v>28</v>
       </c>
@@ -15655,7 +16085,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="144" spans="1:28" ht="28.35" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:28" ht="28.35" customHeight="1">
       <c r="A144" s="2" t="s">
         <v>28</v>
       </c>
@@ -15737,7 +16167,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="145" spans="1:28" ht="28.35" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:28" ht="28.35" customHeight="1">
       <c r="A145" s="2" t="s">
         <v>28</v>
       </c>
@@ -15821,7 +16251,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="146" spans="1:28" ht="28.35" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:28" ht="28.35" customHeight="1">
       <c r="A146" s="2" t="s">
         <v>28</v>
       </c>
@@ -15905,7 +16335,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="147" spans="1:28" ht="28.35" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:28" ht="28.35" customHeight="1">
       <c r="A147" s="2" t="s">
         <v>28</v>
       </c>
@@ -15989,7 +16419,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="148" spans="1:28" ht="28.35" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:28" ht="28.35" customHeight="1">
       <c r="A148" s="2" t="s">
         <v>28</v>
       </c>
@@ -16073,7 +16503,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="149" spans="1:28" ht="28.35" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:28" ht="28.35" customHeight="1">
       <c r="A149" s="2" t="s">
         <v>28</v>
       </c>
@@ -16157,7 +16587,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="150" spans="1:28" ht="28.35" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:28" ht="28.35" customHeight="1">
       <c r="A150" s="2" t="s">
         <v>28</v>
       </c>
@@ -16241,7 +16671,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="151" spans="1:28" ht="28.35" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:28" ht="28.35" customHeight="1">
       <c r="A151" s="2" t="s">
         <v>28</v>
       </c>
@@ -16325,7 +16755,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="152" spans="1:28" ht="28.35" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:28" ht="28.35" customHeight="1">
       <c r="A152" s="2" t="s">
         <v>28</v>
       </c>
@@ -16409,7 +16839,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="153" spans="1:28" ht="28.35" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:28" ht="28.35" customHeight="1">
       <c r="A153" s="2" t="s">
         <v>28</v>
       </c>
@@ -16493,7 +16923,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="154" spans="1:28" ht="28.35" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:28" ht="28.35" customHeight="1">
       <c r="A154" s="2" t="s">
         <v>28</v>
       </c>
@@ -16577,7 +17007,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="155" spans="1:28" ht="28.35" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:28" ht="28.35" customHeight="1">
       <c r="A155" s="2" t="s">
         <v>28</v>
       </c>
@@ -16661,7 +17091,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="156" spans="1:28" ht="28.35" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:28" ht="28.35" customHeight="1">
       <c r="A156" s="2" t="s">
         <v>28</v>
       </c>
@@ -16745,7 +17175,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="157" spans="1:28" ht="28.35" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:28" ht="28.35" customHeight="1">
       <c r="A157" s="2" t="s">
         <v>28</v>
       </c>
@@ -16829,7 +17259,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="158" spans="1:28" ht="28.35" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:28" ht="28.35" customHeight="1">
       <c r="A158" s="2" t="s">
         <v>28</v>
       </c>
@@ -16913,7 +17343,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="159" spans="1:28" ht="28.35" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:28" ht="28.35" customHeight="1">
       <c r="A159" s="2" t="s">
         <v>28</v>
       </c>
@@ -16997,7 +17427,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="160" spans="1:28" ht="28.35" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:28" ht="28.35" customHeight="1">
       <c r="A160" s="2" t="s">
         <v>28</v>
       </c>
@@ -17081,7 +17511,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="161" spans="1:28" ht="28.35" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:28" ht="28.35" customHeight="1">
       <c r="A161" s="2" t="s">
         <v>28</v>
       </c>
@@ -17165,7 +17595,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="162" spans="1:28" ht="28.35" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:28" ht="28.35" customHeight="1">
       <c r="A162" s="2" t="s">
         <v>28</v>
       </c>
@@ -17249,7 +17679,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="163" spans="1:28" ht="28.35" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:28" ht="28.35" customHeight="1">
       <c r="A163" s="2" t="s">
         <v>28</v>
       </c>
@@ -17333,7 +17763,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="164" spans="1:28" ht="28.35" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:28" ht="28.35" customHeight="1">
       <c r="A164" s="2" t="s">
         <v>28</v>
       </c>
@@ -17417,7 +17847,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="165" spans="1:28" ht="28.35" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:28" ht="28.35" customHeight="1">
       <c r="A165" s="2" t="s">
         <v>28</v>
       </c>
@@ -17501,7 +17931,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="166" spans="1:28" ht="28.35" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:28" ht="28.35" customHeight="1">
       <c r="A166" s="2" t="s">
         <v>28</v>
       </c>
@@ -17585,7 +18015,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="167" spans="1:28" ht="28.35" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:28" ht="28.35" customHeight="1">
       <c r="A167" s="2" t="s">
         <v>28</v>
       </c>
@@ -17669,7 +18099,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="168" spans="1:28" ht="28.35" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:28" ht="28.35" customHeight="1">
       <c r="A168" s="2" t="s">
         <v>28</v>
       </c>
@@ -17753,7 +18183,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="169" spans="1:28" ht="28.35" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:28" ht="28.35" customHeight="1">
       <c r="A169" s="2" t="s">
         <v>28</v>
       </c>
@@ -17837,7 +18267,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="170" spans="1:28" ht="28.35" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:28" ht="28.35" customHeight="1">
       <c r="A170" s="2" t="s">
         <v>28</v>
       </c>
@@ -17915,7 +18345,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="171" spans="1:28" ht="28.35" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:28" ht="28.35" customHeight="1">
       <c r="A171" s="2" t="s">
         <v>28</v>
       </c>
@@ -17993,7 +18423,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="172" spans="1:28" ht="28.35" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:28" ht="28.35" customHeight="1">
       <c r="A172" s="2" t="s">
         <v>28</v>
       </c>
@@ -18001,56 +18431,62 @@
         <v>29</v>
       </c>
       <c r="C172" s="3" t="s">
-        <v>162</v>
+        <v>322</v>
       </c>
       <c r="D172" s="3" t="s">
-        <v>726</v>
+        <v>434</v>
       </c>
       <c r="E172" s="2" t="s">
-        <v>727</v>
+        <v>732</v>
       </c>
       <c r="F172" s="2" t="s">
-        <v>728</v>
+        <v>733</v>
       </c>
       <c r="G172" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="H172" s="2"/>
+      <c r="H172" s="2" t="s">
+        <v>35</v>
+      </c>
       <c r="I172" s="3" t="s">
-        <v>166</v>
-      </c>
-      <c r="J172" s="3"/>
-      <c r="K172" s="2"/>
-      <c r="L172" s="2" t="s">
-        <v>167</v>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="J172" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="K172" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="L172" s="2"/>
       <c r="M172" s="2" t="s">
         <v>39</v>
       </c>
       <c r="N172" s="3" t="s">
-        <v>732</v>
+        <v>734</v>
       </c>
       <c r="O172" s="2" t="s">
-        <v>733</v>
+        <v>128</v>
       </c>
       <c r="P172" s="2">
         <v>2026</v>
       </c>
       <c r="Q172" s="2">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="R172" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="S172" s="2"/>
+        <v>124</v>
+      </c>
+      <c r="S172" s="2" t="s">
+        <v>446</v>
+      </c>
       <c r="T172" s="4" t="s">
         <v>87</v>
       </c>
       <c r="U172" s="4" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="V172" s="4" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="W172" s="4" t="s">
         <v>49</v>
@@ -18062,16 +18498,16 @@
         <v>49</v>
       </c>
       <c r="Z172" s="4" t="s">
-        <v>98</v>
+        <v>50</v>
       </c>
       <c r="AA172" s="4" t="s">
         <v>46</v>
       </c>
       <c r="AB172" s="5">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="173" spans="1:28" ht="28.35" customHeight="1" x14ac:dyDescent="0.3">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="173" spans="1:28" ht="28.35" customHeight="1">
       <c r="A173" s="2" t="s">
         <v>28</v>
       </c>
@@ -18082,16 +18518,16 @@
         <v>322</v>
       </c>
       <c r="D173" s="3" t="s">
-        <v>434</v>
+        <v>735</v>
       </c>
       <c r="E173" s="2" t="s">
-        <v>734</v>
+        <v>736</v>
       </c>
       <c r="F173" s="2" t="s">
-        <v>735</v>
+        <v>737</v>
       </c>
       <c r="G173" s="2" t="s">
-        <v>94</v>
+        <v>590</v>
       </c>
       <c r="H173" s="2" t="s">
         <v>35</v>
@@ -18100,7 +18536,7 @@
         <v>36</v>
       </c>
       <c r="J173" s="3" t="s">
-        <v>82</v>
+        <v>558</v>
       </c>
       <c r="K173" s="2" t="s">
         <v>38</v>
@@ -18110,34 +18546,34 @@
         <v>39</v>
       </c>
       <c r="N173" s="3" t="s">
-        <v>736</v>
+        <v>738</v>
       </c>
       <c r="O173" s="2" t="s">
-        <v>128</v>
+        <v>85</v>
       </c>
       <c r="P173" s="2">
         <v>2026</v>
       </c>
       <c r="Q173" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="R173" s="2" t="s">
-        <v>124</v>
+        <v>58</v>
       </c>
       <c r="S173" s="2" t="s">
-        <v>446</v>
+        <v>739</v>
       </c>
       <c r="T173" s="4" t="s">
-        <v>87</v>
+        <v>562</v>
       </c>
       <c r="U173" s="4" t="s">
-        <v>47</v>
+        <v>77</v>
       </c>
       <c r="V173" s="4" t="s">
         <v>47</v>
       </c>
       <c r="W173" s="4" t="s">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="X173" s="4" t="s">
         <v>49</v>
@@ -18152,10 +18588,10 @@
         <v>46</v>
       </c>
       <c r="AB173" s="5">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="174" spans="1:28" ht="28.35" customHeight="1" x14ac:dyDescent="0.3">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="174" spans="1:28" ht="28.35" customHeight="1">
       <c r="A174" s="2" t="s">
         <v>28</v>
       </c>
@@ -18163,19 +18599,19 @@
         <v>29</v>
       </c>
       <c r="C174" s="3" t="s">
-        <v>322</v>
+        <v>30</v>
       </c>
       <c r="D174" s="3" t="s">
-        <v>737</v>
+        <v>31</v>
       </c>
       <c r="E174" s="2" t="s">
-        <v>738</v>
+        <v>740</v>
       </c>
       <c r="F174" s="2" t="s">
-        <v>739</v>
+        <v>741</v>
       </c>
       <c r="G174" s="2" t="s">
-        <v>590</v>
+        <v>599</v>
       </c>
       <c r="H174" s="2" t="s">
         <v>35</v>
@@ -18184,44 +18620,44 @@
         <v>36</v>
       </c>
       <c r="J174" s="3" t="s">
-        <v>558</v>
+        <v>37</v>
       </c>
       <c r="K174" s="2" t="s">
-        <v>38</v>
+        <v>72</v>
       </c>
       <c r="L174" s="2"/>
       <c r="M174" s="2" t="s">
         <v>39</v>
       </c>
       <c r="N174" s="3" t="s">
-        <v>740</v>
+        <v>742</v>
       </c>
       <c r="O174" s="2" t="s">
-        <v>85</v>
+        <v>566</v>
       </c>
       <c r="P174" s="2">
         <v>2026</v>
       </c>
       <c r="Q174" s="2">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="R174" s="2" t="s">
-        <v>58</v>
+        <v>580</v>
       </c>
       <c r="S174" s="2" t="s">
-        <v>741</v>
+        <v>743</v>
       </c>
       <c r="T174" s="4" t="s">
-        <v>562</v>
+        <v>44</v>
       </c>
       <c r="U174" s="4" t="s">
-        <v>77</v>
+        <v>744</v>
       </c>
       <c r="V174" s="4" t="s">
-        <v>47</v>
+        <v>109</v>
       </c>
       <c r="W174" s="4" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="X174" s="4" t="s">
         <v>49</v>
@@ -18230,16 +18666,16 @@
         <v>49</v>
       </c>
       <c r="Z174" s="4" t="s">
-        <v>50</v>
+        <v>122</v>
       </c>
       <c r="AA174" s="4" t="s">
         <v>46</v>
       </c>
       <c r="AB174" s="5">
-        <v>315</v>
-      </c>
-    </row>
-    <row r="175" spans="1:28" ht="28.35" customHeight="1" x14ac:dyDescent="0.3">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="175" spans="1:28" ht="28.35" customHeight="1">
       <c r="A175" s="2" t="s">
         <v>28</v>
       </c>
@@ -18247,16 +18683,16 @@
         <v>29</v>
       </c>
       <c r="C175" s="3" t="s">
-        <v>30</v>
+        <v>206</v>
       </c>
       <c r="D175" s="3" t="s">
-        <v>31</v>
+        <v>745</v>
       </c>
       <c r="E175" s="2" t="s">
-        <v>742</v>
+        <v>746</v>
       </c>
       <c r="F175" s="2" t="s">
-        <v>743</v>
+        <v>747</v>
       </c>
       <c r="G175" s="2" t="s">
         <v>599</v>
@@ -18268,44 +18704,44 @@
         <v>36</v>
       </c>
       <c r="J175" s="3" t="s">
-        <v>37</v>
+        <v>82</v>
       </c>
       <c r="K175" s="2" t="s">
-        <v>72</v>
+        <v>38</v>
       </c>
       <c r="L175" s="2"/>
       <c r="M175" s="2" t="s">
         <v>39</v>
       </c>
       <c r="N175" s="3" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
       <c r="O175" s="2" t="s">
-        <v>566</v>
+        <v>219</v>
       </c>
       <c r="P175" s="2">
         <v>2026</v>
       </c>
       <c r="Q175" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R175" s="2" t="s">
-        <v>580</v>
+        <v>247</v>
       </c>
       <c r="S175" s="2" t="s">
-        <v>745</v>
+        <v>749</v>
       </c>
       <c r="T175" s="4" t="s">
-        <v>44</v>
+        <v>87</v>
       </c>
       <c r="U175" s="4" t="s">
-        <v>746</v>
+        <v>46</v>
       </c>
       <c r="V175" s="4" t="s">
-        <v>109</v>
+        <v>46</v>
       </c>
       <c r="W175" s="4" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="X175" s="4" t="s">
         <v>49</v>
@@ -18314,16 +18750,16 @@
         <v>49</v>
       </c>
       <c r="Z175" s="4" t="s">
-        <v>122</v>
+        <v>98</v>
       </c>
       <c r="AA175" s="4" t="s">
         <v>46</v>
       </c>
       <c r="AB175" s="5">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="176" spans="1:28" ht="28.35" customHeight="1" x14ac:dyDescent="0.3">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="176" spans="1:28" ht="28.35" customHeight="1">
       <c r="A176" s="2" t="s">
         <v>28</v>
       </c>
@@ -18334,13 +18770,13 @@
         <v>206</v>
       </c>
       <c r="D176" s="3" t="s">
+        <v>745</v>
+      </c>
+      <c r="E176" s="2" t="s">
+        <v>746</v>
+      </c>
+      <c r="F176" s="2" t="s">
         <v>747</v>
-      </c>
-      <c r="E176" s="2" t="s">
-        <v>748</v>
-      </c>
-      <c r="F176" s="2" t="s">
-        <v>749</v>
       </c>
       <c r="G176" s="2" t="s">
         <v>599</v>
@@ -18365,19 +18801,19 @@
         <v>750</v>
       </c>
       <c r="O176" s="2" t="s">
-        <v>219</v>
+        <v>96</v>
       </c>
       <c r="P176" s="2">
         <v>2026</v>
       </c>
       <c r="Q176" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R176" s="2" t="s">
-        <v>247</v>
+        <v>569</v>
       </c>
       <c r="S176" s="2" t="s">
-        <v>751</v>
+        <v>133</v>
       </c>
       <c r="T176" s="4" t="s">
         <v>87</v>
@@ -18407,7 +18843,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="177" spans="1:28" ht="28.35" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:28" ht="28.35" customHeight="1">
       <c r="A177" s="2" t="s">
         <v>28</v>
       </c>
@@ -18415,19 +18851,19 @@
         <v>29</v>
       </c>
       <c r="C177" s="3" t="s">
-        <v>206</v>
+        <v>110</v>
       </c>
       <c r="D177" s="3" t="s">
-        <v>747</v>
+        <v>704</v>
       </c>
       <c r="E177" s="2" t="s">
-        <v>748</v>
+        <v>751</v>
       </c>
       <c r="F177" s="2" t="s">
-        <v>749</v>
+        <v>752</v>
       </c>
       <c r="G177" s="2" t="s">
-        <v>599</v>
+        <v>707</v>
       </c>
       <c r="H177" s="2" t="s">
         <v>35</v>
@@ -18436,7 +18872,7 @@
         <v>36</v>
       </c>
       <c r="J177" s="3" t="s">
-        <v>82</v>
+        <v>37</v>
       </c>
       <c r="K177" s="2" t="s">
         <v>38</v>
@@ -18446,34 +18882,34 @@
         <v>39</v>
       </c>
       <c r="N177" s="3" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="O177" s="2" t="s">
-        <v>96</v>
+        <v>754</v>
       </c>
       <c r="P177" s="2">
         <v>2026</v>
       </c>
       <c r="Q177" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R177" s="2" t="s">
-        <v>569</v>
+        <v>618</v>
       </c>
       <c r="S177" s="2" t="s">
-        <v>133</v>
+        <v>755</v>
       </c>
       <c r="T177" s="4" t="s">
-        <v>87</v>
+        <v>44</v>
       </c>
       <c r="U177" s="4" t="s">
-        <v>46</v>
+        <v>60</v>
       </c>
       <c r="V177" s="4" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="W177" s="4" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="X177" s="4" t="s">
         <v>49</v>
@@ -18482,16 +18918,16 @@
         <v>49</v>
       </c>
       <c r="Z177" s="4" t="s">
-        <v>98</v>
+        <v>50</v>
       </c>
       <c r="AA177" s="4" t="s">
         <v>46</v>
       </c>
       <c r="AB177" s="5">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="178" spans="1:28" ht="28.35" customHeight="1" x14ac:dyDescent="0.3">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="178" spans="1:28" ht="28.35" customHeight="1">
       <c r="A178" s="2" t="s">
         <v>28</v>
       </c>
@@ -18505,10 +18941,10 @@
         <v>704</v>
       </c>
       <c r="E178" s="2" t="s">
-        <v>753</v>
+        <v>751</v>
       </c>
       <c r="F178" s="2" t="s">
-        <v>754</v>
+        <v>752</v>
       </c>
       <c r="G178" s="2" t="s">
         <v>707</v>
@@ -18530,37 +18966,37 @@
         <v>39</v>
       </c>
       <c r="N178" s="3" t="s">
-        <v>755</v>
+        <v>542</v>
       </c>
       <c r="O178" s="2" t="s">
-        <v>756</v>
+        <v>543</v>
       </c>
       <c r="P178" s="2">
         <v>2026</v>
       </c>
       <c r="Q178" s="2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="R178" s="2" t="s">
-        <v>618</v>
+        <v>188</v>
       </c>
       <c r="S178" s="2" t="s">
-        <v>757</v>
+        <v>544</v>
       </c>
       <c r="T178" s="4" t="s">
         <v>44</v>
       </c>
       <c r="U178" s="4" t="s">
-        <v>60</v>
+        <v>77</v>
       </c>
       <c r="V178" s="4" t="s">
         <v>47</v>
       </c>
       <c r="W178" s="4" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="X178" s="4" t="s">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="Y178" s="4" t="s">
         <v>49</v>
@@ -18575,7 +19011,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="179" spans="1:28" ht="28.35" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:28" ht="28.35" customHeight="1">
       <c r="A179" s="2" t="s">
         <v>28</v>
       </c>
@@ -18589,10 +19025,10 @@
         <v>704</v>
       </c>
       <c r="E179" s="2" t="s">
-        <v>753</v>
+        <v>751</v>
       </c>
       <c r="F179" s="2" t="s">
-        <v>754</v>
+        <v>752</v>
       </c>
       <c r="G179" s="2" t="s">
         <v>707</v>
@@ -18614,37 +19050,37 @@
         <v>39</v>
       </c>
       <c r="N179" s="3" t="s">
-        <v>542</v>
+        <v>756</v>
       </c>
       <c r="O179" s="2" t="s">
-        <v>543</v>
+        <v>188</v>
       </c>
       <c r="P179" s="2">
         <v>2026</v>
       </c>
       <c r="Q179" s="2">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="R179" s="2" t="s">
-        <v>188</v>
+        <v>42</v>
       </c>
       <c r="S179" s="2" t="s">
-        <v>544</v>
+        <v>757</v>
       </c>
       <c r="T179" s="4" t="s">
         <v>44</v>
       </c>
       <c r="U179" s="4" t="s">
-        <v>77</v>
+        <v>60</v>
       </c>
       <c r="V179" s="4" t="s">
         <v>47</v>
       </c>
       <c r="W179" s="4" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="X179" s="4" t="s">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="Y179" s="4" t="s">
         <v>49</v>
@@ -18659,7 +19095,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="180" spans="1:28" ht="28.35" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:28" ht="28.35" customHeight="1">
       <c r="A180" s="2" t="s">
         <v>28</v>
       </c>
@@ -18667,19 +19103,19 @@
         <v>29</v>
       </c>
       <c r="C180" s="3" t="s">
-        <v>110</v>
+        <v>758</v>
       </c>
       <c r="D180" s="3" t="s">
-        <v>704</v>
+        <v>759</v>
       </c>
       <c r="E180" s="2" t="s">
-        <v>753</v>
+        <v>760</v>
       </c>
       <c r="F180" s="2" t="s">
-        <v>754</v>
+        <v>761</v>
       </c>
       <c r="G180" s="2" t="s">
-        <v>707</v>
+        <v>599</v>
       </c>
       <c r="H180" s="2" t="s">
         <v>35</v>
@@ -18691,41 +19127,41 @@
         <v>37</v>
       </c>
       <c r="K180" s="2" t="s">
-        <v>38</v>
+        <v>72</v>
       </c>
       <c r="L180" s="2"/>
       <c r="M180" s="2" t="s">
         <v>39</v>
       </c>
       <c r="N180" s="3" t="s">
-        <v>758</v>
+        <v>762</v>
       </c>
       <c r="O180" s="2" t="s">
-        <v>188</v>
+        <v>455</v>
       </c>
       <c r="P180" s="2">
         <v>2026</v>
       </c>
       <c r="Q180" s="2">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="R180" s="2" t="s">
-        <v>42</v>
+        <v>100</v>
       </c>
       <c r="S180" s="2" t="s">
-        <v>759</v>
+        <v>592</v>
       </c>
       <c r="T180" s="4" t="s">
         <v>44</v>
       </c>
       <c r="U180" s="4" t="s">
+        <v>763</v>
+      </c>
+      <c r="V180" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="V180" s="4" t="s">
-        <v>47</v>
-      </c>
       <c r="W180" s="4" t="s">
-        <v>46</v>
+        <v>256</v>
       </c>
       <c r="X180" s="4" t="s">
         <v>49</v>
@@ -18734,16 +19170,16 @@
         <v>49</v>
       </c>
       <c r="Z180" s="4" t="s">
-        <v>50</v>
+        <v>122</v>
       </c>
       <c r="AA180" s="4" t="s">
         <v>46</v>
       </c>
       <c r="AB180" s="5">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="181" spans="1:28" ht="28.35" customHeight="1" x14ac:dyDescent="0.3">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="181" spans="1:28" ht="28.35" customHeight="1">
       <c r="A181" s="2" t="s">
         <v>28</v>
       </c>
@@ -18751,16 +19187,16 @@
         <v>29</v>
       </c>
       <c r="C181" s="3" t="s">
-        <v>760</v>
+        <v>352</v>
       </c>
       <c r="D181" s="3" t="s">
-        <v>761</v>
+        <v>386</v>
       </c>
       <c r="E181" s="2" t="s">
-        <v>762</v>
+        <v>764</v>
       </c>
       <c r="F181" s="2" t="s">
-        <v>763</v>
+        <v>765</v>
       </c>
       <c r="G181" s="2" t="s">
         <v>599</v>
@@ -18772,44 +19208,44 @@
         <v>36</v>
       </c>
       <c r="J181" s="3" t="s">
-        <v>37</v>
+        <v>558</v>
       </c>
       <c r="K181" s="2" t="s">
-        <v>72</v>
+        <v>38</v>
       </c>
       <c r="L181" s="2"/>
       <c r="M181" s="2" t="s">
         <v>39</v>
       </c>
       <c r="N181" s="3" t="s">
-        <v>764</v>
+        <v>766</v>
       </c>
       <c r="O181" s="2" t="s">
-        <v>455</v>
+        <v>219</v>
       </c>
       <c r="P181" s="2">
         <v>2026</v>
       </c>
       <c r="Q181" s="2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="R181" s="2" t="s">
-        <v>100</v>
+        <v>767</v>
       </c>
       <c r="S181" s="2" t="s">
-        <v>592</v>
+        <v>768</v>
       </c>
       <c r="T181" s="4" t="s">
-        <v>44</v>
+        <v>562</v>
       </c>
       <c r="U181" s="4" t="s">
-        <v>765</v>
+        <v>109</v>
       </c>
       <c r="V181" s="4" t="s">
-        <v>60</v>
+        <v>47</v>
       </c>
       <c r="W181" s="4" t="s">
-        <v>256</v>
+        <v>47</v>
       </c>
       <c r="X181" s="4" t="s">
         <v>49</v>
@@ -18818,16 +19254,16 @@
         <v>49</v>
       </c>
       <c r="Z181" s="4" t="s">
-        <v>122</v>
+        <v>50</v>
       </c>
       <c r="AA181" s="4" t="s">
         <v>46</v>
       </c>
       <c r="AB181" s="5">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="182" spans="1:28" ht="28.35" customHeight="1" x14ac:dyDescent="0.3">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="182" spans="1:28" ht="28.35" customHeight="1">
       <c r="A182" s="2" t="s">
         <v>28</v>
       </c>
@@ -18835,19 +19271,19 @@
         <v>29</v>
       </c>
       <c r="C182" s="3" t="s">
-        <v>352</v>
+        <v>212</v>
       </c>
       <c r="D182" s="3" t="s">
-        <v>386</v>
+        <v>213</v>
       </c>
       <c r="E182" s="2" t="s">
-        <v>766</v>
+        <v>769</v>
       </c>
       <c r="F182" s="2" t="s">
-        <v>767</v>
+        <v>770</v>
       </c>
       <c r="G182" s="2" t="s">
-        <v>599</v>
+        <v>404</v>
       </c>
       <c r="H182" s="2" t="s">
         <v>35</v>
@@ -18856,35 +19292,35 @@
         <v>36</v>
       </c>
       <c r="J182" s="3" t="s">
-        <v>558</v>
+        <v>82</v>
       </c>
       <c r="K182" s="2" t="s">
-        <v>38</v>
+        <v>72</v>
       </c>
       <c r="L182" s="2"/>
       <c r="M182" s="2" t="s">
         <v>39</v>
       </c>
       <c r="N182" s="3" t="s">
-        <v>768</v>
+        <v>771</v>
       </c>
       <c r="O182" s="2" t="s">
-        <v>219</v>
+        <v>234</v>
       </c>
       <c r="P182" s="2">
         <v>2026</v>
       </c>
       <c r="Q182" s="2">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="R182" s="2" t="s">
-        <v>769</v>
+        <v>100</v>
       </c>
       <c r="S182" s="2" t="s">
-        <v>770</v>
+        <v>299</v>
       </c>
       <c r="T182" s="4" t="s">
-        <v>562</v>
+        <v>87</v>
       </c>
       <c r="U182" s="4" t="s">
         <v>109</v>
@@ -18902,16 +19338,16 @@
         <v>49</v>
       </c>
       <c r="Z182" s="4" t="s">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="AA182" s="4" t="s">
         <v>46</v>
       </c>
       <c r="AB182" s="5">
-        <v>315</v>
-      </c>
-    </row>
-    <row r="183" spans="1:28" ht="28.35" customHeight="1" x14ac:dyDescent="0.3">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="183" spans="1:28" ht="28.35" customHeight="1">
       <c r="A183" s="2" t="s">
         <v>28</v>
       </c>
@@ -18925,16 +19361,16 @@
         <v>213</v>
       </c>
       <c r="E183" s="2" t="s">
-        <v>771</v>
+        <v>769</v>
       </c>
       <c r="F183" s="2" t="s">
-        <v>772</v>
+        <v>770</v>
       </c>
       <c r="G183" s="2" t="s">
         <v>404</v>
       </c>
       <c r="H183" s="2" t="s">
-        <v>35</v>
+        <v>240</v>
       </c>
       <c r="I183" s="3" t="s">
         <v>36</v>
@@ -18943,29 +19379,29 @@
         <v>82</v>
       </c>
       <c r="K183" s="2" t="s">
-        <v>72</v>
+        <v>38</v>
       </c>
       <c r="L183" s="2"/>
       <c r="M183" s="2" t="s">
         <v>39</v>
       </c>
       <c r="N183" s="3" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="O183" s="2" t="s">
-        <v>234</v>
+        <v>96</v>
       </c>
       <c r="P183" s="2">
         <v>2026</v>
       </c>
       <c r="Q183" s="2">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="R183" s="2" t="s">
-        <v>100</v>
+        <v>773</v>
       </c>
       <c r="S183" s="2" t="s">
-        <v>299</v>
+        <v>306</v>
       </c>
       <c r="T183" s="4" t="s">
         <v>87</v>
@@ -18986,16 +19422,16 @@
         <v>49</v>
       </c>
       <c r="Z183" s="4" t="s">
-        <v>78</v>
+        <v>50</v>
       </c>
       <c r="AA183" s="4" t="s">
         <v>46</v>
       </c>
       <c r="AB183" s="5">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="184" spans="1:28" ht="28.35" customHeight="1" x14ac:dyDescent="0.3">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="184" spans="1:28" ht="28.35" customHeight="1">
       <c r="A184" s="2" t="s">
         <v>28</v>
       </c>
@@ -19009,16 +19445,16 @@
         <v>213</v>
       </c>
       <c r="E184" s="2" t="s">
-        <v>771</v>
+        <v>769</v>
       </c>
       <c r="F184" s="2" t="s">
-        <v>772</v>
+        <v>770</v>
       </c>
       <c r="G184" s="2" t="s">
         <v>404</v>
       </c>
       <c r="H184" s="2" t="s">
-        <v>240</v>
+        <v>35</v>
       </c>
       <c r="I184" s="3" t="s">
         <v>36</v>
@@ -19037,19 +19473,19 @@
         <v>774</v>
       </c>
       <c r="O184" s="2" t="s">
-        <v>96</v>
+        <v>74</v>
       </c>
       <c r="P184" s="2">
         <v>2026</v>
       </c>
       <c r="Q184" s="2">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="R184" s="2" t="s">
+        <v>429</v>
+      </c>
+      <c r="S184" s="2" t="s">
         <v>775</v>
-      </c>
-      <c r="S184" s="2" t="s">
-        <v>306</v>
       </c>
       <c r="T184" s="4" t="s">
         <v>87</v>
@@ -19079,7 +19515,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="185" spans="1:28" ht="28.35" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:28" ht="28.35" customHeight="1">
       <c r="A185" s="2" t="s">
         <v>28</v>
       </c>
@@ -19093,10 +19529,10 @@
         <v>213</v>
       </c>
       <c r="E185" s="2" t="s">
-        <v>771</v>
+        <v>769</v>
       </c>
       <c r="F185" s="2" t="s">
-        <v>772</v>
+        <v>770</v>
       </c>
       <c r="G185" s="2" t="s">
         <v>404</v>
@@ -19121,19 +19557,19 @@
         <v>776</v>
       </c>
       <c r="O185" s="2" t="s">
-        <v>74</v>
+        <v>96</v>
       </c>
       <c r="P185" s="2">
         <v>2026</v>
       </c>
       <c r="Q185" s="2">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="R185" s="2" t="s">
-        <v>429</v>
+        <v>580</v>
       </c>
       <c r="S185" s="2" t="s">
-        <v>777</v>
+        <v>145</v>
       </c>
       <c r="T185" s="4" t="s">
         <v>87</v>
@@ -19163,7 +19599,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="186" spans="1:28" ht="28.35" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:28" ht="28.35" customHeight="1">
       <c r="A186" s="2" t="s">
         <v>28</v>
       </c>
@@ -19174,13 +19610,13 @@
         <v>212</v>
       </c>
       <c r="D186" s="3" t="s">
-        <v>213</v>
+        <v>347</v>
       </c>
       <c r="E186" s="2" t="s">
-        <v>771</v>
+        <v>777</v>
       </c>
       <c r="F186" s="2" t="s">
-        <v>772</v>
+        <v>778</v>
       </c>
       <c r="G186" s="2" t="s">
         <v>404</v>
@@ -19202,31 +19638,31 @@
         <v>39</v>
       </c>
       <c r="N186" s="3" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="O186" s="2" t="s">
-        <v>96</v>
+        <v>74</v>
       </c>
       <c r="P186" s="2">
         <v>2026</v>
       </c>
       <c r="Q186" s="2">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="R186" s="2" t="s">
-        <v>580</v>
+        <v>144</v>
       </c>
       <c r="S186" s="2" t="s">
-        <v>145</v>
+        <v>780</v>
       </c>
       <c r="T186" s="4" t="s">
         <v>87</v>
       </c>
       <c r="U186" s="4" t="s">
-        <v>109</v>
+        <v>60</v>
       </c>
       <c r="V186" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="W186" s="4" t="s">
         <v>47</v>
@@ -19247,7 +19683,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="187" spans="1:28" ht="28.35" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:28" ht="28.35" customHeight="1">
       <c r="A187" s="2" t="s">
         <v>28</v>
       </c>
@@ -19255,16 +19691,16 @@
         <v>29</v>
       </c>
       <c r="C187" s="3" t="s">
-        <v>212</v>
+        <v>758</v>
       </c>
       <c r="D187" s="3" t="s">
-        <v>347</v>
+        <v>781</v>
       </c>
       <c r="E187" s="2" t="s">
-        <v>779</v>
+        <v>782</v>
       </c>
       <c r="F187" s="2" t="s">
-        <v>780</v>
+        <v>783</v>
       </c>
       <c r="G187" s="2" t="s">
         <v>404</v>
@@ -19276,7 +19712,7 @@
         <v>36</v>
       </c>
       <c r="J187" s="3" t="s">
-        <v>82</v>
+        <v>37</v>
       </c>
       <c r="K187" s="2" t="s">
         <v>38</v>
@@ -19286,31 +19722,31 @@
         <v>39</v>
       </c>
       <c r="N187" s="3" t="s">
-        <v>781</v>
+        <v>784</v>
       </c>
       <c r="O187" s="2" t="s">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="P187" s="2">
         <v>2026</v>
       </c>
       <c r="Q187" s="2">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="R187" s="2" t="s">
-        <v>144</v>
+        <v>293</v>
       </c>
       <c r="S187" s="2" t="s">
-        <v>782</v>
+        <v>785</v>
       </c>
       <c r="T187" s="4" t="s">
-        <v>87</v>
+        <v>44</v>
       </c>
       <c r="U187" s="4" t="s">
-        <v>60</v>
+        <v>109</v>
       </c>
       <c r="V187" s="4" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="W187" s="4" t="s">
         <v>47</v>
@@ -19328,10 +19764,10 @@
         <v>46</v>
       </c>
       <c r="AB187" s="5">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="188" spans="1:28" ht="28.35" customHeight="1" x14ac:dyDescent="0.3">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="188" spans="1:28" ht="28.35" customHeight="1">
       <c r="A188" s="2" t="s">
         <v>28</v>
       </c>
@@ -19339,16 +19775,16 @@
         <v>29</v>
       </c>
       <c r="C188" s="3" t="s">
-        <v>760</v>
+        <v>758</v>
       </c>
       <c r="D188" s="3" t="s">
+        <v>781</v>
+      </c>
+      <c r="E188" s="2" t="s">
+        <v>782</v>
+      </c>
+      <c r="F188" s="2" t="s">
         <v>783</v>
-      </c>
-      <c r="E188" s="2" t="s">
-        <v>784</v>
-      </c>
-      <c r="F188" s="2" t="s">
-        <v>785</v>
       </c>
       <c r="G188" s="2" t="s">
         <v>404</v>
@@ -19373,16 +19809,16 @@
         <v>786</v>
       </c>
       <c r="O188" s="2" t="s">
-        <v>84</v>
+        <v>150</v>
       </c>
       <c r="P188" s="2">
         <v>2026</v>
       </c>
       <c r="Q188" s="2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="R188" s="2" t="s">
-        <v>293</v>
+        <v>229</v>
       </c>
       <c r="S188" s="2" t="s">
         <v>787</v>
@@ -19391,13 +19827,13 @@
         <v>44</v>
       </c>
       <c r="U188" s="4" t="s">
-        <v>109</v>
+        <v>46</v>
       </c>
       <c r="V188" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="W188" s="4" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="X188" s="4" t="s">
         <v>49</v>
@@ -19406,16 +19842,16 @@
         <v>49</v>
       </c>
       <c r="Z188" s="4" t="s">
-        <v>50</v>
+        <v>98</v>
       </c>
       <c r="AA188" s="4" t="s">
         <v>46</v>
       </c>
       <c r="AB188" s="5">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="189" spans="1:28" ht="28.35" customHeight="1" x14ac:dyDescent="0.3">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="189" spans="1:28" ht="28.35" customHeight="1">
       <c r="A189" s="2" t="s">
         <v>28</v>
       </c>
@@ -19423,16 +19859,16 @@
         <v>29</v>
       </c>
       <c r="C189" s="3" t="s">
-        <v>760</v>
+        <v>758</v>
       </c>
       <c r="D189" s="3" t="s">
+        <v>781</v>
+      </c>
+      <c r="E189" s="2" t="s">
+        <v>782</v>
+      </c>
+      <c r="F189" s="2" t="s">
         <v>783</v>
-      </c>
-      <c r="E189" s="2" t="s">
-        <v>784</v>
-      </c>
-      <c r="F189" s="2" t="s">
-        <v>785</v>
       </c>
       <c r="G189" s="2" t="s">
         <v>404</v>
@@ -19457,16 +19893,16 @@
         <v>788</v>
       </c>
       <c r="O189" s="2" t="s">
-        <v>150</v>
+        <v>84</v>
       </c>
       <c r="P189" s="2">
         <v>2026</v>
       </c>
       <c r="Q189" s="2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="R189" s="2" t="s">
-        <v>229</v>
+        <v>336</v>
       </c>
       <c r="S189" s="2" t="s">
         <v>789</v>
@@ -19499,7 +19935,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="190" spans="1:28" ht="28.35" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:28" ht="28.35" customHeight="1">
       <c r="A190" s="2" t="s">
         <v>28</v>
       </c>
@@ -19507,16 +19943,16 @@
         <v>29</v>
       </c>
       <c r="C190" s="3" t="s">
-        <v>760</v>
+        <v>190</v>
       </c>
       <c r="D190" s="3" t="s">
-        <v>783</v>
+        <v>191</v>
       </c>
       <c r="E190" s="2" t="s">
-        <v>784</v>
+        <v>790</v>
       </c>
       <c r="F190" s="2" t="s">
-        <v>785</v>
+        <v>791</v>
       </c>
       <c r="G190" s="2" t="s">
         <v>404</v>
@@ -19538,34 +19974,34 @@
         <v>39</v>
       </c>
       <c r="N190" s="3" t="s">
-        <v>790</v>
+        <v>792</v>
       </c>
       <c r="O190" s="2" t="s">
-        <v>84</v>
+        <v>793</v>
       </c>
       <c r="P190" s="2">
         <v>2026</v>
       </c>
       <c r="Q190" s="2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="R190" s="2" t="s">
-        <v>336</v>
+        <v>608</v>
       </c>
       <c r="S190" s="2" t="s">
-        <v>791</v>
+        <v>609</v>
       </c>
       <c r="T190" s="4" t="s">
         <v>44</v>
       </c>
       <c r="U190" s="4" t="s">
-        <v>46</v>
+        <v>109</v>
       </c>
       <c r="V190" s="4" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="W190" s="4" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="X190" s="4" t="s">
         <v>49</v>
@@ -19574,16 +20010,16 @@
         <v>49</v>
       </c>
       <c r="Z190" s="4" t="s">
-        <v>98</v>
+        <v>50</v>
       </c>
       <c r="AA190" s="4" t="s">
         <v>46</v>
       </c>
       <c r="AB190" s="5">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="191" spans="1:28" ht="28.35" customHeight="1" x14ac:dyDescent="0.3">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="191" spans="1:28" ht="28.35" customHeight="1">
       <c r="A191" s="2" t="s">
         <v>28</v>
       </c>
@@ -19597,10 +20033,10 @@
         <v>191</v>
       </c>
       <c r="E191" s="2" t="s">
-        <v>792</v>
+        <v>790</v>
       </c>
       <c r="F191" s="2" t="s">
-        <v>793</v>
+        <v>791</v>
       </c>
       <c r="G191" s="2" t="s">
         <v>404</v>
@@ -19615,7 +20051,7 @@
         <v>37</v>
       </c>
       <c r="K191" s="2" t="s">
-        <v>38</v>
+        <v>72</v>
       </c>
       <c r="L191" s="2"/>
       <c r="M191" s="2" t="s">
@@ -19631,25 +20067,25 @@
         <v>2026</v>
       </c>
       <c r="Q191" s="2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="R191" s="2" t="s">
         <v>608</v>
       </c>
       <c r="S191" s="2" t="s">
-        <v>609</v>
+        <v>396</v>
       </c>
       <c r="T191" s="4" t="s">
         <v>44</v>
       </c>
       <c r="U191" s="4" t="s">
-        <v>109</v>
+        <v>77</v>
       </c>
       <c r="V191" s="4" t="s">
         <v>47</v>
       </c>
       <c r="W191" s="4" t="s">
-        <v>47</v>
+        <v>60</v>
       </c>
       <c r="X191" s="4" t="s">
         <v>49</v>
@@ -19658,16 +20094,16 @@
         <v>49</v>
       </c>
       <c r="Z191" s="4" t="s">
-        <v>50</v>
+        <v>379</v>
       </c>
       <c r="AA191" s="4" t="s">
         <v>46</v>
       </c>
       <c r="AB191" s="5">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="192" spans="1:28" ht="28.35" customHeight="1" x14ac:dyDescent="0.3">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="192" spans="1:28" ht="28.35" customHeight="1">
       <c r="A192" s="2" t="s">
         <v>28</v>
       </c>
@@ -19675,16 +20111,16 @@
         <v>29</v>
       </c>
       <c r="C192" s="3" t="s">
-        <v>190</v>
+        <v>206</v>
       </c>
       <c r="D192" s="3" t="s">
-        <v>191</v>
+        <v>207</v>
       </c>
       <c r="E192" s="2" t="s">
-        <v>792</v>
+        <v>796</v>
       </c>
       <c r="F192" s="2" t="s">
-        <v>793</v>
+        <v>797</v>
       </c>
       <c r="G192" s="2" t="s">
         <v>404</v>
@@ -19696,20 +20132,20 @@
         <v>36</v>
       </c>
       <c r="J192" s="3" t="s">
-        <v>37</v>
+        <v>82</v>
       </c>
       <c r="K192" s="2" t="s">
-        <v>72</v>
+        <v>38</v>
       </c>
       <c r="L192" s="2"/>
       <c r="M192" s="2" t="s">
         <v>39</v>
       </c>
       <c r="N192" s="3" t="s">
-        <v>796</v>
+        <v>798</v>
       </c>
       <c r="O192" s="2" t="s">
-        <v>797</v>
+        <v>219</v>
       </c>
       <c r="P192" s="2">
         <v>2026</v>
@@ -19718,22 +20154,22 @@
         <v>3</v>
       </c>
       <c r="R192" s="2" t="s">
-        <v>608</v>
+        <v>247</v>
       </c>
       <c r="S192" s="2" t="s">
-        <v>396</v>
+        <v>799</v>
       </c>
       <c r="T192" s="4" t="s">
-        <v>44</v>
+        <v>87</v>
       </c>
       <c r="U192" s="4" t="s">
-        <v>77</v>
+        <v>46</v>
       </c>
       <c r="V192" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="W192" s="4" t="s">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="X192" s="4" t="s">
         <v>49</v>
@@ -19742,16 +20178,16 @@
         <v>49</v>
       </c>
       <c r="Z192" s="4" t="s">
-        <v>379</v>
+        <v>98</v>
       </c>
       <c r="AA192" s="4" t="s">
         <v>46</v>
       </c>
       <c r="AB192" s="5">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="193" spans="1:28" ht="28.35" customHeight="1" x14ac:dyDescent="0.3">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="193" spans="1:28" ht="28.35" customHeight="1">
       <c r="A193" s="2" t="s">
         <v>28</v>
       </c>
@@ -19759,16 +20195,16 @@
         <v>29</v>
       </c>
       <c r="C193" s="3" t="s">
-        <v>206</v>
+        <v>212</v>
       </c>
       <c r="D193" s="3" t="s">
-        <v>207</v>
+        <v>484</v>
       </c>
       <c r="E193" s="2" t="s">
-        <v>798</v>
+        <v>800</v>
       </c>
       <c r="F193" s="2" t="s">
-        <v>799</v>
+        <v>801</v>
       </c>
       <c r="G193" s="2" t="s">
         <v>404</v>
@@ -19780,44 +20216,44 @@
         <v>36</v>
       </c>
       <c r="J193" s="3" t="s">
-        <v>82</v>
+        <v>37</v>
       </c>
       <c r="K193" s="2" t="s">
-        <v>38</v>
+        <v>72</v>
       </c>
       <c r="L193" s="2"/>
       <c r="M193" s="2" t="s">
         <v>39</v>
       </c>
       <c r="N193" s="3" t="s">
-        <v>800</v>
+        <v>802</v>
       </c>
       <c r="O193" s="2" t="s">
-        <v>219</v>
+        <v>173</v>
       </c>
       <c r="P193" s="2">
         <v>2026</v>
       </c>
       <c r="Q193" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R193" s="2" t="s">
         <v>247</v>
       </c>
       <c r="S193" s="2" t="s">
-        <v>801</v>
+        <v>803</v>
       </c>
       <c r="T193" s="4" t="s">
-        <v>87</v>
+        <v>44</v>
       </c>
       <c r="U193" s="4" t="s">
-        <v>46</v>
+        <v>121</v>
       </c>
       <c r="V193" s="4" t="s">
         <v>46</v>
       </c>
       <c r="W193" s="4" t="s">
-        <v>49</v>
+        <v>88</v>
       </c>
       <c r="X193" s="4" t="s">
         <v>49</v>
@@ -19826,16 +20262,16 @@
         <v>49</v>
       </c>
       <c r="Z193" s="4" t="s">
-        <v>98</v>
+        <v>122</v>
       </c>
       <c r="AA193" s="4" t="s">
         <v>46</v>
       </c>
       <c r="AB193" s="5">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="194" spans="1:28" ht="28.35" customHeight="1" x14ac:dyDescent="0.3">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="194" spans="1:28" ht="28.35" customHeight="1">
       <c r="A194" s="2" t="s">
         <v>28</v>
       </c>
@@ -19843,19 +20279,19 @@
         <v>29</v>
       </c>
       <c r="C194" s="3" t="s">
-        <v>212</v>
+        <v>236</v>
       </c>
       <c r="D194" s="3" t="s">
-        <v>484</v>
+        <v>804</v>
       </c>
       <c r="E194" s="2" t="s">
-        <v>802</v>
+        <v>805</v>
       </c>
       <c r="F194" s="2" t="s">
-        <v>803</v>
+        <v>806</v>
       </c>
       <c r="G194" s="2" t="s">
-        <v>404</v>
+        <v>34</v>
       </c>
       <c r="H194" s="2" t="s">
         <v>35</v>
@@ -19864,44 +20300,44 @@
         <v>36</v>
       </c>
       <c r="J194" s="3" t="s">
-        <v>37</v>
+        <v>82</v>
       </c>
       <c r="K194" s="2" t="s">
-        <v>72</v>
+        <v>38</v>
       </c>
       <c r="L194" s="2"/>
       <c r="M194" s="2" t="s">
         <v>39</v>
       </c>
       <c r="N194" s="3" t="s">
-        <v>804</v>
+        <v>807</v>
       </c>
       <c r="O194" s="2" t="s">
-        <v>173</v>
+        <v>84</v>
       </c>
       <c r="P194" s="2">
         <v>2026</v>
       </c>
       <c r="Q194" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R194" s="2" t="s">
-        <v>247</v>
+        <v>66</v>
       </c>
       <c r="S194" s="2" t="s">
-        <v>805</v>
+        <v>715</v>
       </c>
       <c r="T194" s="4" t="s">
-        <v>44</v>
+        <v>87</v>
       </c>
       <c r="U194" s="4" t="s">
-        <v>121</v>
+        <v>47</v>
       </c>
       <c r="V194" s="4" t="s">
         <v>46</v>
       </c>
       <c r="W194" s="4" t="s">
-        <v>88</v>
+        <v>46</v>
       </c>
       <c r="X194" s="4" t="s">
         <v>49</v>
@@ -19910,16 +20346,16 @@
         <v>49</v>
       </c>
       <c r="Z194" s="4" t="s">
-        <v>122</v>
+        <v>50</v>
       </c>
       <c r="AA194" s="4" t="s">
         <v>46</v>
       </c>
       <c r="AB194" s="5">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="195" spans="1:28" ht="28.35" customHeight="1" x14ac:dyDescent="0.3">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="195" spans="1:28" ht="28.35" customHeight="1">
       <c r="A195" s="2" t="s">
         <v>28</v>
       </c>
@@ -19927,65 +20363,59 @@
         <v>29</v>
       </c>
       <c r="C195" s="3" t="s">
-        <v>236</v>
+        <v>162</v>
       </c>
       <c r="D195" s="3" t="s">
-        <v>806</v>
+        <v>808</v>
       </c>
       <c r="E195" s="2" t="s">
-        <v>807</v>
+        <v>809</v>
       </c>
       <c r="F195" s="2" t="s">
-        <v>808</v>
+        <v>810</v>
       </c>
       <c r="G195" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="H195" s="2" t="s">
-        <v>35</v>
-      </c>
+        <v>811</v>
+      </c>
+      <c r="H195" s="2"/>
       <c r="I195" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="J195" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="K195" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="L195" s="2"/>
+        <v>166</v>
+      </c>
+      <c r="J195" s="3"/>
+      <c r="K195" s="2"/>
+      <c r="L195" s="2" t="s">
+        <v>812</v>
+      </c>
       <c r="M195" s="2" t="s">
         <v>39</v>
       </c>
       <c r="N195" s="3" t="s">
-        <v>809</v>
+        <v>813</v>
       </c>
       <c r="O195" s="2" t="s">
-        <v>84</v>
+        <v>566</v>
       </c>
       <c r="P195" s="2">
         <v>2026</v>
       </c>
       <c r="Q195" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R195" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="S195" s="2" t="s">
-        <v>715</v>
-      </c>
+        <v>119</v>
+      </c>
+      <c r="S195" s="2"/>
       <c r="T195" s="4" t="s">
-        <v>87</v>
+        <v>814</v>
       </c>
       <c r="U195" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="V195" s="4" t="s">
         <v>46</v>
       </c>
       <c r="W195" s="4" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="X195" s="4" t="s">
         <v>49</v>
@@ -19994,16 +20424,16 @@
         <v>49</v>
       </c>
       <c r="Z195" s="4" t="s">
-        <v>50</v>
+        <v>98</v>
       </c>
       <c r="AA195" s="4" t="s">
         <v>46</v>
       </c>
       <c r="AB195" s="5">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="196" spans="1:28" ht="28.35" customHeight="1" x14ac:dyDescent="0.3">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="196" spans="1:28" ht="28.35" customHeight="1">
       <c r="A196" s="2" t="s">
         <v>28</v>
       </c>
@@ -20011,77 +20441,85 @@
         <v>29</v>
       </c>
       <c r="C196" s="3" t="s">
-        <v>162</v>
+        <v>190</v>
       </c>
       <c r="D196" s="3" t="s">
-        <v>810</v>
+        <v>258</v>
       </c>
       <c r="E196" s="2" t="s">
-        <v>811</v>
+        <v>815</v>
       </c>
       <c r="F196" s="2" t="s">
-        <v>812</v>
+        <v>816</v>
       </c>
       <c r="G196" s="2" t="s">
-        <v>813</v>
-      </c>
-      <c r="H196" s="2"/>
+        <v>404</v>
+      </c>
+      <c r="H196" s="2" t="s">
+        <v>35</v>
+      </c>
       <c r="I196" s="3" t="s">
-        <v>166</v>
-      </c>
-      <c r="J196" s="3"/>
-      <c r="K196" s="2"/>
+        <v>36</v>
+      </c>
+      <c r="J196" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="K196" s="2" t="s">
+        <v>38</v>
+      </c>
       <c r="L196" s="2" t="s">
-        <v>814</v>
+        <v>817</v>
       </c>
       <c r="M196" s="2" t="s">
         <v>39</v>
       </c>
       <c r="N196" s="3" t="s">
-        <v>815</v>
+        <v>818</v>
       </c>
       <c r="O196" s="2" t="s">
-        <v>566</v>
+        <v>66</v>
       </c>
       <c r="P196" s="2">
         <v>2026</v>
       </c>
       <c r="Q196" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R196" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="S196" s="2"/>
+        <v>42</v>
+      </c>
+      <c r="S196" s="2" t="s">
+        <v>819</v>
+      </c>
       <c r="T196" s="4" t="s">
-        <v>816</v>
+        <v>44</v>
       </c>
       <c r="U196" s="4" t="s">
-        <v>46</v>
+        <v>60</v>
       </c>
       <c r="V196" s="4" t="s">
         <v>46</v>
       </c>
       <c r="W196" s="4" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="X196" s="4" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="Y196" s="4" t="s">
         <v>49</v>
       </c>
       <c r="Z196" s="4" t="s">
-        <v>98</v>
+        <v>50</v>
       </c>
       <c r="AA196" s="4" t="s">
         <v>46</v>
       </c>
       <c r="AB196" s="5">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="197" spans="1:28" ht="28.35" customHeight="1" x14ac:dyDescent="0.3">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="197" spans="1:28" ht="28.35" customHeight="1">
       <c r="A197" s="2" t="s">
         <v>28</v>
       </c>
@@ -20089,16 +20527,16 @@
         <v>29</v>
       </c>
       <c r="C197" s="3" t="s">
-        <v>190</v>
+        <v>30</v>
       </c>
       <c r="D197" s="3" t="s">
-        <v>258</v>
+        <v>31</v>
       </c>
       <c r="E197" s="2" t="s">
-        <v>817</v>
+        <v>820</v>
       </c>
       <c r="F197" s="2" t="s">
-        <v>818</v>
+        <v>821</v>
       </c>
       <c r="G197" s="2" t="s">
         <v>404</v>
@@ -20115,59 +20553,57 @@
       <c r="K197" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="L197" s="2" t="s">
-        <v>819</v>
-      </c>
+      <c r="L197" s="2"/>
       <c r="M197" s="2" t="s">
         <v>39</v>
       </c>
       <c r="N197" s="3" t="s">
-        <v>820</v>
+        <v>822</v>
       </c>
       <c r="O197" s="2" t="s">
-        <v>66</v>
+        <v>150</v>
       </c>
       <c r="P197" s="2">
         <v>2026</v>
       </c>
       <c r="Q197" s="2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="R197" s="2" t="s">
-        <v>42</v>
+        <v>823</v>
       </c>
       <c r="S197" s="2" t="s">
-        <v>821</v>
+        <v>824</v>
       </c>
       <c r="T197" s="4" t="s">
         <v>44</v>
       </c>
       <c r="U197" s="4" t="s">
+        <v>744</v>
+      </c>
+      <c r="V197" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="V197" s="4" t="s">
-        <v>46</v>
-      </c>
       <c r="W197" s="4" t="s">
-        <v>46</v>
+        <v>524</v>
       </c>
       <c r="X197" s="4" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="Y197" s="4" t="s">
         <v>49</v>
       </c>
       <c r="Z197" s="4" t="s">
-        <v>50</v>
+        <v>295</v>
       </c>
       <c r="AA197" s="4" t="s">
         <v>46</v>
       </c>
       <c r="AB197" s="5">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="198" spans="1:28" ht="28.35" customHeight="1" x14ac:dyDescent="0.3">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="198" spans="1:28" ht="28.35" customHeight="1">
       <c r="A198" s="2" t="s">
         <v>28</v>
       </c>
@@ -20181,10 +20617,10 @@
         <v>31</v>
       </c>
       <c r="E198" s="2" t="s">
-        <v>822</v>
+        <v>820</v>
       </c>
       <c r="F198" s="2" t="s">
-        <v>823</v>
+        <v>821</v>
       </c>
       <c r="G198" s="2" t="s">
         <v>404</v>
@@ -20206,34 +20642,34 @@
         <v>39</v>
       </c>
       <c r="N198" s="3" t="s">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="O198" s="2" t="s">
-        <v>150</v>
+        <v>407</v>
       </c>
       <c r="P198" s="2">
         <v>2026</v>
       </c>
       <c r="Q198" s="2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="R198" s="2" t="s">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="S198" s="2" t="s">
-        <v>826</v>
+        <v>743</v>
       </c>
       <c r="T198" s="4" t="s">
         <v>44</v>
       </c>
       <c r="U198" s="4" t="s">
-        <v>746</v>
+        <v>827</v>
       </c>
       <c r="V198" s="4" t="s">
-        <v>60</v>
+        <v>88</v>
       </c>
       <c r="W198" s="4" t="s">
-        <v>524</v>
+        <v>48</v>
       </c>
       <c r="X198" s="4" t="s">
         <v>49</v>
@@ -20242,16 +20678,16 @@
         <v>49</v>
       </c>
       <c r="Z198" s="4" t="s">
-        <v>295</v>
+        <v>379</v>
       </c>
       <c r="AA198" s="4" t="s">
         <v>46</v>
       </c>
       <c r="AB198" s="5">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="199" spans="1:28" ht="28.35" customHeight="1" x14ac:dyDescent="0.3">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="199" spans="1:28" ht="28.35" customHeight="1">
       <c r="A199" s="2" t="s">
         <v>28</v>
       </c>
@@ -20265,10 +20701,10 @@
         <v>31</v>
       </c>
       <c r="E199" s="2" t="s">
-        <v>822</v>
+        <v>820</v>
       </c>
       <c r="F199" s="2" t="s">
-        <v>823</v>
+        <v>821</v>
       </c>
       <c r="G199" s="2" t="s">
         <v>404</v>
@@ -20290,10 +20726,10 @@
         <v>39</v>
       </c>
       <c r="N199" s="3" t="s">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="O199" s="2" t="s">
-        <v>407</v>
+        <v>66</v>
       </c>
       <c r="P199" s="2">
         <v>2026</v>
@@ -20302,22 +20738,22 @@
         <v>3</v>
       </c>
       <c r="R199" s="2" t="s">
-        <v>828</v>
+        <v>63</v>
       </c>
       <c r="S199" s="2" t="s">
-        <v>745</v>
+        <v>829</v>
       </c>
       <c r="T199" s="4" t="s">
         <v>44</v>
       </c>
       <c r="U199" s="4" t="s">
-        <v>829</v>
+        <v>524</v>
       </c>
       <c r="V199" s="4" t="s">
-        <v>88</v>
+        <v>121</v>
       </c>
       <c r="W199" s="4" t="s">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="X199" s="4" t="s">
         <v>49</v>
@@ -20332,10 +20768,10 @@
         <v>46</v>
       </c>
       <c r="AB199" s="5">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="200" spans="1:28" ht="28.35" customHeight="1" x14ac:dyDescent="0.3">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="200" spans="1:28" ht="28.35" customHeight="1">
       <c r="A200" s="2" t="s">
         <v>28</v>
       </c>
@@ -20346,38 +20782,36 @@
         <v>30</v>
       </c>
       <c r="D200" s="3" t="s">
-        <v>31</v>
+        <v>490</v>
       </c>
       <c r="E200" s="2" t="s">
-        <v>822</v>
+        <v>830</v>
       </c>
       <c r="F200" s="2" t="s">
-        <v>823</v>
+        <v>831</v>
       </c>
       <c r="G200" s="2" t="s">
         <v>404</v>
       </c>
-      <c r="H200" s="2" t="s">
-        <v>35</v>
-      </c>
+      <c r="H200" s="2"/>
       <c r="I200" s="3" t="s">
-        <v>36</v>
+        <v>114</v>
       </c>
       <c r="J200" s="3" t="s">
-        <v>37</v>
+        <v>115</v>
       </c>
       <c r="K200" s="2" t="s">
-        <v>38</v>
+        <v>72</v>
       </c>
       <c r="L200" s="2"/>
       <c r="M200" s="2" t="s">
         <v>39</v>
       </c>
       <c r="N200" s="3" t="s">
-        <v>830</v>
+        <v>832</v>
       </c>
       <c r="O200" s="2" t="s">
-        <v>66</v>
+        <v>503</v>
       </c>
       <c r="P200" s="2">
         <v>2026</v>
@@ -20386,22 +20820,20 @@
         <v>3</v>
       </c>
       <c r="R200" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="S200" s="2" t="s">
-        <v>831</v>
-      </c>
+        <v>337</v>
+      </c>
+      <c r="S200" s="2"/>
       <c r="T200" s="4" t="s">
-        <v>44</v>
+        <v>120</v>
       </c>
       <c r="U200" s="4" t="s">
-        <v>524</v>
+        <v>48</v>
       </c>
       <c r="V200" s="4" t="s">
-        <v>121</v>
+        <v>49</v>
       </c>
       <c r="W200" s="4" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="X200" s="4" t="s">
         <v>49</v>
@@ -20410,16 +20842,16 @@
         <v>49</v>
       </c>
       <c r="Z200" s="4" t="s">
-        <v>379</v>
+        <v>122</v>
       </c>
       <c r="AA200" s="4" t="s">
         <v>46</v>
       </c>
       <c r="AB200" s="5">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="201" spans="1:28" ht="28.35" customHeight="1" x14ac:dyDescent="0.3">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="201" spans="1:28" ht="28.35" customHeight="1">
       <c r="A201" s="2" t="s">
         <v>28</v>
       </c>
@@ -20433,33 +20865,35 @@
         <v>490</v>
       </c>
       <c r="E201" s="2" t="s">
-        <v>832</v>
+        <v>830</v>
       </c>
       <c r="F201" s="2" t="s">
-        <v>833</v>
+        <v>831</v>
       </c>
       <c r="G201" s="2" t="s">
         <v>404</v>
       </c>
-      <c r="H201" s="2"/>
+      <c r="H201" s="2" t="s">
+        <v>35</v>
+      </c>
       <c r="I201" s="3" t="s">
-        <v>114</v>
+        <v>36</v>
       </c>
       <c r="J201" s="3" t="s">
-        <v>115</v>
+        <v>37</v>
       </c>
       <c r="K201" s="2" t="s">
-        <v>72</v>
+        <v>38</v>
       </c>
       <c r="L201" s="2"/>
       <c r="M201" s="2" t="s">
         <v>39</v>
       </c>
       <c r="N201" s="3" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="O201" s="2" t="s">
-        <v>503</v>
+        <v>176</v>
       </c>
       <c r="P201" s="2">
         <v>2026</v>
@@ -20468,20 +20902,22 @@
         <v>3</v>
       </c>
       <c r="R201" s="2" t="s">
-        <v>337</v>
-      </c>
-      <c r="S201" s="2"/>
+        <v>566</v>
+      </c>
+      <c r="S201" s="2" t="s">
+        <v>775</v>
+      </c>
       <c r="T201" s="4" t="s">
-        <v>120</v>
+        <v>44</v>
       </c>
       <c r="U201" s="4" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="V201" s="4" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="W201" s="4" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="X201" s="4" t="s">
         <v>49</v>
@@ -20490,16 +20926,16 @@
         <v>49</v>
       </c>
       <c r="Z201" s="4" t="s">
-        <v>122</v>
+        <v>98</v>
       </c>
       <c r="AA201" s="4" t="s">
         <v>46</v>
       </c>
       <c r="AB201" s="5">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="202" spans="1:28" ht="28.35" customHeight="1" x14ac:dyDescent="0.3">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="202" spans="1:28" ht="28.35" customHeight="1">
       <c r="A202" s="2" t="s">
         <v>28</v>
       </c>
@@ -20507,41 +20943,41 @@
         <v>29</v>
       </c>
       <c r="C202" s="3" t="s">
-        <v>30</v>
+        <v>322</v>
       </c>
       <c r="D202" s="3" t="s">
-        <v>490</v>
+        <v>735</v>
       </c>
       <c r="E202" s="2" t="s">
-        <v>832</v>
+        <v>834</v>
       </c>
       <c r="F202" s="2" t="s">
-        <v>833</v>
+        <v>835</v>
       </c>
       <c r="G202" s="2" t="s">
-        <v>404</v>
-      </c>
-      <c r="H202" s="2" t="s">
-        <v>35</v>
-      </c>
+        <v>599</v>
+      </c>
+      <c r="H202" s="2"/>
       <c r="I202" s="3" t="s">
-        <v>36</v>
+        <v>114</v>
       </c>
       <c r="J202" s="3" t="s">
-        <v>37</v>
+        <v>115</v>
       </c>
       <c r="K202" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="L202" s="2"/>
+        <v>72</v>
+      </c>
+      <c r="L202" s="2" t="s">
+        <v>836</v>
+      </c>
       <c r="M202" s="2" t="s">
         <v>39</v>
       </c>
       <c r="N202" s="3" t="s">
-        <v>835</v>
+        <v>837</v>
       </c>
       <c r="O202" s="2" t="s">
-        <v>176</v>
+        <v>838</v>
       </c>
       <c r="P202" s="2">
         <v>2026</v>
@@ -20550,22 +20986,20 @@
         <v>3</v>
       </c>
       <c r="R202" s="2" t="s">
-        <v>566</v>
-      </c>
-      <c r="S202" s="2" t="s">
-        <v>777</v>
-      </c>
+        <v>337</v>
+      </c>
+      <c r="S202" s="2"/>
       <c r="T202" s="4" t="s">
-        <v>44</v>
+        <v>120</v>
       </c>
       <c r="U202" s="4" t="s">
-        <v>46</v>
+        <v>256</v>
       </c>
       <c r="V202" s="4" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="W202" s="4" t="s">
-        <v>49</v>
+        <v>256</v>
       </c>
       <c r="X202" s="4" t="s">
         <v>49</v>
@@ -20574,16 +21008,16 @@
         <v>49</v>
       </c>
       <c r="Z202" s="4" t="s">
-        <v>98</v>
+        <v>122</v>
       </c>
       <c r="AA202" s="4" t="s">
         <v>46</v>
       </c>
       <c r="AB202" s="5">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="203" spans="1:28" ht="28.35" customHeight="1" x14ac:dyDescent="0.3">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="203" spans="1:28" ht="28.35" customHeight="1">
       <c r="A203" s="2" t="s">
         <v>28</v>
       </c>
@@ -20594,30 +21028,30 @@
         <v>322</v>
       </c>
       <c r="D203" s="3" t="s">
-        <v>737</v>
+        <v>735</v>
       </c>
       <c r="E203" s="2" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
       <c r="F203" s="2" t="s">
-        <v>837</v>
+        <v>835</v>
       </c>
       <c r="G203" s="2" t="s">
         <v>599</v>
       </c>
-      <c r="H203" s="2"/>
+      <c r="H203" s="2" t="s">
+        <v>35</v>
+      </c>
       <c r="I203" s="3" t="s">
-        <v>114</v>
+        <v>36</v>
       </c>
       <c r="J203" s="3" t="s">
-        <v>115</v>
+        <v>558</v>
       </c>
       <c r="K203" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="L203" s="2" t="s">
-        <v>838</v>
-      </c>
+        <v>38</v>
+      </c>
+      <c r="L203" s="2"/>
       <c r="M203" s="2" t="s">
         <v>39</v>
       </c>
@@ -20631,23 +21065,25 @@
         <v>2026</v>
       </c>
       <c r="Q203" s="2">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="R203" s="2" t="s">
-        <v>337</v>
-      </c>
-      <c r="S203" s="2"/>
+        <v>204</v>
+      </c>
+      <c r="S203" s="2" t="s">
+        <v>841</v>
+      </c>
       <c r="T203" s="4" t="s">
-        <v>120</v>
+        <v>562</v>
       </c>
       <c r="U203" s="4" t="s">
-        <v>256</v>
+        <v>46</v>
       </c>
       <c r="V203" s="4" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="W203" s="4" t="s">
-        <v>256</v>
+        <v>49</v>
       </c>
       <c r="X203" s="4" t="s">
         <v>49</v>
@@ -20656,16 +21092,16 @@
         <v>49</v>
       </c>
       <c r="Z203" s="4" t="s">
-        <v>122</v>
+        <v>98</v>
       </c>
       <c r="AA203" s="4" t="s">
         <v>46</v>
       </c>
       <c r="AB203" s="5">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="204" spans="1:28" ht="28.35" customHeight="1" x14ac:dyDescent="0.3">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="204" spans="1:28" ht="28.35" customHeight="1">
       <c r="A204" s="2" t="s">
         <v>28</v>
       </c>
@@ -20673,19 +21109,19 @@
         <v>29</v>
       </c>
       <c r="C204" s="3" t="s">
-        <v>322</v>
+        <v>110</v>
       </c>
       <c r="D204" s="3" t="s">
-        <v>737</v>
+        <v>842</v>
       </c>
       <c r="E204" s="2" t="s">
-        <v>836</v>
+        <v>843</v>
       </c>
       <c r="F204" s="2" t="s">
-        <v>837</v>
+        <v>844</v>
       </c>
       <c r="G204" s="2" t="s">
-        <v>599</v>
+        <v>590</v>
       </c>
       <c r="H204" s="2" t="s">
         <v>35</v>
@@ -20694,7 +21130,7 @@
         <v>36</v>
       </c>
       <c r="J204" s="3" t="s">
-        <v>558</v>
+        <v>82</v>
       </c>
       <c r="K204" s="2" t="s">
         <v>38</v>
@@ -20704,25 +21140,25 @@
         <v>39</v>
       </c>
       <c r="N204" s="3" t="s">
-        <v>841</v>
+        <v>845</v>
       </c>
       <c r="O204" s="2" t="s">
-        <v>842</v>
+        <v>254</v>
       </c>
       <c r="P204" s="2">
         <v>2026</v>
       </c>
       <c r="Q204" s="2">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="R204" s="2" t="s">
-        <v>204</v>
+        <v>580</v>
       </c>
       <c r="S204" s="2" t="s">
-        <v>843</v>
+        <v>220</v>
       </c>
       <c r="T204" s="4" t="s">
-        <v>562</v>
+        <v>87</v>
       </c>
       <c r="U204" s="4" t="s">
         <v>46</v>
@@ -20746,10 +21182,10 @@
         <v>46</v>
       </c>
       <c r="AB204" s="5">
-        <v>450</v>
-      </c>
-    </row>
-    <row r="205" spans="1:28" ht="28.35" customHeight="1" x14ac:dyDescent="0.3">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="205" spans="1:28" ht="28.35" customHeight="1">
       <c r="A205" s="2" t="s">
         <v>28</v>
       </c>
@@ -20757,19 +21193,19 @@
         <v>29</v>
       </c>
       <c r="C205" s="3" t="s">
-        <v>110</v>
+        <v>90</v>
       </c>
       <c r="D205" s="3" t="s">
-        <v>844</v>
+        <v>846</v>
       </c>
       <c r="E205" s="2" t="s">
-        <v>845</v>
+        <v>847</v>
       </c>
       <c r="F205" s="2" t="s">
-        <v>846</v>
+        <v>848</v>
       </c>
       <c r="G205" s="2" t="s">
-        <v>590</v>
+        <v>707</v>
       </c>
       <c r="H205" s="2" t="s">
         <v>35</v>
@@ -20778,7 +21214,7 @@
         <v>36</v>
       </c>
       <c r="J205" s="3" t="s">
-        <v>82</v>
+        <v>279</v>
       </c>
       <c r="K205" s="2" t="s">
         <v>38</v>
@@ -20788,10 +21224,10 @@
         <v>39</v>
       </c>
       <c r="N205" s="3" t="s">
-        <v>847</v>
+        <v>849</v>
       </c>
       <c r="O205" s="2" t="s">
-        <v>254</v>
+        <v>219</v>
       </c>
       <c r="P205" s="2">
         <v>2026</v>
@@ -20800,19 +21236,19 @@
         <v>3</v>
       </c>
       <c r="R205" s="2" t="s">
-        <v>580</v>
+        <v>180</v>
       </c>
       <c r="S205" s="2" t="s">
-        <v>220</v>
+        <v>67</v>
       </c>
       <c r="T205" s="4" t="s">
         <v>87</v>
       </c>
       <c r="U205" s="4" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="V205" s="4" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="W205" s="4" t="s">
         <v>49</v>
@@ -20824,16 +21260,16 @@
         <v>49</v>
       </c>
       <c r="Z205" s="4" t="s">
-        <v>98</v>
+        <v>50</v>
       </c>
       <c r="AA205" s="4" t="s">
         <v>46</v>
       </c>
       <c r="AB205" s="5">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="206" spans="1:28" ht="28.35" customHeight="1" x14ac:dyDescent="0.3">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="206" spans="1:28" ht="28.35" customHeight="1">
       <c r="A206" s="2" t="s">
         <v>28</v>
       </c>
@@ -20844,13 +21280,13 @@
         <v>90</v>
       </c>
       <c r="D206" s="3" t="s">
+        <v>846</v>
+      </c>
+      <c r="E206" s="2" t="s">
+        <v>847</v>
+      </c>
+      <c r="F206" s="2" t="s">
         <v>848</v>
-      </c>
-      <c r="E206" s="2" t="s">
-        <v>849</v>
-      </c>
-      <c r="F206" s="2" t="s">
-        <v>850</v>
       </c>
       <c r="G206" s="2" t="s">
         <v>707</v>
@@ -20862,7 +21298,7 @@
         <v>36</v>
       </c>
       <c r="J206" s="3" t="s">
-        <v>279</v>
+        <v>82</v>
       </c>
       <c r="K206" s="2" t="s">
         <v>38</v>
@@ -20872,31 +21308,31 @@
         <v>39</v>
       </c>
       <c r="N206" s="3" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="O206" s="2" t="s">
-        <v>219</v>
+        <v>74</v>
       </c>
       <c r="P206" s="2">
         <v>2026</v>
       </c>
       <c r="Q206" s="2">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="R206" s="2" t="s">
-        <v>180</v>
+        <v>851</v>
       </c>
       <c r="S206" s="2" t="s">
-        <v>67</v>
+        <v>852</v>
       </c>
       <c r="T206" s="4" t="s">
         <v>87</v>
       </c>
       <c r="U206" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="V206" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="W206" s="4" t="s">
         <v>49</v>
@@ -20908,16 +21344,16 @@
         <v>49</v>
       </c>
       <c r="Z206" s="4" t="s">
-        <v>50</v>
+        <v>98</v>
       </c>
       <c r="AA206" s="4" t="s">
         <v>46</v>
       </c>
       <c r="AB206" s="5">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="207" spans="1:28" ht="28.35" customHeight="1" x14ac:dyDescent="0.3">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="207" spans="1:28" ht="28.35" customHeight="1">
       <c r="A207" s="2" t="s">
         <v>28</v>
       </c>
@@ -20928,13 +21364,13 @@
         <v>90</v>
       </c>
       <c r="D207" s="3" t="s">
+        <v>846</v>
+      </c>
+      <c r="E207" s="2" t="s">
+        <v>847</v>
+      </c>
+      <c r="F207" s="2" t="s">
         <v>848</v>
-      </c>
-      <c r="E207" s="2" t="s">
-        <v>849</v>
-      </c>
-      <c r="F207" s="2" t="s">
-        <v>850</v>
       </c>
       <c r="G207" s="2" t="s">
         <v>707</v>
@@ -20946,7 +21382,7 @@
         <v>36</v>
       </c>
       <c r="J207" s="3" t="s">
-        <v>82</v>
+        <v>131</v>
       </c>
       <c r="K207" s="2" t="s">
         <v>38</v>
@@ -20956,25 +21392,25 @@
         <v>39</v>
       </c>
       <c r="N207" s="3" t="s">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="O207" s="2" t="s">
-        <v>74</v>
+        <v>128</v>
       </c>
       <c r="P207" s="2">
         <v>2026</v>
       </c>
       <c r="Q207" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="R207" s="2" t="s">
-        <v>853</v>
+        <v>851</v>
       </c>
       <c r="S207" s="2" t="s">
         <v>854</v>
       </c>
       <c r="T207" s="4" t="s">
-        <v>87</v>
+        <v>134</v>
       </c>
       <c r="U207" s="4" t="s">
         <v>46</v>
@@ -20998,10 +21434,10 @@
         <v>46</v>
       </c>
       <c r="AB207" s="5">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="208" spans="1:28" ht="28.35" customHeight="1" x14ac:dyDescent="0.3">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="208" spans="1:28" ht="28.35" customHeight="1">
       <c r="A208" s="2" t="s">
         <v>28</v>
       </c>
@@ -21012,13 +21448,13 @@
         <v>90</v>
       </c>
       <c r="D208" s="3" t="s">
+        <v>846</v>
+      </c>
+      <c r="E208" s="2" t="s">
+        <v>847</v>
+      </c>
+      <c r="F208" s="2" t="s">
         <v>848</v>
-      </c>
-      <c r="E208" s="2" t="s">
-        <v>849</v>
-      </c>
-      <c r="F208" s="2" t="s">
-        <v>850</v>
       </c>
       <c r="G208" s="2" t="s">
         <v>707</v>
@@ -21030,7 +21466,7 @@
         <v>36</v>
       </c>
       <c r="J208" s="3" t="s">
-        <v>131</v>
+        <v>82</v>
       </c>
       <c r="K208" s="2" t="s">
         <v>38</v>
@@ -21043,31 +21479,31 @@
         <v>855</v>
       </c>
       <c r="O208" s="2" t="s">
-        <v>128</v>
+        <v>74</v>
       </c>
       <c r="P208" s="2">
         <v>2026</v>
       </c>
       <c r="Q208" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="R208" s="2" t="s">
-        <v>853</v>
+        <v>851</v>
       </c>
       <c r="S208" s="2" t="s">
-        <v>856</v>
+        <v>852</v>
       </c>
       <c r="T208" s="4" t="s">
-        <v>134</v>
+        <v>87</v>
       </c>
       <c r="U208" s="4" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="V208" s="4" t="s">
         <v>46</v>
       </c>
       <c r="W208" s="4" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="X208" s="4" t="s">
         <v>49</v>
@@ -21076,7 +21512,7 @@
         <v>49</v>
       </c>
       <c r="Z208" s="4" t="s">
-        <v>98</v>
+        <v>50</v>
       </c>
       <c r="AA208" s="4" t="s">
         <v>46</v>
@@ -21085,7 +21521,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="209" spans="1:28" ht="28.35" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:28" ht="28.35" customHeight="1">
       <c r="A209" s="2" t="s">
         <v>28</v>
       </c>
@@ -21093,19 +21529,19 @@
         <v>29</v>
       </c>
       <c r="C209" s="3" t="s">
-        <v>90</v>
+        <v>68</v>
       </c>
       <c r="D209" s="3" t="s">
-        <v>848</v>
+        <v>499</v>
       </c>
       <c r="E209" s="2" t="s">
-        <v>849</v>
+        <v>856</v>
       </c>
       <c r="F209" s="2" t="s">
-        <v>850</v>
+        <v>857</v>
       </c>
       <c r="G209" s="2" t="s">
-        <v>707</v>
+        <v>404</v>
       </c>
       <c r="H209" s="2" t="s">
         <v>35</v>
@@ -21114,7 +21550,7 @@
         <v>36</v>
       </c>
       <c r="J209" s="3" t="s">
-        <v>82</v>
+        <v>37</v>
       </c>
       <c r="K209" s="2" t="s">
         <v>38</v>
@@ -21124,34 +21560,34 @@
         <v>39</v>
       </c>
       <c r="N209" s="3" t="s">
-        <v>857</v>
+        <v>858</v>
       </c>
       <c r="O209" s="2" t="s">
-        <v>74</v>
+        <v>144</v>
       </c>
       <c r="P209" s="2">
         <v>2026</v>
       </c>
       <c r="Q209" s="2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="R209" s="2" t="s">
-        <v>853</v>
+        <v>58</v>
       </c>
       <c r="S209" s="2" t="s">
-        <v>854</v>
+        <v>859</v>
       </c>
       <c r="T209" s="4" t="s">
-        <v>87</v>
+        <v>44</v>
       </c>
       <c r="U209" s="4" t="s">
-        <v>47</v>
+        <v>256</v>
       </c>
       <c r="V209" s="4" t="s">
-        <v>46</v>
+        <v>77</v>
       </c>
       <c r="W209" s="4" t="s">
-        <v>46</v>
+        <v>60</v>
       </c>
       <c r="X209" s="4" t="s">
         <v>49</v>
@@ -21160,16 +21596,16 @@
         <v>49</v>
       </c>
       <c r="Z209" s="4" t="s">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="AA209" s="4" t="s">
         <v>46</v>
       </c>
       <c r="AB209" s="5">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="210" spans="1:28" ht="28.35" customHeight="1" x14ac:dyDescent="0.3">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="210" spans="1:28" ht="28.35" customHeight="1">
       <c r="A210" s="2" t="s">
         <v>28</v>
       </c>
@@ -21183,10 +21619,10 @@
         <v>499</v>
       </c>
       <c r="E210" s="2" t="s">
-        <v>858</v>
+        <v>856</v>
       </c>
       <c r="F210" s="2" t="s">
-        <v>859</v>
+        <v>857</v>
       </c>
       <c r="G210" s="2" t="s">
         <v>404</v>
@@ -21211,31 +21647,31 @@
         <v>860</v>
       </c>
       <c r="O210" s="2" t="s">
-        <v>144</v>
+        <v>861</v>
       </c>
       <c r="P210" s="2">
         <v>2026</v>
       </c>
       <c r="Q210" s="2">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="R210" s="2" t="s">
         <v>58</v>
       </c>
       <c r="S210" s="2" t="s">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="T210" s="4" t="s">
         <v>44</v>
       </c>
       <c r="U210" s="4" t="s">
-        <v>256</v>
+        <v>77</v>
       </c>
       <c r="V210" s="4" t="s">
-        <v>77</v>
+        <v>60</v>
       </c>
       <c r="W210" s="4" t="s">
-        <v>60</v>
+        <v>47</v>
       </c>
       <c r="X210" s="4" t="s">
         <v>49</v>
@@ -21244,16 +21680,16 @@
         <v>49</v>
       </c>
       <c r="Z210" s="4" t="s">
-        <v>78</v>
+        <v>295</v>
       </c>
       <c r="AA210" s="4" t="s">
         <v>46</v>
       </c>
       <c r="AB210" s="5">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="211" spans="1:28" ht="28.35" customHeight="1" x14ac:dyDescent="0.3">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="211" spans="1:28" ht="28.35" customHeight="1">
       <c r="A211" s="2" t="s">
         <v>28</v>
       </c>
@@ -21267,10 +21703,10 @@
         <v>499</v>
       </c>
       <c r="E211" s="2" t="s">
-        <v>858</v>
+        <v>856</v>
       </c>
       <c r="F211" s="2" t="s">
-        <v>859</v>
+        <v>857</v>
       </c>
       <c r="G211" s="2" t="s">
         <v>404</v>
@@ -21292,52 +21728,52 @@
         <v>39</v>
       </c>
       <c r="N211" s="3" t="s">
-        <v>862</v>
+        <v>863</v>
       </c>
       <c r="O211" s="2" t="s">
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="P211" s="2">
         <v>2026</v>
       </c>
       <c r="Q211" s="2">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="R211" s="2" t="s">
-        <v>58</v>
+        <v>107</v>
       </c>
       <c r="S211" s="2" t="s">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="T211" s="4" t="s">
         <v>44</v>
       </c>
       <c r="U211" s="4" t="s">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="V211" s="4" t="s">
-        <v>60</v>
+        <v>109</v>
       </c>
       <c r="W211" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="X211" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="X211" s="4" t="s">
-        <v>49</v>
-      </c>
       <c r="Y211" s="4" t="s">
         <v>49</v>
       </c>
       <c r="Z211" s="4" t="s">
-        <v>295</v>
+        <v>257</v>
       </c>
       <c r="AA211" s="4" t="s">
         <v>46</v>
       </c>
       <c r="AB211" s="5">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="212" spans="1:28" ht="28.35" customHeight="1" x14ac:dyDescent="0.3">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="212" spans="1:28" ht="28.35" customHeight="1">
       <c r="A212" s="2" t="s">
         <v>28</v>
       </c>
@@ -21345,83 +21781,81 @@
         <v>29</v>
       </c>
       <c r="C212" s="3" t="s">
-        <v>68</v>
+        <v>30</v>
       </c>
       <c r="D212" s="3" t="s">
-        <v>499</v>
+        <v>331</v>
       </c>
       <c r="E212" s="2" t="s">
-        <v>858</v>
+        <v>866</v>
       </c>
       <c r="F212" s="2" t="s">
-        <v>859</v>
+        <v>867</v>
       </c>
       <c r="G212" s="2" t="s">
         <v>404</v>
       </c>
-      <c r="H212" s="2" t="s">
-        <v>35</v>
-      </c>
+      <c r="H212" s="2"/>
       <c r="I212" s="3" t="s">
-        <v>36</v>
+        <v>114</v>
       </c>
       <c r="J212" s="3" t="s">
-        <v>37</v>
+        <v>115</v>
       </c>
       <c r="K212" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="L212" s="2"/>
+        <v>72</v>
+      </c>
+      <c r="L212" s="2" t="s">
+        <v>868</v>
+      </c>
       <c r="M212" s="2" t="s">
         <v>39</v>
       </c>
       <c r="N212" s="3" t="s">
-        <v>865</v>
+        <v>335</v>
       </c>
       <c r="O212" s="2" t="s">
-        <v>866</v>
+        <v>336</v>
       </c>
       <c r="P212" s="2">
         <v>2026</v>
       </c>
       <c r="Q212" s="2">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="R212" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="S212" s="2" t="s">
-        <v>867</v>
-      </c>
+        <v>419</v>
+      </c>
+      <c r="S212" s="2"/>
       <c r="T212" s="4" t="s">
-        <v>44</v>
+        <v>120</v>
       </c>
       <c r="U212" s="4" t="s">
-        <v>88</v>
+        <v>46</v>
       </c>
       <c r="V212" s="4" t="s">
-        <v>109</v>
+        <v>49</v>
       </c>
       <c r="W212" s="4" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="X212" s="4" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="Y212" s="4" t="s">
         <v>49</v>
       </c>
       <c r="Z212" s="4" t="s">
-        <v>257</v>
+        <v>98</v>
       </c>
       <c r="AA212" s="4" t="s">
         <v>46</v>
       </c>
       <c r="AB212" s="5">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="213" spans="1:28" ht="28.35" customHeight="1" x14ac:dyDescent="0.3">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="213" spans="1:28" ht="28.35" customHeight="1">
       <c r="A213" s="2" t="s">
         <v>28</v>
       </c>
@@ -21435,57 +21869,59 @@
         <v>331</v>
       </c>
       <c r="E213" s="2" t="s">
-        <v>868</v>
+        <v>866</v>
       </c>
       <c r="F213" s="2" t="s">
-        <v>869</v>
+        <v>867</v>
       </c>
       <c r="G213" s="2" t="s">
         <v>404</v>
       </c>
-      <c r="H213" s="2"/>
+      <c r="H213" s="2" t="s">
+        <v>35</v>
+      </c>
       <c r="I213" s="3" t="s">
-        <v>114</v>
+        <v>36</v>
       </c>
       <c r="J213" s="3" t="s">
-        <v>115</v>
+        <v>37</v>
       </c>
       <c r="K213" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="L213" s="2" t="s">
-        <v>870</v>
-      </c>
+      <c r="L213" s="2"/>
       <c r="M213" s="2" t="s">
         <v>39</v>
       </c>
       <c r="N213" s="3" t="s">
-        <v>335</v>
+        <v>869</v>
       </c>
       <c r="O213" s="2" t="s">
-        <v>336</v>
+        <v>870</v>
       </c>
       <c r="P213" s="2">
         <v>2026</v>
       </c>
       <c r="Q213" s="2">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="R213" s="2" t="s">
-        <v>419</v>
-      </c>
-      <c r="S213" s="2"/>
+        <v>75</v>
+      </c>
+      <c r="S213" s="2" t="s">
+        <v>871</v>
+      </c>
       <c r="T213" s="4" t="s">
-        <v>120</v>
+        <v>44</v>
       </c>
       <c r="U213" s="4" t="s">
-        <v>46</v>
+        <v>872</v>
       </c>
       <c r="V213" s="4" t="s">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="W213" s="4" t="s">
-        <v>46</v>
+        <v>873</v>
       </c>
       <c r="X213" s="4" t="s">
         <v>49</v>
@@ -21494,16 +21930,16 @@
         <v>49</v>
       </c>
       <c r="Z213" s="4" t="s">
-        <v>98</v>
+        <v>122</v>
       </c>
       <c r="AA213" s="4" t="s">
         <v>46</v>
       </c>
       <c r="AB213" s="5">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="214" spans="1:28" ht="28.35" customHeight="1" x14ac:dyDescent="0.3">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="214" spans="1:28" ht="28.35" customHeight="1">
       <c r="A214" s="2" t="s">
         <v>28</v>
       </c>
@@ -21517,10 +21953,10 @@
         <v>331</v>
       </c>
       <c r="E214" s="2" t="s">
-        <v>868</v>
+        <v>866</v>
       </c>
       <c r="F214" s="2" t="s">
-        <v>869</v>
+        <v>867</v>
       </c>
       <c r="G214" s="2" t="s">
         <v>404</v>
@@ -21535,42 +21971,42 @@
         <v>37</v>
       </c>
       <c r="K214" s="2" t="s">
-        <v>72</v>
+        <v>38</v>
       </c>
       <c r="L214" s="2"/>
       <c r="M214" s="2" t="s">
         <v>39</v>
       </c>
       <c r="N214" s="3" t="s">
-        <v>871</v>
+        <v>874</v>
       </c>
       <c r="O214" s="2" t="s">
-        <v>872</v>
+        <v>151</v>
       </c>
       <c r="P214" s="2">
         <v>2026</v>
       </c>
       <c r="Q214" s="2">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="R214" s="2" t="s">
         <v>75</v>
       </c>
       <c r="S214" s="2" t="s">
-        <v>873</v>
+        <v>875</v>
       </c>
       <c r="T214" s="4" t="s">
         <v>44</v>
       </c>
       <c r="U214" s="4" t="s">
-        <v>874</v>
+        <v>77</v>
       </c>
       <c r="V214" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="W214" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="W214" s="4" t="s">
-        <v>875</v>
-      </c>
       <c r="X214" s="4" t="s">
         <v>49</v>
       </c>
@@ -21578,16 +22014,16 @@
         <v>49</v>
       </c>
       <c r="Z214" s="4" t="s">
-        <v>122</v>
+        <v>50</v>
       </c>
       <c r="AA214" s="4" t="s">
         <v>46</v>
       </c>
       <c r="AB214" s="5">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="215" spans="1:28" ht="28.35" customHeight="1" x14ac:dyDescent="0.3">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="215" spans="1:28" ht="28.35" customHeight="1">
       <c r="A215" s="2" t="s">
         <v>28</v>
       </c>
@@ -21601,10 +22037,10 @@
         <v>331</v>
       </c>
       <c r="E215" s="2" t="s">
-        <v>868</v>
+        <v>866</v>
       </c>
       <c r="F215" s="2" t="s">
-        <v>869</v>
+        <v>867</v>
       </c>
       <c r="G215" s="2" t="s">
         <v>404</v>
@@ -21619,7 +22055,7 @@
         <v>37</v>
       </c>
       <c r="K215" s="2" t="s">
-        <v>38</v>
+        <v>72</v>
       </c>
       <c r="L215" s="2"/>
       <c r="M215" s="2" t="s">
@@ -21629,13 +22065,13 @@
         <v>876</v>
       </c>
       <c r="O215" s="2" t="s">
-        <v>151</v>
+        <v>339</v>
       </c>
       <c r="P215" s="2">
         <v>2026</v>
       </c>
       <c r="Q215" s="2">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="R215" s="2" t="s">
         <v>75</v>
@@ -21647,13 +22083,13 @@
         <v>44</v>
       </c>
       <c r="U215" s="4" t="s">
-        <v>77</v>
+        <v>878</v>
       </c>
       <c r="V215" s="4" t="s">
         <v>47</v>
       </c>
       <c r="W215" s="4" t="s">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="X215" s="4" t="s">
         <v>49</v>
@@ -21662,16 +22098,16 @@
         <v>49</v>
       </c>
       <c r="Z215" s="4" t="s">
-        <v>50</v>
+        <v>122</v>
       </c>
       <c r="AA215" s="4" t="s">
         <v>46</v>
       </c>
       <c r="AB215" s="5">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="216" spans="1:28" ht="28.35" customHeight="1" x14ac:dyDescent="0.3">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="216" spans="1:28" ht="28.35" customHeight="1">
       <c r="A216" s="2" t="s">
         <v>28</v>
       </c>
@@ -21679,16 +22115,16 @@
         <v>29</v>
       </c>
       <c r="C216" s="3" t="s">
-        <v>30</v>
+        <v>352</v>
       </c>
       <c r="D216" s="3" t="s">
-        <v>331</v>
+        <v>353</v>
       </c>
       <c r="E216" s="2" t="s">
-        <v>868</v>
+        <v>879</v>
       </c>
       <c r="F216" s="2" t="s">
-        <v>869</v>
+        <v>880</v>
       </c>
       <c r="G216" s="2" t="s">
         <v>404</v>
@@ -21700,44 +22136,44 @@
         <v>36</v>
       </c>
       <c r="J216" s="3" t="s">
-        <v>37</v>
+        <v>82</v>
       </c>
       <c r="K216" s="2" t="s">
-        <v>72</v>
+        <v>38</v>
       </c>
       <c r="L216" s="2"/>
       <c r="M216" s="2" t="s">
         <v>39</v>
       </c>
       <c r="N216" s="3" t="s">
-        <v>878</v>
+        <v>881</v>
       </c>
       <c r="O216" s="2" t="s">
-        <v>339</v>
+        <v>580</v>
       </c>
       <c r="P216" s="2">
         <v>2026</v>
       </c>
       <c r="Q216" s="2">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="R216" s="2" t="s">
-        <v>75</v>
+        <v>429</v>
       </c>
       <c r="S216" s="2" t="s">
-        <v>879</v>
+        <v>446</v>
       </c>
       <c r="T216" s="4" t="s">
-        <v>44</v>
+        <v>87</v>
       </c>
       <c r="U216" s="4" t="s">
-        <v>880</v>
+        <v>60</v>
       </c>
       <c r="V216" s="4" t="s">
         <v>47</v>
       </c>
       <c r="W216" s="4" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="X216" s="4" t="s">
         <v>49</v>
@@ -21746,16 +22182,16 @@
         <v>49</v>
       </c>
       <c r="Z216" s="4" t="s">
-        <v>122</v>
+        <v>50</v>
       </c>
       <c r="AA216" s="4" t="s">
         <v>46</v>
       </c>
       <c r="AB216" s="5">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="217" spans="1:28" ht="28.35" customHeight="1" x14ac:dyDescent="0.3">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="217" spans="1:28" ht="28.35" customHeight="1">
       <c r="A217" s="2" t="s">
         <v>28</v>
       </c>
@@ -21763,19 +22199,19 @@
         <v>29</v>
       </c>
       <c r="C217" s="3" t="s">
-        <v>352</v>
+        <v>51</v>
       </c>
       <c r="D217" s="3" t="s">
-        <v>353</v>
+        <v>52</v>
       </c>
       <c r="E217" s="2" t="s">
-        <v>881</v>
+        <v>882</v>
       </c>
       <c r="F217" s="2" t="s">
-        <v>882</v>
+        <v>883</v>
       </c>
       <c r="G217" s="2" t="s">
-        <v>404</v>
+        <v>590</v>
       </c>
       <c r="H217" s="2" t="s">
         <v>35</v>
@@ -21794,34 +22230,34 @@
         <v>39</v>
       </c>
       <c r="N217" s="3" t="s">
-        <v>883</v>
+        <v>884</v>
       </c>
       <c r="O217" s="2" t="s">
-        <v>580</v>
+        <v>74</v>
       </c>
       <c r="P217" s="2">
         <v>2026</v>
       </c>
       <c r="Q217" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="R217" s="2" t="s">
-        <v>429</v>
+        <v>885</v>
       </c>
       <c r="S217" s="2" t="s">
-        <v>446</v>
+        <v>886</v>
       </c>
       <c r="T217" s="4" t="s">
         <v>87</v>
       </c>
       <c r="U217" s="4" t="s">
-        <v>60</v>
+        <v>46</v>
       </c>
       <c r="V217" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="W217" s="4" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="X217" s="4" t="s">
         <v>49</v>
@@ -21830,16 +22266,16 @@
         <v>49</v>
       </c>
       <c r="Z217" s="4" t="s">
-        <v>50</v>
+        <v>98</v>
       </c>
       <c r="AA217" s="4" t="s">
         <v>46</v>
       </c>
       <c r="AB217" s="5">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="218" spans="1:28" ht="28.35" customHeight="1" x14ac:dyDescent="0.3">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="218" spans="1:28" ht="28.35" customHeight="1">
       <c r="A218" s="2" t="s">
         <v>28</v>
       </c>
@@ -21847,19 +22283,19 @@
         <v>29</v>
       </c>
       <c r="C218" s="3" t="s">
-        <v>51</v>
+        <v>190</v>
       </c>
       <c r="D218" s="3" t="s">
-        <v>52</v>
+        <v>368</v>
       </c>
       <c r="E218" s="2" t="s">
-        <v>884</v>
+        <v>887</v>
       </c>
       <c r="F218" s="2" t="s">
-        <v>885</v>
+        <v>888</v>
       </c>
       <c r="G218" s="2" t="s">
-        <v>590</v>
+        <v>404</v>
       </c>
       <c r="H218" s="2" t="s">
         <v>35</v>
@@ -21868,44 +22304,44 @@
         <v>36</v>
       </c>
       <c r="J218" s="3" t="s">
-        <v>82</v>
+        <v>37</v>
       </c>
       <c r="K218" s="2" t="s">
-        <v>38</v>
+        <v>72</v>
       </c>
       <c r="L218" s="2"/>
       <c r="M218" s="2" t="s">
         <v>39</v>
       </c>
       <c r="N218" s="3" t="s">
-        <v>886</v>
+        <v>889</v>
       </c>
       <c r="O218" s="2" t="s">
-        <v>74</v>
+        <v>628</v>
       </c>
       <c r="P218" s="2">
         <v>2026</v>
       </c>
       <c r="Q218" s="2">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="R218" s="2" t="s">
-        <v>887</v>
+        <v>413</v>
       </c>
       <c r="S218" s="2" t="s">
-        <v>888</v>
+        <v>890</v>
       </c>
       <c r="T218" s="4" t="s">
-        <v>87</v>
+        <v>44</v>
       </c>
       <c r="U218" s="4" t="s">
-        <v>46</v>
+        <v>77</v>
       </c>
       <c r="V218" s="4" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="W218" s="4" t="s">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="X218" s="4" t="s">
         <v>49</v>
@@ -21914,16 +22350,16 @@
         <v>49</v>
       </c>
       <c r="Z218" s="4" t="s">
-        <v>98</v>
+        <v>379</v>
       </c>
       <c r="AA218" s="4" t="s">
         <v>46</v>
       </c>
       <c r="AB218" s="5">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="219" spans="1:28" ht="28.35" customHeight="1" x14ac:dyDescent="0.3">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="219" spans="1:28" ht="28.35" customHeight="1">
       <c r="A219" s="2" t="s">
         <v>28</v>
       </c>
@@ -21937,10 +22373,10 @@
         <v>368</v>
       </c>
       <c r="E219" s="2" t="s">
-        <v>889</v>
+        <v>887</v>
       </c>
       <c r="F219" s="2" t="s">
-        <v>890</v>
+        <v>888</v>
       </c>
       <c r="G219" s="2" t="s">
         <v>404</v>
@@ -21952,10 +22388,10 @@
         <v>36</v>
       </c>
       <c r="J219" s="3" t="s">
-        <v>37</v>
+        <v>279</v>
       </c>
       <c r="K219" s="2" t="s">
-        <v>72</v>
+        <v>38</v>
       </c>
       <c r="L219" s="2"/>
       <c r="M219" s="2" t="s">
@@ -21965,31 +22401,31 @@
         <v>891</v>
       </c>
       <c r="O219" s="2" t="s">
-        <v>628</v>
+        <v>254</v>
       </c>
       <c r="P219" s="2">
         <v>2026</v>
       </c>
       <c r="Q219" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R219" s="2" t="s">
-        <v>413</v>
+        <v>144</v>
       </c>
       <c r="S219" s="2" t="s">
-        <v>892</v>
+        <v>373</v>
       </c>
       <c r="T219" s="4" t="s">
-        <v>44</v>
+        <v>87</v>
       </c>
       <c r="U219" s="4" t="s">
-        <v>77</v>
+        <v>60</v>
       </c>
       <c r="V219" s="4" t="s">
         <v>47</v>
       </c>
       <c r="W219" s="4" t="s">
-        <v>60</v>
+        <v>46</v>
       </c>
       <c r="X219" s="4" t="s">
         <v>49</v>
@@ -21998,16 +22434,16 @@
         <v>49</v>
       </c>
       <c r="Z219" s="4" t="s">
-        <v>379</v>
+        <v>50</v>
       </c>
       <c r="AA219" s="4" t="s">
         <v>46</v>
       </c>
       <c r="AB219" s="5">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="220" spans="1:28" ht="28.35" customHeight="1" x14ac:dyDescent="0.3">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="220" spans="1:28" ht="28.35" customHeight="1">
       <c r="A220" s="2" t="s">
         <v>28</v>
       </c>
@@ -22015,65 +22451,63 @@
         <v>29</v>
       </c>
       <c r="C220" s="3" t="s">
-        <v>190</v>
+        <v>206</v>
       </c>
       <c r="D220" s="3" t="s">
-        <v>368</v>
+        <v>643</v>
       </c>
       <c r="E220" s="2" t="s">
-        <v>889</v>
+        <v>892</v>
       </c>
       <c r="F220" s="2" t="s">
-        <v>890</v>
+        <v>893</v>
       </c>
       <c r="G220" s="2" t="s">
         <v>404</v>
       </c>
-      <c r="H220" s="2" t="s">
-        <v>35</v>
-      </c>
+      <c r="H220" s="2"/>
       <c r="I220" s="3" t="s">
-        <v>36</v>
+        <v>114</v>
       </c>
       <c r="J220" s="3" t="s">
-        <v>279</v>
+        <v>894</v>
       </c>
       <c r="K220" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="L220" s="2"/>
+      <c r="L220" s="2" t="s">
+        <v>167</v>
+      </c>
       <c r="M220" s="2" t="s">
         <v>39</v>
       </c>
       <c r="N220" s="3" t="s">
-        <v>893</v>
+        <v>895</v>
       </c>
       <c r="O220" s="2" t="s">
-        <v>254</v>
+        <v>57</v>
       </c>
       <c r="P220" s="2">
         <v>2026</v>
       </c>
       <c r="Q220" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R220" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="S220" s="2" t="s">
-        <v>373</v>
-      </c>
+        <v>119</v>
+      </c>
+      <c r="S220" s="2"/>
       <c r="T220" s="4" t="s">
-        <v>87</v>
+        <v>44</v>
       </c>
       <c r="U220" s="4" t="s">
-        <v>60</v>
+        <v>46</v>
       </c>
       <c r="V220" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="W220" s="4" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="X220" s="4" t="s">
         <v>49</v>
@@ -22082,16 +22516,16 @@
         <v>49</v>
       </c>
       <c r="Z220" s="4" t="s">
-        <v>50</v>
+        <v>98</v>
       </c>
       <c r="AA220" s="4" t="s">
         <v>46</v>
       </c>
       <c r="AB220" s="5">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="221" spans="1:28" ht="28.35" customHeight="1" x14ac:dyDescent="0.3">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="221" spans="1:28" ht="28.35" customHeight="1">
       <c r="A221" s="2" t="s">
         <v>28</v>
       </c>
@@ -22105,10 +22539,10 @@
         <v>643</v>
       </c>
       <c r="E221" s="2" t="s">
-        <v>894</v>
+        <v>892</v>
       </c>
       <c r="F221" s="2" t="s">
-        <v>895</v>
+        <v>893</v>
       </c>
       <c r="G221" s="2" t="s">
         <v>404</v>
@@ -22121,7 +22555,7 @@
         <v>896</v>
       </c>
       <c r="K221" s="2" t="s">
-        <v>38</v>
+        <v>72</v>
       </c>
       <c r="L221" s="2" t="s">
         <v>167</v>
@@ -22133,47 +22567,47 @@
         <v>897</v>
       </c>
       <c r="O221" s="2" t="s">
-        <v>57</v>
+        <v>219</v>
       </c>
       <c r="P221" s="2">
         <v>2026</v>
       </c>
       <c r="Q221" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R221" s="2" t="s">
         <v>119</v>
       </c>
       <c r="S221" s="2"/>
       <c r="T221" s="4" t="s">
-        <v>44</v>
+        <v>87</v>
       </c>
       <c r="U221" s="4" t="s">
-        <v>46</v>
+        <v>121</v>
       </c>
       <c r="V221" s="4" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="W221" s="4" t="s">
-        <v>49</v>
+        <v>109</v>
       </c>
       <c r="X221" s="4" t="s">
         <v>49</v>
       </c>
       <c r="Y221" s="4" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="Z221" s="4" t="s">
-        <v>98</v>
+        <v>379</v>
       </c>
       <c r="AA221" s="4" t="s">
         <v>46</v>
       </c>
       <c r="AB221" s="5">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="222" spans="1:28" ht="28.35" customHeight="1" x14ac:dyDescent="0.3">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="222" spans="1:28" ht="28.35" customHeight="1">
       <c r="A222" s="2" t="s">
         <v>28</v>
       </c>
@@ -22187,75 +22621,77 @@
         <v>643</v>
       </c>
       <c r="E222" s="2" t="s">
-        <v>894</v>
+        <v>892</v>
       </c>
       <c r="F222" s="2" t="s">
-        <v>895</v>
+        <v>893</v>
       </c>
       <c r="G222" s="2" t="s">
         <v>404</v>
       </c>
-      <c r="H222" s="2"/>
+      <c r="H222" s="2" t="s">
+        <v>35</v>
+      </c>
       <c r="I222" s="3" t="s">
-        <v>114</v>
+        <v>36</v>
       </c>
       <c r="J222" s="3" t="s">
-        <v>898</v>
+        <v>82</v>
       </c>
       <c r="K222" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="L222" s="2" t="s">
-        <v>167</v>
-      </c>
+        <v>38</v>
+      </c>
+      <c r="L222" s="2"/>
       <c r="M222" s="2" t="s">
         <v>39</v>
       </c>
       <c r="N222" s="3" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="O222" s="2" t="s">
-        <v>219</v>
+        <v>96</v>
       </c>
       <c r="P222" s="2">
         <v>2026</v>
       </c>
       <c r="Q222" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R222" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="S222" s="2"/>
+        <v>242</v>
+      </c>
+      <c r="S222" s="2" t="s">
+        <v>899</v>
+      </c>
       <c r="T222" s="4" t="s">
         <v>87</v>
       </c>
       <c r="U222" s="4" t="s">
-        <v>121</v>
+        <v>46</v>
       </c>
       <c r="V222" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="W222" s="4" t="s">
-        <v>109</v>
+        <v>49</v>
       </c>
       <c r="X222" s="4" t="s">
         <v>49</v>
       </c>
       <c r="Y222" s="4" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="Z222" s="4" t="s">
-        <v>379</v>
+        <v>98</v>
       </c>
       <c r="AA222" s="4" t="s">
         <v>46</v>
       </c>
       <c r="AB222" s="5">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="223" spans="1:28" ht="28.35" customHeight="1" x14ac:dyDescent="0.3">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="223" spans="1:28" ht="28.35" customHeight="1">
       <c r="A223" s="2" t="s">
         <v>28</v>
       </c>
@@ -22269,10 +22705,10 @@
         <v>643</v>
       </c>
       <c r="E223" s="2" t="s">
-        <v>894</v>
+        <v>892</v>
       </c>
       <c r="F223" s="2" t="s">
-        <v>895</v>
+        <v>893</v>
       </c>
       <c r="G223" s="2" t="s">
         <v>404</v>
@@ -22297,16 +22733,16 @@
         <v>900</v>
       </c>
       <c r="O223" s="2" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="P223" s="2">
         <v>2026</v>
       </c>
       <c r="Q223" s="2">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="R223" s="2" t="s">
-        <v>242</v>
+        <v>100</v>
       </c>
       <c r="S223" s="2" t="s">
         <v>901</v>
@@ -22339,7 +22775,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="224" spans="1:28" ht="28.35" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:28" ht="28.35" customHeight="1">
       <c r="A224" s="2" t="s">
         <v>28</v>
       </c>
@@ -22347,16 +22783,16 @@
         <v>29</v>
       </c>
       <c r="C224" s="3" t="s">
-        <v>206</v>
+        <v>212</v>
       </c>
       <c r="D224" s="3" t="s">
-        <v>643</v>
+        <v>347</v>
       </c>
       <c r="E224" s="2" t="s">
-        <v>894</v>
+        <v>902</v>
       </c>
       <c r="F224" s="2" t="s">
-        <v>895</v>
+        <v>903</v>
       </c>
       <c r="G224" s="2" t="s">
         <v>404</v>
@@ -22378,7 +22814,7 @@
         <v>39</v>
       </c>
       <c r="N224" s="3" t="s">
-        <v>902</v>
+        <v>904</v>
       </c>
       <c r="O224" s="2" t="s">
         <v>100</v>
@@ -22390,19 +22826,19 @@
         <v>8</v>
       </c>
       <c r="R224" s="2" t="s">
-        <v>100</v>
+        <v>58</v>
       </c>
       <c r="S224" s="2" t="s">
-        <v>903</v>
+        <v>905</v>
       </c>
       <c r="T224" s="4" t="s">
         <v>87</v>
       </c>
       <c r="U224" s="4" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="V224" s="4" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="W224" s="4" t="s">
         <v>49</v>
@@ -22414,16 +22850,16 @@
         <v>49</v>
       </c>
       <c r="Z224" s="4" t="s">
-        <v>98</v>
+        <v>50</v>
       </c>
       <c r="AA224" s="4" t="s">
         <v>46</v>
       </c>
       <c r="AB224" s="5">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="225" spans="1:28" ht="28.35" customHeight="1" x14ac:dyDescent="0.3">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="225" spans="1:29" ht="28.35" customHeight="1">
       <c r="A225" s="2" t="s">
         <v>28</v>
       </c>
@@ -22437,10 +22873,10 @@
         <v>347</v>
       </c>
       <c r="E225" s="2" t="s">
-        <v>904</v>
+        <v>902</v>
       </c>
       <c r="F225" s="2" t="s">
-        <v>905</v>
+        <v>903</v>
       </c>
       <c r="G225" s="2" t="s">
         <v>404</v>
@@ -22465,19 +22901,19 @@
         <v>906</v>
       </c>
       <c r="O225" s="2" t="s">
-        <v>100</v>
+        <v>74</v>
       </c>
       <c r="P225" s="2">
         <v>2026</v>
       </c>
       <c r="Q225" s="2">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="R225" s="2" t="s">
         <v>58</v>
       </c>
       <c r="S225" s="2" t="s">
-        <v>907</v>
+        <v>581</v>
       </c>
       <c r="T225" s="4" t="s">
         <v>87</v>
@@ -22507,7 +22943,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="226" spans="1:28" ht="28.35" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:29" ht="28.35" customHeight="1">
       <c r="A226" s="2" t="s">
         <v>28</v>
       </c>
@@ -22521,10 +22957,10 @@
         <v>347</v>
       </c>
       <c r="E226" s="2" t="s">
-        <v>904</v>
+        <v>902</v>
       </c>
       <c r="F226" s="2" t="s">
-        <v>905</v>
+        <v>903</v>
       </c>
       <c r="G226" s="2" t="s">
         <v>404</v>
@@ -22546,34 +22982,34 @@
         <v>39</v>
       </c>
       <c r="N226" s="3" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="O226" s="2" t="s">
-        <v>74</v>
+        <v>234</v>
       </c>
       <c r="P226" s="2">
         <v>2026</v>
       </c>
       <c r="Q226" s="2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="R226" s="2" t="s">
         <v>58</v>
       </c>
       <c r="S226" s="2" t="s">
-        <v>581</v>
+        <v>555</v>
       </c>
       <c r="T226" s="4" t="s">
         <v>87</v>
       </c>
       <c r="U226" s="4" t="s">
-        <v>47</v>
+        <v>60</v>
       </c>
       <c r="V226" s="4" t="s">
         <v>47</v>
       </c>
       <c r="W226" s="4" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="X226" s="4" t="s">
         <v>49</v>
@@ -22591,7 +23027,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="227" spans="1:28" ht="28.35" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:29" ht="28.35" customHeight="1">
       <c r="A227" s="2" t="s">
         <v>28</v>
       </c>
@@ -22599,16 +23035,16 @@
         <v>29</v>
       </c>
       <c r="C227" s="3" t="s">
-        <v>212</v>
+        <v>138</v>
       </c>
       <c r="D227" s="3" t="s">
-        <v>347</v>
+        <v>908</v>
       </c>
       <c r="E227" s="2" t="s">
-        <v>904</v>
+        <v>909</v>
       </c>
       <c r="F227" s="2" t="s">
-        <v>905</v>
+        <v>910</v>
       </c>
       <c r="G227" s="2" t="s">
         <v>404</v>
@@ -22620,44 +23056,44 @@
         <v>36</v>
       </c>
       <c r="J227" s="3" t="s">
-        <v>82</v>
+        <v>37</v>
       </c>
       <c r="K227" s="2" t="s">
-        <v>38</v>
+        <v>72</v>
       </c>
       <c r="L227" s="2"/>
       <c r="M227" s="2" t="s">
         <v>39</v>
       </c>
       <c r="N227" s="3" t="s">
-        <v>909</v>
+        <v>911</v>
       </c>
       <c r="O227" s="2" t="s">
-        <v>234</v>
+        <v>912</v>
       </c>
       <c r="P227" s="2">
         <v>2026</v>
       </c>
       <c r="Q227" s="2">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="R227" s="2" t="s">
-        <v>58</v>
+        <v>412</v>
       </c>
       <c r="S227" s="2" t="s">
-        <v>555</v>
+        <v>913</v>
       </c>
       <c r="T227" s="4" t="s">
-        <v>87</v>
+        <v>44</v>
       </c>
       <c r="U227" s="4" t="s">
-        <v>60</v>
+        <v>121</v>
       </c>
       <c r="V227" s="4" t="s">
         <v>47</v>
       </c>
       <c r="W227" s="4" t="s">
-        <v>46</v>
+        <v>77</v>
       </c>
       <c r="X227" s="4" t="s">
         <v>49</v>
@@ -22666,16 +23102,16 @@
         <v>49</v>
       </c>
       <c r="Z227" s="4" t="s">
-        <v>50</v>
+        <v>122</v>
       </c>
       <c r="AA227" s="4" t="s">
         <v>46</v>
       </c>
       <c r="AB227" s="5">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="228" spans="1:28" ht="28.35" customHeight="1" x14ac:dyDescent="0.3">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="228" spans="1:29" ht="28.35" customHeight="1">
       <c r="A228" s="2" t="s">
         <v>28</v>
       </c>
@@ -22683,19 +23119,19 @@
         <v>29</v>
       </c>
       <c r="C228" s="3" t="s">
-        <v>138</v>
+        <v>68</v>
       </c>
       <c r="D228" s="3" t="s">
-        <v>910</v>
+        <v>620</v>
       </c>
       <c r="E228" s="2" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="F228" s="2" t="s">
-        <v>912</v>
+        <v>915</v>
       </c>
       <c r="G228" s="2" t="s">
-        <v>404</v>
+        <v>916</v>
       </c>
       <c r="H228" s="2" t="s">
         <v>35</v>
@@ -22704,62 +23140,62 @@
         <v>36</v>
       </c>
       <c r="J228" s="3" t="s">
-        <v>37</v>
+        <v>82</v>
       </c>
       <c r="K228" s="2" t="s">
-        <v>72</v>
+        <v>38</v>
       </c>
       <c r="L228" s="2"/>
       <c r="M228" s="2" t="s">
         <v>39</v>
       </c>
       <c r="N228" s="3" t="s">
-        <v>913</v>
+        <v>917</v>
       </c>
       <c r="O228" s="2" t="s">
-        <v>914</v>
+        <v>100</v>
       </c>
       <c r="P228" s="2">
         <v>2026</v>
       </c>
       <c r="Q228" s="2">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="R228" s="2" t="s">
-        <v>412</v>
+        <v>58</v>
       </c>
       <c r="S228" s="2" t="s">
-        <v>915</v>
+        <v>918</v>
       </c>
       <c r="T228" s="4" t="s">
-        <v>44</v>
+        <v>87</v>
       </c>
       <c r="U228" s="4" t="s">
-        <v>121</v>
+        <v>77</v>
       </c>
       <c r="V228" s="4" t="s">
         <v>47</v>
       </c>
       <c r="W228" s="4" t="s">
-        <v>77</v>
+        <v>47</v>
       </c>
       <c r="X228" s="4" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="Y228" s="4" t="s">
         <v>49</v>
       </c>
       <c r="Z228" s="4" t="s">
-        <v>122</v>
+        <v>50</v>
       </c>
       <c r="AA228" s="4" t="s">
         <v>46</v>
       </c>
       <c r="AB228" s="5">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="229" spans="1:28" ht="28.35" customHeight="1" x14ac:dyDescent="0.3">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="229" spans="1:29" ht="28.35" customHeight="1">
       <c r="A229" s="2" t="s">
         <v>28</v>
       </c>
@@ -22770,16 +23206,16 @@
         <v>68</v>
       </c>
       <c r="D229" s="3" t="s">
-        <v>620</v>
+        <v>919</v>
       </c>
       <c r="E229" s="2" t="s">
-        <v>916</v>
+        <v>920</v>
       </c>
       <c r="F229" s="2" t="s">
-        <v>917</v>
+        <v>921</v>
       </c>
       <c r="G229" s="2" t="s">
-        <v>918</v>
+        <v>404</v>
       </c>
       <c r="H229" s="2" t="s">
         <v>35</v>
@@ -22788,7 +23224,7 @@
         <v>36</v>
       </c>
       <c r="J229" s="3" t="s">
-        <v>82</v>
+        <v>37</v>
       </c>
       <c r="K229" s="2" t="s">
         <v>38</v>
@@ -22798,52 +23234,52 @@
         <v>39</v>
       </c>
       <c r="N229" s="3" t="s">
-        <v>919</v>
+        <v>922</v>
       </c>
       <c r="O229" s="2" t="s">
-        <v>100</v>
+        <v>580</v>
       </c>
       <c r="P229" s="2">
         <v>2026</v>
       </c>
       <c r="Q229" s="2">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="R229" s="2" t="s">
-        <v>58</v>
+        <v>413</v>
       </c>
       <c r="S229" s="2" t="s">
-        <v>920</v>
+        <v>923</v>
       </c>
       <c r="T229" s="4" t="s">
-        <v>87</v>
+        <v>44</v>
       </c>
       <c r="U229" s="4" t="s">
+        <v>878</v>
+      </c>
+      <c r="V229" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="V229" s="4" t="s">
-        <v>47</v>
-      </c>
       <c r="W229" s="4" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="X229" s="4" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="Y229" s="4" t="s">
         <v>49</v>
       </c>
       <c r="Z229" s="4" t="s">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="AA229" s="4" t="s">
         <v>46</v>
       </c>
       <c r="AB229" s="5">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="230" spans="1:28" ht="28.35" customHeight="1" x14ac:dyDescent="0.3">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="230" spans="1:29" ht="28.35" customHeight="1">
       <c r="A230" s="2" t="s">
         <v>28</v>
       </c>
@@ -22854,13 +23290,13 @@
         <v>68</v>
       </c>
       <c r="D230" s="3" t="s">
-        <v>921</v>
+        <v>408</v>
       </c>
       <c r="E230" s="2" t="s">
-        <v>922</v>
+        <v>924</v>
       </c>
       <c r="F230" s="2" t="s">
-        <v>923</v>
+        <v>925</v>
       </c>
       <c r="G230" s="2" t="s">
         <v>404</v>
@@ -22875,41 +23311,41 @@
         <v>37</v>
       </c>
       <c r="K230" s="2" t="s">
-        <v>38</v>
+        <v>72</v>
       </c>
       <c r="L230" s="2"/>
       <c r="M230" s="2" t="s">
         <v>39</v>
       </c>
       <c r="N230" s="3" t="s">
-        <v>924</v>
+        <v>926</v>
       </c>
       <c r="O230" s="2" t="s">
-        <v>580</v>
+        <v>327</v>
       </c>
       <c r="P230" s="2">
         <v>2026</v>
       </c>
       <c r="Q230" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R230" s="2" t="s">
         <v>413</v>
       </c>
       <c r="S230" s="2" t="s">
-        <v>925</v>
+        <v>927</v>
       </c>
       <c r="T230" s="4" t="s">
         <v>44</v>
       </c>
       <c r="U230" s="4" t="s">
-        <v>880</v>
+        <v>60</v>
       </c>
       <c r="V230" s="4" t="s">
-        <v>77</v>
+        <v>47</v>
       </c>
       <c r="W230" s="4" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="X230" s="4" t="s">
         <v>49</v>
@@ -22924,10 +23360,10 @@
         <v>46</v>
       </c>
       <c r="AB230" s="5">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="231" spans="1:28" ht="28.35" customHeight="1" x14ac:dyDescent="0.3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="231" spans="1:29" ht="28.35" customHeight="1">
       <c r="A231" s="2" t="s">
         <v>28</v>
       </c>
@@ -22935,16 +23371,16 @@
         <v>29</v>
       </c>
       <c r="C231" s="3" t="s">
-        <v>68</v>
+        <v>190</v>
       </c>
       <c r="D231" s="3" t="s">
-        <v>408</v>
+        <v>358</v>
       </c>
       <c r="E231" s="2" t="s">
-        <v>926</v>
+        <v>928</v>
       </c>
       <c r="F231" s="2" t="s">
-        <v>927</v>
+        <v>929</v>
       </c>
       <c r="G231" s="2" t="s">
         <v>404</v>
@@ -22959,17 +23395,17 @@
         <v>37</v>
       </c>
       <c r="K231" s="2" t="s">
-        <v>72</v>
+        <v>38</v>
       </c>
       <c r="L231" s="2"/>
       <c r="M231" s="2" t="s">
         <v>39</v>
       </c>
       <c r="N231" s="3" t="s">
-        <v>928</v>
+        <v>930</v>
       </c>
       <c r="O231" s="2" t="s">
-        <v>327</v>
+        <v>96</v>
       </c>
       <c r="P231" s="2">
         <v>2026</v>
@@ -22978,22 +23414,22 @@
         <v>4</v>
       </c>
       <c r="R231" s="2" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="S231" s="2" t="s">
-        <v>929</v>
+        <v>609</v>
       </c>
       <c r="T231" s="4" t="s">
         <v>44</v>
       </c>
       <c r="U231" s="4" t="s">
-        <v>60</v>
+        <v>46</v>
       </c>
       <c r="V231" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="W231" s="4" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="X231" s="4" t="s">
         <v>49</v>
@@ -23002,16 +23438,16 @@
         <v>49</v>
       </c>
       <c r="Z231" s="4" t="s">
-        <v>78</v>
+        <v>98</v>
       </c>
       <c r="AA231" s="4" t="s">
         <v>46</v>
       </c>
       <c r="AB231" s="5">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="232" spans="1:28" ht="28.35" customHeight="1" x14ac:dyDescent="0.3">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="232" spans="1:29" ht="28.35" customHeight="1">
       <c r="A232" s="2" t="s">
         <v>28</v>
       </c>
@@ -23019,65 +23455,63 @@
         <v>29</v>
       </c>
       <c r="C232" s="3" t="s">
-        <v>190</v>
+        <v>30</v>
       </c>
       <c r="D232" s="3" t="s">
-        <v>358</v>
+        <v>331</v>
       </c>
       <c r="E232" s="2" t="s">
-        <v>930</v>
+        <v>931</v>
       </c>
       <c r="F232" s="2" t="s">
-        <v>931</v>
+        <v>932</v>
       </c>
       <c r="G232" s="2" t="s">
         <v>404</v>
       </c>
-      <c r="H232" s="2" t="s">
-        <v>35</v>
-      </c>
+      <c r="H232" s="2"/>
       <c r="I232" s="3" t="s">
-        <v>36</v>
+        <v>114</v>
       </c>
       <c r="J232" s="3" t="s">
-        <v>37</v>
+        <v>115</v>
       </c>
       <c r="K232" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="L232" s="2"/>
+        <v>72</v>
+      </c>
+      <c r="L232" s="2" t="s">
+        <v>933</v>
+      </c>
       <c r="M232" s="2" t="s">
         <v>39</v>
       </c>
       <c r="N232" s="3" t="s">
-        <v>932</v>
+        <v>335</v>
       </c>
       <c r="O232" s="2" t="s">
-        <v>96</v>
+        <v>336</v>
       </c>
       <c r="P232" s="2">
         <v>2026</v>
       </c>
       <c r="Q232" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R232" s="2" t="s">
-        <v>412</v>
-      </c>
-      <c r="S232" s="2" t="s">
-        <v>609</v>
-      </c>
+        <v>419</v>
+      </c>
+      <c r="S232" s="2"/>
       <c r="T232" s="4" t="s">
-        <v>44</v>
+        <v>120</v>
       </c>
       <c r="U232" s="4" t="s">
         <v>46</v>
       </c>
       <c r="V232" s="4" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="W232" s="4" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="X232" s="4" t="s">
         <v>49</v>
@@ -23092,10 +23526,10 @@
         <v>46</v>
       </c>
       <c r="AB232" s="5">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="233" spans="1:28" ht="28.35" customHeight="1" x14ac:dyDescent="0.3">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="233" spans="1:29" ht="28.35" customHeight="1">
       <c r="A233" s="2" t="s">
         <v>28</v>
       </c>
@@ -23109,57 +23543,59 @@
         <v>331</v>
       </c>
       <c r="E233" s="2" t="s">
-        <v>933</v>
+        <v>931</v>
       </c>
       <c r="F233" s="2" t="s">
-        <v>934</v>
+        <v>932</v>
       </c>
       <c r="G233" s="2" t="s">
         <v>404</v>
       </c>
-      <c r="H233" s="2"/>
+      <c r="H233" s="2" t="s">
+        <v>35</v>
+      </c>
       <c r="I233" s="3" t="s">
-        <v>114</v>
+        <v>36</v>
       </c>
       <c r="J233" s="3" t="s">
-        <v>115</v>
+        <v>37</v>
       </c>
       <c r="K233" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="L233" s="2" t="s">
-        <v>935</v>
-      </c>
+      <c r="L233" s="2"/>
       <c r="M233" s="2" t="s">
         <v>39</v>
       </c>
       <c r="N233" s="3" t="s">
-        <v>335</v>
+        <v>934</v>
       </c>
       <c r="O233" s="2" t="s">
-        <v>336</v>
+        <v>124</v>
       </c>
       <c r="P233" s="2">
         <v>2026</v>
       </c>
       <c r="Q233" s="2">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="R233" s="2" t="s">
-        <v>419</v>
-      </c>
-      <c r="S233" s="2"/>
+        <v>608</v>
+      </c>
+      <c r="S233" s="2" t="s">
+        <v>935</v>
+      </c>
       <c r="T233" s="4" t="s">
-        <v>120</v>
+        <v>44</v>
       </c>
       <c r="U233" s="4" t="s">
-        <v>46</v>
+        <v>524</v>
       </c>
       <c r="V233" s="4" t="s">
-        <v>49</v>
+        <v>109</v>
       </c>
       <c r="W233" s="4" t="s">
-        <v>46</v>
+        <v>88</v>
       </c>
       <c r="X233" s="4" t="s">
         <v>49</v>
@@ -23168,16 +23604,16 @@
         <v>49</v>
       </c>
       <c r="Z233" s="4" t="s">
-        <v>98</v>
+        <v>122</v>
       </c>
       <c r="AA233" s="4" t="s">
         <v>46</v>
       </c>
       <c r="AB233" s="5">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="234" spans="1:28" ht="28.35" customHeight="1" x14ac:dyDescent="0.3">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="234" spans="1:29" ht="28.35" customHeight="1">
       <c r="A234" s="2" t="s">
         <v>28</v>
       </c>
@@ -23191,10 +23627,10 @@
         <v>331</v>
       </c>
       <c r="E234" s="2" t="s">
-        <v>933</v>
+        <v>931</v>
       </c>
       <c r="F234" s="2" t="s">
-        <v>934</v>
+        <v>932</v>
       </c>
       <c r="G234" s="2" t="s">
         <v>404</v>
@@ -23219,7 +23655,7 @@
         <v>936</v>
       </c>
       <c r="O234" s="2" t="s">
-        <v>124</v>
+        <v>234</v>
       </c>
       <c r="P234" s="2">
         <v>2026</v>
@@ -23237,13 +23673,13 @@
         <v>44</v>
       </c>
       <c r="U234" s="4" t="s">
-        <v>524</v>
+        <v>48</v>
       </c>
       <c r="V234" s="4" t="s">
         <v>109</v>
       </c>
       <c r="W234" s="4" t="s">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="X234" s="4" t="s">
         <v>49</v>
@@ -23258,10 +23694,10 @@
         <v>46</v>
       </c>
       <c r="AB234" s="5">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="235" spans="1:28" ht="28.35" customHeight="1" x14ac:dyDescent="0.3">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="235" spans="1:29" ht="28.35" customHeight="1">
       <c r="A235" s="2" t="s">
         <v>28</v>
       </c>
@@ -23275,10 +23711,10 @@
         <v>331</v>
       </c>
       <c r="E235" s="2" t="s">
-        <v>933</v>
+        <v>931</v>
       </c>
       <c r="F235" s="2" t="s">
-        <v>934</v>
+        <v>932</v>
       </c>
       <c r="G235" s="2" t="s">
         <v>404</v>
@@ -23290,10 +23726,10 @@
         <v>36</v>
       </c>
       <c r="J235" s="3" t="s">
-        <v>37</v>
+        <v>82</v>
       </c>
       <c r="K235" s="2" t="s">
-        <v>72</v>
+        <v>38</v>
       </c>
       <c r="L235" s="2"/>
       <c r="M235" s="2" t="s">
@@ -23303,31 +23739,31 @@
         <v>938</v>
       </c>
       <c r="O235" s="2" t="s">
-        <v>234</v>
+        <v>96</v>
       </c>
       <c r="P235" s="2">
         <v>2026</v>
       </c>
       <c r="Q235" s="2">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="R235" s="2" t="s">
-        <v>608</v>
+        <v>293</v>
       </c>
       <c r="S235" s="2" t="s">
         <v>939</v>
       </c>
       <c r="T235" s="4" t="s">
-        <v>44</v>
+        <v>87</v>
       </c>
       <c r="U235" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="V235" s="4" t="s">
-        <v>109</v>
+        <v>47</v>
       </c>
       <c r="W235" s="4" t="s">
-        <v>77</v>
+        <v>49</v>
       </c>
       <c r="X235" s="4" t="s">
         <v>49</v>
@@ -23336,16 +23772,16 @@
         <v>49</v>
       </c>
       <c r="Z235" s="4" t="s">
-        <v>122</v>
+        <v>50</v>
       </c>
       <c r="AA235" s="4" t="s">
         <v>46</v>
       </c>
       <c r="AB235" s="5">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="236" spans="1:28" ht="28.35" customHeight="1" x14ac:dyDescent="0.3">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="236" spans="1:29" ht="28.35" customHeight="1">
       <c r="A236" s="2" t="s">
         <v>28</v>
       </c>
@@ -23353,19 +23789,19 @@
         <v>29</v>
       </c>
       <c r="C236" s="3" t="s">
-        <v>30</v>
+        <v>162</v>
       </c>
       <c r="D236" s="3" t="s">
-        <v>331</v>
+        <v>808</v>
       </c>
       <c r="E236" s="2" t="s">
-        <v>933</v>
+        <v>940</v>
       </c>
       <c r="F236" s="2" t="s">
-        <v>934</v>
+        <v>941</v>
       </c>
       <c r="G236" s="2" t="s">
-        <v>404</v>
+        <v>811</v>
       </c>
       <c r="H236" s="2" t="s">
         <v>35</v>
@@ -23384,31 +23820,31 @@
         <v>39</v>
       </c>
       <c r="N236" s="3" t="s">
-        <v>940</v>
+        <v>942</v>
       </c>
       <c r="O236" s="2" t="s">
-        <v>96</v>
+        <v>943</v>
       </c>
       <c r="P236" s="2">
         <v>2026</v>
       </c>
       <c r="Q236" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R236" s="2" t="s">
-        <v>293</v>
+        <v>57</v>
       </c>
       <c r="S236" s="2" t="s">
-        <v>941</v>
+        <v>944</v>
       </c>
       <c r="T236" s="4" t="s">
         <v>87</v>
       </c>
       <c r="U236" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="V236" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="W236" s="4" t="s">
         <v>49</v>
@@ -23420,16 +23856,16 @@
         <v>49</v>
       </c>
       <c r="Z236" s="4" t="s">
-        <v>50</v>
+        <v>98</v>
       </c>
       <c r="AA236" s="4" t="s">
         <v>46</v>
       </c>
       <c r="AB236" s="5">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="237" spans="1:28" ht="28.35" customHeight="1" x14ac:dyDescent="0.3">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="237" spans="1:29" ht="28.35" customHeight="1">
       <c r="A237" s="2" t="s">
         <v>28</v>
       </c>
@@ -23440,38 +23876,34 @@
         <v>162</v>
       </c>
       <c r="D237" s="3" t="s">
-        <v>810</v>
+        <v>808</v>
       </c>
       <c r="E237" s="2" t="s">
-        <v>942</v>
+        <v>940</v>
       </c>
       <c r="F237" s="2" t="s">
-        <v>943</v>
+        <v>941</v>
       </c>
       <c r="G237" s="2" t="s">
-        <v>813</v>
-      </c>
-      <c r="H237" s="2" t="s">
-        <v>35</v>
-      </c>
+        <v>811</v>
+      </c>
+      <c r="H237" s="2"/>
       <c r="I237" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="J237" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="K237" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="L237" s="2"/>
+        <v>166</v>
+      </c>
+      <c r="J237" s="3"/>
+      <c r="K237" s="2"/>
+      <c r="L237" s="2" t="s">
+        <v>167</v>
+      </c>
       <c r="M237" s="2" t="s">
         <v>39</v>
       </c>
       <c r="N237" s="3" t="s">
-        <v>944</v>
+        <v>945</v>
       </c>
       <c r="O237" s="2" t="s">
-        <v>945</v>
+        <v>41</v>
       </c>
       <c r="P237" s="2">
         <v>2026</v>
@@ -23480,13 +23912,11 @@
         <v>3</v>
       </c>
       <c r="R237" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="S237" s="2" t="s">
-        <v>946</v>
-      </c>
+        <v>119</v>
+      </c>
+      <c r="S237" s="2"/>
       <c r="T237" s="4" t="s">
-        <v>87</v>
+        <v>814</v>
       </c>
       <c r="U237" s="4" t="s">
         <v>46</v>
@@ -23510,10 +23940,10 @@
         <v>46</v>
       </c>
       <c r="AB237" s="5">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="238" spans="1:28" ht="28.35" customHeight="1" x14ac:dyDescent="0.3">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="238" spans="1:29" ht="28.35" customHeight="1">
       <c r="A238" s="2" t="s">
         <v>28</v>
       </c>
@@ -23524,16 +23954,16 @@
         <v>162</v>
       </c>
       <c r="D238" s="3" t="s">
-        <v>810</v>
+        <v>808</v>
       </c>
       <c r="E238" s="2" t="s">
-        <v>942</v>
+        <v>940</v>
       </c>
       <c r="F238" s="2" t="s">
-        <v>943</v>
+        <v>941</v>
       </c>
       <c r="G238" s="2" t="s">
-        <v>813</v>
+        <v>811</v>
       </c>
       <c r="H238" s="2"/>
       <c r="I238" s="3" t="s">
@@ -23548,23 +23978,23 @@
         <v>39</v>
       </c>
       <c r="N238" s="3" t="s">
-        <v>947</v>
+        <v>946</v>
       </c>
       <c r="O238" s="2" t="s">
-        <v>41</v>
+        <v>543</v>
       </c>
       <c r="P238" s="2">
         <v>2026</v>
       </c>
       <c r="Q238" s="2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="R238" s="2" t="s">
         <v>119</v>
       </c>
       <c r="S238" s="2"/>
       <c r="T238" s="4" t="s">
-        <v>816</v>
+        <v>814</v>
       </c>
       <c r="U238" s="4" t="s">
         <v>46</v>
@@ -23591,7 +24021,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="239" spans="1:28" ht="28.35" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:29" ht="28.35" customHeight="1">
       <c r="A239" s="2" t="s">
         <v>28</v>
       </c>
@@ -23602,16 +24032,16 @@
         <v>162</v>
       </c>
       <c r="D239" s="3" t="s">
-        <v>810</v>
+        <v>808</v>
       </c>
       <c r="E239" s="2" t="s">
-        <v>942</v>
+        <v>940</v>
       </c>
       <c r="F239" s="2" t="s">
-        <v>943</v>
+        <v>941</v>
       </c>
       <c r="G239" s="2" t="s">
-        <v>813</v>
+        <v>811</v>
       </c>
       <c r="H239" s="2"/>
       <c r="I239" s="3" t="s">
@@ -23626,23 +24056,23 @@
         <v>39</v>
       </c>
       <c r="N239" s="3" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
       <c r="O239" s="2" t="s">
-        <v>543</v>
+        <v>264</v>
       </c>
       <c r="P239" s="2">
         <v>2026</v>
       </c>
       <c r="Q239" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R239" s="2" t="s">
         <v>119</v>
       </c>
       <c r="S239" s="2"/>
       <c r="T239" s="4" t="s">
-        <v>816</v>
+        <v>814</v>
       </c>
       <c r="U239" s="4" t="s">
         <v>46</v>
@@ -23669,7 +24099,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="240" spans="1:28" ht="28.35" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:29" ht="28.35" customHeight="1">
       <c r="A240" s="2" t="s">
         <v>28</v>
       </c>
@@ -23677,50 +24107,52 @@
         <v>29</v>
       </c>
       <c r="C240" s="3" t="s">
-        <v>162</v>
+        <v>206</v>
       </c>
       <c r="D240" s="3" t="s">
-        <v>810</v>
+        <v>948</v>
       </c>
       <c r="E240" s="2" t="s">
-        <v>942</v>
+        <v>949</v>
       </c>
       <c r="F240" s="2" t="s">
-        <v>943</v>
+        <v>950</v>
       </c>
       <c r="G240" s="2" t="s">
-        <v>813</v>
+        <v>599</v>
       </c>
       <c r="H240" s="2"/>
       <c r="I240" s="3" t="s">
-        <v>166</v>
-      </c>
-      <c r="J240" s="3"/>
-      <c r="K240" s="2"/>
-      <c r="L240" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="M240" s="2" t="s">
-        <v>39</v>
-      </c>
+        <v>114</v>
+      </c>
+      <c r="J240" s="3" t="s">
+        <v>951</v>
+      </c>
+      <c r="K240" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="L240" s="2"/>
+      <c r="M240" s="6"/>
       <c r="N240" s="3" t="s">
-        <v>949</v>
+        <v>952</v>
       </c>
       <c r="O240" s="2" t="s">
-        <v>264</v>
+        <v>953</v>
       </c>
       <c r="P240" s="2">
+        <f t="shared" ref="P240" si="0">IF(ISBLANK(O240),"",YEAR(O240))</f>
         <v>2026</v>
       </c>
       <c r="Q240" s="2">
-        <v>4</v>
+        <f t="shared" ref="Q240" si="1">IF(ISBLANK(O240),"",MONTH(O240))</f>
+        <v>3</v>
       </c>
       <c r="R240" s="2" t="s">
-        <v>119</v>
+        <v>419</v>
       </c>
       <c r="S240" s="2"/>
       <c r="T240" s="4" t="s">
-        <v>816</v>
+        <v>120</v>
       </c>
       <c r="U240" s="4" t="s">
         <v>46</v>
@@ -23744,10 +24176,13 @@
         <v>46</v>
       </c>
       <c r="AB240" s="5">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="241" spans="1:29" ht="28.35" customHeight="1" x14ac:dyDescent="0.3">
+        <v>100</v>
+      </c>
+      <c r="AC240" s="7" t="s">
+        <v>954</v>
+      </c>
+    </row>
+    <row r="241" spans="1:29" ht="28.35" customHeight="1">
       <c r="A241" s="2" t="s">
         <v>28</v>
       </c>
@@ -23758,13 +24193,13 @@
         <v>206</v>
       </c>
       <c r="D241" s="3" t="s">
-        <v>950</v>
+        <v>643</v>
       </c>
       <c r="E241" s="2" t="s">
-        <v>951</v>
+        <v>644</v>
       </c>
       <c r="F241" s="2" t="s">
-        <v>952</v>
+        <v>645</v>
       </c>
       <c r="G241" s="2" t="s">
         <v>599</v>
@@ -23774,29 +24209,29 @@
         <v>114</v>
       </c>
       <c r="J241" s="3" t="s">
-        <v>953</v>
+        <v>955</v>
       </c>
       <c r="K241" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="L241" s="2"/>
+      <c r="L241" s="2" t="s">
+        <v>167</v>
+      </c>
       <c r="M241" s="6"/>
       <c r="N241" s="3" t="s">
-        <v>954</v>
+        <v>956</v>
       </c>
       <c r="O241" s="2" t="s">
-        <v>955</v>
+        <v>118</v>
       </c>
       <c r="P241" s="2">
-        <f t="shared" ref="P241" si="0">IF(ISBLANK(O241),"",YEAR(O241))</f>
         <v>2026</v>
       </c>
       <c r="Q241" s="2">
-        <f t="shared" ref="Q241" si="1">IF(ISBLANK(O241),"",MONTH(O241))</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R241" s="2" t="s">
-        <v>419</v>
+        <v>119</v>
       </c>
       <c r="S241" s="2"/>
       <c r="T241" s="4" t="s">
@@ -23827,94 +24262,10 @@
         <v>100</v>
       </c>
       <c r="AC241" s="7" t="s">
-        <v>956</v>
-      </c>
-    </row>
-    <row r="242" spans="1:29" ht="28.35" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A242" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="B242" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="C242" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="D242" s="3" t="s">
-        <v>643</v>
-      </c>
-      <c r="E242" s="2" t="s">
-        <v>644</v>
-      </c>
-      <c r="F242" s="2" t="s">
-        <v>645</v>
-      </c>
-      <c r="G242" s="2" t="s">
-        <v>599</v>
-      </c>
-      <c r="H242" s="2"/>
-      <c r="I242" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="J242" s="3" t="s">
-        <v>957</v>
-      </c>
-      <c r="K242" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="L242" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="M242" s="6"/>
-      <c r="N242" s="3" t="s">
-        <v>958</v>
-      </c>
-      <c r="O242" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="P242" s="2">
-        <v>2026</v>
-      </c>
-      <c r="Q242" s="2">
-        <v>4</v>
-      </c>
-      <c r="R242" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="S242" s="2"/>
-      <c r="T242" s="4" t="s">
-        <v>120</v>
-      </c>
-      <c r="U242" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="V242" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="W242" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="X242" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="Y242" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="Z242" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="AA242" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="AB242" s="5">
-        <v>100</v>
-      </c>
-      <c r="AC242" s="7" t="s">
-        <v>956</v>
+        <v>954</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AC242" xr:uid="{D22922A1-C246-4033-BBC7-189F670E2F18}"/>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -23924,31 +24275,31 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EA2C2622-F2C4-402B-90B9-7E376B4FD75D}">
   <dimension ref="A1:E13"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5">
       <c r="A1" t="s">
         <v>16</v>
       </c>
       <c r="B1" t="s">
-        <v>959</v>
+        <v>957</v>
       </c>
       <c r="C1" t="s">
+        <v>966</v>
+      </c>
+      <c r="D1" t="s">
+        <v>967</v>
+      </c>
+      <c r="E1" t="s">
         <v>968</v>
       </c>
-      <c r="D1" t="s">
-        <v>969</v>
-      </c>
-      <c r="E1" t="s">
-        <v>970</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    </row>
+    <row r="2" spans="1:5">
       <c r="A2" t="s">
-        <v>960</v>
+        <v>958</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>966</v>
+        <v>964</v>
       </c>
       <c r="C2" s="10">
         <v>121</v>
@@ -23960,12 +24311,12 @@
         <v>105.5</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:5" ht="17.25" thickBot="1">
       <c r="A3" t="s">
-        <v>960</v>
+        <v>958</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>967</v>
+        <v>965</v>
       </c>
       <c r="C3" s="11">
         <v>7</v>
@@ -23977,12 +24328,12 @@
         <v>3.4</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="17.25" thickTop="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5" ht="17.25" thickTop="1">
       <c r="A4" t="s">
-        <v>961</v>
+        <v>959</v>
       </c>
       <c r="B4" s="13" t="s">
-        <v>966</v>
+        <v>964</v>
       </c>
       <c r="C4" s="18">
         <v>37</v>
@@ -23994,12 +24345,12 @@
         <v>77.099999999999994</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:5" ht="17.25" thickBot="1">
       <c r="A5" t="s">
-        <v>961</v>
+        <v>959</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>967</v>
+        <v>965</v>
       </c>
       <c r="C5" s="19">
         <v>23</v>
@@ -24011,12 +24362,12 @@
         <v>16.399999999999999</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="17.25" thickTop="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5" ht="17.25" thickTop="1">
       <c r="A6" t="s">
-        <v>962</v>
+        <v>960</v>
       </c>
       <c r="B6" s="22" t="s">
-        <v>966</v>
+        <v>964</v>
       </c>
       <c r="C6" s="20">
         <v>76</v>
@@ -24028,12 +24379,12 @@
         <v>29.3</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:5" ht="17.25" thickBot="1">
       <c r="A7" t="s">
-        <v>962</v>
+        <v>960</v>
       </c>
       <c r="B7" s="24" t="s">
-        <v>967</v>
+        <v>965</v>
       </c>
       <c r="C7" s="21">
         <v>11</v>
@@ -24045,12 +24396,12 @@
         <v>4.7</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="17.25" thickTop="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:5" ht="17.25" thickTop="1">
       <c r="A8" t="s">
-        <v>963</v>
+        <v>961</v>
       </c>
       <c r="B8" s="30" t="s">
-        <v>966</v>
+        <v>964</v>
       </c>
       <c r="C8" s="31">
         <v>16</v>
@@ -24062,12 +24413,12 @@
         <v>51.7</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:5" ht="17.25" thickBot="1">
       <c r="A9" t="s">
-        <v>963</v>
+        <v>961</v>
       </c>
       <c r="B9" s="33" t="s">
-        <v>967</v>
+        <v>965</v>
       </c>
       <c r="C9" s="34">
         <v>12</v>
@@ -24079,12 +24430,12 @@
         <v>11.4</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="17.25" thickTop="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:5" ht="17.25" thickTop="1">
       <c r="A10" t="s">
+        <v>962</v>
+      </c>
+      <c r="B10" s="30" t="s">
         <v>964</v>
-      </c>
-      <c r="B10" s="30" t="s">
-        <v>966</v>
       </c>
       <c r="C10" s="31">
         <v>12</v>
@@ -24096,12 +24447,12 @@
         <v>10.5</v>
       </c>
     </row>
-    <row r="11" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:5" ht="17.25" thickBot="1">
       <c r="A11" t="s">
-        <v>964</v>
+        <v>962</v>
       </c>
       <c r="B11" s="33" t="s">
-        <v>967</v>
+        <v>965</v>
       </c>
       <c r="C11" s="34">
         <v>15</v>
@@ -24113,12 +24464,12 @@
         <v>7.9</v>
       </c>
     </row>
-    <row r="12" spans="1:5" ht="17.25" thickTop="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:5" ht="17.25" thickTop="1">
       <c r="A12" t="s">
-        <v>965</v>
+        <v>963</v>
       </c>
       <c r="B12" s="26" t="s">
-        <v>966</v>
+        <v>964</v>
       </c>
       <c r="C12" s="27">
         <v>100</v>
@@ -24130,12 +24481,12 @@
         <v>52.7</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:5" ht="17.25" thickBot="1">
       <c r="A13" t="s">
+        <v>963</v>
+      </c>
+      <c r="B13" s="29" t="s">
         <v>965</v>
-      </c>
-      <c r="B13" s="29" t="s">
-        <v>967</v>
       </c>
       <c r="C13" s="36">
         <v>10</v>
@@ -24151,4 +24502,918 @@
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5D4790DA-C6AC-4E0A-97F5-AFF3509C31BA}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:O5"/>
+  <sheetFormatPr defaultColWidth="7.625" defaultRowHeight="16.5"/>
+  <cols>
+    <col min="1" max="1" width="7" style="42" customWidth="1"/>
+    <col min="2" max="2" width="17.5" style="42" customWidth="1"/>
+    <col min="3" max="14" width="6.125" style="42" customWidth="1"/>
+    <col min="15" max="16384" width="7.625" style="42"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:15" ht="30" customHeight="1">
+      <c r="A1" s="38" t="s">
+        <v>969</v>
+      </c>
+      <c r="B1" s="39" t="s">
+        <v>970</v>
+      </c>
+      <c r="C1" s="39" t="s">
+        <v>971</v>
+      </c>
+      <c r="D1" s="39" t="s">
+        <v>972</v>
+      </c>
+      <c r="E1" s="39" t="s">
+        <v>973</v>
+      </c>
+      <c r="F1" s="39" t="s">
+        <v>974</v>
+      </c>
+      <c r="G1" s="39" t="s">
+        <v>975</v>
+      </c>
+      <c r="H1" s="39" t="s">
+        <v>976</v>
+      </c>
+      <c r="I1" s="39" t="s">
+        <v>977</v>
+      </c>
+      <c r="J1" s="39" t="s">
+        <v>978</v>
+      </c>
+      <c r="K1" s="39" t="s">
+        <v>979</v>
+      </c>
+      <c r="L1" s="39" t="s">
+        <v>980</v>
+      </c>
+      <c r="M1" s="39" t="s">
+        <v>981</v>
+      </c>
+      <c r="N1" s="40" t="s">
+        <v>982</v>
+      </c>
+      <c r="O1" s="41"/>
+    </row>
+    <row r="2" spans="1:15" ht="15" customHeight="1">
+      <c r="A2" s="43" t="s">
+        <v>36</v>
+      </c>
+      <c r="B2" s="44">
+        <v>56</v>
+      </c>
+      <c r="C2" s="44">
+        <v>38</v>
+      </c>
+      <c r="D2" s="44">
+        <v>44</v>
+      </c>
+      <c r="E2" s="44">
+        <v>74</v>
+      </c>
+      <c r="F2" s="44">
+        <v>23</v>
+      </c>
+      <c r="G2" s="44">
+        <v>58</v>
+      </c>
+      <c r="H2" s="44">
+        <v>65</v>
+      </c>
+      <c r="I2" s="44">
+        <v>44</v>
+      </c>
+      <c r="J2" s="44">
+        <v>52</v>
+      </c>
+      <c r="K2" s="44">
+        <v>80</v>
+      </c>
+      <c r="L2" s="44">
+        <v>35</v>
+      </c>
+      <c r="M2" s="44">
+        <v>60</v>
+      </c>
+      <c r="N2" s="45">
+        <f>SUM(B2:M2)</f>
+        <v>629</v>
+      </c>
+      <c r="O2" s="46"/>
+    </row>
+    <row r="3" spans="1:15" ht="17.25" customHeight="1">
+      <c r="A3" s="43" t="s">
+        <v>114</v>
+      </c>
+      <c r="B3" s="44">
+        <v>7</v>
+      </c>
+      <c r="C3" s="44">
+        <v>3</v>
+      </c>
+      <c r="D3" s="44">
+        <v>6</v>
+      </c>
+      <c r="E3" s="44">
+        <v>5</v>
+      </c>
+      <c r="F3" s="44">
+        <v>0</v>
+      </c>
+      <c r="G3" s="44">
+        <v>6</v>
+      </c>
+      <c r="H3" s="44">
+        <v>7</v>
+      </c>
+      <c r="I3" s="44">
+        <v>5</v>
+      </c>
+      <c r="J3" s="44">
+        <v>7</v>
+      </c>
+      <c r="K3" s="44">
+        <v>6</v>
+      </c>
+      <c r="L3" s="44">
+        <v>5</v>
+      </c>
+      <c r="M3" s="44">
+        <v>12</v>
+      </c>
+      <c r="N3" s="45">
+        <f>SUM(B3:M3)</f>
+        <v>69</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" ht="21.75" customHeight="1">
+      <c r="A4" s="43" t="s">
+        <v>983</v>
+      </c>
+      <c r="B4" s="44">
+        <v>2</v>
+      </c>
+      <c r="C4" s="44">
+        <v>2</v>
+      </c>
+      <c r="D4" s="44">
+        <v>2</v>
+      </c>
+      <c r="E4" s="44">
+        <v>2</v>
+      </c>
+      <c r="F4" s="44">
+        <v>3</v>
+      </c>
+      <c r="G4" s="44">
+        <v>2</v>
+      </c>
+      <c r="H4" s="44">
+        <v>5</v>
+      </c>
+      <c r="I4" s="44">
+        <v>4</v>
+      </c>
+      <c r="J4" s="44">
+        <v>7</v>
+      </c>
+      <c r="K4" s="44">
+        <v>5</v>
+      </c>
+      <c r="L4" s="44">
+        <v>3</v>
+      </c>
+      <c r="M4" s="44">
+        <v>1</v>
+      </c>
+      <c r="N4" s="45">
+        <f>SUM(B4:M4)</f>
+        <v>38</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" ht="19.5" customHeight="1">
+      <c r="A5" s="43" t="s">
+        <v>984</v>
+      </c>
+      <c r="B5" s="44">
+        <v>0</v>
+      </c>
+      <c r="C5" s="44">
+        <v>0</v>
+      </c>
+      <c r="D5" s="44">
+        <v>7</v>
+      </c>
+      <c r="E5" s="44">
+        <v>4</v>
+      </c>
+      <c r="F5" s="44">
+        <v>6</v>
+      </c>
+      <c r="G5" s="44">
+        <v>5</v>
+      </c>
+      <c r="H5" s="44">
+        <v>2</v>
+      </c>
+      <c r="I5" s="44">
+        <v>0</v>
+      </c>
+      <c r="J5" s="44">
+        <v>6</v>
+      </c>
+      <c r="K5" s="44">
+        <v>8</v>
+      </c>
+      <c r="L5" s="44">
+        <v>0</v>
+      </c>
+      <c r="M5" s="44">
+        <v>0</v>
+      </c>
+      <c r="N5" s="45">
+        <f>SUM(B5:M5)</f>
+        <v>38</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
+  <pageMargins left="0.75" right="0.40972222222222199" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" fitToHeight="0" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{551D17E9-D0B9-416B-BA57-F5AA470A58BD}">
+  <dimension ref="A1:N5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="16384" width="9" style="47"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:14">
+      <c r="A1" s="38" t="s">
+        <v>969</v>
+      </c>
+      <c r="B1" s="39" t="s">
+        <v>970</v>
+      </c>
+      <c r="C1" s="39" t="s">
+        <v>971</v>
+      </c>
+      <c r="D1" s="39" t="s">
+        <v>972</v>
+      </c>
+      <c r="E1" s="39" t="s">
+        <v>973</v>
+      </c>
+      <c r="F1" s="39" t="s">
+        <v>974</v>
+      </c>
+      <c r="G1" s="39" t="s">
+        <v>975</v>
+      </c>
+      <c r="H1" s="39" t="s">
+        <v>976</v>
+      </c>
+      <c r="I1" s="39" t="s">
+        <v>977</v>
+      </c>
+      <c r="J1" s="39" t="s">
+        <v>978</v>
+      </c>
+      <c r="K1" s="39" t="s">
+        <v>979</v>
+      </c>
+      <c r="L1" s="39" t="s">
+        <v>980</v>
+      </c>
+      <c r="M1" s="39" t="s">
+        <v>981</v>
+      </c>
+      <c r="N1" s="40" t="s">
+        <v>982</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14">
+      <c r="A2" s="43" t="s">
+        <v>36</v>
+      </c>
+      <c r="B2" s="44">
+        <v>62</v>
+      </c>
+      <c r="C2" s="44">
+        <v>42</v>
+      </c>
+      <c r="D2" s="44">
+        <v>52</v>
+      </c>
+      <c r="E2" s="44">
+        <v>64</v>
+      </c>
+      <c r="F2" s="44">
+        <v>26</v>
+      </c>
+      <c r="G2" s="44">
+        <v>56</v>
+      </c>
+      <c r="H2" s="44">
+        <v>59</v>
+      </c>
+      <c r="I2" s="44">
+        <v>39</v>
+      </c>
+      <c r="J2" s="44">
+        <v>70</v>
+      </c>
+      <c r="K2" s="44">
+        <v>78</v>
+      </c>
+      <c r="L2" s="44">
+        <v>48</v>
+      </c>
+      <c r="M2" s="44">
+        <v>66</v>
+      </c>
+      <c r="N2" s="45">
+        <f>SUM(B2:M2)</f>
+        <v>662</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
+      <c r="A3" s="43" t="s">
+        <v>114</v>
+      </c>
+      <c r="B3" s="44">
+        <v>12</v>
+      </c>
+      <c r="C3" s="44">
+        <v>3</v>
+      </c>
+      <c r="D3" s="44">
+        <v>7</v>
+      </c>
+      <c r="E3" s="44">
+        <v>8</v>
+      </c>
+      <c r="F3" s="44">
+        <v>2</v>
+      </c>
+      <c r="G3" s="44">
+        <v>9</v>
+      </c>
+      <c r="H3" s="44">
+        <v>6</v>
+      </c>
+      <c r="I3" s="44">
+        <v>3</v>
+      </c>
+      <c r="J3" s="44">
+        <v>2</v>
+      </c>
+      <c r="K3" s="44">
+        <v>7</v>
+      </c>
+      <c r="L3" s="44">
+        <v>5</v>
+      </c>
+      <c r="M3" s="44">
+        <v>8</v>
+      </c>
+      <c r="N3" s="45">
+        <f>SUM(B3:M3)</f>
+        <v>72</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" ht="25.5">
+      <c r="A4" s="43" t="s">
+        <v>983</v>
+      </c>
+      <c r="B4" s="44">
+        <v>1</v>
+      </c>
+      <c r="C4" s="44">
+        <v>3</v>
+      </c>
+      <c r="D4" s="44">
+        <v>2</v>
+      </c>
+      <c r="E4" s="44">
+        <v>6</v>
+      </c>
+      <c r="F4" s="44">
+        <v>3</v>
+      </c>
+      <c r="G4" s="44">
+        <v>2</v>
+      </c>
+      <c r="H4" s="44">
+        <v>5</v>
+      </c>
+      <c r="I4" s="44">
+        <v>6</v>
+      </c>
+      <c r="J4" s="44">
+        <v>12</v>
+      </c>
+      <c r="K4" s="44">
+        <v>5</v>
+      </c>
+      <c r="L4" s="44">
+        <v>2</v>
+      </c>
+      <c r="M4" s="44">
+        <v>3</v>
+      </c>
+      <c r="N4" s="45">
+        <f>SUM(B4:M4)</f>
+        <v>50</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" ht="25.5">
+      <c r="A5" s="43" t="s">
+        <v>984</v>
+      </c>
+      <c r="B5" s="44">
+        <v>0</v>
+      </c>
+      <c r="C5" s="44">
+        <v>1</v>
+      </c>
+      <c r="D5" s="44">
+        <v>4</v>
+      </c>
+      <c r="E5" s="44">
+        <v>5</v>
+      </c>
+      <c r="F5" s="44">
+        <v>1</v>
+      </c>
+      <c r="G5" s="44">
+        <v>5</v>
+      </c>
+      <c r="H5" s="44">
+        <v>1</v>
+      </c>
+      <c r="I5" s="44">
+        <v>3</v>
+      </c>
+      <c r="J5" s="44">
+        <v>1</v>
+      </c>
+      <c r="K5" s="44">
+        <v>9</v>
+      </c>
+      <c r="L5" s="44">
+        <v>1</v>
+      </c>
+      <c r="M5" s="44">
+        <v>7</v>
+      </c>
+      <c r="N5" s="45">
+        <f>SUM(B5:M5)</f>
+        <v>38</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5AC6C9D8-C651-4C1F-BA0C-1E6F254BBD16}">
+  <dimension ref="A1:N5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="16384" width="9" style="47"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:14">
+      <c r="A1" s="38" t="s">
+        <v>969</v>
+      </c>
+      <c r="B1" s="39" t="s">
+        <v>970</v>
+      </c>
+      <c r="C1" s="39" t="s">
+        <v>971</v>
+      </c>
+      <c r="D1" s="39" t="s">
+        <v>972</v>
+      </c>
+      <c r="E1" s="39" t="s">
+        <v>973</v>
+      </c>
+      <c r="F1" s="39" t="s">
+        <v>974</v>
+      </c>
+      <c r="G1" s="39" t="s">
+        <v>975</v>
+      </c>
+      <c r="H1" s="39" t="s">
+        <v>976</v>
+      </c>
+      <c r="I1" s="39" t="s">
+        <v>977</v>
+      </c>
+      <c r="J1" s="39" t="s">
+        <v>978</v>
+      </c>
+      <c r="K1" s="39" t="s">
+        <v>979</v>
+      </c>
+      <c r="L1" s="39" t="s">
+        <v>980</v>
+      </c>
+      <c r="M1" s="39" t="s">
+        <v>981</v>
+      </c>
+      <c r="N1" s="40" t="s">
+        <v>982</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14">
+      <c r="A2" s="43" t="s">
+        <v>36</v>
+      </c>
+      <c r="B2" s="44">
+        <v>55</v>
+      </c>
+      <c r="C2" s="44">
+        <v>59</v>
+      </c>
+      <c r="D2" s="44">
+        <v>63</v>
+      </c>
+      <c r="E2" s="44">
+        <v>75</v>
+      </c>
+      <c r="F2" s="44">
+        <v>44</v>
+      </c>
+      <c r="G2" s="44">
+        <v>74</v>
+      </c>
+      <c r="H2" s="44">
+        <v>65</v>
+      </c>
+      <c r="I2" s="44">
+        <v>54</v>
+      </c>
+      <c r="J2" s="44">
+        <v>46</v>
+      </c>
+      <c r="K2" s="44">
+        <v>105</v>
+      </c>
+      <c r="L2" s="44">
+        <v>38</v>
+      </c>
+      <c r="M2" s="44">
+        <v>60</v>
+      </c>
+      <c r="N2" s="45">
+        <f>SUM(B2:M2)</f>
+        <v>738</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
+      <c r="A3" s="43" t="s">
+        <v>114</v>
+      </c>
+      <c r="B3" s="44">
+        <v>7</v>
+      </c>
+      <c r="C3" s="44">
+        <v>1</v>
+      </c>
+      <c r="D3" s="44">
+        <v>4</v>
+      </c>
+      <c r="E3" s="44">
+        <v>4</v>
+      </c>
+      <c r="F3" s="44">
+        <v>3</v>
+      </c>
+      <c r="G3" s="44">
+        <v>3</v>
+      </c>
+      <c r="H3" s="44">
+        <v>11</v>
+      </c>
+      <c r="I3" s="44">
+        <v>2</v>
+      </c>
+      <c r="J3" s="44">
+        <v>5</v>
+      </c>
+      <c r="K3" s="44">
+        <v>12</v>
+      </c>
+      <c r="L3" s="44">
+        <v>2</v>
+      </c>
+      <c r="M3" s="44">
+        <v>7</v>
+      </c>
+      <c r="N3" s="45">
+        <f>SUM(B3:M3)</f>
+        <v>61</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" ht="25.5">
+      <c r="A4" s="43" t="s">
+        <v>983</v>
+      </c>
+      <c r="B4" s="44">
+        <v>3</v>
+      </c>
+      <c r="C4" s="44">
+        <v>3</v>
+      </c>
+      <c r="D4" s="44">
+        <v>2</v>
+      </c>
+      <c r="E4" s="44">
+        <v>8</v>
+      </c>
+      <c r="F4" s="44">
+        <v>4</v>
+      </c>
+      <c r="G4" s="44">
+        <v>6</v>
+      </c>
+      <c r="H4" s="44">
+        <v>9</v>
+      </c>
+      <c r="I4" s="44">
+        <v>4</v>
+      </c>
+      <c r="J4" s="44">
+        <v>9</v>
+      </c>
+      <c r="K4" s="44">
+        <v>4</v>
+      </c>
+      <c r="L4" s="44">
+        <v>1</v>
+      </c>
+      <c r="M4" s="44">
+        <v>3</v>
+      </c>
+      <c r="N4" s="45">
+        <f>SUM(B4:M4)</f>
+        <v>56</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" ht="25.5">
+      <c r="A5" s="43" t="s">
+        <v>984</v>
+      </c>
+      <c r="B5" s="44">
+        <v>0</v>
+      </c>
+      <c r="C5" s="44">
+        <v>0</v>
+      </c>
+      <c r="D5" s="44">
+        <v>11</v>
+      </c>
+      <c r="E5" s="44">
+        <v>8</v>
+      </c>
+      <c r="F5" s="44">
+        <v>0</v>
+      </c>
+      <c r="G5" s="44">
+        <v>7</v>
+      </c>
+      <c r="H5" s="44">
+        <v>4</v>
+      </c>
+      <c r="I5" s="44">
+        <v>3</v>
+      </c>
+      <c r="J5" s="44">
+        <v>2</v>
+      </c>
+      <c r="K5" s="44">
+        <v>9</v>
+      </c>
+      <c r="L5" s="44">
+        <v>3</v>
+      </c>
+      <c r="M5" s="44">
+        <v>0</v>
+      </c>
+      <c r="N5" s="45">
+        <f>SUM(B5:M5)</f>
+        <v>47</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{618796F0-6965-4EFF-856F-D6168297D422}">
+  <dimension ref="A1:N5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="16384" width="9" style="47"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:14">
+      <c r="A1" s="38" t="s">
+        <v>969</v>
+      </c>
+      <c r="B1" s="39" t="s">
+        <v>970</v>
+      </c>
+      <c r="C1" s="39" t="s">
+        <v>971</v>
+      </c>
+      <c r="D1" s="39" t="s">
+        <v>972</v>
+      </c>
+      <c r="E1" s="39" t="s">
+        <v>973</v>
+      </c>
+      <c r="F1" s="39" t="s">
+        <v>974</v>
+      </c>
+      <c r="G1" s="39" t="s">
+        <v>975</v>
+      </c>
+      <c r="H1" s="39" t="s">
+        <v>976</v>
+      </c>
+      <c r="I1" s="39" t="s">
+        <v>977</v>
+      </c>
+      <c r="J1" s="39" t="s">
+        <v>978</v>
+      </c>
+      <c r="K1" s="39" t="s">
+        <v>979</v>
+      </c>
+      <c r="L1" s="39" t="s">
+        <v>980</v>
+      </c>
+      <c r="M1" s="39" t="s">
+        <v>981</v>
+      </c>
+      <c r="N1" s="40" t="s">
+        <v>982</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14">
+      <c r="A2" s="43" t="s">
+        <v>36</v>
+      </c>
+      <c r="B2" s="48">
+        <v>48</v>
+      </c>
+      <c r="C2" s="49">
+        <v>42</v>
+      </c>
+      <c r="D2" s="49">
+        <v>38</v>
+      </c>
+      <c r="E2" s="49">
+        <v>47</v>
+      </c>
+      <c r="F2" s="49">
+        <v>17</v>
+      </c>
+      <c r="G2" s="44">
+        <v>16</v>
+      </c>
+      <c r="H2" s="44"/>
+      <c r="I2" s="44"/>
+      <c r="J2" s="44"/>
+      <c r="K2" s="44"/>
+      <c r="L2" s="44"/>
+      <c r="M2" s="44"/>
+      <c r="N2" s="45">
+        <f>SUM(B2:M2)</f>
+        <v>208</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
+      <c r="A3" s="43" t="s">
+        <v>114</v>
+      </c>
+      <c r="B3" s="49">
+        <v>10</v>
+      </c>
+      <c r="C3" s="49">
+        <v>6</v>
+      </c>
+      <c r="D3" s="49">
+        <v>0</v>
+      </c>
+      <c r="E3" s="49">
+        <v>0</v>
+      </c>
+      <c r="F3" s="49">
+        <v>0</v>
+      </c>
+      <c r="G3" s="44">
+        <v>0</v>
+      </c>
+      <c r="H3" s="44"/>
+      <c r="I3" s="44"/>
+      <c r="J3" s="44"/>
+      <c r="K3" s="44"/>
+      <c r="L3" s="44"/>
+      <c r="M3" s="44"/>
+      <c r="N3" s="45">
+        <f>SUM(B3:M3)</f>
+        <v>16</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" ht="25.5">
+      <c r="A4" s="43" t="s">
+        <v>983</v>
+      </c>
+      <c r="B4" s="44">
+        <v>6</v>
+      </c>
+      <c r="C4" s="44">
+        <v>5</v>
+      </c>
+      <c r="D4" s="44">
+        <v>5</v>
+      </c>
+      <c r="E4" s="44">
+        <v>0</v>
+      </c>
+      <c r="F4" s="44">
+        <v>0</v>
+      </c>
+      <c r="G4" s="44">
+        <v>0</v>
+      </c>
+      <c r="H4" s="44"/>
+      <c r="I4" s="44"/>
+      <c r="J4" s="44"/>
+      <c r="K4" s="44"/>
+      <c r="L4" s="44"/>
+      <c r="M4" s="44"/>
+      <c r="N4" s="45">
+        <f>SUM(B4:M4)</f>
+        <v>16</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" ht="25.5">
+      <c r="A5" s="43" t="s">
+        <v>984</v>
+      </c>
+      <c r="B5" s="44">
+        <v>0</v>
+      </c>
+      <c r="C5" s="44">
+        <v>0</v>
+      </c>
+      <c r="D5" s="44">
+        <v>1</v>
+      </c>
+      <c r="E5" s="44">
+        <v>0</v>
+      </c>
+      <c r="F5" s="44">
+        <v>0</v>
+      </c>
+      <c r="G5" s="44">
+        <v>0</v>
+      </c>
+      <c r="H5" s="44"/>
+      <c r="I5" s="44"/>
+      <c r="J5" s="44"/>
+      <c r="K5" s="44"/>
+      <c r="L5" s="44"/>
+      <c r="M5" s="44"/>
+      <c r="N5" s="45">
+        <f>SUM(B5:M5)</f>
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
+</worksheet>
 </file>
--- a/rawdata_2608.xlsx
+++ b/rawdata_2608.xlsx
@@ -8,22 +8,24 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Desktop\연구전략기획팀(26.09.~)\1. 연구 현황 종합 보고(월간)\26.08\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11748D16-BA4F-4E9E-8E64-439CE6C31700}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{649523AE-257B-410C-A08F-0D46DDE63311}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{A72AC5CA-02C8-41D1-B4F6-8C7A45B1F0D9}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{A72AC5CA-02C8-41D1-B4F6-8C7A45B1F0D9}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet1-1" sheetId="7" r:id="rId2"/>
-    <sheet name="Sheet2" sheetId="2" r:id="rId3"/>
-    <sheet name="2023" sheetId="3" r:id="rId4"/>
-    <sheet name="2024" sheetId="4" r:id="rId5"/>
-    <sheet name="2025" sheetId="5" r:id="rId6"/>
-    <sheet name="2026" sheetId="6" r:id="rId7"/>
+    <sheet name="7월승인" sheetId="1" r:id="rId1"/>
+    <sheet name="8월승인" sheetId="7" r:id="rId2"/>
+    <sheet name="8월미승인" sheetId="8" r:id="rId3"/>
+    <sheet name="8월산단" sheetId="2" r:id="rId4"/>
+    <sheet name="2023" sheetId="3" r:id="rId5"/>
+    <sheet name="2024" sheetId="4" r:id="rId6"/>
+    <sheet name="2025" sheetId="5" r:id="rId7"/>
+    <sheet name="2026" sheetId="6" r:id="rId8"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$AC$241</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Sheet1-1'!$A$1:$AB$179</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'7월승인'!$A$1:$AC$241</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'8월미승인'!$A$1:$P$129</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'8월승인'!$A$1:$AB$179</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -47,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10067" uniqueCount="995">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11870" uniqueCount="1373">
   <si>
     <t>연도</t>
   </si>
@@ -3285,6 +3287,1143 @@
   <si>
     <t>102()</t>
   </si>
+  <si>
+    <t>부서2</t>
+  </si>
+  <si>
+    <t>년도</t>
+  </si>
+  <si>
+    <t>연번</t>
+  </si>
+  <si>
+    <t>제목</t>
+  </si>
+  <si>
+    <t>참여</t>
+  </si>
+  <si>
+    <t>기관</t>
+  </si>
+  <si>
+    <t>국내/외</t>
+  </si>
+  <si>
+    <t>20090111</t>
+  </si>
+  <si>
+    <t>이현주</t>
+  </si>
+  <si>
+    <t>인생을 탓하기 전에 심리학을 공부했다</t>
+  </si>
+  <si>
+    <t>어떤책</t>
+  </si>
+  <si>
+    <t>국내</t>
+  </si>
+  <si>
+    <t>전문교양서적</t>
+  </si>
+  <si>
+    <t>디지털콘텐츠디자인학과</t>
+  </si>
+  <si>
+    <t>20110675</t>
+  </si>
+  <si>
+    <t>장희목</t>
+  </si>
+  <si>
+    <t>Routledge Handbook of the Economic History of Colonialism</t>
+  </si>
+  <si>
+    <t>2026-08-20</t>
+  </si>
+  <si>
+    <t>Routledge</t>
+  </si>
+  <si>
+    <t>국외</t>
+  </si>
+  <si>
+    <t>국제전문학술서적(신간)</t>
+  </si>
+  <si>
+    <t>나이 묻는 사회</t>
+  </si>
+  <si>
+    <t>한겨례출판</t>
+  </si>
+  <si>
+    <t>기후·에너지 시대의 과학기술정책 -이론과 현실-</t>
+  </si>
+  <si>
+    <t>윤성사</t>
+  </si>
+  <si>
+    <t>AI정보과학전공</t>
+  </si>
+  <si>
+    <t>20190302</t>
+  </si>
+  <si>
+    <t>윤석용</t>
+  </si>
+  <si>
+    <t>주석민법 [물권 I]</t>
+  </si>
+  <si>
+    <t>2026-08-27</t>
+  </si>
+  <si>
+    <t>한국사법행정학회</t>
+  </si>
+  <si>
+    <t>주석서(기타업적)</t>
+  </si>
+  <si>
+    <t>한 번에 배우는 10가지 도구 통계 실습 : 엑셀·SPSS·R 샤이니·R 스크립트·파이썬·dBSTAT·jabovi·JASP·SAS·stata</t>
+  </si>
+  <si>
+    <t>북앤에듀</t>
+  </si>
+  <si>
+    <t>우리 아이, 오늘 처음 초등학교 갑니다.</t>
+  </si>
+  <si>
+    <t>시원북스</t>
+  </si>
+  <si>
+    <t>The Sage Encyclopedia of Environmental Justice</t>
+  </si>
+  <si>
+    <t>SAGE</t>
+  </si>
+  <si>
+    <t>편서</t>
+  </si>
+  <si>
+    <t>Springer</t>
+  </si>
+  <si>
+    <t>19931004</t>
+  </si>
+  <si>
+    <t>이계한</t>
+  </si>
+  <si>
+    <t>Enhancing cardiovascular risk prediction: the role of wall viscoelasticity in machine learning models</t>
+  </si>
+  <si>
+    <t>Taylor Francis</t>
+  </si>
+  <si>
+    <t>학술지 게재논문</t>
+  </si>
+  <si>
+    <t>Machine Learning–Based Cardiovascular Risk Classification Using Dynamic Time-Series Features From Carotid Duplex Sonography</t>
+  </si>
+  <si>
+    <t>Wiley</t>
+  </si>
+  <si>
+    <t>TransparentandRobustLiCl–OrganohydrogelTriboelectricNanogeneratorWithDeepLearningAssistedSensing</t>
+  </si>
+  <si>
+    <t>One-pot sugar conversion to N-aryl pyrrole-2- carbaldehydes for the synthesis and cytotoxic evaluation of lamellarin R analogues</t>
+  </si>
+  <si>
+    <t>Royal Chemical Society</t>
+  </si>
+  <si>
+    <t>The impact of dance/movement psychotherapy on social skills in individuals with autism spectrum disorder: a meta-analysis</t>
+  </si>
+  <si>
+    <t>Frontiers</t>
+  </si>
+  <si>
+    <t>지방정치와 행정재판</t>
+  </si>
+  <si>
+    <t>행정법이론실무학회</t>
+  </si>
+  <si>
+    <t>20020574</t>
+  </si>
+  <si>
+    <t>이지연</t>
+  </si>
+  <si>
+    <t>6주기 명지대학교 교원양성기관 역량진단 자체 진단 보고서</t>
+  </si>
+  <si>
+    <t>명지대학교</t>
+  </si>
+  <si>
+    <t>외부인증기관제출 자체평가보고서</t>
+  </si>
+  <si>
+    <t>Springer Dordrecht</t>
+  </si>
+  <si>
+    <t>만성 조현병 성인의 심리사회재활을 위한 낮병원 음악치료 프로그램 개발: 당사자와 전문가 요구 조사를 중심으로</t>
+  </si>
+  <si>
+    <t>한국음악치료교육학회</t>
+  </si>
+  <si>
+    <t>주양육자의 정서적 상호작용이 영유아의 친사회적 행동에 미치는 영향: 영유아의 자기조절 매개효과와 주양육자의 비지지적 정서반응의 조절된 매개효과</t>
+  </si>
+  <si>
+    <t>2026-06-21</t>
+  </si>
+  <si>
+    <t>한국인간발달학회</t>
+  </si>
+  <si>
+    <t>Silicon nitride chamber dry cleaning with carbonyl fluoride and nitrous oxide additives</t>
+  </si>
+  <si>
+    <t>The Society of Japanse Physics</t>
+  </si>
+  <si>
+    <t>Enhancement of PECVD Chamber Dry-cleaning with Carbonyl Fluoride by Additive Gases</t>
+  </si>
+  <si>
+    <t>IEEE</t>
+  </si>
+  <si>
+    <t>20050370</t>
+  </si>
+  <si>
+    <t>신혜련</t>
+  </si>
+  <si>
+    <t>모바일 RPG 게임 사용성 평가를 위한 하위 장르 기반 휴리스틱 평가 프레임워크 개발</t>
+  </si>
+  <si>
+    <t>한국디지털콘텐츠학회</t>
+  </si>
+  <si>
+    <t>MDPI</t>
+  </si>
+  <si>
+    <t>생활체육교육학과</t>
+  </si>
+  <si>
+    <t>20060709</t>
+  </si>
+  <si>
+    <t>이선경</t>
+  </si>
+  <si>
+    <t>유아의 수면시간에 따른 기본생활습관의 실태 및 과제</t>
+  </si>
+  <si>
+    <t>2026-07-11</t>
+  </si>
+  <si>
+    <t>한국시민문화학회</t>
+  </si>
+  <si>
+    <t>Springer Nature</t>
+  </si>
+  <si>
+    <t>국제일반학술지</t>
+  </si>
+  <si>
+    <t>Analysis of hourglass shaped channel gate all around field effect transistors</t>
+  </si>
+  <si>
+    <t>물-결합재비에 따른 이론적 최대 수축률 상관관계를 반영한 국내 콘크리트 자기수축 예측 모델 제</t>
+  </si>
+  <si>
+    <t>한국콘크리트학회</t>
+  </si>
+  <si>
+    <t>concrete compressive strength prediction by a hybrid ml-maturity web platform</t>
+  </si>
+  <si>
+    <t>2026-08-29</t>
+  </si>
+  <si>
+    <t>elsevier</t>
+  </si>
+  <si>
+    <t>20080032</t>
+  </si>
+  <si>
+    <t>김종만</t>
+  </si>
+  <si>
+    <t>Comparison of ERAS-Based Same-Day and Non-Same Day Protocols in IDEM Spinal Cord Tumor Surgeries : A Propensity Score-Matched Analysis</t>
+  </si>
+  <si>
+    <t>Korean Neurosurgical Society</t>
+  </si>
+  <si>
+    <t>20080579</t>
+  </si>
+  <si>
+    <t>박경진</t>
+  </si>
+  <si>
+    <t>외부감사법상 과징금 제도의 구조와 실효성에 관한 연구</t>
+  </si>
+  <si>
+    <t>한국회계정보학회</t>
+  </si>
+  <si>
+    <t>Analyst Coverage, Group Affiliation, and Cost Stickiness: Evidence from South Korea</t>
+  </si>
+  <si>
+    <t>Universiti Malaya</t>
+  </si>
+  <si>
+    <t>20080584</t>
+  </si>
+  <si>
+    <t>김건하</t>
+  </si>
+  <si>
+    <t>Are Consumers Really Attracted to</t>
+  </si>
+  <si>
+    <t>한국경영학회</t>
+  </si>
+  <si>
+    <t>20090601</t>
+  </si>
+  <si>
+    <t>기현석</t>
+  </si>
+  <si>
+    <t>선거일 선거운동 금지규정의 위헌성에 관한 검토-헌재 2021. 12. 23. 2018헌바152 결정에 대한 평석을 중심으로-</t>
+  </si>
+  <si>
+    <t>세계헌법학회</t>
+  </si>
+  <si>
+    <t>20090673</t>
+  </si>
+  <si>
+    <t>권나현</t>
+  </si>
+  <si>
+    <t>Economic effectiveness of training personnel for infectious disease response and improving information systems in Republic of Korea: a cost-benefit analysis</t>
+  </si>
+  <si>
+    <t>Korea Disease Control and Prevention Agency</t>
+  </si>
+  <si>
+    <t>공공도서관 이용의 경제적 가치 측정 모형 개발에 관한 연구</t>
+  </si>
+  <si>
+    <t>한국정보관리학회</t>
+  </si>
+  <si>
+    <t>예술심리치료학과</t>
+  </si>
+  <si>
+    <t>20090728</t>
+  </si>
+  <si>
+    <t>최명선</t>
+  </si>
+  <si>
+    <t>인터넷·스마트폰 중독 예술치료와 예술매체 활용 동향</t>
+  </si>
+  <si>
+    <t>한국예술치료학</t>
+  </si>
+  <si>
+    <t>20100035</t>
+  </si>
+  <si>
+    <t>김현명</t>
+  </si>
+  <si>
+    <t>Modeling the Demand for Demand Responsive Transit Service in Shrinking Rural Areas</t>
+  </si>
+  <si>
+    <t>SAGE Publications</t>
+  </si>
+  <si>
+    <t>20100038</t>
+  </si>
+  <si>
+    <t>원승연</t>
+  </si>
+  <si>
+    <t>우리나라 개인 펀드 투자 정체 원인</t>
+  </si>
+  <si>
+    <t>한국금융정보학회</t>
+  </si>
+  <si>
+    <t>20100167</t>
+  </si>
+  <si>
+    <t>이은미</t>
+  </si>
+  <si>
+    <t>일본인 여대생 대화에 나타난 「かもしれない」의 사용양상-친소차에 주목하여-</t>
+  </si>
+  <si>
+    <t>부경대학교 인문사회과학연구소</t>
+  </si>
+  <si>
+    <t>20110360</t>
+  </si>
+  <si>
+    <t>우윤철</t>
+  </si>
+  <si>
+    <t>Highly-Efficient Seawater Hydrogen Production via a Plug-and-Play Solar-Powered Membrane Distillation-Electrolysis System</t>
+  </si>
+  <si>
+    <t>ACS Publications</t>
+  </si>
+  <si>
+    <t>Elsevier</t>
+  </si>
+  <si>
+    <t>계량서지학적 다각화를 통한 생성형 AI 시대의 도서관과 인공지능 연구 동향 분석</t>
+  </si>
+  <si>
+    <t>Association of healthy lifestyle and dietary practices with prediabetes among young Korean adults: sex-specific findings from KNHANES 2020–2024</t>
+  </si>
+  <si>
+    <t>Korean Nutrition Society and Korean Society of Community Nutrition</t>
+  </si>
+  <si>
+    <t>한국 성인의 지속가능한 식생활을 위한 식단전환 지침 개발</t>
+  </si>
+  <si>
+    <t>한국식생활문화학회</t>
+  </si>
+  <si>
+    <t>20130133</t>
+  </si>
+  <si>
+    <t>김준형</t>
+  </si>
+  <si>
+    <t>주택유형과 소득이 공동체의식에 미치는 영향</t>
+  </si>
+  <si>
+    <t>한국주택학회</t>
+  </si>
+  <si>
+    <t>Dual-mode conductive hydrogel sensor combining triboelectric and piezoresistive mechanisms for signal verification and differentiation</t>
+  </si>
+  <si>
+    <t>WILEY-V</t>
+  </si>
+  <si>
+    <t>20150022</t>
+  </si>
+  <si>
+    <t>김민재</t>
+  </si>
+  <si>
+    <t>Research on Advanced Electric Vehicles Using Detachable Energy Pack and New Efficiency Improvement Factors</t>
+  </si>
+  <si>
+    <t>KSAE</t>
+  </si>
+  <si>
+    <t>20150069</t>
+  </si>
+  <si>
+    <t>김영옥</t>
+  </si>
+  <si>
+    <t>생성형 AI 영상의 초현실적 감각설계 - FlowTV채널사례를 중심으로</t>
+  </si>
+  <si>
+    <t>(사)한국만화애니메이션학회</t>
+  </si>
+  <si>
+    <t>An LLC–Buck Bidirectional DC–DC Converter With Secondary-Side Series–Parallel Reconfiguration Achieving Above 97.5% Efficiency Over 100–1000 V Range</t>
+  </si>
+  <si>
+    <t>Uneven returns to digital enablement: innovative work behavior and performance across government tiers in Korea</t>
+  </si>
+  <si>
+    <t>The Korean Association for Public Administration</t>
+  </si>
+  <si>
+    <t>An Integrated Approach of Microscopic Train Operation Simulation and Macroscopic Optimization Model for Railway Capacity Assessment</t>
+  </si>
+  <si>
+    <t>Journal of the Korean Society for Railway</t>
+  </si>
+  <si>
+    <t>공간디자인학과</t>
+  </si>
+  <si>
+    <t>20190105</t>
+  </si>
+  <si>
+    <t>양지윤</t>
+  </si>
+  <si>
+    <t>한국공간디자인학회</t>
+  </si>
+  <si>
+    <t>디지털 플랫폼 서비스 브랜드의 팝업스토어의 스페이스 브랜딩 표현특성 연구</t>
+  </si>
+  <si>
+    <t>공간 스토리텔링 관점에서 본 팝업스토어의 공간 특성 연</t>
+  </si>
+  <si>
+    <t>어반 인테리어 관점에서 본 도시 공공공간의 내부성 특성 분석</t>
+  </si>
+  <si>
+    <t>카테고리 상대 Ordinal AUM 기반 LLM 파이프라인을 이용한 이커머스 상품 데이터의 수치 노이즈 탐지</t>
+  </si>
+  <si>
+    <t>한국컴퓨터정보학회</t>
+  </si>
+  <si>
+    <t>20190376</t>
+  </si>
+  <si>
+    <t>송효종</t>
+  </si>
+  <si>
+    <t>Traffic Volume Estimation Using Deep Learning for High-Resolution Greenhouse Gas Inventory</t>
+  </si>
+  <si>
+    <t>체육학과</t>
+  </si>
+  <si>
+    <t>20190456</t>
+  </si>
+  <si>
+    <t>전병오</t>
+  </si>
+  <si>
+    <t>Machine Learning Classification of Current Functional Impairment in Older Adults with Diabetes: Evidence from CHARLS 2015</t>
+  </si>
+  <si>
+    <t>20200264</t>
+  </si>
+  <si>
+    <t>이유진</t>
+  </si>
+  <si>
+    <t>Gut microbe-generated metabolite trimethylamine N-oxide and risk of abdominal aortic aneurysm: a cohort study</t>
+  </si>
+  <si>
+    <t>2026-07-15</t>
+  </si>
+  <si>
+    <t>Oxford University Press</t>
+  </si>
+  <si>
+    <t>Salt-resistant polypyrrole‑sodium alginate hybrid aerogels supported on poly(ethylene terephthalate) nanofiber scaffolds for efficient solar-driven desalination and wastewater purification</t>
+  </si>
+  <si>
+    <t>2026-06-20</t>
+  </si>
+  <si>
+    <t>ENGINEERING, CHEMICAL</t>
+  </si>
+  <si>
+    <t>AI system to explore R&amp;D in startups through open government data and performance evaluation</t>
+  </si>
+  <si>
+    <t>2026-04-21</t>
+  </si>
+  <si>
+    <t>Taylor &amp; Francis</t>
+  </si>
+  <si>
+    <t>The Algorithm Paradox: why data-driven film production systematically misses blockbusters</t>
+  </si>
+  <si>
+    <t>2026-04-27</t>
+  </si>
+  <si>
+    <t>AI for decision-making: Exploring the linkage from AI capability to firm performance</t>
+  </si>
+  <si>
+    <t>Emerald Publishing</t>
+  </si>
+  <si>
+    <t>PL-FBF: A Partitioned Learned Functional Bloom Filter With Adaptive Memory Allocation for Key–Value Stores</t>
+  </si>
+  <si>
+    <t>20210268</t>
+  </si>
+  <si>
+    <t>박형근</t>
+  </si>
+  <si>
+    <t>Political Business Cycle and Electoral Forecast: Does LocalFinancial Condition Worsen When Electoral Victory Seems(Un)Likely?</t>
+  </si>
+  <si>
+    <t>2026-08-28</t>
+  </si>
+  <si>
+    <t>Entropy-Assisted Thermodynamic Frustration Enables Durable Amorphous Multimetallic TMD Catalysts for High-Current Acidic Hydrogen Evolution</t>
+  </si>
+  <si>
+    <t>ACS publication</t>
+  </si>
+  <si>
+    <t>20210270</t>
+  </si>
+  <si>
+    <t>이효찬</t>
+  </si>
+  <si>
+    <t>Modulation of electrochemical reactivity of supported graphene via charged-impurity-induced cation accumulation</t>
+  </si>
+  <si>
+    <t>20210271</t>
+  </si>
+  <si>
+    <t>이택상</t>
+  </si>
+  <si>
+    <t>A flap mechanics testbed for skin reconstructive surgery: Evaluating the mechanical interaction between flap design and anisotropy</t>
+  </si>
+  <si>
+    <t>Annotation-free phenotype prediction using knowledge-augmented clustering from single-cell RNA sequencing data</t>
+  </si>
+  <si>
+    <t>Oxford University Press (OUP)</t>
+  </si>
+  <si>
+    <t>scFANCL: Dual contrastive learning with false-negative correction at cell level for single-cell RNA-seq clustering</t>
+  </si>
+  <si>
+    <t>2026-07-17</t>
+  </si>
+  <si>
+    <t>Springer Science and Business Media LLC</t>
+  </si>
+  <si>
+    <t>Integrative evidence-knowledge marker selection enhances LLM-based cell type annotation in single-cell RNA-seq analysis</t>
+  </si>
+  <si>
+    <t>Machine Learning Based Plasma Proteomic Analysis Identifies Disease Differentiating Biomarkers in Atopic Dermatitis</t>
+  </si>
+  <si>
+    <t>Journal of Korean Medical Science</t>
+  </si>
+  <si>
+    <t>20220342</t>
+  </si>
+  <si>
+    <t>방정미</t>
+  </si>
+  <si>
+    <t>Regulatory Governance of AI in the Generative AI Era: A Comparative Study of South Korea’s AI Basic Act and the EU AI Act for Sustainable Digital Transformation</t>
+  </si>
+  <si>
+    <t>20230020</t>
+  </si>
+  <si>
+    <t>노유니아</t>
+  </si>
+  <si>
+    <t>국가를 위한 디자인: 1960년대 초 산업미술가협회의 관광포스터 제작 활동</t>
+  </si>
+  <si>
+    <t>미술사학연구회</t>
+  </si>
+  <si>
+    <t>Obstacle avoidance dynamics on Riemannian manifolds</t>
+  </si>
+  <si>
+    <t>Success and Failure of the Stochastic Asymptotic Tracking in Pursuer-Evader Dynamics</t>
+  </si>
+  <si>
+    <t>2026-06-03</t>
+  </si>
+  <si>
+    <t>Selective Convergence of Followers to Multiple Leaders With Repulsion and Cohesion on Riemannian Manifolds</t>
+  </si>
+  <si>
+    <t>2026-06-17</t>
+  </si>
+  <si>
+    <t>Wiely</t>
+  </si>
+  <si>
+    <t>Asymptotic target tracking for multi-agent systems under small communication delays in alignment interactions</t>
+  </si>
+  <si>
+    <t>2026-07-21</t>
+  </si>
+  <si>
+    <t>American Institute of Physics</t>
+  </si>
+  <si>
+    <t>20230033</t>
+  </si>
+  <si>
+    <t>조용민</t>
+  </si>
+  <si>
+    <t>A Caenorhabditis elegans-based whole-organism microfluidic biosensing platform for detecting lung cancer cell-derived volatile organic compounds</t>
+  </si>
+  <si>
+    <t>Oleic Acid-Mediated Double Emulsification Enables Enhanced Aqueous Stability and Localized Photothermal Heating of Liquid Metal Droplets</t>
+  </si>
+  <si>
+    <t>ACS</t>
+  </si>
+  <si>
+    <t>20240276</t>
+  </si>
+  <si>
+    <t>김한솔</t>
+  </si>
+  <si>
+    <t>Natural-sunlight-driven photocatalytic degradation of the organophosphorusnerve agent (GD) and sulfur mustard (HD) by TiO2</t>
+  </si>
+  <si>
+    <t>2026-07-10</t>
+  </si>
+  <si>
+    <t>Modulated Structure-Electronic Coupling at Pt/CeOx-TiO2 Interfaces Boosts Low-Temperature Preferential CO Oxidation</t>
+  </si>
+  <si>
+    <t>2026-08-07</t>
+  </si>
+  <si>
+    <t>Wiley-VCH</t>
+  </si>
+  <si>
+    <t>Operando study of CO2 adsorption on PtGa(111) surface with ambient pressure XPS</t>
+  </si>
+  <si>
+    <t>2026-08-10</t>
+  </si>
+  <si>
+    <t>Physics-based Compact Modeling of Advanced 3D Nanoscale Vertical NAND Flash Memory</t>
+  </si>
+  <si>
+    <t>Capacitor Array-Based Physically Unclonable Function Using Voltage Differentiators</t>
+  </si>
+  <si>
+    <t>IEIE</t>
+  </si>
+  <si>
+    <t>20250076</t>
+  </si>
+  <si>
+    <t>이정호</t>
+  </si>
+  <si>
+    <t>Recent trends in dual-acting hybrid  antibiotics and combination therapies  against Gram-negative pathogens</t>
+  </si>
+  <si>
+    <t>The Microbiological Society of Korea</t>
+  </si>
+  <si>
+    <t>20260017</t>
+  </si>
+  <si>
+    <t>이승엽</t>
+  </si>
+  <si>
+    <t>A machine learning-based framework for basin-specific flood damage warning-support in rapid-response basins</t>
+  </si>
+  <si>
+    <t>20260023</t>
+  </si>
+  <si>
+    <t>장성보</t>
+  </si>
+  <si>
+    <t>On the Effectiveness of Integration Methods for Multimodal Dialogue Response Retrieval</t>
+  </si>
+  <si>
+    <t>Association for Computing Machinery</t>
+  </si>
+  <si>
+    <t>학술대회 Proceeding</t>
+  </si>
+  <si>
+    <t>공연,대국</t>
+  </si>
+  <si>
+    <t>공연(음악)</t>
+  </si>
+  <si>
+    <t>작곡:초연 작품 발표</t>
+  </si>
+  <si>
+    <t>우리가 사랑했던 그 여름 (관현악 모음곡)</t>
+  </si>
+  <si>
+    <t>2026-06-10</t>
+  </si>
+  <si>
+    <t>3.14</t>
+  </si>
+  <si>
+    <t>그해, 여름 (Vocal &amp; Ensemble)</t>
+  </si>
+  <si>
+    <t>오늘의 기쁨 (관현악 모음곡)</t>
+  </si>
+  <si>
+    <t>2026-07-08</t>
+  </si>
+  <si>
+    <t>머무는 시선 (Vocal &amp; Ensemble)</t>
+  </si>
+  <si>
+    <t>2026-07-22</t>
+  </si>
+  <si>
+    <t>빛을 향한 서사 (관현악모음곡)</t>
+  </si>
+  <si>
+    <t>2026-08-05</t>
+  </si>
+  <si>
+    <t>하루를 비추는 색들 (관현악 모음곡)</t>
+  </si>
+  <si>
+    <t>20050672</t>
+  </si>
+  <si>
+    <t>김영진</t>
+  </si>
+  <si>
+    <t>현대 한국 장르영화의 역사</t>
+  </si>
+  <si>
+    <t>씨네 21</t>
+  </si>
+  <si>
+    <t>영화(2012~)</t>
+  </si>
+  <si>
+    <t>영화:국내 영화전문지 평론 및 작품비평</t>
+  </si>
+  <si>
+    <t>한국경제신문 아르떼 [이언정의 시네마테라피]_영화 &lt;마거리트의 정리&gt; 비평</t>
+  </si>
+  <si>
+    <t>한국경제신문 아르떼 [이언정의 시네마테라피]_영화 &lt;비포 선라이즈&gt; 비평</t>
+  </si>
+  <si>
+    <t>2026-07-05</t>
+  </si>
+  <si>
+    <t>한국경제신문 아르떼 [이언정의 시네마테라피]_영화 &lt;작은 아씨들&gt; 비평</t>
+  </si>
+  <si>
+    <t>학술대회발표</t>
+  </si>
+  <si>
+    <t>학술대회 발표논문</t>
+  </si>
+  <si>
+    <t>전문학회발표논문</t>
+  </si>
+  <si>
+    <t>국제 학술회의 주제 강연, 논문발표(기타업적)</t>
+  </si>
+  <si>
+    <t>건설산업 AI 활용의 구조화를 위한 업무기능 –조직유형 기반 개념적 프레임워크</t>
+  </si>
+  <si>
+    <t>2026-08-21</t>
+  </si>
+  <si>
+    <t>한국CDE학회</t>
+  </si>
+  <si>
+    <t>국내 학술회의 주제 강연, 논문발표(기타업적)</t>
+  </si>
+  <si>
+    <t>20060649</t>
+  </si>
+  <si>
+    <t>유철우</t>
+  </si>
+  <si>
+    <t>VQ-VAE 기반 시맨틱 통신에서 채널 손실에 따른 재구성 성능 분석</t>
+  </si>
+  <si>
+    <t>한국통신학회</t>
+  </si>
+  <si>
+    <t>엣지-클라우드 분할형 VLM을 활용한 교통사고 영상의 시맨틱 전송 및 텍스트 리포팅</t>
+  </si>
+  <si>
+    <t>Distortion-Aware LLR for OFDM Systems With PAPR Reduction in LEO satellite Link</t>
+  </si>
+  <si>
+    <t>IEC 61968 기반 CIM 메시지의 온라인 적합성 검증 기법</t>
+  </si>
+  <si>
+    <t>대한전기학회</t>
+  </si>
+  <si>
+    <t>국내 콘크리트 장기거동 모델 개선을 위한 기존 탄성계수 추정식의 시험 데이터 기반 유효성 검토</t>
+  </si>
+  <si>
+    <t>2026-05-07</t>
+  </si>
+  <si>
+    <t>유변학적 시험과 관입 저항 실험을 활용한 콘크리트 작업성의 정량적 평가 가능성 연구</t>
+  </si>
+  <si>
+    <t>기원의 소설, 소설의 기원-윤후명 소설에 나타난 유년 체험</t>
+  </si>
+  <si>
+    <t>윤후명작가추모위원회 외</t>
+  </si>
+  <si>
+    <t>20130033</t>
+  </si>
+  <si>
+    <t>장지연</t>
+  </si>
+  <si>
+    <t>Korean University Students’ Attitudes Toward Two Types of AI-Generated Feedback on English Writing</t>
+  </si>
+  <si>
+    <t>한국영어교육학회</t>
+  </si>
+  <si>
+    <t>20180460</t>
+  </si>
+  <si>
+    <t>임지숙</t>
+  </si>
+  <si>
+    <t>[특별기획 세션Ⅰ: 지방주도 성장]  고립의 시대, 공동체에 거는 기대-각자도생에서 공존으로: 자기자비를 통해 살펴본 한국 노인</t>
+  </si>
+  <si>
+    <t>한국심리학회</t>
+  </si>
+  <si>
+    <t>멀티홉 질의응답을 위한 커버리지 기반 증거 선택과 선택적 증거 보완</t>
+  </si>
+  <si>
+    <t>정보과학회</t>
+  </si>
+  <si>
+    <t>문서 순서 순열에 따른 대형 언어 모델의 신뢰도를 활용한 Reranking 방법</t>
+  </si>
+  <si>
+    <t>20210022</t>
+  </si>
+  <si>
+    <t>안혜성</t>
+  </si>
+  <si>
+    <t>Selective CSI Coverage: The Role of Prior CSI, Geopolitical Adversaries, and CSR History</t>
+  </si>
+  <si>
+    <t>2026-08-02</t>
+  </si>
+  <si>
+    <t>Academy of Management</t>
+  </si>
+  <si>
+    <t>20210025</t>
+  </si>
+  <si>
+    <t>한민탁</t>
+  </si>
+  <si>
+    <t>부정 리뷰를 중심으로 한 가정간편식의 공정 개선 우선순위 도출</t>
+  </si>
+  <si>
+    <t>대한산업공학회</t>
+  </si>
+  <si>
+    <t>기타학술대회발표논문</t>
+  </si>
+  <si>
+    <t>모바일 앱 업데이트 전략 최적화를 위한 사용자 리뷰 기반 리스크 분석 및 전략 제안</t>
+  </si>
+  <si>
+    <t>20250287</t>
+  </si>
+  <si>
+    <t>심재삼</t>
+  </si>
+  <si>
+    <t>유연 전극을 적용한 트라이보일렉트릭 나노발전기 성능분석</t>
+  </si>
+  <si>
+    <t>마이크로나노시스템학회</t>
+  </si>
+  <si>
+    <t>경량 접이식 열음향 스피커를 위한 난연 기능화 MXene-한지</t>
+  </si>
+  <si>
+    <t>2026-03-26</t>
+  </si>
+  <si>
+    <t>연구수탁</t>
+  </si>
+  <si>
+    <t>[RCMS] [4-1차년]저비용 Bio-H2 생산을 위한 PSA-멤브레인 하이브리드 정제 공정 및 핵심 소재 개발</t>
+  </si>
+  <si>
+    <t>한국에너지기술평가원</t>
+  </si>
+  <si>
+    <t>교외연구수탁</t>
+  </si>
+  <si>
+    <t>교외 위탁 연구 수주 건 수</t>
+  </si>
+  <si>
+    <t>전시,설계,디자인</t>
+  </si>
+  <si>
+    <t>디자인학부 비주얼커뮤니케이션디자인전공</t>
+  </si>
+  <si>
+    <t>19961320</t>
+  </si>
+  <si>
+    <t>최재은</t>
+  </si>
+  <si>
+    <t>The Korean Society of Illustration Research 2026 International Invitation Exhibition</t>
+  </si>
+  <si>
+    <t>(사)한국일러스트레이션학회</t>
+  </si>
+  <si>
+    <t>디자인, 공간(2012~)</t>
+  </si>
+  <si>
+    <t>디자인:한국연구재단등재지 주최 디자인 국제전</t>
+  </si>
+  <si>
+    <t>20030042</t>
+  </si>
+  <si>
+    <t>이명주</t>
+  </si>
+  <si>
+    <t>설계,디자인,전시(~2011)</t>
+  </si>
+  <si>
+    <t>서울주택도시개발공사 남부여성발전센터 양육친화도시 설계공모  2등 수상</t>
+  </si>
+  <si>
+    <t>서울주택도시개발공사</t>
+  </si>
+  <si>
+    <t>건축, 공간(2012~)</t>
+  </si>
+  <si>
+    <t>건축:국내 저명 설계 및 디자인 공모전 입상(장려상 이상)</t>
+  </si>
+  <si>
+    <t>20050628</t>
+  </si>
+  <si>
+    <t>서동애</t>
+  </si>
+  <si>
+    <t>한국콘텐츠학회</t>
+  </si>
+  <si>
+    <t>디자인:한국연구재단등재지 주회 디자인 국내전</t>
+  </si>
+  <si>
+    <t>2026 한국기초조형학회 오타와 국제초대작품전</t>
+  </si>
+  <si>
+    <t>한국기초조형학회</t>
+  </si>
+  <si>
+    <t>디자인학부 인더스트리얼디자인전공</t>
+  </si>
+  <si>
+    <t>20070060</t>
+  </si>
+  <si>
+    <t>이성훈</t>
+  </si>
+  <si>
+    <t>칼턴대학교</t>
+  </si>
+  <si>
+    <t>국제공인단체, 국가공공기관, 관련학회 주최의 초대전</t>
+  </si>
+  <si>
+    <t>AI-native and Content Transformation: The Interplay of Creativity, Technology, and Humanity</t>
+  </si>
+  <si>
+    <t>휴먼터치와 AI사이</t>
+  </si>
+  <si>
+    <t>Borders - 경계</t>
+  </si>
+  <si>
+    <t>한국상품문화디자인학회</t>
+  </si>
+  <si>
+    <t>자연과 인간의 공존 ANBD 하치노혜 특별전</t>
+  </si>
+  <si>
+    <t>ANBD</t>
+  </si>
+  <si>
+    <t>2026 한국디자인학회 봄 국제 초대전</t>
+  </si>
+  <si>
+    <t>한국디자인학회</t>
+  </si>
+  <si>
+    <t>한국콘텐츠학회 2026 Poland Rzeszou 국제초대전</t>
+  </si>
+  <si>
+    <t>2026-08-24</t>
+  </si>
+  <si>
+    <t>국제공인단체, 국가공공기관, 관련학회 주최 디자인초대전 및 단체전</t>
+  </si>
+  <si>
+    <t>2026 KSBDA OTTAWA INTERNATIONAL INVITATIONAL EXHIBITION</t>
+  </si>
+  <si>
+    <t>20180434</t>
+  </si>
+  <si>
+    <t>오동우</t>
+  </si>
+  <si>
+    <t>2026 한국기초조형학회 춘계 국제초대작품전</t>
+  </si>
+  <si>
+    <t>서울대학교 조형연구소, BK사업단, 10-10사업단</t>
+  </si>
+  <si>
+    <t>소속(대)</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>구분명칭</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>연구분류</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
@@ -3294,7 +4433,7 @@
     <numFmt numFmtId="176" formatCode="0_ "/>
     <numFmt numFmtId="177" formatCode="#,##0;#,##0;\-"/>
   </numFmts>
-  <fonts count="21">
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color indexed="8"/>
@@ -3451,8 +4590,15 @@
       <family val="3"/>
       <charset val="129"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF000000"/>
+      <name val="굴림체"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -3494,8 +4640,13 @@
         <bgColor rgb="FFF2F2F2"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD6E6F5"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="15">
+  <borders count="16">
     <border>
       <left/>
       <right/>
@@ -3693,6 +4844,19 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="0"/>
+      </left>
+      <right style="thin">
+        <color indexed="0"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="0"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -3703,7 +4867,7 @@
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="50">
+  <cellXfs count="56">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -3848,6 +5012,24 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="177" fontId="18" fillId="4" borderId="13" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="21" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="21" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="8" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -39268,6 +40450,6624 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{93A4203A-85D9-47F5-9539-BD61E8705C84}">
+  <sheetPr>
+    <pageSetUpPr autoPageBreaks="0"/>
+  </sheetPr>
+  <dimension ref="A1:P129"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
+  <cols>
+    <col min="1" max="1" width="16" customWidth="1"/>
+    <col min="2" max="2" width="23.375" customWidth="1"/>
+    <col min="3" max="3" width="30.625" customWidth="1"/>
+    <col min="4" max="4" width="8.375" customWidth="1"/>
+    <col min="5" max="5" width="10.625" customWidth="1"/>
+    <col min="6" max="6" width="5.875" customWidth="1"/>
+    <col min="7" max="7" width="4.375" customWidth="1"/>
+    <col min="8" max="8" width="48.125" customWidth="1"/>
+    <col min="9" max="10" width="10.25" customWidth="1"/>
+    <col min="11" max="11" width="6.25" customWidth="1"/>
+    <col min="12" max="12" width="25.875" customWidth="1"/>
+    <col min="13" max="13" width="7.25" customWidth="1"/>
+    <col min="14" max="14" width="17.5" customWidth="1"/>
+    <col min="15" max="15" width="7.25" customWidth="1"/>
+    <col min="16" max="16" width="35" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:16" ht="16.899999999999999" customHeight="1">
+      <c r="A1" s="55" t="s">
+        <v>1371</v>
+      </c>
+      <c r="B1" s="50" t="s">
+        <v>1370</v>
+      </c>
+      <c r="C1" s="50" t="s">
+        <v>995</v>
+      </c>
+      <c r="D1" s="50" t="s">
+        <v>4</v>
+      </c>
+      <c r="E1" s="50" t="s">
+        <v>5</v>
+      </c>
+      <c r="F1" s="50" t="s">
+        <v>996</v>
+      </c>
+      <c r="G1" s="50" t="s">
+        <v>997</v>
+      </c>
+      <c r="H1" s="50" t="s">
+        <v>998</v>
+      </c>
+      <c r="I1" s="50" t="s">
+        <v>14</v>
+      </c>
+      <c r="J1" s="50" t="s">
+        <v>16</v>
+      </c>
+      <c r="K1" s="50" t="s">
+        <v>999</v>
+      </c>
+      <c r="L1" s="50" t="s">
+        <v>1000</v>
+      </c>
+      <c r="M1" s="50" t="s">
+        <v>1001</v>
+      </c>
+      <c r="N1" s="51">
+        <v>1</v>
+      </c>
+      <c r="O1" s="51">
+        <v>2</v>
+      </c>
+      <c r="P1" s="51" t="s">
+        <v>1372</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" ht="25.5" customHeight="1">
+      <c r="A2" s="52" t="s">
+        <v>36</v>
+      </c>
+      <c r="B2" s="52" t="s">
+        <v>190</v>
+      </c>
+      <c r="C2" s="52" t="s">
+        <v>662</v>
+      </c>
+      <c r="D2" s="52" t="s">
+        <v>1083</v>
+      </c>
+      <c r="E2" s="52" t="s">
+        <v>1084</v>
+      </c>
+      <c r="F2" s="52" t="s">
+        <v>28</v>
+      </c>
+      <c r="G2" s="53">
+        <v>1</v>
+      </c>
+      <c r="H2" s="54" t="s">
+        <v>1085</v>
+      </c>
+      <c r="I2" s="52" t="s">
+        <v>336</v>
+      </c>
+      <c r="J2" s="52">
+        <f>MONTH(I2)</f>
+        <v>3</v>
+      </c>
+      <c r="K2" s="52" t="s">
+        <v>72</v>
+      </c>
+      <c r="L2" s="54" t="s">
+        <v>1086</v>
+      </c>
+      <c r="M2" s="52" t="s">
+        <v>1006</v>
+      </c>
+      <c r="N2" s="52" t="s">
+        <v>1039</v>
+      </c>
+      <c r="O2" s="52" t="s">
+        <v>1014</v>
+      </c>
+      <c r="P2" s="54" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" ht="25.5" customHeight="1">
+      <c r="A3" s="52" t="s">
+        <v>36</v>
+      </c>
+      <c r="B3" s="52" t="s">
+        <v>68</v>
+      </c>
+      <c r="C3" s="52" t="s">
+        <v>620</v>
+      </c>
+      <c r="D3" s="52" t="s">
+        <v>1124</v>
+      </c>
+      <c r="E3" s="52" t="s">
+        <v>1125</v>
+      </c>
+      <c r="F3" s="52" t="s">
+        <v>28</v>
+      </c>
+      <c r="G3" s="53">
+        <v>1</v>
+      </c>
+      <c r="H3" s="54" t="s">
+        <v>1126</v>
+      </c>
+      <c r="I3" s="52" t="s">
+        <v>795</v>
+      </c>
+      <c r="J3" s="52">
+        <f>MONTH(I3)</f>
+        <v>3</v>
+      </c>
+      <c r="K3" s="52" t="s">
+        <v>72</v>
+      </c>
+      <c r="L3" s="54" t="s">
+        <v>1127</v>
+      </c>
+      <c r="M3" s="52" t="s">
+        <v>1014</v>
+      </c>
+      <c r="N3" s="52" t="s">
+        <v>1039</v>
+      </c>
+      <c r="O3" s="52" t="s">
+        <v>1014</v>
+      </c>
+      <c r="P3" s="54" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" ht="25.5" customHeight="1">
+      <c r="A4" s="52" t="s">
+        <v>36</v>
+      </c>
+      <c r="B4" s="52" t="s">
+        <v>68</v>
+      </c>
+      <c r="C4" s="52" t="s">
+        <v>79</v>
+      </c>
+      <c r="D4" s="52" t="s">
+        <v>1140</v>
+      </c>
+      <c r="E4" s="52" t="s">
+        <v>1141</v>
+      </c>
+      <c r="F4" s="52" t="s">
+        <v>28</v>
+      </c>
+      <c r="G4" s="53">
+        <v>1</v>
+      </c>
+      <c r="H4" s="54" t="s">
+        <v>1142</v>
+      </c>
+      <c r="I4" s="52" t="s">
+        <v>795</v>
+      </c>
+      <c r="J4" s="52">
+        <f>MONTH(I4)</f>
+        <v>3</v>
+      </c>
+      <c r="K4" s="52" t="s">
+        <v>38</v>
+      </c>
+      <c r="L4" s="54" t="s">
+        <v>1143</v>
+      </c>
+      <c r="M4" s="52" t="s">
+        <v>1006</v>
+      </c>
+      <c r="N4" s="52" t="s">
+        <v>1039</v>
+      </c>
+      <c r="O4" s="52" t="s">
+        <v>1014</v>
+      </c>
+      <c r="P4" s="54" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" ht="25.5" customHeight="1">
+      <c r="A5" s="52" t="s">
+        <v>36</v>
+      </c>
+      <c r="B5" s="52" t="s">
+        <v>190</v>
+      </c>
+      <c r="C5" s="52" t="s">
+        <v>368</v>
+      </c>
+      <c r="D5" s="52" t="s">
+        <v>887</v>
+      </c>
+      <c r="E5" s="52" t="s">
+        <v>888</v>
+      </c>
+      <c r="F5" s="52" t="s">
+        <v>28</v>
+      </c>
+      <c r="G5" s="53">
+        <v>2</v>
+      </c>
+      <c r="H5" s="54" t="s">
+        <v>1235</v>
+      </c>
+      <c r="I5" s="52" t="s">
+        <v>560</v>
+      </c>
+      <c r="J5" s="52">
+        <f>MONTH(I5)</f>
+        <v>3</v>
+      </c>
+      <c r="K5" s="52" t="s">
+        <v>38</v>
+      </c>
+      <c r="L5" s="54" t="s">
+        <v>1041</v>
+      </c>
+      <c r="M5" s="52" t="s">
+        <v>1014</v>
+      </c>
+      <c r="N5" s="52" t="s">
+        <v>1039</v>
+      </c>
+      <c r="O5" s="52" t="s">
+        <v>1014</v>
+      </c>
+      <c r="P5" s="54" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" ht="25.5" customHeight="1">
+      <c r="A6" s="52" t="s">
+        <v>36</v>
+      </c>
+      <c r="B6" s="52" t="s">
+        <v>68</v>
+      </c>
+      <c r="C6" s="52" t="s">
+        <v>69</v>
+      </c>
+      <c r="D6" s="52" t="s">
+        <v>1112</v>
+      </c>
+      <c r="E6" s="52" t="s">
+        <v>1113</v>
+      </c>
+      <c r="F6" s="52" t="s">
+        <v>28</v>
+      </c>
+      <c r="G6" s="53">
+        <v>1</v>
+      </c>
+      <c r="H6" s="54" t="s">
+        <v>1114</v>
+      </c>
+      <c r="I6" s="52" t="s">
+        <v>42</v>
+      </c>
+      <c r="J6" s="52">
+        <f>MONTH(I6)</f>
+        <v>3</v>
+      </c>
+      <c r="K6" s="52" t="s">
+        <v>38</v>
+      </c>
+      <c r="L6" s="54" t="s">
+        <v>1115</v>
+      </c>
+      <c r="M6" s="52" t="s">
+        <v>1014</v>
+      </c>
+      <c r="N6" s="52" t="s">
+        <v>1039</v>
+      </c>
+      <c r="O6" s="52" t="s">
+        <v>1014</v>
+      </c>
+      <c r="P6" s="54" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" ht="25.5" customHeight="1">
+      <c r="A7" s="52" t="s">
+        <v>36</v>
+      </c>
+      <c r="B7" s="52" t="s">
+        <v>758</v>
+      </c>
+      <c r="C7" s="52" t="s">
+        <v>781</v>
+      </c>
+      <c r="D7" s="52" t="s">
+        <v>782</v>
+      </c>
+      <c r="E7" s="52" t="s">
+        <v>783</v>
+      </c>
+      <c r="F7" s="52" t="s">
+        <v>28</v>
+      </c>
+      <c r="G7" s="53">
+        <v>4</v>
+      </c>
+      <c r="H7" s="54" t="s">
+        <v>1212</v>
+      </c>
+      <c r="I7" s="52" t="s">
+        <v>953</v>
+      </c>
+      <c r="J7" s="52">
+        <f>MONTH(I7)</f>
+        <v>3</v>
+      </c>
+      <c r="K7" s="52" t="s">
+        <v>38</v>
+      </c>
+      <c r="L7" s="54" t="s">
+        <v>1041</v>
+      </c>
+      <c r="M7" s="52" t="s">
+        <v>1014</v>
+      </c>
+      <c r="N7" s="52" t="s">
+        <v>1039</v>
+      </c>
+      <c r="O7" s="52" t="s">
+        <v>1014</v>
+      </c>
+      <c r="P7" s="54" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" ht="25.5" customHeight="1">
+      <c r="A8" s="52" t="s">
+        <v>1274</v>
+      </c>
+      <c r="B8" s="52" t="s">
+        <v>190</v>
+      </c>
+      <c r="C8" s="52" t="s">
+        <v>258</v>
+      </c>
+      <c r="D8" s="52" t="s">
+        <v>1317</v>
+      </c>
+      <c r="E8" s="52" t="s">
+        <v>1318</v>
+      </c>
+      <c r="F8" s="52" t="s">
+        <v>28</v>
+      </c>
+      <c r="G8" s="53">
+        <v>2</v>
+      </c>
+      <c r="H8" s="54" t="s">
+        <v>1321</v>
+      </c>
+      <c r="I8" s="52" t="s">
+        <v>1322</v>
+      </c>
+      <c r="J8" s="52">
+        <f>MONTH(I8)</f>
+        <v>3</v>
+      </c>
+      <c r="K8" s="52" t="s">
+        <v>72</v>
+      </c>
+      <c r="L8" s="54" t="s">
+        <v>1320</v>
+      </c>
+      <c r="M8" s="52" t="s">
+        <v>1006</v>
+      </c>
+      <c r="N8" s="52" t="s">
+        <v>1275</v>
+      </c>
+      <c r="O8" s="52" t="s">
+        <v>1006</v>
+      </c>
+      <c r="P8" s="54" t="s">
+        <v>1281</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" ht="25.5" customHeight="1">
+      <c r="A9" s="52" t="s">
+        <v>1274</v>
+      </c>
+      <c r="B9" s="52" t="s">
+        <v>190</v>
+      </c>
+      <c r="C9" s="52" t="s">
+        <v>258</v>
+      </c>
+      <c r="D9" s="52" t="s">
+        <v>1317</v>
+      </c>
+      <c r="E9" s="52" t="s">
+        <v>1318</v>
+      </c>
+      <c r="F9" s="52" t="s">
+        <v>28</v>
+      </c>
+      <c r="G9" s="53">
+        <v>1</v>
+      </c>
+      <c r="H9" s="54" t="s">
+        <v>1319</v>
+      </c>
+      <c r="I9" s="52" t="s">
+        <v>407</v>
+      </c>
+      <c r="J9" s="52">
+        <f>MONTH(I9)</f>
+        <v>3</v>
+      </c>
+      <c r="K9" s="52" t="s">
+        <v>38</v>
+      </c>
+      <c r="L9" s="54" t="s">
+        <v>1320</v>
+      </c>
+      <c r="M9" s="52" t="s">
+        <v>1006</v>
+      </c>
+      <c r="N9" s="52" t="s">
+        <v>1275</v>
+      </c>
+      <c r="O9" s="52" t="s">
+        <v>1006</v>
+      </c>
+      <c r="P9" s="54" t="s">
+        <v>1281</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" ht="25.5" customHeight="1">
+      <c r="A10" s="52" t="s">
+        <v>36</v>
+      </c>
+      <c r="B10" s="52" t="s">
+        <v>206</v>
+      </c>
+      <c r="C10" s="52" t="s">
+        <v>270</v>
+      </c>
+      <c r="D10" s="52" t="s">
+        <v>452</v>
+      </c>
+      <c r="E10" s="52" t="s">
+        <v>453</v>
+      </c>
+      <c r="F10" s="52" t="s">
+        <v>28</v>
+      </c>
+      <c r="G10" s="53">
+        <v>1</v>
+      </c>
+      <c r="H10" s="54" t="s">
+        <v>1129</v>
+      </c>
+      <c r="I10" s="52" t="s">
+        <v>337</v>
+      </c>
+      <c r="J10" s="52">
+        <f>MONTH(I10)</f>
+        <v>3</v>
+      </c>
+      <c r="K10" s="52" t="s">
+        <v>38</v>
+      </c>
+      <c r="L10" s="54" t="s">
+        <v>1106</v>
+      </c>
+      <c r="M10" s="52" t="s">
+        <v>1006</v>
+      </c>
+      <c r="N10" s="52" t="s">
+        <v>1039</v>
+      </c>
+      <c r="O10" s="52" t="s">
+        <v>1006</v>
+      </c>
+      <c r="P10" s="54" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" ht="25.5" customHeight="1">
+      <c r="A11" s="52" t="s">
+        <v>36</v>
+      </c>
+      <c r="B11" s="52" t="s">
+        <v>352</v>
+      </c>
+      <c r="C11" s="52" t="s">
+        <v>353</v>
+      </c>
+      <c r="D11" s="52" t="s">
+        <v>1087</v>
+      </c>
+      <c r="E11" s="52" t="s">
+        <v>1088</v>
+      </c>
+      <c r="F11" s="52" t="s">
+        <v>28</v>
+      </c>
+      <c r="G11" s="53">
+        <v>1</v>
+      </c>
+      <c r="H11" s="54" t="s">
+        <v>1089</v>
+      </c>
+      <c r="I11" s="52" t="s">
+        <v>219</v>
+      </c>
+      <c r="J11" s="52">
+        <f>MONTH(I11)</f>
+        <v>3</v>
+      </c>
+      <c r="K11" s="52" t="s">
+        <v>38</v>
+      </c>
+      <c r="L11" s="54" t="s">
+        <v>1090</v>
+      </c>
+      <c r="M11" s="52" t="s">
+        <v>1006</v>
+      </c>
+      <c r="N11" s="52" t="s">
+        <v>1039</v>
+      </c>
+      <c r="O11" s="52" t="s">
+        <v>1006</v>
+      </c>
+      <c r="P11" s="54" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" ht="25.5" customHeight="1">
+      <c r="A12" s="52" t="s">
+        <v>36</v>
+      </c>
+      <c r="B12" s="52" t="s">
+        <v>30</v>
+      </c>
+      <c r="C12" s="52" t="s">
+        <v>249</v>
+      </c>
+      <c r="D12" s="52" t="s">
+        <v>1238</v>
+      </c>
+      <c r="E12" s="52" t="s">
+        <v>1239</v>
+      </c>
+      <c r="F12" s="52" t="s">
+        <v>28</v>
+      </c>
+      <c r="G12" s="53">
+        <v>1</v>
+      </c>
+      <c r="H12" s="54" t="s">
+        <v>1240</v>
+      </c>
+      <c r="I12" s="52" t="s">
+        <v>219</v>
+      </c>
+      <c r="J12" s="52">
+        <f>MONTH(I12)</f>
+        <v>3</v>
+      </c>
+      <c r="K12" s="52" t="s">
+        <v>72</v>
+      </c>
+      <c r="L12" s="54" t="s">
+        <v>1241</v>
+      </c>
+      <c r="M12" s="52" t="s">
+        <v>1006</v>
+      </c>
+      <c r="N12" s="52" t="s">
+        <v>1039</v>
+      </c>
+      <c r="O12" s="52" t="s">
+        <v>1006</v>
+      </c>
+      <c r="P12" s="54" t="s">
+        <v>1076</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" ht="25.5" customHeight="1">
+      <c r="A13" s="52" t="s">
+        <v>1328</v>
+      </c>
+      <c r="B13" s="52" t="s">
+        <v>102</v>
+      </c>
+      <c r="C13" s="52" t="s">
+        <v>103</v>
+      </c>
+      <c r="D13" s="52" t="s">
+        <v>1336</v>
+      </c>
+      <c r="E13" s="52" t="s">
+        <v>1337</v>
+      </c>
+      <c r="F13" s="52" t="s">
+        <v>28</v>
+      </c>
+      <c r="G13" s="53">
+        <v>1</v>
+      </c>
+      <c r="H13" s="54" t="s">
+        <v>1339</v>
+      </c>
+      <c r="I13" s="52" t="s">
+        <v>173</v>
+      </c>
+      <c r="J13" s="52">
+        <f>MONTH(I13)</f>
+        <v>4</v>
+      </c>
+      <c r="K13" s="52" t="s">
+        <v>72</v>
+      </c>
+      <c r="L13" s="54" t="s">
+        <v>1340</v>
+      </c>
+      <c r="M13" s="52" t="s">
+        <v>1006</v>
+      </c>
+      <c r="N13" s="52" t="s">
+        <v>1341</v>
+      </c>
+      <c r="O13" s="52" t="s">
+        <v>1006</v>
+      </c>
+      <c r="P13" s="54" t="s">
+        <v>1342</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" ht="25.5" customHeight="1">
+      <c r="A14" s="52" t="s">
+        <v>114</v>
+      </c>
+      <c r="B14" s="52" t="s">
+        <v>352</v>
+      </c>
+      <c r="C14" s="52" t="s">
+        <v>386</v>
+      </c>
+      <c r="D14" s="52" t="s">
+        <v>688</v>
+      </c>
+      <c r="E14" s="52" t="s">
+        <v>689</v>
+      </c>
+      <c r="F14" s="52" t="s">
+        <v>28</v>
+      </c>
+      <c r="G14" s="53">
+        <v>1</v>
+      </c>
+      <c r="H14" s="54" t="s">
+        <v>1027</v>
+      </c>
+      <c r="I14" s="52" t="s">
+        <v>522</v>
+      </c>
+      <c r="J14" s="52">
+        <f>MONTH(I14)</f>
+        <v>4</v>
+      </c>
+      <c r="K14" s="52" t="s">
+        <v>72</v>
+      </c>
+      <c r="L14" s="54" t="s">
+        <v>1028</v>
+      </c>
+      <c r="M14" s="52" t="s">
+        <v>1006</v>
+      </c>
+      <c r="N14" s="52" t="s">
+        <v>114</v>
+      </c>
+      <c r="O14" s="52" t="s">
+        <v>1006</v>
+      </c>
+      <c r="P14" s="54" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" ht="25.5" customHeight="1">
+      <c r="A15" s="52" t="s">
+        <v>36</v>
+      </c>
+      <c r="B15" s="52" t="s">
+        <v>68</v>
+      </c>
+      <c r="C15" s="52" t="s">
+        <v>620</v>
+      </c>
+      <c r="D15" s="52" t="s">
+        <v>1162</v>
+      </c>
+      <c r="E15" s="52" t="s">
+        <v>1163</v>
+      </c>
+      <c r="F15" s="52" t="s">
+        <v>28</v>
+      </c>
+      <c r="G15" s="53">
+        <v>1</v>
+      </c>
+      <c r="H15" s="54" t="s">
+        <v>1164</v>
+      </c>
+      <c r="I15" s="52" t="s">
+        <v>57</v>
+      </c>
+      <c r="J15" s="52">
+        <f>MONTH(I15)</f>
+        <v>4</v>
+      </c>
+      <c r="K15" s="52" t="s">
+        <v>38</v>
+      </c>
+      <c r="L15" s="54" t="s">
+        <v>1115</v>
+      </c>
+      <c r="M15" s="52" t="s">
+        <v>1014</v>
+      </c>
+      <c r="N15" s="52" t="s">
+        <v>1039</v>
+      </c>
+      <c r="O15" s="52" t="s">
+        <v>1014</v>
+      </c>
+      <c r="P15" s="54" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" ht="25.5" customHeight="1">
+      <c r="A16" s="52" t="s">
+        <v>36</v>
+      </c>
+      <c r="B16" s="52" t="s">
+        <v>190</v>
+      </c>
+      <c r="C16" s="52" t="s">
+        <v>258</v>
+      </c>
+      <c r="D16" s="52" t="s">
+        <v>259</v>
+      </c>
+      <c r="E16" s="52" t="s">
+        <v>260</v>
+      </c>
+      <c r="F16" s="52" t="s">
+        <v>28</v>
+      </c>
+      <c r="G16" s="53">
+        <v>2</v>
+      </c>
+      <c r="H16" s="54" t="s">
+        <v>1060</v>
+      </c>
+      <c r="I16" s="52" t="s">
+        <v>247</v>
+      </c>
+      <c r="J16" s="52">
+        <f>MONTH(I16)</f>
+        <v>4</v>
+      </c>
+      <c r="K16" s="52" t="s">
+        <v>38</v>
+      </c>
+      <c r="L16" s="54" t="s">
+        <v>1061</v>
+      </c>
+      <c r="M16" s="52" t="s">
+        <v>1014</v>
+      </c>
+      <c r="N16" s="52" t="s">
+        <v>1039</v>
+      </c>
+      <c r="O16" s="52" t="s">
+        <v>1014</v>
+      </c>
+      <c r="P16" s="54" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16" ht="25.5" customHeight="1">
+      <c r="A17" s="52" t="s">
+        <v>114</v>
+      </c>
+      <c r="B17" s="52" t="s">
+        <v>51</v>
+      </c>
+      <c r="C17" s="52" t="s">
+        <v>576</v>
+      </c>
+      <c r="D17" s="52" t="s">
+        <v>1002</v>
+      </c>
+      <c r="E17" s="52" t="s">
+        <v>1003</v>
+      </c>
+      <c r="F17" s="52" t="s">
+        <v>28</v>
+      </c>
+      <c r="G17" s="53">
+        <v>1</v>
+      </c>
+      <c r="H17" s="54" t="s">
+        <v>1004</v>
+      </c>
+      <c r="I17" s="52" t="s">
+        <v>118</v>
+      </c>
+      <c r="J17" s="52">
+        <f>MONTH(I17)</f>
+        <v>4</v>
+      </c>
+      <c r="K17" s="52" t="s">
+        <v>38</v>
+      </c>
+      <c r="L17" s="54" t="s">
+        <v>1005</v>
+      </c>
+      <c r="M17" s="52" t="s">
+        <v>1006</v>
+      </c>
+      <c r="N17" s="52" t="s">
+        <v>114</v>
+      </c>
+      <c r="O17" s="52" t="s">
+        <v>1006</v>
+      </c>
+      <c r="P17" s="54" t="s">
+        <v>1007</v>
+      </c>
+    </row>
+    <row r="18" spans="1:16" ht="25.5" customHeight="1">
+      <c r="A18" s="52" t="s">
+        <v>36</v>
+      </c>
+      <c r="B18" s="52" t="s">
+        <v>322</v>
+      </c>
+      <c r="C18" s="52" t="s">
+        <v>711</v>
+      </c>
+      <c r="D18" s="52" t="s">
+        <v>712</v>
+      </c>
+      <c r="E18" s="52" t="s">
+        <v>713</v>
+      </c>
+      <c r="F18" s="52" t="s">
+        <v>28</v>
+      </c>
+      <c r="G18" s="53">
+        <v>3</v>
+      </c>
+      <c r="H18" s="54" t="s">
+        <v>1177</v>
+      </c>
+      <c r="I18" s="52" t="s">
+        <v>1178</v>
+      </c>
+      <c r="J18" s="52">
+        <f>MONTH(I18)</f>
+        <v>4</v>
+      </c>
+      <c r="K18" s="52" t="s">
+        <v>38</v>
+      </c>
+      <c r="L18" s="54" t="s">
+        <v>1179</v>
+      </c>
+      <c r="M18" s="52" t="s">
+        <v>1014</v>
+      </c>
+      <c r="N18" s="52" t="s">
+        <v>1039</v>
+      </c>
+      <c r="O18" s="52" t="s">
+        <v>1014</v>
+      </c>
+      <c r="P18" s="54" t="s">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="19" spans="1:16" ht="25.5" customHeight="1">
+      <c r="A19" s="52" t="s">
+        <v>36</v>
+      </c>
+      <c r="B19" s="52" t="s">
+        <v>322</v>
+      </c>
+      <c r="C19" s="52" t="s">
+        <v>711</v>
+      </c>
+      <c r="D19" s="52" t="s">
+        <v>712</v>
+      </c>
+      <c r="E19" s="52" t="s">
+        <v>713</v>
+      </c>
+      <c r="F19" s="52" t="s">
+        <v>28</v>
+      </c>
+      <c r="G19" s="53">
+        <v>4</v>
+      </c>
+      <c r="H19" s="54" t="s">
+        <v>1180</v>
+      </c>
+      <c r="I19" s="52" t="s">
+        <v>1181</v>
+      </c>
+      <c r="J19" s="52">
+        <f>MONTH(I19)</f>
+        <v>4</v>
+      </c>
+      <c r="K19" s="52" t="s">
+        <v>38</v>
+      </c>
+      <c r="L19" s="54" t="s">
+        <v>1179</v>
+      </c>
+      <c r="M19" s="52" t="s">
+        <v>1014</v>
+      </c>
+      <c r="N19" s="52" t="s">
+        <v>1039</v>
+      </c>
+      <c r="O19" s="52" t="s">
+        <v>1014</v>
+      </c>
+      <c r="P19" s="54" t="s">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="20" spans="1:16" ht="25.5" customHeight="1">
+      <c r="A20" s="52" t="s">
+        <v>36</v>
+      </c>
+      <c r="B20" s="52" t="s">
+        <v>102</v>
+      </c>
+      <c r="C20" s="52" t="s">
+        <v>1153</v>
+      </c>
+      <c r="D20" s="52" t="s">
+        <v>1154</v>
+      </c>
+      <c r="E20" s="52" t="s">
+        <v>1155</v>
+      </c>
+      <c r="F20" s="52" t="s">
+        <v>28</v>
+      </c>
+      <c r="G20" s="53">
+        <v>1</v>
+      </c>
+      <c r="H20" s="54" t="s">
+        <v>1157</v>
+      </c>
+      <c r="I20" s="52" t="s">
+        <v>96</v>
+      </c>
+      <c r="J20" s="52">
+        <f>MONTH(I20)</f>
+        <v>4</v>
+      </c>
+      <c r="K20" s="52" t="s">
+        <v>38</v>
+      </c>
+      <c r="L20" s="54" t="s">
+        <v>1156</v>
+      </c>
+      <c r="M20" s="52" t="s">
+        <v>1006</v>
+      </c>
+      <c r="N20" s="52" t="s">
+        <v>1039</v>
+      </c>
+      <c r="O20" s="52" t="s">
+        <v>1006</v>
+      </c>
+      <c r="P20" s="54" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="21" spans="1:16" ht="25.5" customHeight="1">
+      <c r="A21" s="52" t="s">
+        <v>36</v>
+      </c>
+      <c r="B21" s="52" t="s">
+        <v>102</v>
+      </c>
+      <c r="C21" s="52" t="s">
+        <v>1153</v>
+      </c>
+      <c r="D21" s="52" t="s">
+        <v>1154</v>
+      </c>
+      <c r="E21" s="52" t="s">
+        <v>1155</v>
+      </c>
+      <c r="F21" s="52" t="s">
+        <v>28</v>
+      </c>
+      <c r="G21" s="53">
+        <v>2</v>
+      </c>
+      <c r="H21" s="54" t="s">
+        <v>1158</v>
+      </c>
+      <c r="I21" s="52" t="s">
+        <v>96</v>
+      </c>
+      <c r="J21" s="52">
+        <f>MONTH(I21)</f>
+        <v>4</v>
+      </c>
+      <c r="K21" s="52" t="s">
+        <v>38</v>
+      </c>
+      <c r="L21" s="54" t="s">
+        <v>1156</v>
+      </c>
+      <c r="M21" s="52" t="s">
+        <v>1006</v>
+      </c>
+      <c r="N21" s="52" t="s">
+        <v>1039</v>
+      </c>
+      <c r="O21" s="52" t="s">
+        <v>1006</v>
+      </c>
+      <c r="P21" s="54" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="22" spans="1:16" ht="25.5" customHeight="1">
+      <c r="A22" s="52" t="s">
+        <v>1274</v>
+      </c>
+      <c r="B22" s="52" t="s">
+        <v>206</v>
+      </c>
+      <c r="C22" s="52" t="s">
+        <v>464</v>
+      </c>
+      <c r="D22" s="52" t="s">
+        <v>465</v>
+      </c>
+      <c r="E22" s="52" t="s">
+        <v>466</v>
+      </c>
+      <c r="F22" s="52" t="s">
+        <v>28</v>
+      </c>
+      <c r="G22" s="53">
+        <v>1</v>
+      </c>
+      <c r="H22" s="54" t="s">
+        <v>1293</v>
+      </c>
+      <c r="I22" s="52" t="s">
+        <v>150</v>
+      </c>
+      <c r="J22" s="52">
+        <f>MONTH(I22)</f>
+        <v>5</v>
+      </c>
+      <c r="K22" s="52" t="s">
+        <v>38</v>
+      </c>
+      <c r="L22" s="54" t="s">
+        <v>1294</v>
+      </c>
+      <c r="M22" s="52" t="s">
+        <v>1006</v>
+      </c>
+      <c r="N22" s="52" t="s">
+        <v>1275</v>
+      </c>
+      <c r="O22" s="52" t="s">
+        <v>1006</v>
+      </c>
+      <c r="P22" s="54" t="s">
+        <v>1281</v>
+      </c>
+    </row>
+    <row r="23" spans="1:16" ht="25.5" customHeight="1">
+      <c r="A23" s="52" t="s">
+        <v>36</v>
+      </c>
+      <c r="B23" s="52" t="s">
+        <v>68</v>
+      </c>
+      <c r="C23" s="52" t="s">
+        <v>408</v>
+      </c>
+      <c r="D23" s="52" t="s">
+        <v>1035</v>
+      </c>
+      <c r="E23" s="52" t="s">
+        <v>1036</v>
+      </c>
+      <c r="F23" s="52" t="s">
+        <v>28</v>
+      </c>
+      <c r="G23" s="53">
+        <v>2</v>
+      </c>
+      <c r="H23" s="54" t="s">
+        <v>1040</v>
+      </c>
+      <c r="I23" s="52" t="s">
+        <v>569</v>
+      </c>
+      <c r="J23" s="52">
+        <f>MONTH(I23)</f>
+        <v>5</v>
+      </c>
+      <c r="K23" s="52" t="s">
+        <v>38</v>
+      </c>
+      <c r="L23" s="54" t="s">
+        <v>1041</v>
+      </c>
+      <c r="M23" s="52" t="s">
+        <v>1014</v>
+      </c>
+      <c r="N23" s="52" t="s">
+        <v>1039</v>
+      </c>
+      <c r="O23" s="52" t="s">
+        <v>1014</v>
+      </c>
+      <c r="P23" s="54" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="24" spans="1:16" ht="25.5" customHeight="1">
+      <c r="A24" s="52" t="s">
+        <v>1274</v>
+      </c>
+      <c r="B24" s="52" t="s">
+        <v>68</v>
+      </c>
+      <c r="C24" s="52" t="s">
+        <v>146</v>
+      </c>
+      <c r="D24" s="52" t="s">
+        <v>376</v>
+      </c>
+      <c r="E24" s="52" t="s">
+        <v>377</v>
+      </c>
+      <c r="F24" s="52" t="s">
+        <v>28</v>
+      </c>
+      <c r="G24" s="53">
+        <v>1</v>
+      </c>
+      <c r="H24" s="54" t="s">
+        <v>1290</v>
+      </c>
+      <c r="I24" s="52" t="s">
+        <v>1291</v>
+      </c>
+      <c r="J24" s="52">
+        <f>MONTH(I24)</f>
+        <v>5</v>
+      </c>
+      <c r="K24" s="52" t="s">
+        <v>38</v>
+      </c>
+      <c r="L24" s="54" t="s">
+        <v>1079</v>
+      </c>
+      <c r="M24" s="52" t="s">
+        <v>1006</v>
+      </c>
+      <c r="N24" s="52" t="s">
+        <v>1275</v>
+      </c>
+      <c r="O24" s="52" t="s">
+        <v>1006</v>
+      </c>
+      <c r="P24" s="54" t="s">
+        <v>1281</v>
+      </c>
+    </row>
+    <row r="25" spans="1:16" ht="25.5" customHeight="1">
+      <c r="A25" s="52" t="s">
+        <v>1274</v>
+      </c>
+      <c r="B25" s="52" t="s">
+        <v>68</v>
+      </c>
+      <c r="C25" s="52" t="s">
+        <v>146</v>
+      </c>
+      <c r="D25" s="52" t="s">
+        <v>376</v>
+      </c>
+      <c r="E25" s="52" t="s">
+        <v>377</v>
+      </c>
+      <c r="F25" s="52" t="s">
+        <v>28</v>
+      </c>
+      <c r="G25" s="53">
+        <v>2</v>
+      </c>
+      <c r="H25" s="54" t="s">
+        <v>1292</v>
+      </c>
+      <c r="I25" s="52" t="s">
+        <v>1291</v>
+      </c>
+      <c r="J25" s="52">
+        <f>MONTH(I25)</f>
+        <v>5</v>
+      </c>
+      <c r="K25" s="52" t="s">
+        <v>38</v>
+      </c>
+      <c r="L25" s="54" t="s">
+        <v>1079</v>
+      </c>
+      <c r="M25" s="52" t="s">
+        <v>1006</v>
+      </c>
+      <c r="N25" s="52" t="s">
+        <v>1275</v>
+      </c>
+      <c r="O25" s="52" t="s">
+        <v>1006</v>
+      </c>
+      <c r="P25" s="54" t="s">
+        <v>1281</v>
+      </c>
+    </row>
+    <row r="26" spans="1:16" ht="25.5" customHeight="1">
+      <c r="A26" s="52" t="s">
+        <v>1328</v>
+      </c>
+      <c r="B26" s="52" t="s">
+        <v>758</v>
+      </c>
+      <c r="C26" s="52" t="s">
+        <v>1008</v>
+      </c>
+      <c r="D26" s="52" t="s">
+        <v>1009</v>
+      </c>
+      <c r="E26" s="52" t="s">
+        <v>1010</v>
+      </c>
+      <c r="F26" s="52" t="s">
+        <v>28</v>
+      </c>
+      <c r="G26" s="53">
+        <v>4</v>
+      </c>
+      <c r="H26" s="54" t="s">
+        <v>1358</v>
+      </c>
+      <c r="I26" s="52" t="s">
+        <v>151</v>
+      </c>
+      <c r="J26" s="52">
+        <f>MONTH(I26)</f>
+        <v>5</v>
+      </c>
+      <c r="K26" s="52" t="s">
+        <v>38</v>
+      </c>
+      <c r="L26" s="54" t="s">
+        <v>1359</v>
+      </c>
+      <c r="M26" s="52" t="s">
+        <v>1014</v>
+      </c>
+      <c r="N26" s="52" t="s">
+        <v>1338</v>
+      </c>
+      <c r="O26" s="52" t="s">
+        <v>1014</v>
+      </c>
+      <c r="P26" s="54" t="s">
+        <v>1353</v>
+      </c>
+    </row>
+    <row r="27" spans="1:16" ht="25.5" customHeight="1">
+      <c r="A27" s="52" t="s">
+        <v>1328</v>
+      </c>
+      <c r="B27" s="52" t="s">
+        <v>758</v>
+      </c>
+      <c r="C27" s="52" t="s">
+        <v>1008</v>
+      </c>
+      <c r="D27" s="52" t="s">
+        <v>1009</v>
+      </c>
+      <c r="E27" s="52" t="s">
+        <v>1010</v>
+      </c>
+      <c r="F27" s="52" t="s">
+        <v>28</v>
+      </c>
+      <c r="G27" s="53">
+        <v>3</v>
+      </c>
+      <c r="H27" s="54" t="s">
+        <v>1356</v>
+      </c>
+      <c r="I27" s="52" t="s">
+        <v>640</v>
+      </c>
+      <c r="J27" s="52">
+        <f>MONTH(I27)</f>
+        <v>5</v>
+      </c>
+      <c r="K27" s="52" t="s">
+        <v>38</v>
+      </c>
+      <c r="L27" s="54" t="s">
+        <v>1357</v>
+      </c>
+      <c r="M27" s="52" t="s">
+        <v>1006</v>
+      </c>
+      <c r="N27" s="52" t="s">
+        <v>1338</v>
+      </c>
+      <c r="O27" s="52" t="s">
+        <v>1014</v>
+      </c>
+      <c r="P27" s="54" t="s">
+        <v>1353</v>
+      </c>
+    </row>
+    <row r="28" spans="1:16" ht="25.5" customHeight="1">
+      <c r="A28" s="52" t="s">
+        <v>36</v>
+      </c>
+      <c r="B28" s="52" t="s">
+        <v>138</v>
+      </c>
+      <c r="C28" s="52" t="s">
+        <v>571</v>
+      </c>
+      <c r="D28" s="52" t="s">
+        <v>634</v>
+      </c>
+      <c r="E28" s="52" t="s">
+        <v>635</v>
+      </c>
+      <c r="F28" s="52" t="s">
+        <v>28</v>
+      </c>
+      <c r="G28" s="53">
+        <v>1</v>
+      </c>
+      <c r="H28" s="54" t="s">
+        <v>1149</v>
+      </c>
+      <c r="I28" s="52" t="s">
+        <v>383</v>
+      </c>
+      <c r="J28" s="52">
+        <f>MONTH(I28)</f>
+        <v>5</v>
+      </c>
+      <c r="K28" s="52" t="s">
+        <v>38</v>
+      </c>
+      <c r="L28" s="54" t="s">
+        <v>1150</v>
+      </c>
+      <c r="M28" s="52" t="s">
+        <v>1006</v>
+      </c>
+      <c r="N28" s="52" t="s">
+        <v>1039</v>
+      </c>
+      <c r="O28" s="52" t="s">
+        <v>1006</v>
+      </c>
+      <c r="P28" s="54" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="29" spans="1:16" ht="25.5" customHeight="1">
+      <c r="A29" s="52" t="s">
+        <v>114</v>
+      </c>
+      <c r="B29" s="52" t="s">
+        <v>138</v>
+      </c>
+      <c r="C29" s="52" t="s">
+        <v>307</v>
+      </c>
+      <c r="D29" s="52" t="s">
+        <v>480</v>
+      </c>
+      <c r="E29" s="52" t="s">
+        <v>481</v>
+      </c>
+      <c r="F29" s="52" t="s">
+        <v>28</v>
+      </c>
+      <c r="G29" s="53">
+        <v>1</v>
+      </c>
+      <c r="H29" s="54" t="s">
+        <v>1016</v>
+      </c>
+      <c r="I29" s="52" t="s">
+        <v>826</v>
+      </c>
+      <c r="J29" s="52">
+        <f>MONTH(I29)</f>
+        <v>5</v>
+      </c>
+      <c r="K29" s="52" t="s">
+        <v>38</v>
+      </c>
+      <c r="L29" s="54" t="s">
+        <v>1017</v>
+      </c>
+      <c r="M29" s="52" t="s">
+        <v>1006</v>
+      </c>
+      <c r="N29" s="52" t="s">
+        <v>114</v>
+      </c>
+      <c r="O29" s="52" t="s">
+        <v>1006</v>
+      </c>
+      <c r="P29" s="54" t="s">
+        <v>955</v>
+      </c>
+    </row>
+    <row r="30" spans="1:16" ht="25.5" customHeight="1">
+      <c r="A30" s="52" t="s">
+        <v>36</v>
+      </c>
+      <c r="B30" s="52" t="s">
+        <v>138</v>
+      </c>
+      <c r="C30" s="52" t="s">
+        <v>139</v>
+      </c>
+      <c r="D30" s="52" t="s">
+        <v>1205</v>
+      </c>
+      <c r="E30" s="52" t="s">
+        <v>1206</v>
+      </c>
+      <c r="F30" s="52" t="s">
+        <v>28</v>
+      </c>
+      <c r="G30" s="53">
+        <v>1</v>
+      </c>
+      <c r="H30" s="54" t="s">
+        <v>1207</v>
+      </c>
+      <c r="I30" s="52" t="s">
+        <v>183</v>
+      </c>
+      <c r="J30" s="52">
+        <f>MONTH(I30)</f>
+        <v>5</v>
+      </c>
+      <c r="K30" s="52" t="s">
+        <v>38</v>
+      </c>
+      <c r="L30" s="54" t="s">
+        <v>1068</v>
+      </c>
+      <c r="M30" s="52" t="s">
+        <v>1014</v>
+      </c>
+      <c r="N30" s="52" t="s">
+        <v>1039</v>
+      </c>
+      <c r="O30" s="52" t="s">
+        <v>1014</v>
+      </c>
+      <c r="P30" s="54" t="s">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="31" spans="1:16" ht="25.5" customHeight="1">
+      <c r="A31" s="52" t="s">
+        <v>36</v>
+      </c>
+      <c r="B31" s="52" t="s">
+        <v>322</v>
+      </c>
+      <c r="C31" s="52" t="s">
+        <v>711</v>
+      </c>
+      <c r="D31" s="52" t="s">
+        <v>712</v>
+      </c>
+      <c r="E31" s="52" t="s">
+        <v>713</v>
+      </c>
+      <c r="F31" s="52" t="s">
+        <v>28</v>
+      </c>
+      <c r="G31" s="53">
+        <v>5</v>
+      </c>
+      <c r="H31" s="54" t="s">
+        <v>1182</v>
+      </c>
+      <c r="I31" s="52" t="s">
+        <v>580</v>
+      </c>
+      <c r="J31" s="52">
+        <f>MONTH(I31)</f>
+        <v>5</v>
+      </c>
+      <c r="K31" s="52" t="s">
+        <v>72</v>
+      </c>
+      <c r="L31" s="54" t="s">
+        <v>1183</v>
+      </c>
+      <c r="M31" s="52" t="s">
+        <v>1014</v>
+      </c>
+      <c r="N31" s="52" t="s">
+        <v>1039</v>
+      </c>
+      <c r="O31" s="52" t="s">
+        <v>1014</v>
+      </c>
+      <c r="P31" s="54" t="s">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="32" spans="1:16" ht="25.5" customHeight="1">
+      <c r="A32" s="52" t="s">
+        <v>1328</v>
+      </c>
+      <c r="B32" s="52" t="s">
+        <v>162</v>
+      </c>
+      <c r="C32" s="52" t="s">
+        <v>447</v>
+      </c>
+      <c r="D32" s="52" t="s">
+        <v>1343</v>
+      </c>
+      <c r="E32" s="52" t="s">
+        <v>1344</v>
+      </c>
+      <c r="F32" s="52" t="s">
+        <v>28</v>
+      </c>
+      <c r="G32" s="53">
+        <v>1</v>
+      </c>
+      <c r="H32" s="54" t="s">
+        <v>451</v>
+      </c>
+      <c r="I32" s="52" t="s">
+        <v>412</v>
+      </c>
+      <c r="J32" s="52">
+        <f>MONTH(I32)</f>
+        <v>5</v>
+      </c>
+      <c r="K32" s="52" t="s">
+        <v>38</v>
+      </c>
+      <c r="L32" s="54" t="s">
+        <v>1345</v>
+      </c>
+      <c r="M32" s="52" t="s">
+        <v>1006</v>
+      </c>
+      <c r="N32" s="52" t="s">
+        <v>1334</v>
+      </c>
+      <c r="O32" s="52" t="s">
+        <v>1006</v>
+      </c>
+      <c r="P32" s="54" t="s">
+        <v>1346</v>
+      </c>
+    </row>
+    <row r="33" spans="1:16" ht="25.5" customHeight="1">
+      <c r="A33" s="52" t="s">
+        <v>1328</v>
+      </c>
+      <c r="B33" s="52" t="s">
+        <v>758</v>
+      </c>
+      <c r="C33" s="52" t="s">
+        <v>1008</v>
+      </c>
+      <c r="D33" s="52" t="s">
+        <v>1009</v>
+      </c>
+      <c r="E33" s="52" t="s">
+        <v>1010</v>
+      </c>
+      <c r="F33" s="52" t="s">
+        <v>28</v>
+      </c>
+      <c r="G33" s="53">
+        <v>1</v>
+      </c>
+      <c r="H33" s="54" t="s">
+        <v>1354</v>
+      </c>
+      <c r="I33" s="52" t="s">
+        <v>412</v>
+      </c>
+      <c r="J33" s="52">
+        <f>MONTH(I33)</f>
+        <v>5</v>
+      </c>
+      <c r="K33" s="52" t="s">
+        <v>38</v>
+      </c>
+      <c r="L33" s="54" t="s">
+        <v>1345</v>
+      </c>
+      <c r="M33" s="52" t="s">
+        <v>1006</v>
+      </c>
+      <c r="N33" s="52" t="s">
+        <v>1338</v>
+      </c>
+      <c r="O33" s="52" t="s">
+        <v>1006</v>
+      </c>
+      <c r="P33" s="54" t="s">
+        <v>1353</v>
+      </c>
+    </row>
+    <row r="34" spans="1:16" ht="25.5" customHeight="1">
+      <c r="A34" s="52" t="s">
+        <v>114</v>
+      </c>
+      <c r="B34" s="52" t="s">
+        <v>322</v>
+      </c>
+      <c r="C34" s="52" t="s">
+        <v>735</v>
+      </c>
+      <c r="D34" s="52" t="s">
+        <v>834</v>
+      </c>
+      <c r="E34" s="52" t="s">
+        <v>835</v>
+      </c>
+      <c r="F34" s="52" t="s">
+        <v>28</v>
+      </c>
+      <c r="G34" s="53">
+        <v>2</v>
+      </c>
+      <c r="H34" s="54" t="s">
+        <v>1029</v>
+      </c>
+      <c r="I34" s="52" t="s">
+        <v>169</v>
+      </c>
+      <c r="J34" s="52">
+        <f>MONTH(I34)</f>
+        <v>5</v>
+      </c>
+      <c r="K34" s="52" t="s">
+        <v>72</v>
+      </c>
+      <c r="L34" s="54" t="s">
+        <v>1030</v>
+      </c>
+      <c r="M34" s="52" t="s">
+        <v>1006</v>
+      </c>
+      <c r="N34" s="52" t="s">
+        <v>114</v>
+      </c>
+      <c r="O34" s="52" t="s">
+        <v>1006</v>
+      </c>
+      <c r="P34" s="54" t="s">
+        <v>955</v>
+      </c>
+    </row>
+    <row r="35" spans="1:16" ht="25.5" customHeight="1">
+      <c r="A35" s="52" t="s">
+        <v>1328</v>
+      </c>
+      <c r="B35" s="52" t="s">
+        <v>758</v>
+      </c>
+      <c r="C35" s="52" t="s">
+        <v>1008</v>
+      </c>
+      <c r="D35" s="52" t="s">
+        <v>1009</v>
+      </c>
+      <c r="E35" s="52" t="s">
+        <v>1010</v>
+      </c>
+      <c r="F35" s="52" t="s">
+        <v>28</v>
+      </c>
+      <c r="G35" s="53">
+        <v>2</v>
+      </c>
+      <c r="H35" s="54" t="s">
+        <v>1355</v>
+      </c>
+      <c r="I35" s="52" t="s">
+        <v>793</v>
+      </c>
+      <c r="J35" s="52">
+        <f>MONTH(I35)</f>
+        <v>5</v>
+      </c>
+      <c r="K35" s="52" t="s">
+        <v>38</v>
+      </c>
+      <c r="L35" s="54" t="s">
+        <v>1348</v>
+      </c>
+      <c r="M35" s="52" t="s">
+        <v>1006</v>
+      </c>
+      <c r="N35" s="52" t="s">
+        <v>1338</v>
+      </c>
+      <c r="O35" s="52" t="s">
+        <v>1006</v>
+      </c>
+      <c r="P35" s="54" t="s">
+        <v>1353</v>
+      </c>
+    </row>
+    <row r="36" spans="1:16" ht="25.5" customHeight="1">
+      <c r="A36" s="52" t="s">
+        <v>1328</v>
+      </c>
+      <c r="B36" s="52" t="s">
+        <v>162</v>
+      </c>
+      <c r="C36" s="52" t="s">
+        <v>1329</v>
+      </c>
+      <c r="D36" s="52" t="s">
+        <v>1366</v>
+      </c>
+      <c r="E36" s="52" t="s">
+        <v>1367</v>
+      </c>
+      <c r="F36" s="52" t="s">
+        <v>28</v>
+      </c>
+      <c r="G36" s="53">
+        <v>1</v>
+      </c>
+      <c r="H36" s="54" t="s">
+        <v>1368</v>
+      </c>
+      <c r="I36" s="52" t="s">
+        <v>793</v>
+      </c>
+      <c r="J36" s="52">
+        <f>MONTH(I36)</f>
+        <v>5</v>
+      </c>
+      <c r="K36" s="52" t="s">
+        <v>38</v>
+      </c>
+      <c r="L36" s="54" t="s">
+        <v>1369</v>
+      </c>
+      <c r="M36" s="52" t="s">
+        <v>1006</v>
+      </c>
+      <c r="N36" s="52" t="s">
+        <v>1334</v>
+      </c>
+      <c r="O36" s="52" t="s">
+        <v>1006</v>
+      </c>
+      <c r="P36" s="54" t="s">
+        <v>1335</v>
+      </c>
+    </row>
+    <row r="37" spans="1:16" ht="25.5" customHeight="1">
+      <c r="A37" s="52" t="s">
+        <v>36</v>
+      </c>
+      <c r="B37" s="52" t="s">
+        <v>30</v>
+      </c>
+      <c r="C37" s="52" t="s">
+        <v>490</v>
+      </c>
+      <c r="D37" s="52" t="s">
+        <v>491</v>
+      </c>
+      <c r="E37" s="52" t="s">
+        <v>492</v>
+      </c>
+      <c r="F37" s="52" t="s">
+        <v>28</v>
+      </c>
+      <c r="G37" s="53">
+        <v>2</v>
+      </c>
+      <c r="H37" s="54" t="s">
+        <v>1130</v>
+      </c>
+      <c r="I37" s="52" t="s">
+        <v>128</v>
+      </c>
+      <c r="J37" s="52">
+        <f>MONTH(I37)</f>
+        <v>5</v>
+      </c>
+      <c r="K37" s="52" t="s">
+        <v>38</v>
+      </c>
+      <c r="L37" s="54" t="s">
+        <v>1131</v>
+      </c>
+      <c r="M37" s="52" t="s">
+        <v>1006</v>
+      </c>
+      <c r="N37" s="52" t="s">
+        <v>1039</v>
+      </c>
+      <c r="O37" s="52" t="s">
+        <v>1014</v>
+      </c>
+      <c r="P37" s="54" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="38" spans="1:16" ht="25.5" customHeight="1">
+      <c r="A38" s="52" t="s">
+        <v>36</v>
+      </c>
+      <c r="B38" s="52" t="s">
+        <v>51</v>
+      </c>
+      <c r="C38" s="52" t="s">
+        <v>576</v>
+      </c>
+      <c r="D38" s="52" t="s">
+        <v>1144</v>
+      </c>
+      <c r="E38" s="52" t="s">
+        <v>1145</v>
+      </c>
+      <c r="F38" s="52" t="s">
+        <v>28</v>
+      </c>
+      <c r="G38" s="53">
+        <v>1</v>
+      </c>
+      <c r="H38" s="54" t="s">
+        <v>1146</v>
+      </c>
+      <c r="I38" s="52" t="s">
+        <v>128</v>
+      </c>
+      <c r="J38" s="52">
+        <f>MONTH(I38)</f>
+        <v>5</v>
+      </c>
+      <c r="K38" s="52" t="s">
+        <v>38</v>
+      </c>
+      <c r="L38" s="54" t="s">
+        <v>1147</v>
+      </c>
+      <c r="M38" s="52" t="s">
+        <v>1006</v>
+      </c>
+      <c r="N38" s="52" t="s">
+        <v>1039</v>
+      </c>
+      <c r="O38" s="52" t="s">
+        <v>1006</v>
+      </c>
+      <c r="P38" s="54" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="39" spans="1:16" ht="25.5" customHeight="1">
+      <c r="A39" s="52" t="s">
+        <v>36</v>
+      </c>
+      <c r="B39" s="52" t="s">
+        <v>190</v>
+      </c>
+      <c r="C39" s="52" t="s">
+        <v>368</v>
+      </c>
+      <c r="D39" s="52" t="s">
+        <v>369</v>
+      </c>
+      <c r="E39" s="52" t="s">
+        <v>370</v>
+      </c>
+      <c r="F39" s="52" t="s">
+        <v>28</v>
+      </c>
+      <c r="G39" s="53">
+        <v>3</v>
+      </c>
+      <c r="H39" s="54" t="s">
+        <v>1077</v>
+      </c>
+      <c r="I39" s="52" t="s">
+        <v>129</v>
+      </c>
+      <c r="J39" s="52">
+        <f>MONTH(I39)</f>
+        <v>6</v>
+      </c>
+      <c r="K39" s="52" t="s">
+        <v>38</v>
+      </c>
+      <c r="L39" s="54" t="s">
+        <v>1063</v>
+      </c>
+      <c r="M39" s="52" t="s">
+        <v>1014</v>
+      </c>
+      <c r="N39" s="52" t="s">
+        <v>1039</v>
+      </c>
+      <c r="O39" s="52" t="s">
+        <v>1014</v>
+      </c>
+      <c r="P39" s="54" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="40" spans="1:16" ht="25.5" customHeight="1">
+      <c r="A40" s="52" t="s">
+        <v>36</v>
+      </c>
+      <c r="B40" s="52" t="s">
+        <v>68</v>
+      </c>
+      <c r="C40" s="52" t="s">
+        <v>919</v>
+      </c>
+      <c r="D40" s="52" t="s">
+        <v>1191</v>
+      </c>
+      <c r="E40" s="52" t="s">
+        <v>1192</v>
+      </c>
+      <c r="F40" s="52" t="s">
+        <v>28</v>
+      </c>
+      <c r="G40" s="53">
+        <v>1</v>
+      </c>
+      <c r="H40" s="54" t="s">
+        <v>1193</v>
+      </c>
+      <c r="I40" s="52" t="s">
+        <v>129</v>
+      </c>
+      <c r="J40" s="52">
+        <f>MONTH(I40)</f>
+        <v>6</v>
+      </c>
+      <c r="K40" s="52" t="s">
+        <v>38</v>
+      </c>
+      <c r="L40" s="54" t="s">
+        <v>1128</v>
+      </c>
+      <c r="M40" s="52" t="s">
+        <v>1014</v>
+      </c>
+      <c r="N40" s="52" t="s">
+        <v>1039</v>
+      </c>
+      <c r="O40" s="52" t="s">
+        <v>1014</v>
+      </c>
+      <c r="P40" s="54" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="41" spans="1:16" ht="25.5" customHeight="1">
+      <c r="A41" s="52" t="s">
+        <v>36</v>
+      </c>
+      <c r="B41" s="52" t="s">
+        <v>758</v>
+      </c>
+      <c r="C41" s="52" t="s">
+        <v>781</v>
+      </c>
+      <c r="D41" s="52" t="s">
+        <v>782</v>
+      </c>
+      <c r="E41" s="52" t="s">
+        <v>783</v>
+      </c>
+      <c r="F41" s="52" t="s">
+        <v>28</v>
+      </c>
+      <c r="G41" s="53">
+        <v>9</v>
+      </c>
+      <c r="H41" s="54" t="s">
+        <v>1213</v>
+      </c>
+      <c r="I41" s="52" t="s">
+        <v>1214</v>
+      </c>
+      <c r="J41" s="52">
+        <f>MONTH(I41)</f>
+        <v>6</v>
+      </c>
+      <c r="K41" s="52" t="s">
+        <v>38</v>
+      </c>
+      <c r="L41" s="54" t="s">
+        <v>1034</v>
+      </c>
+      <c r="M41" s="52" t="s">
+        <v>1014</v>
+      </c>
+      <c r="N41" s="52" t="s">
+        <v>1039</v>
+      </c>
+      <c r="O41" s="52" t="s">
+        <v>1014</v>
+      </c>
+      <c r="P41" s="54" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="42" spans="1:16" ht="25.5" customHeight="1">
+      <c r="A42" s="52" t="s">
+        <v>1250</v>
+      </c>
+      <c r="B42" s="52" t="s">
+        <v>162</v>
+      </c>
+      <c r="C42" s="52" t="s">
+        <v>808</v>
+      </c>
+      <c r="D42" s="52" t="s">
+        <v>940</v>
+      </c>
+      <c r="E42" s="52" t="s">
+        <v>941</v>
+      </c>
+      <c r="F42" s="52" t="s">
+        <v>28</v>
+      </c>
+      <c r="G42" s="53">
+        <v>6</v>
+      </c>
+      <c r="H42" s="54" t="s">
+        <v>1270</v>
+      </c>
+      <c r="I42" s="52" t="s">
+        <v>1214</v>
+      </c>
+      <c r="J42" s="52">
+        <f>MONTH(I42)</f>
+        <v>6</v>
+      </c>
+      <c r="K42" s="52" t="s">
+        <v>38</v>
+      </c>
+      <c r="L42" s="54"/>
+      <c r="M42" s="52" t="s">
+        <v>1006</v>
+      </c>
+      <c r="N42" s="52" t="s">
+        <v>1268</v>
+      </c>
+      <c r="O42" s="52" t="s">
+        <v>1006</v>
+      </c>
+      <c r="P42" s="54" t="s">
+        <v>1269</v>
+      </c>
+    </row>
+    <row r="43" spans="1:16" ht="25.5" customHeight="1">
+      <c r="A43" s="52" t="s">
+        <v>36</v>
+      </c>
+      <c r="B43" s="52" t="s">
+        <v>190</v>
+      </c>
+      <c r="C43" s="52" t="s">
+        <v>368</v>
+      </c>
+      <c r="D43" s="52" t="s">
+        <v>720</v>
+      </c>
+      <c r="E43" s="52" t="s">
+        <v>721</v>
+      </c>
+      <c r="F43" s="52" t="s">
+        <v>28</v>
+      </c>
+      <c r="G43" s="53">
+        <v>1</v>
+      </c>
+      <c r="H43" s="54" t="s">
+        <v>1184</v>
+      </c>
+      <c r="I43" s="52" t="s">
+        <v>438</v>
+      </c>
+      <c r="J43" s="52">
+        <f>MONTH(I43)</f>
+        <v>6</v>
+      </c>
+      <c r="K43" s="52" t="s">
+        <v>38</v>
+      </c>
+      <c r="L43" s="54" t="s">
+        <v>1063</v>
+      </c>
+      <c r="M43" s="52" t="s">
+        <v>1014</v>
+      </c>
+      <c r="N43" s="52" t="s">
+        <v>1039</v>
+      </c>
+      <c r="O43" s="52" t="s">
+        <v>1014</v>
+      </c>
+      <c r="P43" s="54" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="44" spans="1:16" ht="25.5" customHeight="1">
+      <c r="A44" s="52" t="s">
+        <v>1274</v>
+      </c>
+      <c r="B44" s="52" t="s">
+        <v>190</v>
+      </c>
+      <c r="C44" s="52" t="s">
+        <v>662</v>
+      </c>
+      <c r="D44" s="52" t="s">
+        <v>1311</v>
+      </c>
+      <c r="E44" s="52" t="s">
+        <v>1312</v>
+      </c>
+      <c r="F44" s="52" t="s">
+        <v>28</v>
+      </c>
+      <c r="G44" s="53">
+        <v>1</v>
+      </c>
+      <c r="H44" s="54" t="s">
+        <v>1313</v>
+      </c>
+      <c r="I44" s="52" t="s">
+        <v>438</v>
+      </c>
+      <c r="J44" s="52">
+        <f>MONTH(I44)</f>
+        <v>6</v>
+      </c>
+      <c r="K44" s="52" t="s">
+        <v>38</v>
+      </c>
+      <c r="L44" s="54" t="s">
+        <v>1314</v>
+      </c>
+      <c r="M44" s="52" t="s">
+        <v>1006</v>
+      </c>
+      <c r="N44" s="52" t="s">
+        <v>1275</v>
+      </c>
+      <c r="O44" s="52" t="s">
+        <v>1006</v>
+      </c>
+      <c r="P44" s="54" t="s">
+        <v>1315</v>
+      </c>
+    </row>
+    <row r="45" spans="1:16" ht="25.5" customHeight="1">
+      <c r="A45" s="52" t="s">
+        <v>1274</v>
+      </c>
+      <c r="B45" s="52" t="s">
+        <v>190</v>
+      </c>
+      <c r="C45" s="52" t="s">
+        <v>662</v>
+      </c>
+      <c r="D45" s="52" t="s">
+        <v>1311</v>
+      </c>
+      <c r="E45" s="52" t="s">
+        <v>1312</v>
+      </c>
+      <c r="F45" s="52" t="s">
+        <v>28</v>
+      </c>
+      <c r="G45" s="53">
+        <v>2</v>
+      </c>
+      <c r="H45" s="54" t="s">
+        <v>1316</v>
+      </c>
+      <c r="I45" s="52" t="s">
+        <v>438</v>
+      </c>
+      <c r="J45" s="52">
+        <f>MONTH(I45)</f>
+        <v>6</v>
+      </c>
+      <c r="K45" s="52" t="s">
+        <v>38</v>
+      </c>
+      <c r="L45" s="54" t="s">
+        <v>1314</v>
+      </c>
+      <c r="M45" s="52" t="s">
+        <v>1006</v>
+      </c>
+      <c r="N45" s="52" t="s">
+        <v>1275</v>
+      </c>
+      <c r="O45" s="52" t="s">
+        <v>1006</v>
+      </c>
+      <c r="P45" s="54" t="s">
+        <v>1315</v>
+      </c>
+    </row>
+    <row r="46" spans="1:16" ht="25.5" customHeight="1">
+      <c r="A46" s="52" t="s">
+        <v>1328</v>
+      </c>
+      <c r="B46" s="52" t="s">
+        <v>758</v>
+      </c>
+      <c r="C46" s="52" t="s">
+        <v>1008</v>
+      </c>
+      <c r="D46" s="52" t="s">
+        <v>1009</v>
+      </c>
+      <c r="E46" s="52" t="s">
+        <v>1010</v>
+      </c>
+      <c r="F46" s="52" t="s">
+        <v>28</v>
+      </c>
+      <c r="G46" s="53">
+        <v>5</v>
+      </c>
+      <c r="H46" s="54" t="s">
+        <v>1360</v>
+      </c>
+      <c r="I46" s="52" t="s">
+        <v>438</v>
+      </c>
+      <c r="J46" s="52">
+        <f>MONTH(I46)</f>
+        <v>6</v>
+      </c>
+      <c r="K46" s="52" t="s">
+        <v>38</v>
+      </c>
+      <c r="L46" s="54" t="s">
+        <v>1361</v>
+      </c>
+      <c r="M46" s="52" t="s">
+        <v>1006</v>
+      </c>
+      <c r="N46" s="52" t="s">
+        <v>1338</v>
+      </c>
+      <c r="O46" s="52" t="s">
+        <v>1014</v>
+      </c>
+      <c r="P46" s="54" t="s">
+        <v>1353</v>
+      </c>
+    </row>
+    <row r="47" spans="1:16" ht="25.5" customHeight="1">
+      <c r="A47" s="52" t="s">
+        <v>1250</v>
+      </c>
+      <c r="B47" s="52" t="s">
+        <v>162</v>
+      </c>
+      <c r="C47" s="52" t="s">
+        <v>163</v>
+      </c>
+      <c r="D47" s="52" t="s">
+        <v>164</v>
+      </c>
+      <c r="E47" s="52" t="s">
+        <v>165</v>
+      </c>
+      <c r="F47" s="52" t="s">
+        <v>28</v>
+      </c>
+      <c r="G47" s="53">
+        <v>8</v>
+      </c>
+      <c r="H47" s="54" t="s">
+        <v>1253</v>
+      </c>
+      <c r="I47" s="52" t="s">
+        <v>1254</v>
+      </c>
+      <c r="J47" s="52">
+        <f>MONTH(I47)</f>
+        <v>6</v>
+      </c>
+      <c r="K47" s="52" t="s">
+        <v>38</v>
+      </c>
+      <c r="L47" s="54" t="s">
+        <v>1255</v>
+      </c>
+      <c r="M47" s="52" t="s">
+        <v>1006</v>
+      </c>
+      <c r="N47" s="52" t="s">
+        <v>1251</v>
+      </c>
+      <c r="O47" s="52" t="s">
+        <v>1006</v>
+      </c>
+      <c r="P47" s="54" t="s">
+        <v>1252</v>
+      </c>
+    </row>
+    <row r="48" spans="1:16" ht="25.5" customHeight="1">
+      <c r="A48" s="52" t="s">
+        <v>36</v>
+      </c>
+      <c r="B48" s="52" t="s">
+        <v>758</v>
+      </c>
+      <c r="C48" s="52" t="s">
+        <v>759</v>
+      </c>
+      <c r="D48" s="52" t="s">
+        <v>1245</v>
+      </c>
+      <c r="E48" s="52" t="s">
+        <v>1246</v>
+      </c>
+      <c r="F48" s="52" t="s">
+        <v>28</v>
+      </c>
+      <c r="G48" s="53">
+        <v>1</v>
+      </c>
+      <c r="H48" s="54" t="s">
+        <v>1247</v>
+      </c>
+      <c r="I48" s="52" t="s">
+        <v>462</v>
+      </c>
+      <c r="J48" s="52">
+        <f>MONTH(I48)</f>
+        <v>6</v>
+      </c>
+      <c r="K48" s="52" t="s">
+        <v>38</v>
+      </c>
+      <c r="L48" s="54" t="s">
+        <v>1248</v>
+      </c>
+      <c r="M48" s="52" t="s">
+        <v>1014</v>
+      </c>
+      <c r="N48" s="52" t="s">
+        <v>1039</v>
+      </c>
+      <c r="O48" s="52" t="s">
+        <v>1014</v>
+      </c>
+      <c r="P48" s="54" t="s">
+        <v>1249</v>
+      </c>
+    </row>
+    <row r="49" spans="1:16" ht="25.5" customHeight="1">
+      <c r="A49" s="52" t="s">
+        <v>36</v>
+      </c>
+      <c r="B49" s="52" t="s">
+        <v>51</v>
+      </c>
+      <c r="C49" s="52" t="s">
+        <v>576</v>
+      </c>
+      <c r="D49" s="52" t="s">
+        <v>985</v>
+      </c>
+      <c r="E49" s="52" t="s">
+        <v>986</v>
+      </c>
+      <c r="F49" s="52" t="s">
+        <v>28</v>
+      </c>
+      <c r="G49" s="53">
+        <v>1</v>
+      </c>
+      <c r="H49" s="54" t="s">
+        <v>989</v>
+      </c>
+      <c r="I49" s="52" t="s">
+        <v>637</v>
+      </c>
+      <c r="J49" s="52">
+        <f>MONTH(I49)</f>
+        <v>6</v>
+      </c>
+      <c r="K49" s="52" t="s">
+        <v>38</v>
+      </c>
+      <c r="L49" s="54" t="s">
+        <v>1054</v>
+      </c>
+      <c r="M49" s="52" t="s">
+        <v>1014</v>
+      </c>
+      <c r="N49" s="52" t="s">
+        <v>1039</v>
+      </c>
+      <c r="O49" s="52" t="s">
+        <v>1014</v>
+      </c>
+      <c r="P49" s="54" t="s">
+        <v>987</v>
+      </c>
+    </row>
+    <row r="50" spans="1:16" ht="25.5" customHeight="1">
+      <c r="A50" s="52" t="s">
+        <v>36</v>
+      </c>
+      <c r="B50" s="52" t="s">
+        <v>758</v>
+      </c>
+      <c r="C50" s="52" t="s">
+        <v>781</v>
+      </c>
+      <c r="D50" s="52" t="s">
+        <v>782</v>
+      </c>
+      <c r="E50" s="52" t="s">
+        <v>783</v>
+      </c>
+      <c r="F50" s="52" t="s">
+        <v>28</v>
+      </c>
+      <c r="G50" s="53">
+        <v>10</v>
+      </c>
+      <c r="H50" s="54" t="s">
+        <v>1215</v>
+      </c>
+      <c r="I50" s="52" t="s">
+        <v>1216</v>
+      </c>
+      <c r="J50" s="52">
+        <f>MONTH(I50)</f>
+        <v>6</v>
+      </c>
+      <c r="K50" s="52" t="s">
+        <v>38</v>
+      </c>
+      <c r="L50" s="54" t="s">
+        <v>1217</v>
+      </c>
+      <c r="M50" s="52" t="s">
+        <v>1014</v>
+      </c>
+      <c r="N50" s="52" t="s">
+        <v>1039</v>
+      </c>
+      <c r="O50" s="52" t="s">
+        <v>1014</v>
+      </c>
+      <c r="P50" s="54" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="51" spans="1:16" ht="25.5" customHeight="1">
+      <c r="A51" s="52" t="s">
+        <v>36</v>
+      </c>
+      <c r="B51" s="52" t="s">
+        <v>190</v>
+      </c>
+      <c r="C51" s="52" t="s">
+        <v>368</v>
+      </c>
+      <c r="D51" s="52" t="s">
+        <v>887</v>
+      </c>
+      <c r="E51" s="52" t="s">
+        <v>888</v>
+      </c>
+      <c r="F51" s="52" t="s">
+        <v>28</v>
+      </c>
+      <c r="G51" s="53">
+        <v>4</v>
+      </c>
+      <c r="H51" s="54" t="s">
+        <v>1236</v>
+      </c>
+      <c r="I51" s="52" t="s">
+        <v>1216</v>
+      </c>
+      <c r="J51" s="52">
+        <f>MONTH(I51)</f>
+        <v>6</v>
+      </c>
+      <c r="K51" s="52" t="s">
+        <v>38</v>
+      </c>
+      <c r="L51" s="54" t="s">
+        <v>1237</v>
+      </c>
+      <c r="M51" s="52" t="s">
+        <v>1006</v>
+      </c>
+      <c r="N51" s="52" t="s">
+        <v>1039</v>
+      </c>
+      <c r="O51" s="52" t="s">
+        <v>1014</v>
+      </c>
+      <c r="P51" s="54" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="52" spans="1:16" ht="25.5" customHeight="1">
+      <c r="A52" s="52" t="s">
+        <v>1274</v>
+      </c>
+      <c r="B52" s="52" t="s">
+        <v>190</v>
+      </c>
+      <c r="C52" s="52" t="s">
+        <v>358</v>
+      </c>
+      <c r="D52" s="52" t="s">
+        <v>1282</v>
+      </c>
+      <c r="E52" s="52" t="s">
+        <v>1283</v>
+      </c>
+      <c r="F52" s="52" t="s">
+        <v>28</v>
+      </c>
+      <c r="G52" s="53">
+        <v>3</v>
+      </c>
+      <c r="H52" s="54" t="s">
+        <v>1284</v>
+      </c>
+      <c r="I52" s="52" t="s">
+        <v>281</v>
+      </c>
+      <c r="J52" s="52">
+        <f>MONTH(I52)</f>
+        <v>6</v>
+      </c>
+      <c r="K52" s="52" t="s">
+        <v>38</v>
+      </c>
+      <c r="L52" s="54" t="s">
+        <v>1285</v>
+      </c>
+      <c r="M52" s="52" t="s">
+        <v>1006</v>
+      </c>
+      <c r="N52" s="52" t="s">
+        <v>1275</v>
+      </c>
+      <c r="O52" s="52" t="s">
+        <v>1006</v>
+      </c>
+      <c r="P52" s="54" t="s">
+        <v>1281</v>
+      </c>
+    </row>
+    <row r="53" spans="1:16" ht="25.5" customHeight="1">
+      <c r="A53" s="52" t="s">
+        <v>1274</v>
+      </c>
+      <c r="B53" s="52" t="s">
+        <v>758</v>
+      </c>
+      <c r="C53" s="52" t="s">
+        <v>759</v>
+      </c>
+      <c r="D53" s="52" t="s">
+        <v>1245</v>
+      </c>
+      <c r="E53" s="52" t="s">
+        <v>1246</v>
+      </c>
+      <c r="F53" s="52" t="s">
+        <v>28</v>
+      </c>
+      <c r="G53" s="53">
+        <v>1</v>
+      </c>
+      <c r="H53" s="54" t="s">
+        <v>1247</v>
+      </c>
+      <c r="I53" s="52" t="s">
+        <v>281</v>
+      </c>
+      <c r="J53" s="52">
+        <f>MONTH(I53)</f>
+        <v>6</v>
+      </c>
+      <c r="K53" s="52" t="s">
+        <v>38</v>
+      </c>
+      <c r="L53" s="54" t="s">
+        <v>1248</v>
+      </c>
+      <c r="M53" s="52" t="s">
+        <v>1014</v>
+      </c>
+      <c r="N53" s="52" t="s">
+        <v>1275</v>
+      </c>
+      <c r="O53" s="52" t="s">
+        <v>1014</v>
+      </c>
+      <c r="P53" s="54" t="s">
+        <v>1276</v>
+      </c>
+    </row>
+    <row r="54" spans="1:16" ht="25.5" customHeight="1">
+      <c r="A54" s="52" t="s">
+        <v>1274</v>
+      </c>
+      <c r="B54" s="52" t="s">
+        <v>190</v>
+      </c>
+      <c r="C54" s="52" t="s">
+        <v>358</v>
+      </c>
+      <c r="D54" s="52" t="s">
+        <v>1282</v>
+      </c>
+      <c r="E54" s="52" t="s">
+        <v>1283</v>
+      </c>
+      <c r="F54" s="52" t="s">
+        <v>28</v>
+      </c>
+      <c r="G54" s="53">
+        <v>1</v>
+      </c>
+      <c r="H54" s="54" t="s">
+        <v>1284</v>
+      </c>
+      <c r="I54" s="52" t="s">
+        <v>413</v>
+      </c>
+      <c r="J54" s="52">
+        <f>MONTH(I54)</f>
+        <v>6</v>
+      </c>
+      <c r="K54" s="52" t="s">
+        <v>38</v>
+      </c>
+      <c r="L54" s="54" t="s">
+        <v>1285</v>
+      </c>
+      <c r="M54" s="52" t="s">
+        <v>1006</v>
+      </c>
+      <c r="N54" s="52" t="s">
+        <v>1275</v>
+      </c>
+      <c r="O54" s="52" t="s">
+        <v>1006</v>
+      </c>
+      <c r="P54" s="54" t="s">
+        <v>1281</v>
+      </c>
+    </row>
+    <row r="55" spans="1:16" ht="25.5" customHeight="1">
+      <c r="A55" s="52" t="s">
+        <v>1274</v>
+      </c>
+      <c r="B55" s="52" t="s">
+        <v>190</v>
+      </c>
+      <c r="C55" s="52" t="s">
+        <v>358</v>
+      </c>
+      <c r="D55" s="52" t="s">
+        <v>1282</v>
+      </c>
+      <c r="E55" s="52" t="s">
+        <v>1283</v>
+      </c>
+      <c r="F55" s="52" t="s">
+        <v>28</v>
+      </c>
+      <c r="G55" s="53">
+        <v>2</v>
+      </c>
+      <c r="H55" s="54" t="s">
+        <v>1286</v>
+      </c>
+      <c r="I55" s="52" t="s">
+        <v>413</v>
+      </c>
+      <c r="J55" s="52">
+        <f>MONTH(I55)</f>
+        <v>6</v>
+      </c>
+      <c r="K55" s="52" t="s">
+        <v>38</v>
+      </c>
+      <c r="L55" s="54" t="s">
+        <v>1285</v>
+      </c>
+      <c r="M55" s="52" t="s">
+        <v>1006</v>
+      </c>
+      <c r="N55" s="52" t="s">
+        <v>1275</v>
+      </c>
+      <c r="O55" s="52" t="s">
+        <v>1006</v>
+      </c>
+      <c r="P55" s="54" t="s">
+        <v>1281</v>
+      </c>
+    </row>
+    <row r="56" spans="1:16" ht="25.5" customHeight="1">
+      <c r="A56" s="52" t="s">
+        <v>36</v>
+      </c>
+      <c r="B56" s="52" t="s">
+        <v>110</v>
+      </c>
+      <c r="C56" s="52" t="s">
+        <v>704</v>
+      </c>
+      <c r="D56" s="52" t="s">
+        <v>705</v>
+      </c>
+      <c r="E56" s="52" t="s">
+        <v>706</v>
+      </c>
+      <c r="F56" s="52" t="s">
+        <v>28</v>
+      </c>
+      <c r="G56" s="53">
+        <v>2</v>
+      </c>
+      <c r="H56" s="54" t="s">
+        <v>1174</v>
+      </c>
+      <c r="I56" s="52" t="s">
+        <v>1175</v>
+      </c>
+      <c r="J56" s="52">
+        <f>MONTH(I56)</f>
+        <v>6</v>
+      </c>
+      <c r="K56" s="52" t="s">
+        <v>38</v>
+      </c>
+      <c r="L56" s="54" t="s">
+        <v>1176</v>
+      </c>
+      <c r="M56" s="52" t="s">
+        <v>1014</v>
+      </c>
+      <c r="N56" s="52" t="s">
+        <v>1039</v>
+      </c>
+      <c r="O56" s="52" t="s">
+        <v>1014</v>
+      </c>
+      <c r="P56" s="54" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="57" spans="1:16" ht="25.5" customHeight="1">
+      <c r="A57" s="52" t="s">
+        <v>36</v>
+      </c>
+      <c r="B57" s="52" t="s">
+        <v>212</v>
+      </c>
+      <c r="C57" s="52" t="s">
+        <v>213</v>
+      </c>
+      <c r="D57" s="52" t="s">
+        <v>226</v>
+      </c>
+      <c r="E57" s="52" t="s">
+        <v>227</v>
+      </c>
+      <c r="F57" s="52" t="s">
+        <v>28</v>
+      </c>
+      <c r="G57" s="53">
+        <v>2</v>
+      </c>
+      <c r="H57" s="54" t="s">
+        <v>1057</v>
+      </c>
+      <c r="I57" s="52" t="s">
+        <v>1058</v>
+      </c>
+      <c r="J57" s="52">
+        <f>MONTH(I57)</f>
+        <v>6</v>
+      </c>
+      <c r="K57" s="52" t="s">
+        <v>38</v>
+      </c>
+      <c r="L57" s="54" t="s">
+        <v>1059</v>
+      </c>
+      <c r="M57" s="52" t="s">
+        <v>1006</v>
+      </c>
+      <c r="N57" s="52" t="s">
+        <v>1039</v>
+      </c>
+      <c r="O57" s="52" t="s">
+        <v>1006</v>
+      </c>
+      <c r="P57" s="54" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="58" spans="1:16" ht="25.5" customHeight="1">
+      <c r="A58" s="52" t="s">
+        <v>36</v>
+      </c>
+      <c r="B58" s="52" t="s">
+        <v>68</v>
+      </c>
+      <c r="C58" s="52" t="s">
+        <v>408</v>
+      </c>
+      <c r="D58" s="52" t="s">
+        <v>534</v>
+      </c>
+      <c r="E58" s="52" t="s">
+        <v>535</v>
+      </c>
+      <c r="F58" s="52" t="s">
+        <v>28</v>
+      </c>
+      <c r="G58" s="53">
+        <v>4</v>
+      </c>
+      <c r="H58" s="54" t="s">
+        <v>1138</v>
+      </c>
+      <c r="I58" s="52" t="s">
+        <v>684</v>
+      </c>
+      <c r="J58" s="52">
+        <f>MONTH(I58)</f>
+        <v>6</v>
+      </c>
+      <c r="K58" s="52" t="s">
+        <v>38</v>
+      </c>
+      <c r="L58" s="54" t="s">
+        <v>1139</v>
+      </c>
+      <c r="M58" s="52" t="s">
+        <v>1014</v>
+      </c>
+      <c r="N58" s="52" t="s">
+        <v>1039</v>
+      </c>
+      <c r="O58" s="52" t="s">
+        <v>1014</v>
+      </c>
+      <c r="P58" s="54" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="59" spans="1:16" ht="25.5" customHeight="1">
+      <c r="A59" s="52" t="s">
+        <v>1250</v>
+      </c>
+      <c r="B59" s="52" t="s">
+        <v>162</v>
+      </c>
+      <c r="C59" s="52" t="s">
+        <v>163</v>
+      </c>
+      <c r="D59" s="52" t="s">
+        <v>164</v>
+      </c>
+      <c r="E59" s="52" t="s">
+        <v>165</v>
+      </c>
+      <c r="F59" s="52" t="s">
+        <v>28</v>
+      </c>
+      <c r="G59" s="53">
+        <v>9</v>
+      </c>
+      <c r="H59" s="54" t="s">
+        <v>1256</v>
+      </c>
+      <c r="I59" s="52" t="s">
+        <v>864</v>
+      </c>
+      <c r="J59" s="52">
+        <f>MONTH(I59)</f>
+        <v>6</v>
+      </c>
+      <c r="K59" s="52" t="s">
+        <v>38</v>
+      </c>
+      <c r="L59" s="54" t="s">
+        <v>1255</v>
+      </c>
+      <c r="M59" s="52" t="s">
+        <v>1006</v>
+      </c>
+      <c r="N59" s="52" t="s">
+        <v>1251</v>
+      </c>
+      <c r="O59" s="52" t="s">
+        <v>1006</v>
+      </c>
+      <c r="P59" s="54" t="s">
+        <v>1252</v>
+      </c>
+    </row>
+    <row r="60" spans="1:16" ht="25.5" customHeight="1">
+      <c r="A60" s="52" t="s">
+        <v>1274</v>
+      </c>
+      <c r="B60" s="52" t="s">
+        <v>190</v>
+      </c>
+      <c r="C60" s="52" t="s">
+        <v>358</v>
+      </c>
+      <c r="D60" s="52" t="s">
+        <v>682</v>
+      </c>
+      <c r="E60" s="52" t="s">
+        <v>683</v>
+      </c>
+      <c r="F60" s="52" t="s">
+        <v>28</v>
+      </c>
+      <c r="G60" s="53">
+        <v>1</v>
+      </c>
+      <c r="H60" s="54" t="s">
+        <v>1303</v>
+      </c>
+      <c r="I60" s="52" t="s">
+        <v>864</v>
+      </c>
+      <c r="J60" s="52">
+        <f>MONTH(I60)</f>
+        <v>6</v>
+      </c>
+      <c r="K60" s="52" t="s">
+        <v>38</v>
+      </c>
+      <c r="L60" s="54" t="s">
+        <v>1304</v>
+      </c>
+      <c r="M60" s="52" t="s">
+        <v>1006</v>
+      </c>
+      <c r="N60" s="52" t="s">
+        <v>1275</v>
+      </c>
+      <c r="O60" s="52" t="s">
+        <v>1006</v>
+      </c>
+      <c r="P60" s="54" t="s">
+        <v>1281</v>
+      </c>
+    </row>
+    <row r="61" spans="1:16" ht="25.5" customHeight="1">
+      <c r="A61" s="52" t="s">
+        <v>1274</v>
+      </c>
+      <c r="B61" s="52" t="s">
+        <v>190</v>
+      </c>
+      <c r="C61" s="52" t="s">
+        <v>358</v>
+      </c>
+      <c r="D61" s="52" t="s">
+        <v>682</v>
+      </c>
+      <c r="E61" s="52" t="s">
+        <v>683</v>
+      </c>
+      <c r="F61" s="52" t="s">
+        <v>28</v>
+      </c>
+      <c r="G61" s="53">
+        <v>2</v>
+      </c>
+      <c r="H61" s="54" t="s">
+        <v>1305</v>
+      </c>
+      <c r="I61" s="52" t="s">
+        <v>864</v>
+      </c>
+      <c r="J61" s="52">
+        <f>MONTH(I61)</f>
+        <v>6</v>
+      </c>
+      <c r="K61" s="52" t="s">
+        <v>38</v>
+      </c>
+      <c r="L61" s="54" t="s">
+        <v>1304</v>
+      </c>
+      <c r="M61" s="52" t="s">
+        <v>1006</v>
+      </c>
+      <c r="N61" s="52" t="s">
+        <v>1275</v>
+      </c>
+      <c r="O61" s="52" t="s">
+        <v>1006</v>
+      </c>
+      <c r="P61" s="54" t="s">
+        <v>1281</v>
+      </c>
+    </row>
+    <row r="62" spans="1:16" ht="25.5" customHeight="1">
+      <c r="A62" s="52" t="s">
+        <v>36</v>
+      </c>
+      <c r="B62" s="52" t="s">
+        <v>68</v>
+      </c>
+      <c r="C62" s="52" t="s">
+        <v>79</v>
+      </c>
+      <c r="D62" s="52" t="s">
+        <v>1226</v>
+      </c>
+      <c r="E62" s="52" t="s">
+        <v>1227</v>
+      </c>
+      <c r="F62" s="52" t="s">
+        <v>28</v>
+      </c>
+      <c r="G62" s="53">
+        <v>1</v>
+      </c>
+      <c r="H62" s="54" t="s">
+        <v>1196</v>
+      </c>
+      <c r="I62" s="52" t="s">
+        <v>203</v>
+      </c>
+      <c r="J62" s="52">
+        <f>MONTH(I62)</f>
+        <v>6</v>
+      </c>
+      <c r="K62" s="52" t="s">
+        <v>72</v>
+      </c>
+      <c r="L62" s="54" t="s">
+        <v>1128</v>
+      </c>
+      <c r="M62" s="52" t="s">
+        <v>1006</v>
+      </c>
+      <c r="N62" s="52" t="s">
+        <v>1039</v>
+      </c>
+      <c r="O62" s="52" t="s">
+        <v>1014</v>
+      </c>
+      <c r="P62" s="54" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="63" spans="1:16" ht="25.5" customHeight="1">
+      <c r="A63" s="52" t="s">
+        <v>114</v>
+      </c>
+      <c r="B63" s="52" t="s">
+        <v>51</v>
+      </c>
+      <c r="C63" s="52" t="s">
+        <v>52</v>
+      </c>
+      <c r="D63" s="52" t="s">
+        <v>882</v>
+      </c>
+      <c r="E63" s="52" t="s">
+        <v>883</v>
+      </c>
+      <c r="F63" s="52" t="s">
+        <v>28</v>
+      </c>
+      <c r="G63" s="53">
+        <v>1</v>
+      </c>
+      <c r="H63" s="54" t="s">
+        <v>1031</v>
+      </c>
+      <c r="I63" s="52" t="s">
+        <v>642</v>
+      </c>
+      <c r="J63" s="52">
+        <f>MONTH(I63)</f>
+        <v>6</v>
+      </c>
+      <c r="K63" s="52" t="s">
+        <v>72</v>
+      </c>
+      <c r="L63" s="54" t="s">
+        <v>1032</v>
+      </c>
+      <c r="M63" s="52" t="s">
+        <v>1014</v>
+      </c>
+      <c r="N63" s="52" t="s">
+        <v>1033</v>
+      </c>
+      <c r="O63" s="52" t="s">
+        <v>1014</v>
+      </c>
+      <c r="P63" s="54" t="s">
+        <v>955</v>
+      </c>
+    </row>
+    <row r="64" spans="1:16" ht="25.5" customHeight="1">
+      <c r="A64" s="52" t="s">
+        <v>36</v>
+      </c>
+      <c r="B64" s="52" t="s">
+        <v>758</v>
+      </c>
+      <c r="C64" s="52" t="s">
+        <v>1008</v>
+      </c>
+      <c r="D64" s="52" t="s">
+        <v>1064</v>
+      </c>
+      <c r="E64" s="52" t="s">
+        <v>1065</v>
+      </c>
+      <c r="F64" s="52" t="s">
+        <v>28</v>
+      </c>
+      <c r="G64" s="53">
+        <v>1</v>
+      </c>
+      <c r="H64" s="54" t="s">
+        <v>1066</v>
+      </c>
+      <c r="I64" s="52" t="s">
+        <v>74</v>
+      </c>
+      <c r="J64" s="52">
+        <f>MONTH(I64)</f>
+        <v>6</v>
+      </c>
+      <c r="K64" s="52" t="s">
+        <v>38</v>
+      </c>
+      <c r="L64" s="54" t="s">
+        <v>1067</v>
+      </c>
+      <c r="M64" s="52" t="s">
+        <v>1006</v>
+      </c>
+      <c r="N64" s="52" t="s">
+        <v>1039</v>
+      </c>
+      <c r="O64" s="52" t="s">
+        <v>1006</v>
+      </c>
+      <c r="P64" s="54" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="65" spans="1:16" ht="25.5" customHeight="1">
+      <c r="A65" s="52" t="s">
+        <v>36</v>
+      </c>
+      <c r="B65" s="52" t="s">
+        <v>68</v>
+      </c>
+      <c r="C65" s="52" t="s">
+        <v>146</v>
+      </c>
+      <c r="D65" s="52" t="s">
+        <v>376</v>
+      </c>
+      <c r="E65" s="52" t="s">
+        <v>377</v>
+      </c>
+      <c r="F65" s="52" t="s">
+        <v>28</v>
+      </c>
+      <c r="G65" s="53">
+        <v>2</v>
+      </c>
+      <c r="H65" s="54" t="s">
+        <v>1078</v>
+      </c>
+      <c r="I65" s="52" t="s">
+        <v>74</v>
+      </c>
+      <c r="J65" s="52">
+        <f>MONTH(I65)</f>
+        <v>6</v>
+      </c>
+      <c r="K65" s="52" t="s">
+        <v>72</v>
+      </c>
+      <c r="L65" s="54" t="s">
+        <v>1079</v>
+      </c>
+      <c r="M65" s="52" t="s">
+        <v>1006</v>
+      </c>
+      <c r="N65" s="52" t="s">
+        <v>1039</v>
+      </c>
+      <c r="O65" s="52" t="s">
+        <v>1006</v>
+      </c>
+      <c r="P65" s="54" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="66" spans="1:16" ht="25.5" customHeight="1">
+      <c r="A66" s="52" t="s">
+        <v>36</v>
+      </c>
+      <c r="B66" s="52" t="s">
+        <v>352</v>
+      </c>
+      <c r="C66" s="52" t="s">
+        <v>353</v>
+      </c>
+      <c r="D66" s="52" t="s">
+        <v>1087</v>
+      </c>
+      <c r="E66" s="52" t="s">
+        <v>1088</v>
+      </c>
+      <c r="F66" s="52" t="s">
+        <v>28</v>
+      </c>
+      <c r="G66" s="53">
+        <v>2</v>
+      </c>
+      <c r="H66" s="54" t="s">
+        <v>1091</v>
+      </c>
+      <c r="I66" s="52" t="s">
+        <v>74</v>
+      </c>
+      <c r="J66" s="52">
+        <f>MONTH(I66)</f>
+        <v>6</v>
+      </c>
+      <c r="K66" s="52" t="s">
+        <v>72</v>
+      </c>
+      <c r="L66" s="54" t="s">
+        <v>1092</v>
+      </c>
+      <c r="M66" s="52" t="s">
+        <v>1014</v>
+      </c>
+      <c r="N66" s="52" t="s">
+        <v>1039</v>
+      </c>
+      <c r="O66" s="52" t="s">
+        <v>1014</v>
+      </c>
+      <c r="P66" s="54" t="s">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="67" spans="1:16" ht="25.5" customHeight="1">
+      <c r="A67" s="52" t="s">
+        <v>36</v>
+      </c>
+      <c r="B67" s="52" t="s">
+        <v>206</v>
+      </c>
+      <c r="C67" s="52" t="s">
+        <v>270</v>
+      </c>
+      <c r="D67" s="52" t="s">
+        <v>1101</v>
+      </c>
+      <c r="E67" s="52" t="s">
+        <v>1102</v>
+      </c>
+      <c r="F67" s="52" t="s">
+        <v>28</v>
+      </c>
+      <c r="G67" s="53">
+        <v>2</v>
+      </c>
+      <c r="H67" s="54" t="s">
+        <v>1105</v>
+      </c>
+      <c r="I67" s="52" t="s">
+        <v>74</v>
+      </c>
+      <c r="J67" s="52">
+        <f>MONTH(I67)</f>
+        <v>6</v>
+      </c>
+      <c r="K67" s="52" t="s">
+        <v>38</v>
+      </c>
+      <c r="L67" s="54" t="s">
+        <v>1106</v>
+      </c>
+      <c r="M67" s="52" t="s">
+        <v>1006</v>
+      </c>
+      <c r="N67" s="52" t="s">
+        <v>1039</v>
+      </c>
+      <c r="O67" s="52" t="s">
+        <v>1006</v>
+      </c>
+      <c r="P67" s="54" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="68" spans="1:16" ht="25.5" customHeight="1">
+      <c r="A68" s="52" t="s">
+        <v>36</v>
+      </c>
+      <c r="B68" s="52" t="s">
+        <v>352</v>
+      </c>
+      <c r="C68" s="52" t="s">
+        <v>353</v>
+      </c>
+      <c r="D68" s="52" t="s">
+        <v>1116</v>
+      </c>
+      <c r="E68" s="52" t="s">
+        <v>1117</v>
+      </c>
+      <c r="F68" s="52" t="s">
+        <v>28</v>
+      </c>
+      <c r="G68" s="53">
+        <v>1</v>
+      </c>
+      <c r="H68" s="54" t="s">
+        <v>1118</v>
+      </c>
+      <c r="I68" s="52" t="s">
+        <v>74</v>
+      </c>
+      <c r="J68" s="52">
+        <f>MONTH(I68)</f>
+        <v>6</v>
+      </c>
+      <c r="K68" s="52" t="s">
+        <v>38</v>
+      </c>
+      <c r="L68" s="54" t="s">
+        <v>1119</v>
+      </c>
+      <c r="M68" s="52" t="s">
+        <v>1006</v>
+      </c>
+      <c r="N68" s="52" t="s">
+        <v>1039</v>
+      </c>
+      <c r="O68" s="52" t="s">
+        <v>1006</v>
+      </c>
+      <c r="P68" s="54" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="69" spans="1:16" ht="25.5" customHeight="1">
+      <c r="A69" s="52" t="s">
+        <v>36</v>
+      </c>
+      <c r="B69" s="52" t="s">
+        <v>30</v>
+      </c>
+      <c r="C69" s="52" t="s">
+        <v>490</v>
+      </c>
+      <c r="D69" s="52" t="s">
+        <v>491</v>
+      </c>
+      <c r="E69" s="52" t="s">
+        <v>492</v>
+      </c>
+      <c r="F69" s="52" t="s">
+        <v>28</v>
+      </c>
+      <c r="G69" s="53">
+        <v>3</v>
+      </c>
+      <c r="H69" s="54" t="s">
+        <v>1132</v>
+      </c>
+      <c r="I69" s="52" t="s">
+        <v>74</v>
+      </c>
+      <c r="J69" s="52">
+        <f>MONTH(I69)</f>
+        <v>6</v>
+      </c>
+      <c r="K69" s="52" t="s">
+        <v>38</v>
+      </c>
+      <c r="L69" s="54" t="s">
+        <v>1133</v>
+      </c>
+      <c r="M69" s="52" t="s">
+        <v>1006</v>
+      </c>
+      <c r="N69" s="52" t="s">
+        <v>1039</v>
+      </c>
+      <c r="O69" s="52" t="s">
+        <v>1006</v>
+      </c>
+      <c r="P69" s="54" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="70" spans="1:16" ht="25.5" customHeight="1">
+      <c r="A70" s="52" t="s">
+        <v>36</v>
+      </c>
+      <c r="B70" s="52" t="s">
+        <v>206</v>
+      </c>
+      <c r="C70" s="52" t="s">
+        <v>643</v>
+      </c>
+      <c r="D70" s="52" t="s">
+        <v>1208</v>
+      </c>
+      <c r="E70" s="52" t="s">
+        <v>1209</v>
+      </c>
+      <c r="F70" s="52" t="s">
+        <v>28</v>
+      </c>
+      <c r="G70" s="53">
+        <v>1</v>
+      </c>
+      <c r="H70" s="54" t="s">
+        <v>1210</v>
+      </c>
+      <c r="I70" s="52" t="s">
+        <v>74</v>
+      </c>
+      <c r="J70" s="52">
+        <f>MONTH(I70)</f>
+        <v>6</v>
+      </c>
+      <c r="K70" s="52" t="s">
+        <v>38</v>
+      </c>
+      <c r="L70" s="54" t="s">
+        <v>1211</v>
+      </c>
+      <c r="M70" s="52" t="s">
+        <v>1006</v>
+      </c>
+      <c r="N70" s="52" t="s">
+        <v>1039</v>
+      </c>
+      <c r="O70" s="52" t="s">
+        <v>1006</v>
+      </c>
+      <c r="P70" s="54" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="71" spans="1:16" ht="25.5" customHeight="1">
+      <c r="A71" s="52" t="s">
+        <v>1250</v>
+      </c>
+      <c r="B71" s="52" t="s">
+        <v>162</v>
+      </c>
+      <c r="C71" s="52" t="s">
+        <v>808</v>
+      </c>
+      <c r="D71" s="52" t="s">
+        <v>1264</v>
+      </c>
+      <c r="E71" s="52" t="s">
+        <v>1265</v>
+      </c>
+      <c r="F71" s="52" t="s">
+        <v>28</v>
+      </c>
+      <c r="G71" s="53">
+        <v>1</v>
+      </c>
+      <c r="H71" s="54" t="s">
+        <v>1266</v>
+      </c>
+      <c r="I71" s="52" t="s">
+        <v>74</v>
+      </c>
+      <c r="J71" s="52">
+        <f>MONTH(I71)</f>
+        <v>6</v>
+      </c>
+      <c r="K71" s="52" t="s">
+        <v>38</v>
+      </c>
+      <c r="L71" s="54" t="s">
+        <v>1267</v>
+      </c>
+      <c r="M71" s="52" t="s">
+        <v>1006</v>
+      </c>
+      <c r="N71" s="52" t="s">
+        <v>1268</v>
+      </c>
+      <c r="O71" s="52" t="s">
+        <v>1006</v>
+      </c>
+      <c r="P71" s="54" t="s">
+        <v>1269</v>
+      </c>
+    </row>
+    <row r="72" spans="1:16" ht="25.5" customHeight="1">
+      <c r="A72" s="52" t="s">
+        <v>36</v>
+      </c>
+      <c r="B72" s="52" t="s">
+        <v>68</v>
+      </c>
+      <c r="C72" s="52" t="s">
+        <v>408</v>
+      </c>
+      <c r="D72" s="52" t="s">
+        <v>1035</v>
+      </c>
+      <c r="E72" s="52" t="s">
+        <v>1036</v>
+      </c>
+      <c r="F72" s="52" t="s">
+        <v>28</v>
+      </c>
+      <c r="G72" s="53">
+        <v>1</v>
+      </c>
+      <c r="H72" s="54" t="s">
+        <v>1037</v>
+      </c>
+      <c r="I72" s="52" t="s">
+        <v>188</v>
+      </c>
+      <c r="J72" s="52">
+        <f>MONTH(I72)</f>
+        <v>7</v>
+      </c>
+      <c r="K72" s="52" t="s">
+        <v>38</v>
+      </c>
+      <c r="L72" s="54" t="s">
+        <v>1038</v>
+      </c>
+      <c r="M72" s="52" t="s">
+        <v>1006</v>
+      </c>
+      <c r="N72" s="52" t="s">
+        <v>1039</v>
+      </c>
+      <c r="O72" s="52" t="s">
+        <v>1014</v>
+      </c>
+      <c r="P72" s="54" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="73" spans="1:16" ht="25.5" customHeight="1">
+      <c r="A73" s="52" t="s">
+        <v>36</v>
+      </c>
+      <c r="B73" s="52" t="s">
+        <v>68</v>
+      </c>
+      <c r="C73" s="52" t="s">
+        <v>408</v>
+      </c>
+      <c r="D73" s="52" t="s">
+        <v>1035</v>
+      </c>
+      <c r="E73" s="52" t="s">
+        <v>1036</v>
+      </c>
+      <c r="F73" s="52" t="s">
+        <v>28</v>
+      </c>
+      <c r="G73" s="53">
+        <v>3</v>
+      </c>
+      <c r="H73" s="54" t="s">
+        <v>1042</v>
+      </c>
+      <c r="I73" s="52" t="s">
+        <v>188</v>
+      </c>
+      <c r="J73" s="52">
+        <f>MONTH(I73)</f>
+        <v>7</v>
+      </c>
+      <c r="K73" s="52" t="s">
+        <v>72</v>
+      </c>
+      <c r="L73" s="54" t="s">
+        <v>1041</v>
+      </c>
+      <c r="M73" s="52" t="s">
+        <v>1014</v>
+      </c>
+      <c r="N73" s="52" t="s">
+        <v>1039</v>
+      </c>
+      <c r="O73" s="52" t="s">
+        <v>1014</v>
+      </c>
+      <c r="P73" s="54" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="74" spans="1:16" ht="25.5" customHeight="1">
+      <c r="A74" s="52" t="s">
+        <v>36</v>
+      </c>
+      <c r="B74" s="52" t="s">
+        <v>190</v>
+      </c>
+      <c r="C74" s="52" t="s">
+        <v>258</v>
+      </c>
+      <c r="D74" s="52" t="s">
+        <v>259</v>
+      </c>
+      <c r="E74" s="52" t="s">
+        <v>260</v>
+      </c>
+      <c r="F74" s="52" t="s">
+        <v>28</v>
+      </c>
+      <c r="G74" s="53">
+        <v>5</v>
+      </c>
+      <c r="H74" s="54" t="s">
+        <v>1062</v>
+      </c>
+      <c r="I74" s="52" t="s">
+        <v>188</v>
+      </c>
+      <c r="J74" s="52">
+        <f>MONTH(I74)</f>
+        <v>7</v>
+      </c>
+      <c r="K74" s="52" t="s">
+        <v>38</v>
+      </c>
+      <c r="L74" s="54" t="s">
+        <v>1063</v>
+      </c>
+      <c r="M74" s="52" t="s">
+        <v>1014</v>
+      </c>
+      <c r="N74" s="52" t="s">
+        <v>1039</v>
+      </c>
+      <c r="O74" s="52" t="s">
+        <v>1014</v>
+      </c>
+      <c r="P74" s="54" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="75" spans="1:16" ht="25.5" customHeight="1">
+      <c r="A75" s="52" t="s">
+        <v>1323</v>
+      </c>
+      <c r="B75" s="52" t="s">
+        <v>68</v>
+      </c>
+      <c r="C75" s="52" t="s">
+        <v>620</v>
+      </c>
+      <c r="D75" s="52" t="s">
+        <v>1124</v>
+      </c>
+      <c r="E75" s="52" t="s">
+        <v>1125</v>
+      </c>
+      <c r="F75" s="52" t="s">
+        <v>28</v>
+      </c>
+      <c r="G75" s="53">
+        <v>5</v>
+      </c>
+      <c r="H75" s="54" t="s">
+        <v>1324</v>
+      </c>
+      <c r="I75" s="52" t="s">
+        <v>188</v>
+      </c>
+      <c r="J75" s="52">
+        <f>MONTH(I75)</f>
+        <v>7</v>
+      </c>
+      <c r="K75" s="52" t="s">
+        <v>38</v>
+      </c>
+      <c r="L75" s="54" t="s">
+        <v>1325</v>
+      </c>
+      <c r="M75" s="52" t="s">
+        <v>1006</v>
+      </c>
+      <c r="N75" s="52" t="s">
+        <v>1326</v>
+      </c>
+      <c r="O75" s="52" t="s">
+        <v>1006</v>
+      </c>
+      <c r="P75" s="54" t="s">
+        <v>1327</v>
+      </c>
+    </row>
+    <row r="76" spans="1:16" ht="25.5" customHeight="1">
+      <c r="A76" s="52" t="s">
+        <v>1274</v>
+      </c>
+      <c r="B76" s="52" t="s">
+        <v>322</v>
+      </c>
+      <c r="C76" s="52" t="s">
+        <v>587</v>
+      </c>
+      <c r="D76" s="52" t="s">
+        <v>1295</v>
+      </c>
+      <c r="E76" s="52" t="s">
+        <v>1296</v>
+      </c>
+      <c r="F76" s="52" t="s">
+        <v>28</v>
+      </c>
+      <c r="G76" s="53">
+        <v>1</v>
+      </c>
+      <c r="H76" s="54" t="s">
+        <v>1297</v>
+      </c>
+      <c r="I76" s="52" t="s">
+        <v>851</v>
+      </c>
+      <c r="J76" s="52">
+        <f>MONTH(I76)</f>
+        <v>7</v>
+      </c>
+      <c r="K76" s="52" t="s">
+        <v>38</v>
+      </c>
+      <c r="L76" s="54" t="s">
+        <v>1298</v>
+      </c>
+      <c r="M76" s="52" t="s">
+        <v>1006</v>
+      </c>
+      <c r="N76" s="52" t="s">
+        <v>1275</v>
+      </c>
+      <c r="O76" s="52" t="s">
+        <v>1006</v>
+      </c>
+      <c r="P76" s="54" t="s">
+        <v>1281</v>
+      </c>
+    </row>
+    <row r="77" spans="1:16" ht="25.5" customHeight="1">
+      <c r="A77" s="52" t="s">
+        <v>1328</v>
+      </c>
+      <c r="B77" s="52" t="s">
+        <v>162</v>
+      </c>
+      <c r="C77" s="52" t="s">
+        <v>447</v>
+      </c>
+      <c r="D77" s="52" t="s">
+        <v>1343</v>
+      </c>
+      <c r="E77" s="52" t="s">
+        <v>1344</v>
+      </c>
+      <c r="F77" s="52" t="s">
+        <v>28</v>
+      </c>
+      <c r="G77" s="53">
+        <v>2</v>
+      </c>
+      <c r="H77" s="54" t="s">
+        <v>1347</v>
+      </c>
+      <c r="I77" s="52" t="s">
+        <v>851</v>
+      </c>
+      <c r="J77" s="52">
+        <f>MONTH(I77)</f>
+        <v>7</v>
+      </c>
+      <c r="K77" s="52" t="s">
+        <v>72</v>
+      </c>
+      <c r="L77" s="54" t="s">
+        <v>1348</v>
+      </c>
+      <c r="M77" s="52" t="s">
+        <v>1014</v>
+      </c>
+      <c r="N77" s="52" t="s">
+        <v>1334</v>
+      </c>
+      <c r="O77" s="52" t="s">
+        <v>1014</v>
+      </c>
+      <c r="P77" s="54" t="s">
+        <v>1335</v>
+      </c>
+    </row>
+    <row r="78" spans="1:16" ht="25.5" customHeight="1">
+      <c r="A78" s="52" t="s">
+        <v>1328</v>
+      </c>
+      <c r="B78" s="52" t="s">
+        <v>162</v>
+      </c>
+      <c r="C78" s="52" t="s">
+        <v>1349</v>
+      </c>
+      <c r="D78" s="52" t="s">
+        <v>1350</v>
+      </c>
+      <c r="E78" s="52" t="s">
+        <v>1351</v>
+      </c>
+      <c r="F78" s="52" t="s">
+        <v>28</v>
+      </c>
+      <c r="G78" s="53">
+        <v>1</v>
+      </c>
+      <c r="H78" s="54" t="s">
+        <v>1347</v>
+      </c>
+      <c r="I78" s="52" t="s">
+        <v>851</v>
+      </c>
+      <c r="J78" s="52">
+        <f>MONTH(I78)</f>
+        <v>7</v>
+      </c>
+      <c r="K78" s="52" t="s">
+        <v>38</v>
+      </c>
+      <c r="L78" s="54" t="s">
+        <v>1352</v>
+      </c>
+      <c r="M78" s="52" t="s">
+        <v>1014</v>
+      </c>
+      <c r="N78" s="52" t="s">
+        <v>1334</v>
+      </c>
+      <c r="O78" s="52" t="s">
+        <v>1014</v>
+      </c>
+      <c r="P78" s="54" t="s">
+        <v>1335</v>
+      </c>
+    </row>
+    <row r="79" spans="1:16" ht="25.5" customHeight="1">
+      <c r="A79" s="52" t="s">
+        <v>1328</v>
+      </c>
+      <c r="B79" s="52" t="s">
+        <v>162</v>
+      </c>
+      <c r="C79" s="52" t="s">
+        <v>447</v>
+      </c>
+      <c r="D79" s="52" t="s">
+        <v>448</v>
+      </c>
+      <c r="E79" s="52" t="s">
+        <v>449</v>
+      </c>
+      <c r="F79" s="52" t="s">
+        <v>28</v>
+      </c>
+      <c r="G79" s="53">
+        <v>2</v>
+      </c>
+      <c r="H79" s="54" t="s">
+        <v>1365</v>
+      </c>
+      <c r="I79" s="52" t="s">
+        <v>851</v>
+      </c>
+      <c r="J79" s="52">
+        <f>MONTH(I79)</f>
+        <v>7</v>
+      </c>
+      <c r="K79" s="52" t="s">
+        <v>38</v>
+      </c>
+      <c r="L79" s="54" t="s">
+        <v>1348</v>
+      </c>
+      <c r="M79" s="52" t="s">
+        <v>1014</v>
+      </c>
+      <c r="N79" s="52" t="s">
+        <v>1334</v>
+      </c>
+      <c r="O79" s="52" t="s">
+        <v>1014</v>
+      </c>
+      <c r="P79" s="54" t="s">
+        <v>1335</v>
+      </c>
+    </row>
+    <row r="80" spans="1:16" ht="25.5" customHeight="1">
+      <c r="A80" s="52" t="s">
+        <v>1250</v>
+      </c>
+      <c r="B80" s="52" t="s">
+        <v>162</v>
+      </c>
+      <c r="C80" s="52" t="s">
+        <v>808</v>
+      </c>
+      <c r="D80" s="52" t="s">
+        <v>940</v>
+      </c>
+      <c r="E80" s="52" t="s">
+        <v>941</v>
+      </c>
+      <c r="F80" s="52" t="s">
+        <v>28</v>
+      </c>
+      <c r="G80" s="53">
+        <v>7</v>
+      </c>
+      <c r="H80" s="54" t="s">
+        <v>1271</v>
+      </c>
+      <c r="I80" s="52" t="s">
+        <v>1272</v>
+      </c>
+      <c r="J80" s="52">
+        <f>MONTH(I80)</f>
+        <v>7</v>
+      </c>
+      <c r="K80" s="52" t="s">
+        <v>38</v>
+      </c>
+      <c r="L80" s="54"/>
+      <c r="M80" s="52" t="s">
+        <v>1006</v>
+      </c>
+      <c r="N80" s="52" t="s">
+        <v>1268</v>
+      </c>
+      <c r="O80" s="52" t="s">
+        <v>1006</v>
+      </c>
+      <c r="P80" s="54" t="s">
+        <v>1269</v>
+      </c>
+    </row>
+    <row r="81" spans="1:16" ht="25.5" customHeight="1">
+      <c r="A81" s="52" t="s">
+        <v>1250</v>
+      </c>
+      <c r="B81" s="52" t="s">
+        <v>162</v>
+      </c>
+      <c r="C81" s="52" t="s">
+        <v>163</v>
+      </c>
+      <c r="D81" s="52" t="s">
+        <v>164</v>
+      </c>
+      <c r="E81" s="52" t="s">
+        <v>165</v>
+      </c>
+      <c r="F81" s="52" t="s">
+        <v>28</v>
+      </c>
+      <c r="G81" s="53">
+        <v>10</v>
+      </c>
+      <c r="H81" s="54" t="s">
+        <v>1257</v>
+      </c>
+      <c r="I81" s="52" t="s">
+        <v>1258</v>
+      </c>
+      <c r="J81" s="52">
+        <f>MONTH(I81)</f>
+        <v>7</v>
+      </c>
+      <c r="K81" s="52" t="s">
+        <v>38</v>
+      </c>
+      <c r="L81" s="54" t="s">
+        <v>1255</v>
+      </c>
+      <c r="M81" s="52" t="s">
+        <v>1006</v>
+      </c>
+      <c r="N81" s="52" t="s">
+        <v>1251</v>
+      </c>
+      <c r="O81" s="52" t="s">
+        <v>1006</v>
+      </c>
+      <c r="P81" s="54" t="s">
+        <v>1252</v>
+      </c>
+    </row>
+    <row r="82" spans="1:16" ht="25.5" customHeight="1">
+      <c r="A82" s="52" t="s">
+        <v>1274</v>
+      </c>
+      <c r="B82" s="52" t="s">
+        <v>190</v>
+      </c>
+      <c r="C82" s="52" t="s">
+        <v>358</v>
+      </c>
+      <c r="D82" s="52" t="s">
+        <v>1282</v>
+      </c>
+      <c r="E82" s="52" t="s">
+        <v>1283</v>
+      </c>
+      <c r="F82" s="52" t="s">
+        <v>28</v>
+      </c>
+      <c r="G82" s="53">
+        <v>4</v>
+      </c>
+      <c r="H82" s="54" t="s">
+        <v>1287</v>
+      </c>
+      <c r="I82" s="52" t="s">
+        <v>217</v>
+      </c>
+      <c r="J82" s="52">
+        <f>MONTH(I82)</f>
+        <v>7</v>
+      </c>
+      <c r="K82" s="52" t="s">
+        <v>38</v>
+      </c>
+      <c r="L82" s="54" t="s">
+        <v>1063</v>
+      </c>
+      <c r="M82" s="52" t="s">
+        <v>1014</v>
+      </c>
+      <c r="N82" s="52" t="s">
+        <v>1275</v>
+      </c>
+      <c r="O82" s="52" t="s">
+        <v>1014</v>
+      </c>
+      <c r="P82" s="54" t="s">
+        <v>1277</v>
+      </c>
+    </row>
+    <row r="83" spans="1:16" ht="25.5" customHeight="1">
+      <c r="A83" s="52" t="s">
+        <v>36</v>
+      </c>
+      <c r="B83" s="52" t="s">
+        <v>68</v>
+      </c>
+      <c r="C83" s="52" t="s">
+        <v>499</v>
+      </c>
+      <c r="D83" s="52" t="s">
+        <v>856</v>
+      </c>
+      <c r="E83" s="52" t="s">
+        <v>857</v>
+      </c>
+      <c r="F83" s="52" t="s">
+        <v>28</v>
+      </c>
+      <c r="G83" s="53">
+        <v>2</v>
+      </c>
+      <c r="H83" s="54" t="s">
+        <v>1228</v>
+      </c>
+      <c r="I83" s="52" t="s">
+        <v>1229</v>
+      </c>
+      <c r="J83" s="52">
+        <f>MONTH(I83)</f>
+        <v>7</v>
+      </c>
+      <c r="K83" s="52" t="s">
+        <v>38</v>
+      </c>
+      <c r="L83" s="54" t="s">
+        <v>1179</v>
+      </c>
+      <c r="M83" s="52" t="s">
+        <v>1014</v>
+      </c>
+      <c r="N83" s="52" t="s">
+        <v>1039</v>
+      </c>
+      <c r="O83" s="52" t="s">
+        <v>1014</v>
+      </c>
+      <c r="P83" s="54" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="84" spans="1:16" ht="25.5" customHeight="1">
+      <c r="A84" s="52" t="s">
+        <v>1274</v>
+      </c>
+      <c r="B84" s="52" t="s">
+        <v>190</v>
+      </c>
+      <c r="C84" s="52" t="s">
+        <v>191</v>
+      </c>
+      <c r="D84" s="52" t="s">
+        <v>343</v>
+      </c>
+      <c r="E84" s="52" t="s">
+        <v>344</v>
+      </c>
+      <c r="F84" s="52" t="s">
+        <v>28</v>
+      </c>
+      <c r="G84" s="53">
+        <v>1</v>
+      </c>
+      <c r="H84" s="54" t="s">
+        <v>1288</v>
+      </c>
+      <c r="I84" s="52" t="s">
+        <v>1229</v>
+      </c>
+      <c r="J84" s="52">
+        <f>MONTH(I84)</f>
+        <v>7</v>
+      </c>
+      <c r="K84" s="52" t="s">
+        <v>72</v>
+      </c>
+      <c r="L84" s="54" t="s">
+        <v>1289</v>
+      </c>
+      <c r="M84" s="52" t="s">
+        <v>1006</v>
+      </c>
+      <c r="N84" s="52" t="s">
+        <v>1275</v>
+      </c>
+      <c r="O84" s="52" t="s">
+        <v>1006</v>
+      </c>
+      <c r="P84" s="54" t="s">
+        <v>1281</v>
+      </c>
+    </row>
+    <row r="85" spans="1:16" ht="25.5" customHeight="1">
+      <c r="A85" s="52" t="s">
+        <v>36</v>
+      </c>
+      <c r="B85" s="52" t="s">
+        <v>197</v>
+      </c>
+      <c r="C85" s="52" t="s">
+        <v>1069</v>
+      </c>
+      <c r="D85" s="52" t="s">
+        <v>1070</v>
+      </c>
+      <c r="E85" s="52" t="s">
+        <v>1071</v>
+      </c>
+      <c r="F85" s="52" t="s">
+        <v>28</v>
+      </c>
+      <c r="G85" s="53">
+        <v>1</v>
+      </c>
+      <c r="H85" s="54" t="s">
+        <v>1072</v>
+      </c>
+      <c r="I85" s="52" t="s">
+        <v>1073</v>
+      </c>
+      <c r="J85" s="52">
+        <f>MONTH(I85)</f>
+        <v>7</v>
+      </c>
+      <c r="K85" s="52" t="s">
+        <v>38</v>
+      </c>
+      <c r="L85" s="54" t="s">
+        <v>1074</v>
+      </c>
+      <c r="M85" s="52" t="s">
+        <v>1006</v>
+      </c>
+      <c r="N85" s="52" t="s">
+        <v>1039</v>
+      </c>
+      <c r="O85" s="52" t="s">
+        <v>1006</v>
+      </c>
+      <c r="P85" s="54" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="86" spans="1:16" ht="25.5" customHeight="1">
+      <c r="A86" s="52" t="s">
+        <v>36</v>
+      </c>
+      <c r="B86" s="52" t="s">
+        <v>197</v>
+      </c>
+      <c r="C86" s="52" t="s">
+        <v>1107</v>
+      </c>
+      <c r="D86" s="52" t="s">
+        <v>1108</v>
+      </c>
+      <c r="E86" s="52" t="s">
+        <v>1109</v>
+      </c>
+      <c r="F86" s="52" t="s">
+        <v>28</v>
+      </c>
+      <c r="G86" s="53">
+        <v>1</v>
+      </c>
+      <c r="H86" s="54" t="s">
+        <v>1110</v>
+      </c>
+      <c r="I86" s="52" t="s">
+        <v>97</v>
+      </c>
+      <c r="J86" s="52">
+        <f>MONTH(I86)</f>
+        <v>7</v>
+      </c>
+      <c r="K86" s="52" t="s">
+        <v>38</v>
+      </c>
+      <c r="L86" s="54" t="s">
+        <v>1111</v>
+      </c>
+      <c r="M86" s="52" t="s">
+        <v>1006</v>
+      </c>
+      <c r="N86" s="52" t="s">
+        <v>1039</v>
+      </c>
+      <c r="O86" s="52" t="s">
+        <v>1006</v>
+      </c>
+      <c r="P86" s="54" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="87" spans="1:16" ht="25.5" customHeight="1">
+      <c r="A87" s="52" t="s">
+        <v>36</v>
+      </c>
+      <c r="B87" s="52" t="s">
+        <v>30</v>
+      </c>
+      <c r="C87" s="52" t="s">
+        <v>31</v>
+      </c>
+      <c r="D87" s="52" t="s">
+        <v>740</v>
+      </c>
+      <c r="E87" s="52" t="s">
+        <v>741</v>
+      </c>
+      <c r="F87" s="52" t="s">
+        <v>28</v>
+      </c>
+      <c r="G87" s="53">
+        <v>2</v>
+      </c>
+      <c r="H87" s="54" t="s">
+        <v>1189</v>
+      </c>
+      <c r="I87" s="52" t="s">
+        <v>97</v>
+      </c>
+      <c r="J87" s="52">
+        <f>MONTH(I87)</f>
+        <v>7</v>
+      </c>
+      <c r="K87" s="52" t="s">
+        <v>38</v>
+      </c>
+      <c r="L87" s="54" t="s">
+        <v>1190</v>
+      </c>
+      <c r="M87" s="52" t="s">
+        <v>1014</v>
+      </c>
+      <c r="N87" s="52" t="s">
+        <v>1039</v>
+      </c>
+      <c r="O87" s="52" t="s">
+        <v>1014</v>
+      </c>
+      <c r="P87" s="54" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="88" spans="1:16" ht="25.5" customHeight="1">
+      <c r="A88" s="52" t="s">
+        <v>36</v>
+      </c>
+      <c r="B88" s="52" t="s">
+        <v>30</v>
+      </c>
+      <c r="C88" s="52" t="s">
+        <v>31</v>
+      </c>
+      <c r="D88" s="52" t="s">
+        <v>820</v>
+      </c>
+      <c r="E88" s="52" t="s">
+        <v>821</v>
+      </c>
+      <c r="F88" s="52" t="s">
+        <v>28</v>
+      </c>
+      <c r="G88" s="53">
+        <v>5</v>
+      </c>
+      <c r="H88" s="54" t="s">
+        <v>1189</v>
+      </c>
+      <c r="I88" s="52" t="s">
+        <v>97</v>
+      </c>
+      <c r="J88" s="52">
+        <f>MONTH(I88)</f>
+        <v>7</v>
+      </c>
+      <c r="K88" s="52" t="s">
+        <v>38</v>
+      </c>
+      <c r="L88" s="54" t="s">
+        <v>1225</v>
+      </c>
+      <c r="M88" s="52" t="s">
+        <v>1014</v>
+      </c>
+      <c r="N88" s="52" t="s">
+        <v>1039</v>
+      </c>
+      <c r="O88" s="52" t="s">
+        <v>1014</v>
+      </c>
+      <c r="P88" s="54" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="89" spans="1:16" ht="25.5" customHeight="1">
+      <c r="A89" s="52" t="s">
+        <v>1328</v>
+      </c>
+      <c r="B89" s="52" t="s">
+        <v>162</v>
+      </c>
+      <c r="C89" s="52" t="s">
+        <v>1329</v>
+      </c>
+      <c r="D89" s="52" t="s">
+        <v>1330</v>
+      </c>
+      <c r="E89" s="52" t="s">
+        <v>1331</v>
+      </c>
+      <c r="F89" s="52" t="s">
+        <v>28</v>
+      </c>
+      <c r="G89" s="53">
+        <v>1</v>
+      </c>
+      <c r="H89" s="54" t="s">
+        <v>1332</v>
+      </c>
+      <c r="I89" s="52" t="s">
+        <v>97</v>
+      </c>
+      <c r="J89" s="52">
+        <f>MONTH(I89)</f>
+        <v>7</v>
+      </c>
+      <c r="K89" s="52" t="s">
+        <v>38</v>
+      </c>
+      <c r="L89" s="54" t="s">
+        <v>1333</v>
+      </c>
+      <c r="M89" s="52" t="s">
+        <v>1014</v>
+      </c>
+      <c r="N89" s="52" t="s">
+        <v>1334</v>
+      </c>
+      <c r="O89" s="52" t="s">
+        <v>1014</v>
+      </c>
+      <c r="P89" s="54" t="s">
+        <v>1335</v>
+      </c>
+    </row>
+    <row r="90" spans="1:16" ht="25.5" customHeight="1">
+      <c r="A90" s="52" t="s">
+        <v>36</v>
+      </c>
+      <c r="B90" s="52" t="s">
+        <v>30</v>
+      </c>
+      <c r="C90" s="52" t="s">
+        <v>490</v>
+      </c>
+      <c r="D90" s="52" t="s">
+        <v>1169</v>
+      </c>
+      <c r="E90" s="52" t="s">
+        <v>1170</v>
+      </c>
+      <c r="F90" s="52" t="s">
+        <v>28</v>
+      </c>
+      <c r="G90" s="53">
+        <v>1</v>
+      </c>
+      <c r="H90" s="54" t="s">
+        <v>1171</v>
+      </c>
+      <c r="I90" s="52" t="s">
+        <v>1172</v>
+      </c>
+      <c r="J90" s="52">
+        <f>MONTH(I90)</f>
+        <v>7</v>
+      </c>
+      <c r="K90" s="52" t="s">
+        <v>72</v>
+      </c>
+      <c r="L90" s="54" t="s">
+        <v>1173</v>
+      </c>
+      <c r="M90" s="52" t="s">
+        <v>1014</v>
+      </c>
+      <c r="N90" s="52" t="s">
+        <v>1039</v>
+      </c>
+      <c r="O90" s="52" t="s">
+        <v>1014</v>
+      </c>
+      <c r="P90" s="54" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="91" spans="1:16" ht="25.5" customHeight="1">
+      <c r="A91" s="52" t="s">
+        <v>36</v>
+      </c>
+      <c r="B91" s="52" t="s">
+        <v>758</v>
+      </c>
+      <c r="C91" s="52" t="s">
+        <v>759</v>
+      </c>
+      <c r="D91" s="52" t="s">
+        <v>760</v>
+      </c>
+      <c r="E91" s="52" t="s">
+        <v>761</v>
+      </c>
+      <c r="F91" s="52" t="s">
+        <v>28</v>
+      </c>
+      <c r="G91" s="53">
+        <v>5</v>
+      </c>
+      <c r="H91" s="54" t="s">
+        <v>1203</v>
+      </c>
+      <c r="I91" s="52" t="s">
+        <v>1172</v>
+      </c>
+      <c r="J91" s="52">
+        <f>MONTH(I91)</f>
+        <v>7</v>
+      </c>
+      <c r="K91" s="52" t="s">
+        <v>38</v>
+      </c>
+      <c r="L91" s="54" t="s">
+        <v>1204</v>
+      </c>
+      <c r="M91" s="52" t="s">
+        <v>1006</v>
+      </c>
+      <c r="N91" s="52" t="s">
+        <v>1039</v>
+      </c>
+      <c r="O91" s="52" t="s">
+        <v>1014</v>
+      </c>
+      <c r="P91" s="54" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="92" spans="1:16" ht="25.5" customHeight="1">
+      <c r="A92" s="52" t="s">
+        <v>36</v>
+      </c>
+      <c r="B92" s="52" t="s">
+        <v>758</v>
+      </c>
+      <c r="C92" s="52" t="s">
+        <v>759</v>
+      </c>
+      <c r="D92" s="52" t="s">
+        <v>760</v>
+      </c>
+      <c r="E92" s="52" t="s">
+        <v>761</v>
+      </c>
+      <c r="F92" s="52" t="s">
+        <v>28</v>
+      </c>
+      <c r="G92" s="53">
+        <v>3</v>
+      </c>
+      <c r="H92" s="54" t="s">
+        <v>1199</v>
+      </c>
+      <c r="I92" s="52" t="s">
+        <v>1200</v>
+      </c>
+      <c r="J92" s="52">
+        <f>MONTH(I92)</f>
+        <v>7</v>
+      </c>
+      <c r="K92" s="52" t="s">
+        <v>38</v>
+      </c>
+      <c r="L92" s="54" t="s">
+        <v>1201</v>
+      </c>
+      <c r="M92" s="52" t="s">
+        <v>1014</v>
+      </c>
+      <c r="N92" s="52" t="s">
+        <v>1039</v>
+      </c>
+      <c r="O92" s="52" t="s">
+        <v>1014</v>
+      </c>
+      <c r="P92" s="54" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="93" spans="1:16" ht="25.5" customHeight="1">
+      <c r="A93" s="52" t="s">
+        <v>36</v>
+      </c>
+      <c r="B93" s="52" t="s">
+        <v>68</v>
+      </c>
+      <c r="C93" s="52" t="s">
+        <v>408</v>
+      </c>
+      <c r="D93" s="52" t="s">
+        <v>1194</v>
+      </c>
+      <c r="E93" s="52" t="s">
+        <v>1195</v>
+      </c>
+      <c r="F93" s="52" t="s">
+        <v>28</v>
+      </c>
+      <c r="G93" s="53">
+        <v>1</v>
+      </c>
+      <c r="H93" s="54" t="s">
+        <v>1196</v>
+      </c>
+      <c r="I93" s="52" t="s">
+        <v>107</v>
+      </c>
+      <c r="J93" s="52">
+        <f>MONTH(I93)</f>
+        <v>7</v>
+      </c>
+      <c r="K93" s="52" t="s">
+        <v>38</v>
+      </c>
+      <c r="L93" s="54" t="s">
+        <v>1128</v>
+      </c>
+      <c r="M93" s="52" t="s">
+        <v>1014</v>
+      </c>
+      <c r="N93" s="52" t="s">
+        <v>1039</v>
+      </c>
+      <c r="O93" s="52" t="s">
+        <v>1014</v>
+      </c>
+      <c r="P93" s="54" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="94" spans="1:16" ht="25.5" customHeight="1">
+      <c r="A94" s="52" t="s">
+        <v>36</v>
+      </c>
+      <c r="B94" s="52" t="s">
+        <v>758</v>
+      </c>
+      <c r="C94" s="52" t="s">
+        <v>759</v>
+      </c>
+      <c r="D94" s="52" t="s">
+        <v>760</v>
+      </c>
+      <c r="E94" s="52" t="s">
+        <v>761</v>
+      </c>
+      <c r="F94" s="52" t="s">
+        <v>28</v>
+      </c>
+      <c r="G94" s="53">
+        <v>2</v>
+      </c>
+      <c r="H94" s="54" t="s">
+        <v>1197</v>
+      </c>
+      <c r="I94" s="52" t="s">
+        <v>107</v>
+      </c>
+      <c r="J94" s="52">
+        <f>MONTH(I94)</f>
+        <v>7</v>
+      </c>
+      <c r="K94" s="52" t="s">
+        <v>38</v>
+      </c>
+      <c r="L94" s="54" t="s">
+        <v>1198</v>
+      </c>
+      <c r="M94" s="52" t="s">
+        <v>1014</v>
+      </c>
+      <c r="N94" s="52" t="s">
+        <v>1039</v>
+      </c>
+      <c r="O94" s="52" t="s">
+        <v>1014</v>
+      </c>
+      <c r="P94" s="54" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="95" spans="1:16" ht="25.5" customHeight="1">
+      <c r="A95" s="52" t="s">
+        <v>36</v>
+      </c>
+      <c r="B95" s="52" t="s">
+        <v>758</v>
+      </c>
+      <c r="C95" s="52" t="s">
+        <v>781</v>
+      </c>
+      <c r="D95" s="52" t="s">
+        <v>782</v>
+      </c>
+      <c r="E95" s="52" t="s">
+        <v>783</v>
+      </c>
+      <c r="F95" s="52" t="s">
+        <v>28</v>
+      </c>
+      <c r="G95" s="53">
+        <v>11</v>
+      </c>
+      <c r="H95" s="54" t="s">
+        <v>1218</v>
+      </c>
+      <c r="I95" s="52" t="s">
+        <v>1219</v>
+      </c>
+      <c r="J95" s="52">
+        <f>MONTH(I95)</f>
+        <v>7</v>
+      </c>
+      <c r="K95" s="52" t="s">
+        <v>38</v>
+      </c>
+      <c r="L95" s="54" t="s">
+        <v>1220</v>
+      </c>
+      <c r="M95" s="52" t="s">
+        <v>1014</v>
+      </c>
+      <c r="N95" s="52" t="s">
+        <v>1039</v>
+      </c>
+      <c r="O95" s="52" t="s">
+        <v>1014</v>
+      </c>
+      <c r="P95" s="54" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="96" spans="1:16" ht="25.5" customHeight="1">
+      <c r="A96" s="52" t="s">
+        <v>1250</v>
+      </c>
+      <c r="B96" s="52" t="s">
+        <v>162</v>
+      </c>
+      <c r="C96" s="52" t="s">
+        <v>163</v>
+      </c>
+      <c r="D96" s="52" t="s">
+        <v>164</v>
+      </c>
+      <c r="E96" s="52" t="s">
+        <v>165</v>
+      </c>
+      <c r="F96" s="52" t="s">
+        <v>28</v>
+      </c>
+      <c r="G96" s="53">
+        <v>11</v>
+      </c>
+      <c r="H96" s="54" t="s">
+        <v>1259</v>
+      </c>
+      <c r="I96" s="52" t="s">
+        <v>1260</v>
+      </c>
+      <c r="J96" s="52">
+        <f>MONTH(I96)</f>
+        <v>7</v>
+      </c>
+      <c r="K96" s="52" t="s">
+        <v>38</v>
+      </c>
+      <c r="L96" s="54" t="s">
+        <v>1255</v>
+      </c>
+      <c r="M96" s="52" t="s">
+        <v>1006</v>
+      </c>
+      <c r="N96" s="52" t="s">
+        <v>1251</v>
+      </c>
+      <c r="O96" s="52" t="s">
+        <v>1006</v>
+      </c>
+      <c r="P96" s="54" t="s">
+        <v>1252</v>
+      </c>
+    </row>
+    <row r="97" spans="1:16" ht="25.5" customHeight="1">
+      <c r="A97" s="52" t="s">
+        <v>36</v>
+      </c>
+      <c r="B97" s="52" t="s">
+        <v>51</v>
+      </c>
+      <c r="C97" s="52" t="s">
+        <v>52</v>
+      </c>
+      <c r="D97" s="52" t="s">
+        <v>1049</v>
+      </c>
+      <c r="E97" s="52" t="s">
+        <v>1050</v>
+      </c>
+      <c r="F97" s="52" t="s">
+        <v>28</v>
+      </c>
+      <c r="G97" s="53">
+        <v>1</v>
+      </c>
+      <c r="H97" s="54" t="s">
+        <v>1051</v>
+      </c>
+      <c r="I97" s="52" t="s">
+        <v>840</v>
+      </c>
+      <c r="J97" s="52">
+        <f>MONTH(I97)</f>
+        <v>7</v>
+      </c>
+      <c r="K97" s="52" t="s">
+        <v>72</v>
+      </c>
+      <c r="L97" s="54" t="s">
+        <v>1052</v>
+      </c>
+      <c r="M97" s="52" t="s">
+        <v>1006</v>
+      </c>
+      <c r="N97" s="52" t="s">
+        <v>1039</v>
+      </c>
+      <c r="O97" s="52" t="s">
+        <v>1006</v>
+      </c>
+      <c r="P97" s="54" t="s">
+        <v>1053</v>
+      </c>
+    </row>
+    <row r="98" spans="1:16" ht="25.5" customHeight="1">
+      <c r="A98" s="52" t="s">
+        <v>36</v>
+      </c>
+      <c r="B98" s="52" t="s">
+        <v>190</v>
+      </c>
+      <c r="C98" s="52" t="s">
+        <v>191</v>
+      </c>
+      <c r="D98" s="52" t="s">
+        <v>604</v>
+      </c>
+      <c r="E98" s="52" t="s">
+        <v>605</v>
+      </c>
+      <c r="F98" s="52" t="s">
+        <v>28</v>
+      </c>
+      <c r="G98" s="53">
+        <v>2</v>
+      </c>
+      <c r="H98" s="54" t="s">
+        <v>1148</v>
+      </c>
+      <c r="I98" s="52" t="s">
+        <v>195</v>
+      </c>
+      <c r="J98" s="52">
+        <f>MONTH(I98)</f>
+        <v>8</v>
+      </c>
+      <c r="K98" s="52" t="s">
+        <v>38</v>
+      </c>
+      <c r="L98" s="54" t="s">
+        <v>1063</v>
+      </c>
+      <c r="M98" s="52" t="s">
+        <v>1014</v>
+      </c>
+      <c r="N98" s="52" t="s">
+        <v>1039</v>
+      </c>
+      <c r="O98" s="52" t="s">
+        <v>1014</v>
+      </c>
+      <c r="P98" s="54" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="99" spans="1:16" ht="25.5" customHeight="1">
+      <c r="A99" s="52" t="s">
+        <v>36</v>
+      </c>
+      <c r="B99" s="52" t="s">
+        <v>190</v>
+      </c>
+      <c r="C99" s="52" t="s">
+        <v>662</v>
+      </c>
+      <c r="D99" s="52" t="s">
+        <v>663</v>
+      </c>
+      <c r="E99" s="52" t="s">
+        <v>664</v>
+      </c>
+      <c r="F99" s="52" t="s">
+        <v>28</v>
+      </c>
+      <c r="G99" s="53">
+        <v>4</v>
+      </c>
+      <c r="H99" s="54" t="s">
+        <v>1151</v>
+      </c>
+      <c r="I99" s="52" t="s">
+        <v>195</v>
+      </c>
+      <c r="J99" s="52">
+        <f>MONTH(I99)</f>
+        <v>8</v>
+      </c>
+      <c r="K99" s="52" t="s">
+        <v>38</v>
+      </c>
+      <c r="L99" s="54" t="s">
+        <v>1152</v>
+      </c>
+      <c r="M99" s="52" t="s">
+        <v>1006</v>
+      </c>
+      <c r="N99" s="52" t="s">
+        <v>1039</v>
+      </c>
+      <c r="O99" s="52" t="s">
+        <v>1006</v>
+      </c>
+      <c r="P99" s="54" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="100" spans="1:16" ht="25.5" customHeight="1">
+      <c r="A100" s="52" t="s">
+        <v>1274</v>
+      </c>
+      <c r="B100" s="52" t="s">
+        <v>352</v>
+      </c>
+      <c r="C100" s="52" t="s">
+        <v>353</v>
+      </c>
+      <c r="D100" s="52" t="s">
+        <v>1306</v>
+      </c>
+      <c r="E100" s="52" t="s">
+        <v>1307</v>
+      </c>
+      <c r="F100" s="52" t="s">
+        <v>28</v>
+      </c>
+      <c r="G100" s="53">
+        <v>1</v>
+      </c>
+      <c r="H100" s="54" t="s">
+        <v>1308</v>
+      </c>
+      <c r="I100" s="52" t="s">
+        <v>1309</v>
+      </c>
+      <c r="J100" s="52">
+        <f>MONTH(I100)</f>
+        <v>8</v>
+      </c>
+      <c r="K100" s="52" t="s">
+        <v>38</v>
+      </c>
+      <c r="L100" s="54" t="s">
+        <v>1310</v>
+      </c>
+      <c r="M100" s="52" t="s">
+        <v>1014</v>
+      </c>
+      <c r="N100" s="52" t="s">
+        <v>1275</v>
+      </c>
+      <c r="O100" s="52" t="s">
+        <v>1014</v>
+      </c>
+      <c r="P100" s="54" t="s">
+        <v>1277</v>
+      </c>
+    </row>
+    <row r="101" spans="1:16" ht="25.5" customHeight="1">
+      <c r="A101" s="52" t="s">
+        <v>36</v>
+      </c>
+      <c r="B101" s="52" t="s">
+        <v>110</v>
+      </c>
+      <c r="C101" s="52" t="s">
+        <v>1165</v>
+      </c>
+      <c r="D101" s="52" t="s">
+        <v>1166</v>
+      </c>
+      <c r="E101" s="52" t="s">
+        <v>1167</v>
+      </c>
+      <c r="F101" s="52" t="s">
+        <v>28</v>
+      </c>
+      <c r="G101" s="53">
+        <v>1</v>
+      </c>
+      <c r="H101" s="54" t="s">
+        <v>1168</v>
+      </c>
+      <c r="I101" s="52" t="s">
+        <v>990</v>
+      </c>
+      <c r="J101" s="52">
+        <f>MONTH(I101)</f>
+        <v>8</v>
+      </c>
+      <c r="K101" s="52" t="s">
+        <v>38</v>
+      </c>
+      <c r="L101" s="54" t="s">
+        <v>1068</v>
+      </c>
+      <c r="M101" s="52" t="s">
+        <v>1014</v>
+      </c>
+      <c r="N101" s="52" t="s">
+        <v>1039</v>
+      </c>
+      <c r="O101" s="52" t="s">
+        <v>1014</v>
+      </c>
+      <c r="P101" s="54" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="102" spans="1:16" ht="25.5" customHeight="1">
+      <c r="A102" s="52" t="s">
+        <v>1250</v>
+      </c>
+      <c r="B102" s="52" t="s">
+        <v>162</v>
+      </c>
+      <c r="C102" s="52" t="s">
+        <v>808</v>
+      </c>
+      <c r="D102" s="52" t="s">
+        <v>940</v>
+      </c>
+      <c r="E102" s="52" t="s">
+        <v>941</v>
+      </c>
+      <c r="F102" s="52" t="s">
+        <v>28</v>
+      </c>
+      <c r="G102" s="53">
+        <v>8</v>
+      </c>
+      <c r="H102" s="54" t="s">
+        <v>1273</v>
+      </c>
+      <c r="I102" s="52" t="s">
+        <v>990</v>
+      </c>
+      <c r="J102" s="52">
+        <f>MONTH(I102)</f>
+        <v>8</v>
+      </c>
+      <c r="K102" s="52" t="s">
+        <v>38</v>
+      </c>
+      <c r="L102" s="54"/>
+      <c r="M102" s="52" t="s">
+        <v>1006</v>
+      </c>
+      <c r="N102" s="52" t="s">
+        <v>1268</v>
+      </c>
+      <c r="O102" s="52" t="s">
+        <v>1006</v>
+      </c>
+      <c r="P102" s="54" t="s">
+        <v>1269</v>
+      </c>
+    </row>
+    <row r="103" spans="1:16" ht="25.5" customHeight="1">
+      <c r="A103" s="52" t="s">
+        <v>1250</v>
+      </c>
+      <c r="B103" s="52" t="s">
+        <v>162</v>
+      </c>
+      <c r="C103" s="52" t="s">
+        <v>163</v>
+      </c>
+      <c r="D103" s="52" t="s">
+        <v>164</v>
+      </c>
+      <c r="E103" s="52" t="s">
+        <v>165</v>
+      </c>
+      <c r="F103" s="52" t="s">
+        <v>28</v>
+      </c>
+      <c r="G103" s="53">
+        <v>12</v>
+      </c>
+      <c r="H103" s="54" t="s">
+        <v>1261</v>
+      </c>
+      <c r="I103" s="52" t="s">
+        <v>1262</v>
+      </c>
+      <c r="J103" s="52">
+        <f>MONTH(I103)</f>
+        <v>8</v>
+      </c>
+      <c r="K103" s="52" t="s">
+        <v>38</v>
+      </c>
+      <c r="L103" s="54" t="s">
+        <v>1255</v>
+      </c>
+      <c r="M103" s="52" t="s">
+        <v>1006</v>
+      </c>
+      <c r="N103" s="52" t="s">
+        <v>1251</v>
+      </c>
+      <c r="O103" s="52" t="s">
+        <v>1006</v>
+      </c>
+      <c r="P103" s="54" t="s">
+        <v>1252</v>
+      </c>
+    </row>
+    <row r="104" spans="1:16" ht="25.5" customHeight="1">
+      <c r="A104" s="52" t="s">
+        <v>36</v>
+      </c>
+      <c r="B104" s="52" t="s">
+        <v>90</v>
+      </c>
+      <c r="C104" s="52" t="s">
+        <v>91</v>
+      </c>
+      <c r="D104" s="52" t="s">
+        <v>92</v>
+      </c>
+      <c r="E104" s="52" t="s">
+        <v>93</v>
+      </c>
+      <c r="F104" s="52" t="s">
+        <v>28</v>
+      </c>
+      <c r="G104" s="53">
+        <v>3</v>
+      </c>
+      <c r="H104" s="54" t="s">
+        <v>1045</v>
+      </c>
+      <c r="I104" s="52" t="s">
+        <v>671</v>
+      </c>
+      <c r="J104" s="52">
+        <f>MONTH(I104)</f>
+        <v>8</v>
+      </c>
+      <c r="K104" s="52" t="s">
+        <v>38</v>
+      </c>
+      <c r="L104" s="54" t="s">
+        <v>1046</v>
+      </c>
+      <c r="M104" s="52" t="s">
+        <v>1014</v>
+      </c>
+      <c r="N104" s="52" t="s">
+        <v>1039</v>
+      </c>
+      <c r="O104" s="52" t="s">
+        <v>1014</v>
+      </c>
+      <c r="P104" s="54" t="s">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="105" spans="1:16" ht="25.5" customHeight="1">
+      <c r="A105" s="52" t="s">
+        <v>36</v>
+      </c>
+      <c r="B105" s="52" t="s">
+        <v>68</v>
+      </c>
+      <c r="C105" s="52" t="s">
+        <v>919</v>
+      </c>
+      <c r="D105" s="52" t="s">
+        <v>1221</v>
+      </c>
+      <c r="E105" s="52" t="s">
+        <v>1222</v>
+      </c>
+      <c r="F105" s="52" t="s">
+        <v>28</v>
+      </c>
+      <c r="G105" s="53">
+        <v>1</v>
+      </c>
+      <c r="H105" s="54" t="s">
+        <v>1223</v>
+      </c>
+      <c r="I105" s="52" t="s">
+        <v>671</v>
+      </c>
+      <c r="J105" s="52">
+        <f>MONTH(I105)</f>
+        <v>8</v>
+      </c>
+      <c r="K105" s="52" t="s">
+        <v>38</v>
+      </c>
+      <c r="L105" s="54" t="s">
+        <v>1075</v>
+      </c>
+      <c r="M105" s="52" t="s">
+        <v>1006</v>
+      </c>
+      <c r="N105" s="52" t="s">
+        <v>1039</v>
+      </c>
+      <c r="O105" s="52" t="s">
+        <v>1014</v>
+      </c>
+      <c r="P105" s="54" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="106" spans="1:16" ht="25.5" customHeight="1">
+      <c r="A106" s="52" t="s">
+        <v>36</v>
+      </c>
+      <c r="B106" s="52" t="s">
+        <v>30</v>
+      </c>
+      <c r="C106" s="52" t="s">
+        <v>331</v>
+      </c>
+      <c r="D106" s="52" t="s">
+        <v>866</v>
+      </c>
+      <c r="E106" s="52" t="s">
+        <v>867</v>
+      </c>
+      <c r="F106" s="52" t="s">
+        <v>28</v>
+      </c>
+      <c r="G106" s="53">
+        <v>4</v>
+      </c>
+      <c r="H106" s="54" t="s">
+        <v>1230</v>
+      </c>
+      <c r="I106" s="52" t="s">
+        <v>1231</v>
+      </c>
+      <c r="J106" s="52">
+        <f>MONTH(I106)</f>
+        <v>8</v>
+      </c>
+      <c r="K106" s="52" t="s">
+        <v>72</v>
+      </c>
+      <c r="L106" s="54" t="s">
+        <v>1232</v>
+      </c>
+      <c r="M106" s="52" t="s">
+        <v>1014</v>
+      </c>
+      <c r="N106" s="52" t="s">
+        <v>1039</v>
+      </c>
+      <c r="O106" s="52" t="s">
+        <v>1014</v>
+      </c>
+      <c r="P106" s="54" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="107" spans="1:16" ht="25.5" customHeight="1">
+      <c r="A107" s="52" t="s">
+        <v>36</v>
+      </c>
+      <c r="B107" s="52" t="s">
+        <v>30</v>
+      </c>
+      <c r="C107" s="52" t="s">
+        <v>331</v>
+      </c>
+      <c r="D107" s="52" t="s">
+        <v>866</v>
+      </c>
+      <c r="E107" s="52" t="s">
+        <v>867</v>
+      </c>
+      <c r="F107" s="52" t="s">
+        <v>28</v>
+      </c>
+      <c r="G107" s="53">
+        <v>5</v>
+      </c>
+      <c r="H107" s="54" t="s">
+        <v>1233</v>
+      </c>
+      <c r="I107" s="52" t="s">
+        <v>1234</v>
+      </c>
+      <c r="J107" s="52">
+        <f>MONTH(I107)</f>
+        <v>8</v>
+      </c>
+      <c r="K107" s="52" t="s">
+        <v>72</v>
+      </c>
+      <c r="L107" s="54" t="s">
+        <v>1128</v>
+      </c>
+      <c r="M107" s="52" t="s">
+        <v>1014</v>
+      </c>
+      <c r="N107" s="52" t="s">
+        <v>1039</v>
+      </c>
+      <c r="O107" s="52" t="s">
+        <v>1014</v>
+      </c>
+      <c r="P107" s="54" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="108" spans="1:16" ht="25.5" customHeight="1">
+      <c r="A108" s="52" t="s">
+        <v>36</v>
+      </c>
+      <c r="B108" s="52" t="s">
+        <v>758</v>
+      </c>
+      <c r="C108" s="52" t="s">
+        <v>759</v>
+      </c>
+      <c r="D108" s="52" t="s">
+        <v>760</v>
+      </c>
+      <c r="E108" s="52" t="s">
+        <v>761</v>
+      </c>
+      <c r="F108" s="52" t="s">
+        <v>28</v>
+      </c>
+      <c r="G108" s="53">
+        <v>4</v>
+      </c>
+      <c r="H108" s="54" t="s">
+        <v>1202</v>
+      </c>
+      <c r="I108" s="52" t="s">
+        <v>538</v>
+      </c>
+      <c r="J108" s="52">
+        <f>MONTH(I108)</f>
+        <v>8</v>
+      </c>
+      <c r="K108" s="52" t="s">
+        <v>38</v>
+      </c>
+      <c r="L108" s="54" t="s">
+        <v>1201</v>
+      </c>
+      <c r="M108" s="52" t="s">
+        <v>1014</v>
+      </c>
+      <c r="N108" s="52" t="s">
+        <v>1039</v>
+      </c>
+      <c r="O108" s="52" t="s">
+        <v>1014</v>
+      </c>
+      <c r="P108" s="54" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="109" spans="1:16" ht="25.5" customHeight="1">
+      <c r="A109" s="52" t="s">
+        <v>36</v>
+      </c>
+      <c r="B109" s="52" t="s">
+        <v>30</v>
+      </c>
+      <c r="C109" s="52" t="s">
+        <v>31</v>
+      </c>
+      <c r="D109" s="52" t="s">
+        <v>32</v>
+      </c>
+      <c r="E109" s="52" t="s">
+        <v>33</v>
+      </c>
+      <c r="F109" s="52" t="s">
+        <v>28</v>
+      </c>
+      <c r="G109" s="53">
+        <v>2</v>
+      </c>
+      <c r="H109" s="54" t="s">
+        <v>1043</v>
+      </c>
+      <c r="I109" s="52" t="s">
+        <v>723</v>
+      </c>
+      <c r="J109" s="52">
+        <f>MONTH(I109)</f>
+        <v>8</v>
+      </c>
+      <c r="K109" s="52" t="s">
+        <v>38</v>
+      </c>
+      <c r="L109" s="54" t="s">
+        <v>1044</v>
+      </c>
+      <c r="M109" s="52" t="s">
+        <v>1014</v>
+      </c>
+      <c r="N109" s="52" t="s">
+        <v>1039</v>
+      </c>
+      <c r="O109" s="52" t="s">
+        <v>1014</v>
+      </c>
+      <c r="P109" s="54" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="110" spans="1:16" ht="25.5" customHeight="1">
+      <c r="A110" s="52" t="s">
+        <v>36</v>
+      </c>
+      <c r="B110" s="52" t="s">
+        <v>206</v>
+      </c>
+      <c r="C110" s="52" t="s">
+        <v>270</v>
+      </c>
+      <c r="D110" s="52" t="s">
+        <v>1101</v>
+      </c>
+      <c r="E110" s="52" t="s">
+        <v>1102</v>
+      </c>
+      <c r="F110" s="52" t="s">
+        <v>28</v>
+      </c>
+      <c r="G110" s="53">
+        <v>1</v>
+      </c>
+      <c r="H110" s="54" t="s">
+        <v>1103</v>
+      </c>
+      <c r="I110" s="52" t="s">
+        <v>723</v>
+      </c>
+      <c r="J110" s="52">
+        <f>MONTH(I110)</f>
+        <v>8</v>
+      </c>
+      <c r="K110" s="52" t="s">
+        <v>38</v>
+      </c>
+      <c r="L110" s="54" t="s">
+        <v>1104</v>
+      </c>
+      <c r="M110" s="52" t="s">
+        <v>1006</v>
+      </c>
+      <c r="N110" s="52" t="s">
+        <v>1039</v>
+      </c>
+      <c r="O110" s="52" t="s">
+        <v>1014</v>
+      </c>
+      <c r="P110" s="54" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="111" spans="1:16" ht="25.5" customHeight="1">
+      <c r="A111" s="52" t="s">
+        <v>36</v>
+      </c>
+      <c r="B111" s="52" t="s">
+        <v>68</v>
+      </c>
+      <c r="C111" s="52" t="s">
+        <v>146</v>
+      </c>
+      <c r="D111" s="52" t="s">
+        <v>1242</v>
+      </c>
+      <c r="E111" s="52" t="s">
+        <v>1243</v>
+      </c>
+      <c r="F111" s="52" t="s">
+        <v>28</v>
+      </c>
+      <c r="G111" s="53">
+        <v>1</v>
+      </c>
+      <c r="H111" s="54" t="s">
+        <v>1244</v>
+      </c>
+      <c r="I111" s="52" t="s">
+        <v>723</v>
+      </c>
+      <c r="J111" s="52">
+        <f>MONTH(I111)</f>
+        <v>8</v>
+      </c>
+      <c r="K111" s="52" t="s">
+        <v>38</v>
+      </c>
+      <c r="L111" s="54" t="s">
+        <v>1128</v>
+      </c>
+      <c r="M111" s="52" t="s">
+        <v>1014</v>
+      </c>
+      <c r="N111" s="52" t="s">
+        <v>1039</v>
+      </c>
+      <c r="O111" s="52" t="s">
+        <v>1014</v>
+      </c>
+      <c r="P111" s="54" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="112" spans="1:16" ht="25.5" customHeight="1">
+      <c r="A112" s="52" t="s">
+        <v>36</v>
+      </c>
+      <c r="B112" s="52" t="s">
+        <v>352</v>
+      </c>
+      <c r="C112" s="52" t="s">
+        <v>353</v>
+      </c>
+      <c r="D112" s="52" t="s">
+        <v>1093</v>
+      </c>
+      <c r="E112" s="52" t="s">
+        <v>1094</v>
+      </c>
+      <c r="F112" s="52" t="s">
+        <v>28</v>
+      </c>
+      <c r="G112" s="53">
+        <v>1</v>
+      </c>
+      <c r="H112" s="54" t="s">
+        <v>1095</v>
+      </c>
+      <c r="I112" s="52" t="s">
+        <v>532</v>
+      </c>
+      <c r="J112" s="52">
+        <f>MONTH(I112)</f>
+        <v>8</v>
+      </c>
+      <c r="K112" s="52" t="s">
+        <v>38</v>
+      </c>
+      <c r="L112" s="54" t="s">
+        <v>1096</v>
+      </c>
+      <c r="M112" s="52" t="s">
+        <v>1006</v>
+      </c>
+      <c r="N112" s="52" t="s">
+        <v>1039</v>
+      </c>
+      <c r="O112" s="52" t="s">
+        <v>1006</v>
+      </c>
+      <c r="P112" s="54" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="113" spans="1:16" ht="25.5" customHeight="1">
+      <c r="A113" s="52" t="s">
+        <v>1250</v>
+      </c>
+      <c r="B113" s="52" t="s">
+        <v>162</v>
+      </c>
+      <c r="C113" s="52" t="s">
+        <v>163</v>
+      </c>
+      <c r="D113" s="52" t="s">
+        <v>164</v>
+      </c>
+      <c r="E113" s="52" t="s">
+        <v>165</v>
+      </c>
+      <c r="F113" s="52" t="s">
+        <v>28</v>
+      </c>
+      <c r="G113" s="53">
+        <v>13</v>
+      </c>
+      <c r="H113" s="54" t="s">
+        <v>1263</v>
+      </c>
+      <c r="I113" s="52" t="s">
+        <v>608</v>
+      </c>
+      <c r="J113" s="52">
+        <f>MONTH(I113)</f>
+        <v>8</v>
+      </c>
+      <c r="K113" s="52" t="s">
+        <v>38</v>
+      </c>
+      <c r="L113" s="54" t="s">
+        <v>1255</v>
+      </c>
+      <c r="M113" s="52" t="s">
+        <v>1006</v>
+      </c>
+      <c r="N113" s="52" t="s">
+        <v>1251</v>
+      </c>
+      <c r="O113" s="52" t="s">
+        <v>1006</v>
+      </c>
+      <c r="P113" s="54" t="s">
+        <v>1252</v>
+      </c>
+    </row>
+    <row r="114" spans="1:16" ht="25.5" customHeight="1">
+      <c r="A114" s="52" t="s">
+        <v>114</v>
+      </c>
+      <c r="B114" s="52" t="s">
+        <v>138</v>
+      </c>
+      <c r="C114" s="52" t="s">
+        <v>474</v>
+      </c>
+      <c r="D114" s="52" t="s">
+        <v>475</v>
+      </c>
+      <c r="E114" s="52" t="s">
+        <v>476</v>
+      </c>
+      <c r="F114" s="52" t="s">
+        <v>28</v>
+      </c>
+      <c r="G114" s="53">
+        <v>1</v>
+      </c>
+      <c r="H114" s="54" t="s">
+        <v>1011</v>
+      </c>
+      <c r="I114" s="52" t="s">
+        <v>1012</v>
+      </c>
+      <c r="J114" s="52">
+        <f>MONTH(I114)</f>
+        <v>8</v>
+      </c>
+      <c r="K114" s="52" t="s">
+        <v>72</v>
+      </c>
+      <c r="L114" s="54" t="s">
+        <v>1013</v>
+      </c>
+      <c r="M114" s="52" t="s">
+        <v>1014</v>
+      </c>
+      <c r="N114" s="52" t="s">
+        <v>114</v>
+      </c>
+      <c r="O114" s="52" t="s">
+        <v>1014</v>
+      </c>
+      <c r="P114" s="54" t="s">
+        <v>1015</v>
+      </c>
+    </row>
+    <row r="115" spans="1:16" ht="25.5" customHeight="1">
+      <c r="A115" s="52" t="s">
+        <v>1274</v>
+      </c>
+      <c r="B115" s="52" t="s">
+        <v>102</v>
+      </c>
+      <c r="C115" s="52" t="s">
+        <v>103</v>
+      </c>
+      <c r="D115" s="52" t="s">
+        <v>104</v>
+      </c>
+      <c r="E115" s="52" t="s">
+        <v>105</v>
+      </c>
+      <c r="F115" s="52" t="s">
+        <v>28</v>
+      </c>
+      <c r="G115" s="53">
+        <v>1</v>
+      </c>
+      <c r="H115" s="54" t="s">
+        <v>1278</v>
+      </c>
+      <c r="I115" s="52" t="s">
+        <v>1279</v>
+      </c>
+      <c r="J115" s="52">
+        <f>MONTH(I115)</f>
+        <v>8</v>
+      </c>
+      <c r="K115" s="52" t="s">
+        <v>38</v>
+      </c>
+      <c r="L115" s="54" t="s">
+        <v>1280</v>
+      </c>
+      <c r="M115" s="52" t="s">
+        <v>1006</v>
+      </c>
+      <c r="N115" s="52" t="s">
+        <v>1275</v>
+      </c>
+      <c r="O115" s="52" t="s">
+        <v>1006</v>
+      </c>
+      <c r="P115" s="54" t="s">
+        <v>1276</v>
+      </c>
+    </row>
+    <row r="116" spans="1:16" ht="25.5" customHeight="1">
+      <c r="A116" s="52" t="s">
+        <v>1274</v>
+      </c>
+      <c r="B116" s="52" t="s">
+        <v>90</v>
+      </c>
+      <c r="C116" s="52" t="s">
+        <v>846</v>
+      </c>
+      <c r="D116" s="52" t="s">
+        <v>1299</v>
+      </c>
+      <c r="E116" s="52" t="s">
+        <v>1300</v>
+      </c>
+      <c r="F116" s="52" t="s">
+        <v>28</v>
+      </c>
+      <c r="G116" s="53">
+        <v>1</v>
+      </c>
+      <c r="H116" s="54" t="s">
+        <v>1301</v>
+      </c>
+      <c r="I116" s="52" t="s">
+        <v>1279</v>
+      </c>
+      <c r="J116" s="52">
+        <f>MONTH(I116)</f>
+        <v>8</v>
+      </c>
+      <c r="K116" s="52" t="s">
+        <v>38</v>
+      </c>
+      <c r="L116" s="54" t="s">
+        <v>1302</v>
+      </c>
+      <c r="M116" s="52" t="s">
+        <v>1006</v>
+      </c>
+      <c r="N116" s="52" t="s">
+        <v>1275</v>
+      </c>
+      <c r="O116" s="52" t="s">
+        <v>1006</v>
+      </c>
+      <c r="P116" s="54" t="s">
+        <v>1281</v>
+      </c>
+    </row>
+    <row r="117" spans="1:16" ht="25.5" customHeight="1">
+      <c r="A117" s="52" t="s">
+        <v>1328</v>
+      </c>
+      <c r="B117" s="52" t="s">
+        <v>758</v>
+      </c>
+      <c r="C117" s="52" t="s">
+        <v>1008</v>
+      </c>
+      <c r="D117" s="52" t="s">
+        <v>1009</v>
+      </c>
+      <c r="E117" s="52" t="s">
+        <v>1010</v>
+      </c>
+      <c r="F117" s="52" t="s">
+        <v>28</v>
+      </c>
+      <c r="G117" s="53">
+        <v>6</v>
+      </c>
+      <c r="H117" s="54" t="s">
+        <v>1362</v>
+      </c>
+      <c r="I117" s="52" t="s">
+        <v>1363</v>
+      </c>
+      <c r="J117" s="52">
+        <f>MONTH(I117)</f>
+        <v>8</v>
+      </c>
+      <c r="K117" s="52" t="s">
+        <v>38</v>
+      </c>
+      <c r="L117" s="54" t="s">
+        <v>1345</v>
+      </c>
+      <c r="M117" s="52" t="s">
+        <v>1014</v>
+      </c>
+      <c r="N117" s="52" t="s">
+        <v>1338</v>
+      </c>
+      <c r="O117" s="52" t="s">
+        <v>1014</v>
+      </c>
+      <c r="P117" s="54" t="s">
+        <v>1364</v>
+      </c>
+    </row>
+    <row r="118" spans="1:16" ht="25.5" customHeight="1">
+      <c r="A118" s="52" t="s">
+        <v>114</v>
+      </c>
+      <c r="B118" s="52" t="s">
+        <v>138</v>
+      </c>
+      <c r="C118" s="52" t="s">
+        <v>139</v>
+      </c>
+      <c r="D118" s="52" t="s">
+        <v>676</v>
+      </c>
+      <c r="E118" s="52" t="s">
+        <v>677</v>
+      </c>
+      <c r="F118" s="52" t="s">
+        <v>28</v>
+      </c>
+      <c r="G118" s="53">
+        <v>1</v>
+      </c>
+      <c r="H118" s="54" t="s">
+        <v>1023</v>
+      </c>
+      <c r="I118" s="52" t="s">
+        <v>1024</v>
+      </c>
+      <c r="J118" s="52">
+        <f>MONTH(I118)</f>
+        <v>8</v>
+      </c>
+      <c r="K118" s="52" t="s">
+        <v>72</v>
+      </c>
+      <c r="L118" s="54" t="s">
+        <v>1025</v>
+      </c>
+      <c r="M118" s="52" t="s">
+        <v>1006</v>
+      </c>
+      <c r="N118" s="52" t="s">
+        <v>114</v>
+      </c>
+      <c r="O118" s="52" t="s">
+        <v>1006</v>
+      </c>
+      <c r="P118" s="54" t="s">
+        <v>1026</v>
+      </c>
+    </row>
+    <row r="119" spans="1:16" ht="25.5" customHeight="1">
+      <c r="A119" s="52" t="s">
+        <v>36</v>
+      </c>
+      <c r="B119" s="52" t="s">
+        <v>138</v>
+      </c>
+      <c r="C119" s="52" t="s">
+        <v>571</v>
+      </c>
+      <c r="D119" s="52" t="s">
+        <v>1185</v>
+      </c>
+      <c r="E119" s="52" t="s">
+        <v>1186</v>
+      </c>
+      <c r="F119" s="52" t="s">
+        <v>28</v>
+      </c>
+      <c r="G119" s="53">
+        <v>1</v>
+      </c>
+      <c r="H119" s="54" t="s">
+        <v>1187</v>
+      </c>
+      <c r="I119" s="52" t="s">
+        <v>1188</v>
+      </c>
+      <c r="J119" s="52">
+        <f>MONTH(I119)</f>
+        <v>8</v>
+      </c>
+      <c r="K119" s="52" t="s">
+        <v>38</v>
+      </c>
+      <c r="L119" s="54" t="s">
+        <v>1041</v>
+      </c>
+      <c r="M119" s="52" t="s">
+        <v>1006</v>
+      </c>
+      <c r="N119" s="52" t="s">
+        <v>1039</v>
+      </c>
+      <c r="O119" s="52" t="s">
+        <v>1014</v>
+      </c>
+      <c r="P119" s="54" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="120" spans="1:16" ht="25.5" customHeight="1">
+      <c r="A120" s="52" t="s">
+        <v>36</v>
+      </c>
+      <c r="B120" s="52" t="s">
+        <v>68</v>
+      </c>
+      <c r="C120" s="52" t="s">
+        <v>146</v>
+      </c>
+      <c r="D120" s="52" t="s">
+        <v>376</v>
+      </c>
+      <c r="E120" s="52" t="s">
+        <v>377</v>
+      </c>
+      <c r="F120" s="52" t="s">
+        <v>28</v>
+      </c>
+      <c r="G120" s="53">
+        <v>3</v>
+      </c>
+      <c r="H120" s="54" t="s">
+        <v>1080</v>
+      </c>
+      <c r="I120" s="52" t="s">
+        <v>1081</v>
+      </c>
+      <c r="J120" s="52">
+        <f>MONTH(I120)</f>
+        <v>8</v>
+      </c>
+      <c r="K120" s="52" t="s">
+        <v>72</v>
+      </c>
+      <c r="L120" s="54" t="s">
+        <v>1082</v>
+      </c>
+      <c r="M120" s="52" t="s">
+        <v>1006</v>
+      </c>
+      <c r="N120" s="52" t="s">
+        <v>1039</v>
+      </c>
+      <c r="O120" s="52" t="s">
+        <v>1014</v>
+      </c>
+      <c r="P120" s="54" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="121" spans="1:16" ht="25.5" customHeight="1">
+      <c r="A121" s="52" t="s">
+        <v>36</v>
+      </c>
+      <c r="B121" s="52" t="s">
+        <v>68</v>
+      </c>
+      <c r="C121" s="52" t="s">
+        <v>919</v>
+      </c>
+      <c r="D121" s="52" t="s">
+        <v>1221</v>
+      </c>
+      <c r="E121" s="52" t="s">
+        <v>1222</v>
+      </c>
+      <c r="F121" s="52" t="s">
+        <v>28</v>
+      </c>
+      <c r="G121" s="53">
+        <v>2</v>
+      </c>
+      <c r="H121" s="54" t="s">
+        <v>1224</v>
+      </c>
+      <c r="I121" s="52" t="s">
+        <v>1081</v>
+      </c>
+      <c r="J121" s="52">
+        <f>MONTH(I121)</f>
+        <v>8</v>
+      </c>
+      <c r="K121" s="52" t="s">
+        <v>38</v>
+      </c>
+      <c r="L121" s="54" t="s">
+        <v>1041</v>
+      </c>
+      <c r="M121" s="52" t="s">
+        <v>1014</v>
+      </c>
+      <c r="N121" s="52" t="s">
+        <v>1039</v>
+      </c>
+      <c r="O121" s="52" t="s">
+        <v>1014</v>
+      </c>
+      <c r="P121" s="54" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="122" spans="1:16" ht="25.5" customHeight="1">
+      <c r="A122" s="52" t="s">
+        <v>114</v>
+      </c>
+      <c r="B122" s="52" t="s">
+        <v>138</v>
+      </c>
+      <c r="C122" s="52" t="s">
+        <v>571</v>
+      </c>
+      <c r="D122" s="52" t="s">
+        <v>634</v>
+      </c>
+      <c r="E122" s="52" t="s">
+        <v>635</v>
+      </c>
+      <c r="F122" s="52" t="s">
+        <v>28</v>
+      </c>
+      <c r="G122" s="53">
+        <v>1</v>
+      </c>
+      <c r="H122" s="54" t="s">
+        <v>1018</v>
+      </c>
+      <c r="I122" s="52" t="s">
+        <v>100</v>
+      </c>
+      <c r="J122" s="52">
+        <f>MONTH(I122)</f>
+        <v>8</v>
+      </c>
+      <c r="K122" s="52" t="s">
+        <v>72</v>
+      </c>
+      <c r="L122" s="54" t="s">
+        <v>1019</v>
+      </c>
+      <c r="M122" s="52" t="s">
+        <v>1006</v>
+      </c>
+      <c r="N122" s="52" t="s">
+        <v>114</v>
+      </c>
+      <c r="O122" s="52" t="s">
+        <v>1006</v>
+      </c>
+      <c r="P122" s="54" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="123" spans="1:16" ht="25.5" customHeight="1">
+      <c r="A123" s="52" t="s">
+        <v>36</v>
+      </c>
+      <c r="B123" s="52" t="s">
+        <v>138</v>
+      </c>
+      <c r="C123" s="52" t="s">
+        <v>139</v>
+      </c>
+      <c r="D123" s="52" t="s">
+        <v>140</v>
+      </c>
+      <c r="E123" s="52" t="s">
+        <v>141</v>
+      </c>
+      <c r="F123" s="52" t="s">
+        <v>28</v>
+      </c>
+      <c r="G123" s="53">
+        <v>2</v>
+      </c>
+      <c r="H123" s="54" t="s">
+        <v>1047</v>
+      </c>
+      <c r="I123" s="52" t="s">
+        <v>100</v>
+      </c>
+      <c r="J123" s="52">
+        <f>MONTH(I123)</f>
+        <v>8</v>
+      </c>
+      <c r="K123" s="52" t="s">
+        <v>38</v>
+      </c>
+      <c r="L123" s="54" t="s">
+        <v>1048</v>
+      </c>
+      <c r="M123" s="52" t="s">
+        <v>1006</v>
+      </c>
+      <c r="N123" s="52" t="s">
+        <v>1039</v>
+      </c>
+      <c r="O123" s="52" t="s">
+        <v>1006</v>
+      </c>
+      <c r="P123" s="54" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="124" spans="1:16" ht="25.5" customHeight="1">
+      <c r="A124" s="52" t="s">
+        <v>36</v>
+      </c>
+      <c r="B124" s="52" t="s">
+        <v>197</v>
+      </c>
+      <c r="C124" s="52" t="s">
+        <v>198</v>
+      </c>
+      <c r="D124" s="52" t="s">
+        <v>199</v>
+      </c>
+      <c r="E124" s="52" t="s">
+        <v>200</v>
+      </c>
+      <c r="F124" s="52" t="s">
+        <v>28</v>
+      </c>
+      <c r="G124" s="53">
+        <v>2</v>
+      </c>
+      <c r="H124" s="54" t="s">
+        <v>1055</v>
+      </c>
+      <c r="I124" s="52" t="s">
+        <v>100</v>
+      </c>
+      <c r="J124" s="52">
+        <f>MONTH(I124)</f>
+        <v>8</v>
+      </c>
+      <c r="K124" s="52" t="s">
+        <v>38</v>
+      </c>
+      <c r="L124" s="54" t="s">
+        <v>1056</v>
+      </c>
+      <c r="M124" s="52" t="s">
+        <v>1006</v>
+      </c>
+      <c r="N124" s="52" t="s">
+        <v>1039</v>
+      </c>
+      <c r="O124" s="52" t="s">
+        <v>1006</v>
+      </c>
+      <c r="P124" s="54" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="125" spans="1:16" ht="25.5" customHeight="1">
+      <c r="A125" s="52" t="s">
+        <v>36</v>
+      </c>
+      <c r="B125" s="52" t="s">
+        <v>138</v>
+      </c>
+      <c r="C125" s="52" t="s">
+        <v>139</v>
+      </c>
+      <c r="D125" s="52" t="s">
+        <v>1097</v>
+      </c>
+      <c r="E125" s="52" t="s">
+        <v>1098</v>
+      </c>
+      <c r="F125" s="52" t="s">
+        <v>28</v>
+      </c>
+      <c r="G125" s="53">
+        <v>1</v>
+      </c>
+      <c r="H125" s="54" t="s">
+        <v>1099</v>
+      </c>
+      <c r="I125" s="52" t="s">
+        <v>100</v>
+      </c>
+      <c r="J125" s="52">
+        <f>MONTH(I125)</f>
+        <v>8</v>
+      </c>
+      <c r="K125" s="52" t="s">
+        <v>38</v>
+      </c>
+      <c r="L125" s="54" t="s">
+        <v>1100</v>
+      </c>
+      <c r="M125" s="52" t="s">
+        <v>1006</v>
+      </c>
+      <c r="N125" s="52" t="s">
+        <v>1039</v>
+      </c>
+      <c r="O125" s="52" t="s">
+        <v>1006</v>
+      </c>
+      <c r="P125" s="54" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="126" spans="1:16" ht="25.5" customHeight="1">
+      <c r="A126" s="52" t="s">
+        <v>36</v>
+      </c>
+      <c r="B126" s="52" t="s">
+        <v>206</v>
+      </c>
+      <c r="C126" s="52" t="s">
+        <v>643</v>
+      </c>
+      <c r="D126" s="52" t="s">
+        <v>1120</v>
+      </c>
+      <c r="E126" s="52" t="s">
+        <v>1121</v>
+      </c>
+      <c r="F126" s="52" t="s">
+        <v>28</v>
+      </c>
+      <c r="G126" s="53">
+        <v>1</v>
+      </c>
+      <c r="H126" s="54" t="s">
+        <v>1122</v>
+      </c>
+      <c r="I126" s="52" t="s">
+        <v>100</v>
+      </c>
+      <c r="J126" s="52">
+        <f>MONTH(I126)</f>
+        <v>8</v>
+      </c>
+      <c r="K126" s="52" t="s">
+        <v>38</v>
+      </c>
+      <c r="L126" s="54" t="s">
+        <v>1123</v>
+      </c>
+      <c r="M126" s="52" t="s">
+        <v>1006</v>
+      </c>
+      <c r="N126" s="52" t="s">
+        <v>1039</v>
+      </c>
+      <c r="O126" s="52" t="s">
+        <v>1006</v>
+      </c>
+      <c r="P126" s="54" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="127" spans="1:16" ht="25.5" customHeight="1">
+      <c r="A127" s="52" t="s">
+        <v>36</v>
+      </c>
+      <c r="B127" s="52" t="s">
+        <v>322</v>
+      </c>
+      <c r="C127" s="52" t="s">
+        <v>434</v>
+      </c>
+      <c r="D127" s="52" t="s">
+        <v>1134</v>
+      </c>
+      <c r="E127" s="52" t="s">
+        <v>1135</v>
+      </c>
+      <c r="F127" s="52" t="s">
+        <v>28</v>
+      </c>
+      <c r="G127" s="53">
+        <v>1</v>
+      </c>
+      <c r="H127" s="54" t="s">
+        <v>1136</v>
+      </c>
+      <c r="I127" s="52" t="s">
+        <v>100</v>
+      </c>
+      <c r="J127" s="52">
+        <f>MONTH(I127)</f>
+        <v>8</v>
+      </c>
+      <c r="K127" s="52" t="s">
+        <v>38</v>
+      </c>
+      <c r="L127" s="54" t="s">
+        <v>1137</v>
+      </c>
+      <c r="M127" s="52" t="s">
+        <v>1006</v>
+      </c>
+      <c r="N127" s="52" t="s">
+        <v>1039</v>
+      </c>
+      <c r="O127" s="52" t="s">
+        <v>1006</v>
+      </c>
+      <c r="P127" s="54" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="128" spans="1:16" ht="25.5" customHeight="1">
+      <c r="A128" s="52" t="s">
+        <v>36</v>
+      </c>
+      <c r="B128" s="52" t="s">
+        <v>102</v>
+      </c>
+      <c r="C128" s="52" t="s">
+        <v>1153</v>
+      </c>
+      <c r="D128" s="52" t="s">
+        <v>1154</v>
+      </c>
+      <c r="E128" s="52" t="s">
+        <v>1155</v>
+      </c>
+      <c r="F128" s="52" t="s">
+        <v>28</v>
+      </c>
+      <c r="G128" s="53">
+        <v>3</v>
+      </c>
+      <c r="H128" s="54" t="s">
+        <v>1159</v>
+      </c>
+      <c r="I128" s="52" t="s">
+        <v>100</v>
+      </c>
+      <c r="J128" s="52">
+        <f>MONTH(I128)</f>
+        <v>8</v>
+      </c>
+      <c r="K128" s="52" t="s">
+        <v>38</v>
+      </c>
+      <c r="L128" s="54" t="s">
+        <v>1156</v>
+      </c>
+      <c r="M128" s="52" t="s">
+        <v>1006</v>
+      </c>
+      <c r="N128" s="52" t="s">
+        <v>1039</v>
+      </c>
+      <c r="O128" s="52" t="s">
+        <v>1006</v>
+      </c>
+      <c r="P128" s="54" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="129" spans="1:16" ht="25.5" customHeight="1">
+      <c r="A129" s="52" t="s">
+        <v>36</v>
+      </c>
+      <c r="B129" s="52" t="s">
+        <v>236</v>
+      </c>
+      <c r="C129" s="52" t="s">
+        <v>1020</v>
+      </c>
+      <c r="D129" s="52" t="s">
+        <v>1021</v>
+      </c>
+      <c r="E129" s="52" t="s">
+        <v>1022</v>
+      </c>
+      <c r="F129" s="52" t="s">
+        <v>28</v>
+      </c>
+      <c r="G129" s="53">
+        <v>1</v>
+      </c>
+      <c r="H129" s="54" t="s">
+        <v>1160</v>
+      </c>
+      <c r="I129" s="52" t="s">
+        <v>100</v>
+      </c>
+      <c r="J129" s="52">
+        <f>MONTH(I129)</f>
+        <v>8</v>
+      </c>
+      <c r="K129" s="52" t="s">
+        <v>38</v>
+      </c>
+      <c r="L129" s="54" t="s">
+        <v>1161</v>
+      </c>
+      <c r="M129" s="52" t="s">
+        <v>1006</v>
+      </c>
+      <c r="N129" s="52" t="s">
+        <v>1039</v>
+      </c>
+      <c r="O129" s="52" t="s">
+        <v>1006</v>
+      </c>
+      <c r="P129" s="54" t="s">
+        <v>82</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:P129" xr:uid="{93A4203A-85D9-47F5-9539-BD61E8705C84}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:P129">
+      <sortCondition ref="I1:I129"/>
+    </sortState>
+  </autoFilter>
+  <phoneticPr fontId="4" type="noConversion"/>
+  <pageMargins left="0" right="0" top="0" bottom="0" header="0" footer="0"/>
+  <pageSetup orientation="landscape"/>
+  <rowBreaks count="7" manualBreakCount="7">
+    <brk id="4" max="16383" man="1"/>
+    <brk id="24" max="16383" man="1"/>
+    <brk id="44" max="16383" man="1"/>
+    <brk id="64" max="16383" man="1"/>
+    <brk id="84" max="16383" man="1"/>
+    <brk id="104" max="16383" man="1"/>
+    <brk id="124" max="16383" man="1"/>
+  </rowBreaks>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EA2C2622-F2C4-402B-90B9-7E376B4FD75D}">
   <dimension ref="A1:E13"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
@@ -39499,7 +47299,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5D4790DA-C6AC-4E0A-97F5-AFF3509C31BA}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
@@ -39746,7 +47546,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{551D17E9-D0B9-416B-BA57-F5AA470A58BD}">
   <dimension ref="A1:N5"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -39984,7 +47784,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5AC6C9D8-C651-4C1F-BA0C-1E6F254BBD16}">
   <dimension ref="A1:N5"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -40222,7 +48022,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{618796F0-6965-4EFF-856F-D6168297D422}">
   <dimension ref="A1:N5"/>
   <sheetFormatPr defaultRowHeight="15"/>
